--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08793F1E-7237-4B9C-AC5E-F1F5135B151D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305CEAE1-392D-40C3-A1AD-A20915F8F6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="847">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2549,9 +2549,6 @@
     <t>NV50 Flowcell (PO:0290)- Qty 2 Nos. / Biosci 240 Lamp-6V assembly (PO:0307)- Qty 5 nos. / Wise Road- Qty 1 Nos.</t>
   </si>
   <si>
-    <t>Nilesh Zsir</t>
-  </si>
-  <si>
     <t>AM/PP?0029/2627</t>
   </si>
   <si>
@@ -2559,6 +2556,12 @@
   </si>
   <si>
     <t>W1-Sample Bottle</t>
+  </si>
+  <si>
+    <t>AM/DOM/0009/2627</t>
+  </si>
+  <si>
+    <t>Hitachi Micro Sample Cups- Qty 3000 Nos. ( 500x6)</t>
   </si>
 </sst>
 </file>
@@ -9412,7 +9415,7 @@
         <v>46276</v>
       </c>
       <c r="C247" s="49" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D247" s="26">
         <v>46276</v>
@@ -9427,7 +9430,7 @@
         <v>48</v>
       </c>
       <c r="H247" s="36" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="248" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -17065,7 +17068,7 @@
         <v>46276</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D139" s="55">
         <v>46276</v>
@@ -17080,7 +17083,7 @@
         <v>47</v>
       </c>
       <c r="H139" s="45" t="s">
-        <v>842</v>
+        <v>48</v>
       </c>
       <c r="I139" s="29" t="s">
         <v>841</v>
@@ -17096,11 +17099,30 @@
       <c r="A140" s="27">
         <v>112</v>
       </c>
-      <c r="B140" s="45"/>
-      <c r="D140" s="45"/>
-      <c r="G140" s="45"/>
-      <c r="H140" s="45"/>
-      <c r="I140" s="29"/>
+      <c r="B140" s="55">
+        <v>46280</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="D140" s="55">
+        <v>46280</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="G140" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H140" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I140" s="29" t="s">
+        <v>846</v>
+      </c>
+      <c r="J140" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="141" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A141" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305CEAE1-392D-40C3-A1AD-A20915F8F6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE167C8-D6EE-48E5-AB5D-EF33E3E7AFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="845">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2538,12 +2538,6 @@
   </si>
   <si>
     <t xml:space="preserve">Lamp House Assembly- Autochem Xpert- Qty 10 Nos </t>
-  </si>
-  <si>
-    <t>386 kg</t>
-  </si>
-  <si>
-    <t>378 kg</t>
   </si>
   <si>
     <t>NV50 Flowcell (PO:0290)- Qty 2 Nos. / Biosci 240 Lamp-6V assembly (PO:0307)- Qty 5 nos. / Wise Road- Qty 1 Nos.</t>
@@ -9415,7 +9409,7 @@
         <v>46276</v>
       </c>
       <c r="C247" s="49" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D247" s="26">
         <v>46276</v>
@@ -9430,10 +9424,13 @@
         <v>48</v>
       </c>
       <c r="H247" s="36" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="248" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A248" s="22">
+        <v>190</v>
+      </c>
       <c r="C248" s="49"/>
       <c r="F248" s="49"/>
       <c r="H248" s="36"/>
@@ -17056,8 +17053,8 @@
       <c r="J138" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N138" s="10" t="s">
-        <v>839</v>
+      <c r="N138" s="10">
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -17068,7 +17065,7 @@
         <v>46276</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D139" s="55">
         <v>46276</v>
@@ -17086,13 +17083,13 @@
         <v>48</v>
       </c>
       <c r="I139" s="29" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="J139" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="N139" s="10" t="s">
-        <v>840</v>
+      <c r="N139" s="10">
+        <v>378</v>
       </c>
     </row>
     <row r="140" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -17103,7 +17100,7 @@
         <v>46280</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D140" s="55">
         <v>46280</v>
@@ -17118,14 +17115,16 @@
         <v>48</v>
       </c>
       <c r="I140" s="29" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="J140" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="141" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A141" s="27"/>
+      <c r="A141" s="27">
+        <v>113</v>
+      </c>
       <c r="B141" s="45"/>
       <c r="D141" s="45"/>
       <c r="G141" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE167C8-D6EE-48E5-AB5D-EF33E3E7AFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6C8C55-661E-4318-8071-EDB9CE675566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="846">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2555,7 +2555,10 @@
     <t>AM/DOM/0009/2627</t>
   </si>
   <si>
-    <t>Hitachi Micro Sample Cups- Qty 3000 Nos. ( 500x6)</t>
+    <t>Hitachi Micro Sample Cups- Qty 3000 Nos. ( 500x6) &amp; Small Transparent white Cups- Qty 25 Nos.</t>
+  </si>
+  <si>
+    <t>Tirupti</t>
   </si>
 </sst>
 </file>
@@ -17105,6 +17108,9 @@
       <c r="D140" s="55">
         <v>46280</v>
       </c>
+      <c r="E140" s="10" t="s">
+        <v>845</v>
+      </c>
       <c r="F140" s="10" t="s">
         <v>333</v>
       </c>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6C8C55-661E-4318-8071-EDB9CE675566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D9D1D-D23F-46C7-8A2A-D67BF8F12B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="848">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2559,6 +2559,12 @@
   </si>
   <si>
     <t>Tirupti</t>
+  </si>
+  <si>
+    <t>Photometer Halogen lamp assy Bioelab FA 6V/10W -Qty 10 Pcs</t>
+  </si>
+  <si>
+    <t>AWB#7X110904609</t>
   </si>
 </sst>
 </file>
@@ -9429,14 +9435,38 @@
       <c r="H247" s="36" t="s">
         <v>842</v>
       </c>
+      <c r="I247" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="248" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A248" s="22">
         <v>190</v>
       </c>
-      <c r="C248" s="49"/>
-      <c r="F248" s="49"/>
-      <c r="H248" s="36"/>
+      <c r="B248" s="26">
+        <v>46281</v>
+      </c>
+      <c r="C248" s="49" t="s">
+        <v>847</v>
+      </c>
+      <c r="D248" s="26">
+        <v>46279</v>
+      </c>
+      <c r="E248" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F248" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G248" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H248" s="36" t="s">
+        <v>846</v>
+      </c>
+      <c r="I248" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="249" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C249" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D9D1D-D23F-46C7-8A2A-D67BF8F12B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADD5B59-B61A-45E9-8A9E-72CC767BB9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="851">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2565,6 +2565,15 @@
   </si>
   <si>
     <t>AWB#7X110904609</t>
+  </si>
+  <si>
+    <t>Powr Supply Board -Qty 8 Nos. / Nano Pi board - Qty 8 Nos. / Photometer Board - Qty 3 Nos.</t>
+  </si>
+  <si>
+    <t>Cocern Letter BS/26-27/07/09</t>
+  </si>
+  <si>
+    <t>Yogesh  Sir</t>
   </si>
 </sst>
 </file>
@@ -9469,11 +9478,38 @@
       </c>
     </row>
     <row r="249" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C249" s="49"/>
-      <c r="F249" s="49"/>
-      <c r="H249" s="36"/>
+      <c r="A249" s="22">
+        <v>191</v>
+      </c>
+      <c r="B249" s="26">
+        <v>46281</v>
+      </c>
+      <c r="C249" s="49" t="s">
+        <v>849</v>
+      </c>
+      <c r="D249" s="26">
+        <v>46277</v>
+      </c>
+      <c r="E249" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F249" s="49" t="s">
+        <v>501</v>
+      </c>
+      <c r="G249" s="22" t="s">
+        <v>850</v>
+      </c>
+      <c r="H249" s="36" t="s">
+        <v>848</v>
+      </c>
+      <c r="I249" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="250" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A250" s="22">
+        <v>192</v>
+      </c>
       <c r="C250" s="49"/>
       <c r="F250" s="49"/>
       <c r="H250" s="36"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADD5B59-B61A-45E9-8A9E-72CC767BB9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BA1017-AF5A-4296-8AC0-8B611995601F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="862">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2528,9 +2528,6 @@
     <t>Akshat Biomedical</t>
   </si>
   <si>
-    <t>W1000944050</t>
-  </si>
-  <si>
     <t>Cuvett -Qty 300 Pcs. (40X7 &amp; 1x 20 )</t>
   </si>
   <si>
@@ -2558,9 +2555,6 @@
     <t>Hitachi Micro Sample Cups- Qty 3000 Nos. ( 500x6) &amp; Small Transparent white Cups- Qty 25 Nos.</t>
   </si>
   <si>
-    <t>Tirupti</t>
-  </si>
-  <si>
     <t>Photometer Halogen lamp assy Bioelab FA 6V/10W -Qty 10 Pcs</t>
   </si>
   <si>
@@ -2574,6 +2568,45 @@
   </si>
   <si>
     <t>Yogesh  Sir</t>
+  </si>
+  <si>
+    <t>26-27-ABPL/327</t>
+  </si>
+  <si>
+    <t>AM/PP/0030/2627</t>
+  </si>
+  <si>
+    <t>43x31x33 cm 9 Kg</t>
+  </si>
+  <si>
+    <t>48x43x38 cm 16 Kg</t>
+  </si>
+  <si>
+    <t>Hitachi Micro Sample Cups- Qty 4500 Nos. ( 500x9) - 9 Pckt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33x24x10cm </t>
+  </si>
+  <si>
+    <t>Cuvettes For Fully Auto Analyser- Qty 120 Nos / Lamp For Fully Auto Analyser - Qty 2 Nos / Sample cups For Fully Auto Analyser-Qty 500 Nos</t>
+  </si>
+  <si>
+    <t>AM/PP/0031/2627</t>
+  </si>
+  <si>
+    <t>16 GB Pendrive - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>AM/PP/0032/2627</t>
+  </si>
+  <si>
+    <t>Nilesh Sir- Self</t>
+  </si>
+  <si>
+    <t>Real Time Solution</t>
+  </si>
+  <si>
+    <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 4 Nos.</t>
   </si>
 </sst>
 </file>
@@ -9398,7 +9431,7 @@
         <v>46276</v>
       </c>
       <c r="C246" s="49" t="s">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="D246" s="26">
         <v>46276</v>
@@ -9413,7 +9446,7 @@
         <v>48</v>
       </c>
       <c r="H246" s="36" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="I246" s="22" t="s">
         <v>185</v>
@@ -9427,7 +9460,7 @@
         <v>46276</v>
       </c>
       <c r="C247" s="49" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D247" s="26">
         <v>46276</v>
@@ -9442,7 +9475,7 @@
         <v>48</v>
       </c>
       <c r="H247" s="36" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I247" s="22" t="s">
         <v>50</v>
@@ -9456,7 +9489,7 @@
         <v>46281</v>
       </c>
       <c r="C248" s="49" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D248" s="26">
         <v>46279</v>
@@ -9471,7 +9504,7 @@
         <v>48</v>
       </c>
       <c r="H248" s="36" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="I248" s="22" t="s">
         <v>50</v>
@@ -9485,7 +9518,7 @@
         <v>46281</v>
       </c>
       <c r="C249" s="49" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D249" s="26">
         <v>46277</v>
@@ -9497,10 +9530,10 @@
         <v>501</v>
       </c>
       <c r="G249" s="22" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="H249" s="36" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="I249" s="22" t="s">
         <v>50</v>
@@ -9510,9 +9543,30 @@
       <c r="A250" s="22">
         <v>192</v>
       </c>
-      <c r="C250" s="49"/>
-      <c r="F250" s="49"/>
-      <c r="H250" s="36"/>
+      <c r="B250" s="26">
+        <v>46282</v>
+      </c>
+      <c r="C250" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D250" s="26">
+        <v>46282</v>
+      </c>
+      <c r="E250" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F250" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="G250" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H250" s="36" t="s">
+        <v>857</v>
+      </c>
+      <c r="I250" s="22" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="251" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C251" s="49"/>
@@ -13204,7 +13258,7 @@
     <col min="6" max="6" width="48.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.625" style="38" customWidth="1"/>
     <col min="8" max="8" width="24" style="38" customWidth="1"/>
-    <col min="9" max="9" width="124" style="2" customWidth="1"/>
+    <col min="9" max="9" width="142.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="17.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="14.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="2" hidden="1" customWidth="1"/>
@@ -17099,7 +17153,7 @@
         <v>46276</v>
       </c>
       <c r="C138" s="10" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D138" s="55">
         <v>46276</v>
@@ -17117,7 +17171,7 @@
         <v>48</v>
       </c>
       <c r="I138" s="29" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="J138" s="10" t="s">
         <v>50</v>
@@ -17134,7 +17188,7 @@
         <v>46276</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D139" s="55">
         <v>46276</v>
@@ -17152,7 +17206,7 @@
         <v>48</v>
       </c>
       <c r="I139" s="29" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J139" s="10" t="s">
         <v>50</v>
@@ -17169,13 +17223,13 @@
         <v>46280</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D140" s="55">
         <v>46280</v>
       </c>
       <c r="E140" s="10" t="s">
-        <v>845</v>
+        <v>102</v>
       </c>
       <c r="F140" s="10" t="s">
         <v>333</v>
@@ -17187,40 +17241,121 @@
         <v>48</v>
       </c>
       <c r="I140" s="29" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="J140" s="10" t="s">
         <v>50</v>
+      </c>
+      <c r="N140" s="10" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="141" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A141" s="27">
         <v>113</v>
       </c>
-      <c r="B141" s="45"/>
-      <c r="D141" s="45"/>
-      <c r="G141" s="45"/>
-      <c r="H141" s="45"/>
-      <c r="I141" s="29"/>
+      <c r="B141" s="55">
+        <v>46281</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="D141" s="55">
+        <v>46281</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G141" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H141" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I141" s="29" t="s">
+        <v>853</v>
+      </c>
+      <c r="J141" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N141" s="10" t="s">
+        <v>852</v>
+      </c>
     </row>
     <row r="142" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A142" s="27"/>
-      <c r="B142" s="45"/>
-      <c r="D142" s="45"/>
-      <c r="G142" s="45"/>
-      <c r="H142" s="45"/>
-      <c r="I142" s="29"/>
+      <c r="A142" s="27">
+        <v>114</v>
+      </c>
+      <c r="B142" s="55">
+        <v>46282</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="D142" s="55">
+        <v>46282</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="G142" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H142" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I142" s="29" t="s">
+        <v>855</v>
+      </c>
+      <c r="J142" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N142" s="10" t="s">
+        <v>854</v>
+      </c>
     </row>
     <row r="143" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A143" s="27"/>
-      <c r="B143" s="45"/>
-      <c r="D143" s="45"/>
-      <c r="G143" s="45"/>
-      <c r="H143" s="45"/>
-      <c r="I143" s="29"/>
+      <c r="A143" s="27">
+        <v>115</v>
+      </c>
+      <c r="B143" s="55">
+        <v>46283</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="D143" s="55">
+        <v>46283</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="G143" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H143" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I143" s="29" t="s">
+        <v>861</v>
+      </c>
+      <c r="J143" s="10" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="144" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A144" s="27"/>
+      <c r="A144" s="27">
+        <v>116</v>
+      </c>
       <c r="B144" s="45"/>
       <c r="D144" s="45"/>
       <c r="G144" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BA1017-AF5A-4296-8AC0-8B611995601F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F6068B-9AC4-4348-B3C7-258793AC7738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="865">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2588,9 +2588,6 @@
     <t xml:space="preserve">33x24x10cm </t>
   </si>
   <si>
-    <t>Cuvettes For Fully Auto Analyser- Qty 120 Nos / Lamp For Fully Auto Analyser - Qty 2 Nos / Sample cups For Fully Auto Analyser-Qty 500 Nos</t>
-  </si>
-  <si>
     <t>AM/PP/0031/2627</t>
   </si>
   <si>
@@ -2607,6 +2604,18 @@
   </si>
   <si>
     <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>Cuvettes For Fully Auto Analyser- Qty 120 Nos / Lamp For Fully Auto Analyser 12 V/20W - Qty 2 Nos / Sample cups For Fully Auto Analyser-Qty 500 Nos</t>
+  </si>
+  <si>
+    <t>AM/PP/0033/2627</t>
+  </si>
+  <si>
+    <t>Icon HealthCare Solutions</t>
+  </si>
+  <si>
+    <t>Cuvettes For BioE Lab fully Auto Analyser- Qty 100 Nos.</t>
   </si>
 </sst>
 </file>
@@ -9562,7 +9571,7 @@
         <v>43</v>
       </c>
       <c r="H250" s="36" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I250" s="22" t="s">
         <v>129</v>
@@ -17293,7 +17302,7 @@
         <v>46282</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D142" s="55">
         <v>46282</v>
@@ -17311,7 +17320,7 @@
         <v>48</v>
       </c>
       <c r="I142" s="29" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="J142" s="10" t="s">
         <v>50</v>
@@ -17328,16 +17337,16 @@
         <v>46283</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D143" s="55">
         <v>46283</v>
       </c>
       <c r="E143" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="F143" s="10" t="s">
         <v>859</v>
-      </c>
-      <c r="F143" s="10" t="s">
-        <v>860</v>
       </c>
       <c r="G143" s="45" t="s">
         <v>47</v>
@@ -17346,7 +17355,7 @@
         <v>48</v>
       </c>
       <c r="I143" s="29" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="J143" s="10" t="s">
         <v>48</v>
@@ -17356,11 +17365,30 @@
       <c r="A144" s="27">
         <v>116</v>
       </c>
-      <c r="B144" s="45"/>
-      <c r="D144" s="45"/>
-      <c r="G144" s="45"/>
-      <c r="H144" s="45"/>
-      <c r="I144" s="29"/>
+      <c r="B144" s="55">
+        <v>46286</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="D144" s="55">
+        <v>46286</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="G144" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H144" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I144" s="29" t="s">
+        <v>864</v>
+      </c>
+      <c r="J144" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="145" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A145" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F6068B-9AC4-4348-B3C7-258793AC7738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C8E1B-D49A-4571-84F8-23A866D7F529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2615,7 +2615,7 @@
     <t>Icon HealthCare Solutions</t>
   </si>
   <si>
-    <t>Cuvettes For BioE Lab fully Auto Analyser- Qty 100 Nos.</t>
+    <t>Cuvettes For BioE Lab fully Auto Analyser- Qty 100 Nos.  / Photometer Halogen Lamp Assy Bioelab FA 6V/10W - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C8E1B-D49A-4571-84F8-23A866D7F529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10B5E83-2F61-41E9-B86F-D739C6827C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2103" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="872">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2616,6 +2616,27 @@
   </si>
   <si>
     <t>Cuvettes For BioE Lab fully Auto Analyser- Qty 100 Nos.  / Photometer Halogen Lamp Assy Bioelab FA 6V/10W - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>AM/DOM/0010/2627</t>
+  </si>
+  <si>
+    <t>Photometer Halogen Lamp Assy Bioelab FA 6V/10W- Qty 5 Nos.</t>
+  </si>
+  <si>
+    <t>ASHSKY Chem India Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Sampel Bottel - Qty 6 Nos.( Different Type)</t>
+  </si>
+  <si>
+    <t>Diagnova HealthCare</t>
+  </si>
+  <si>
+    <t>Baba Sampe;l Cuvette- Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t>JP Outer Cover / Flowcell Cover / Switch- Per 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -9578,6 +9599,9 @@
       </c>
     </row>
     <row r="251" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A251" s="22">
+        <v>193</v>
+      </c>
       <c r="C251" s="49"/>
       <c r="F251" s="49"/>
       <c r="H251" s="36"/>
@@ -17374,6 +17398,9 @@
       <c r="D144" s="55">
         <v>46286</v>
       </c>
+      <c r="E144" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="F144" s="10" t="s">
         <v>863</v>
       </c>
@@ -17390,39 +17417,124 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A145" s="27"/>
-      <c r="B145" s="45"/>
-      <c r="D145" s="45"/>
-      <c r="G145" s="45"/>
-      <c r="H145" s="45"/>
-      <c r="I145" s="29"/>
-    </row>
-    <row r="146" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A146" s="27"/>
-      <c r="B146" s="45"/>
-      <c r="D146" s="45"/>
-      <c r="G146" s="45"/>
-      <c r="H146" s="45"/>
-      <c r="I146" s="29"/>
-    </row>
-    <row r="147" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A147" s="27"/>
-      <c r="B147" s="45"/>
-      <c r="D147" s="45"/>
-      <c r="G147" s="45"/>
-      <c r="H147" s="45"/>
-      <c r="I147" s="29"/>
-    </row>
-    <row r="148" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="145" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A145" s="27">
+        <v>117</v>
+      </c>
+      <c r="B145" s="55">
+        <v>46287</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="D145" s="55">
+        <v>46287</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G145" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H145" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I145" s="29" t="s">
+        <v>866</v>
+      </c>
+      <c r="J145" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A146" s="27">
+        <v>118</v>
+      </c>
+      <c r="B146" s="55">
+        <v>46287</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D146" s="55">
+        <v>46287</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="G146" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H146" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I146" s="29" t="s">
+        <v>868</v>
+      </c>
+      <c r="J146" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A147" s="27">
+        <v>119</v>
+      </c>
+      <c r="B147" s="55">
+        <v>46287</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D147" s="55">
+        <v>46287</v>
+      </c>
+      <c r="F147" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="G147" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H147" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I147" s="29" t="s">
+        <v>870</v>
+      </c>
+      <c r="J147" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A148" s="27"/>
-      <c r="B148" s="45"/>
-      <c r="D148" s="45"/>
-      <c r="G148" s="45"/>
-      <c r="H148" s="45"/>
-      <c r="I148" s="29"/>
-    </row>
-    <row r="149" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="B148" s="55">
+        <v>46287</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D148" s="55">
+        <v>46287</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="F148" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="G148" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H148" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I148" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="J148" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A149" s="27"/>
       <c r="B149" s="45"/>
       <c r="D149" s="45"/>
@@ -17430,7 +17542,7 @@
       <c r="H149" s="45"/>
       <c r="I149" s="29"/>
     </row>
-    <row r="150" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="150" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A150" s="27"/>
       <c r="B150" s="45"/>
       <c r="D150" s="45"/>
@@ -17438,7 +17550,7 @@
       <c r="H150" s="45"/>
       <c r="I150" s="29"/>
     </row>
-    <row r="151" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="151" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A151" s="27"/>
       <c r="B151" s="45"/>
       <c r="D151" s="45"/>
@@ -17446,7 +17558,7 @@
       <c r="H151" s="45"/>
       <c r="I151" s="29"/>
     </row>
-    <row r="152" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="152" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A152" s="27"/>
       <c r="B152" s="45"/>
       <c r="D152" s="45"/>
@@ -17454,7 +17566,7 @@
       <c r="H152" s="45"/>
       <c r="I152" s="29"/>
     </row>
-    <row r="153" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="153" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A153" s="27"/>
       <c r="B153" s="45"/>
       <c r="D153" s="45"/>
@@ -17462,7 +17574,7 @@
       <c r="H153" s="45"/>
       <c r="I153" s="29"/>
     </row>
-    <row r="154" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="154" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A154" s="27"/>
       <c r="B154" s="45"/>
       <c r="D154" s="45"/>
@@ -17470,7 +17582,7 @@
       <c r="H154" s="45"/>
       <c r="I154" s="29"/>
     </row>
-    <row r="155" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="155" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A155" s="27"/>
       <c r="B155" s="45"/>
       <c r="D155" s="45"/>
@@ -17478,7 +17590,7 @@
       <c r="H155" s="45"/>
       <c r="I155" s="29"/>
     </row>
-    <row r="156" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="156" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A156" s="27"/>
       <c r="B156" s="45"/>
       <c r="D156" s="45"/>
@@ -17486,7 +17598,7 @@
       <c r="H156" s="45"/>
       <c r="I156" s="29"/>
     </row>
-    <row r="157" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="157" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A157" s="27"/>
       <c r="B157" s="45"/>
       <c r="D157" s="45"/>
@@ -17494,7 +17606,7 @@
       <c r="H157" s="45"/>
       <c r="I157" s="29"/>
     </row>
-    <row r="158" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="158" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="27"/>
       <c r="B158" s="45"/>
       <c r="D158" s="45"/>
@@ -17502,7 +17614,7 @@
       <c r="H158" s="45"/>
       <c r="I158" s="29"/>
     </row>
-    <row r="159" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="159" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A159" s="27"/>
       <c r="B159" s="45"/>
       <c r="D159" s="45"/>
@@ -17510,7 +17622,7 @@
       <c r="H159" s="45"/>
       <c r="I159" s="29"/>
     </row>
-    <row r="160" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="160" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A160" s="27"/>
       <c r="B160" s="45"/>
       <c r="D160" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10B5E83-2F61-41E9-B86F-D739C6827C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978F786C-5643-46C2-A0C4-C5DA1E341747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2129" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="874">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2637,6 +2637,12 @@
   </si>
   <si>
     <t>JP Outer Cover / Flowcell Cover / Switch- Per 2 Nos.</t>
+  </si>
+  <si>
+    <t>Sampel Cups For Fully Auto Analyser - Qty 500 Nos.</t>
+  </si>
+  <si>
+    <t>Tirupti</t>
   </si>
 </sst>
 </file>
@@ -17505,7 +17511,9 @@
       </c>
     </row>
     <row r="148" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A148" s="27"/>
+      <c r="A148" s="27">
+        <v>120</v>
+      </c>
       <c r="B148" s="55">
         <v>46287</v>
       </c>
@@ -17535,12 +17543,36 @@
       </c>
     </row>
     <row r="149" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A149" s="27"/>
-      <c r="B149" s="45"/>
-      <c r="D149" s="45"/>
-      <c r="G149" s="45"/>
-      <c r="H149" s="45"/>
-      <c r="I149" s="29"/>
+      <c r="A149" s="27">
+        <v>121</v>
+      </c>
+      <c r="B149" s="55">
+        <v>46287</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D149" s="55">
+        <v>46287</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="F149" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="G149" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H149" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I149" s="29" t="s">
+        <v>872</v>
+      </c>
+      <c r="J149" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="150" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A150" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978F786C-5643-46C2-A0C4-C5DA1E341747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839FC2D8-EE08-4941-9533-2177DA9B32DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="876">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2643,6 +2643,12 @@
   </si>
   <si>
     <t>Tirupti</t>
+  </si>
+  <si>
+    <t>AWB#7X110908374</t>
+  </si>
+  <si>
+    <t>Photometer Halogen lamp assy Bioelab FA 6V/10W -Qty 5 Pcs</t>
   </si>
 </sst>
 </file>
@@ -9608,9 +9614,27 @@
       <c r="A251" s="22">
         <v>193</v>
       </c>
-      <c r="C251" s="49"/>
-      <c r="F251" s="49"/>
-      <c r="H251" s="36"/>
+      <c r="B251" s="26">
+        <v>46288</v>
+      </c>
+      <c r="C251" s="49" t="s">
+        <v>874</v>
+      </c>
+      <c r="D251" s="26">
+        <v>46284</v>
+      </c>
+      <c r="E251" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F251" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H251" s="36" t="s">
+        <v>875</v>
+      </c>
+      <c r="I251" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="252" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C252" s="49"/>
@@ -17465,6 +17489,9 @@
       <c r="D146" s="55">
         <v>46287</v>
       </c>
+      <c r="E146" s="10" t="s">
+        <v>102</v>
+      </c>
       <c r="F146" s="10" t="s">
         <v>867</v>
       </c>
@@ -17493,6 +17520,9 @@
       </c>
       <c r="D147" s="55">
         <v>46287</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>869</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839FC2D8-EE08-4941-9533-2177DA9B32DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E3A819-357C-4E85-AAED-2EB8B657B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="883">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2649,6 +2649,27 @@
   </si>
   <si>
     <t>Photometer Halogen lamp assy Bioelab FA 6V/10W -Qty 5 Pcs</t>
+  </si>
+  <si>
+    <t>CSPL/26-27/031</t>
+  </si>
+  <si>
+    <t>Cellpro Systems Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Flowcell Wash  (Fully Automatic) - Qty 1 Ltr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 23 Sep 2026</t>
+  </si>
+  <si>
+    <t>AM/DOM/0011//2627</t>
+  </si>
+  <si>
+    <t>BioLab</t>
+  </si>
+  <si>
+    <t>Lamp Assembly For Semi Auto(C-Biosys Chem 300) - Qty 1 No.</t>
   </si>
 </sst>
 </file>
@@ -9629,6 +9650,9 @@
       <c r="F251" s="49" t="s">
         <v>83</v>
       </c>
+      <c r="G251" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="H251" s="36" t="s">
         <v>875</v>
       </c>
@@ -9637,11 +9661,38 @@
       </c>
     </row>
     <row r="252" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C252" s="49"/>
-      <c r="F252" s="49"/>
-      <c r="H252" s="36"/>
+      <c r="A252" s="22">
+        <v>194</v>
+      </c>
+      <c r="B252" s="26">
+        <v>46288</v>
+      </c>
+      <c r="C252" s="49" t="s">
+        <v>876</v>
+      </c>
+      <c r="D252" s="26">
+        <v>46286</v>
+      </c>
+      <c r="E252" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F252" s="49" t="s">
+        <v>877</v>
+      </c>
+      <c r="G252" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H252" s="36" t="s">
+        <v>878</v>
+      </c>
+      <c r="I252" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="253" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A253" s="22">
+        <v>195</v>
+      </c>
       <c r="C253" s="49"/>
       <c r="F253" s="49"/>
       <c r="H253" s="36"/>
@@ -17605,15 +17656,41 @@
       </c>
     </row>
     <row r="150" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A150" s="27"/>
-      <c r="B150" s="45"/>
-      <c r="D150" s="45"/>
-      <c r="G150" s="45"/>
-      <c r="H150" s="45"/>
-      <c r="I150" s="29"/>
+      <c r="A150" s="27">
+        <v>122</v>
+      </c>
+      <c r="B150" s="45" t="s">
+        <v>879</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>880</v>
+      </c>
+      <c r="D150" s="55">
+        <v>46288</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="G150" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H150" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I150" s="29" t="s">
+        <v>882</v>
+      </c>
+      <c r="J150" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="151" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A151" s="27"/>
+      <c r="A151" s="27">
+        <v>123</v>
+      </c>
       <c r="B151" s="45"/>
       <c r="D151" s="45"/>
       <c r="G151" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E3A819-357C-4E85-AAED-2EB8B657B05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CB4E46-53F6-4E2B-841A-8A6BD2D89E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="888">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2670,6 +2670,21 @@
   </si>
   <si>
     <t>Lamp Assembly For Semi Auto(C-Biosys Chem 300) - Qty 1 No.</t>
+  </si>
+  <si>
+    <t>AWB#7X110910508</t>
+  </si>
+  <si>
+    <t>Photometer Halogen lamp assy Bioelab FA 6V/10W -Qty 10Pcs</t>
+  </si>
+  <si>
+    <t>AM/DOM/0012/2627</t>
+  </si>
+  <si>
+    <t>Martuti</t>
+  </si>
+  <si>
+    <t>Lamp Assembly For Elab Analyser FA 6V/10W- Qty 10 Nos.</t>
   </si>
 </sst>
 </file>
@@ -9693,9 +9708,30 @@
       <c r="A253" s="22">
         <v>195</v>
       </c>
-      <c r="C253" s="49"/>
-      <c r="F253" s="49"/>
-      <c r="H253" s="36"/>
+      <c r="B253" s="26">
+        <v>46289</v>
+      </c>
+      <c r="C253" s="49" t="s">
+        <v>883</v>
+      </c>
+      <c r="D253" s="26">
+        <v>46287</v>
+      </c>
+      <c r="E253" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F253" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G253" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H253" s="36" t="s">
+        <v>884</v>
+      </c>
+      <c r="I253" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="254" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C254" s="49"/>
@@ -17691,11 +17727,33 @@
       <c r="A151" s="27">
         <v>123</v>
       </c>
-      <c r="B151" s="45"/>
-      <c r="D151" s="45"/>
-      <c r="G151" s="45"/>
-      <c r="H151" s="45"/>
-      <c r="I151" s="29"/>
+      <c r="B151" s="55">
+        <v>46291</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>885</v>
+      </c>
+      <c r="D151" s="55">
+        <v>46289</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>886</v>
+      </c>
+      <c r="F151" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G151" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H151" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I151" s="29" t="s">
+        <v>887</v>
+      </c>
+      <c r="J151" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="152" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A152" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CB4E46-53F6-4E2B-841A-8A6BD2D89E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F364CB34-D5FB-4344-AC40-C68D4AD0C359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="895">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2685,6 +2685,27 @@
   </si>
   <si>
     <t>Lamp Assembly For Elab Analyser FA 6V/10W- Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t>ADR/26-27/0165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hitachi Micro Sample Cups- Qty </t>
+  </si>
+  <si>
+    <t>7 Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 26 Sep 2026</t>
+  </si>
+  <si>
+    <t>AM/PP/0034/2627</t>
+  </si>
+  <si>
+    <t>Sample Cups Zybio400 (HITachi Cups)- Qty-50000 Nos. / Sample Cups Beckman-Biosystems - Qty 20000</t>
+  </si>
+  <si>
+    <t>24x18x19- (6 Box) - 16x11x9 (1 Box)</t>
   </si>
 </sst>
 </file>
@@ -9734,9 +9755,33 @@
       </c>
     </row>
     <row r="254" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C254" s="49"/>
-      <c r="F254" s="49"/>
-      <c r="H254" s="36"/>
+      <c r="A254" s="22">
+        <v>196</v>
+      </c>
+      <c r="B254" s="26">
+        <v>46290</v>
+      </c>
+      <c r="C254" s="49" t="s">
+        <v>888</v>
+      </c>
+      <c r="D254" s="26">
+        <v>46282</v>
+      </c>
+      <c r="E254" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="F254" s="49" t="s">
+        <v>792</v>
+      </c>
+      <c r="G254" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H254" s="29" t="s">
+        <v>889</v>
+      </c>
+      <c r="I254" s="22" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="255" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C255" s="49"/>
@@ -17534,7 +17579,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="145" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A145" s="27">
         <v>117</v>
       </c>
@@ -17563,7 +17608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="146" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A146" s="27">
         <v>118</v>
       </c>
@@ -17595,7 +17640,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="147" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A147" s="27">
         <v>119</v>
       </c>
@@ -17627,7 +17672,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="148" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="148" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A148" s="27">
         <v>120</v>
       </c>
@@ -17659,7 +17704,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="149" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A149" s="27">
         <v>121</v>
       </c>
@@ -17691,7 +17736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="150" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A150" s="27">
         <v>122</v>
       </c>
@@ -17723,7 +17768,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="151" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A151" s="27">
         <v>123</v>
       </c>
@@ -17755,15 +17800,39 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A152" s="27"/>
-      <c r="B152" s="45"/>
-      <c r="D152" s="45"/>
-      <c r="G152" s="45"/>
-      <c r="H152" s="45"/>
-      <c r="I152" s="29"/>
-    </row>
-    <row r="153" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="152" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A152" s="27">
+        <v>124</v>
+      </c>
+      <c r="B152" s="45" t="s">
+        <v>891</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="D152" s="55">
+        <v>46290</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G152" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H152" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I152" s="29" t="s">
+        <v>893</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>890</v>
+      </c>
+      <c r="O152" s="10" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A153" s="27"/>
       <c r="B153" s="45"/>
       <c r="D153" s="45"/>
@@ -17771,7 +17840,7 @@
       <c r="H153" s="45"/>
       <c r="I153" s="29"/>
     </row>
-    <row r="154" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="154" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A154" s="27"/>
       <c r="B154" s="45"/>
       <c r="D154" s="45"/>
@@ -17779,7 +17848,7 @@
       <c r="H154" s="45"/>
       <c r="I154" s="29"/>
     </row>
-    <row r="155" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="155" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A155" s="27"/>
       <c r="B155" s="45"/>
       <c r="D155" s="45"/>
@@ -17787,7 +17856,7 @@
       <c r="H155" s="45"/>
       <c r="I155" s="29"/>
     </row>
-    <row r="156" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="156" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A156" s="27"/>
       <c r="B156" s="45"/>
       <c r="D156" s="45"/>
@@ -17795,7 +17864,7 @@
       <c r="H156" s="45"/>
       <c r="I156" s="29"/>
     </row>
-    <row r="157" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A157" s="27"/>
       <c r="B157" s="45"/>
       <c r="D157" s="45"/>
@@ -17803,7 +17872,7 @@
       <c r="H157" s="45"/>
       <c r="I157" s="29"/>
     </row>
-    <row r="158" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="27"/>
       <c r="B158" s="45"/>
       <c r="D158" s="45"/>
@@ -17811,7 +17880,7 @@
       <c r="H158" s="45"/>
       <c r="I158" s="29"/>
     </row>
-    <row r="159" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="159" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A159" s="27"/>
       <c r="B159" s="45"/>
       <c r="D159" s="45"/>
@@ -17819,7 +17888,7 @@
       <c r="H159" s="45"/>
       <c r="I159" s="29"/>
     </row>
-    <row r="160" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="160" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A160" s="27"/>
       <c r="B160" s="45"/>
       <c r="D160" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F364CB34-D5FB-4344-AC40-C68D4AD0C359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD9C8C1-264E-4E17-8FC9-304E068F1A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="897">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2706,6 +2706,12 @@
   </si>
   <si>
     <t>24x18x19- (6 Box) - 16x11x9 (1 Box)</t>
+  </si>
+  <si>
+    <t>AM/PP/0035/2627</t>
+  </si>
+  <si>
+    <t>Probe For Fully Auto analyser - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -17833,15 +17839,41 @@
       </c>
     </row>
     <row r="153" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A153" s="27"/>
-      <c r="B153" s="45"/>
-      <c r="D153" s="45"/>
-      <c r="G153" s="45"/>
-      <c r="H153" s="45"/>
-      <c r="I153" s="29"/>
+      <c r="A153" s="27">
+        <v>125</v>
+      </c>
+      <c r="B153" s="55">
+        <v>46291</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="D153" s="55">
+        <v>46291</v>
+      </c>
+      <c r="E153" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="G153" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H153" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I153" s="29" t="s">
+        <v>896</v>
+      </c>
+      <c r="J153" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="154" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A154" s="27"/>
+      <c r="A154" s="27">
+        <v>126</v>
+      </c>
       <c r="B154" s="45"/>
       <c r="D154" s="45"/>
       <c r="G154" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD9C8C1-264E-4E17-8FC9-304E068F1A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC739235-130D-4830-87C6-71A6548EBB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3591,7 +3591,7 @@
     <col min="5" max="5" width="18.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="45.5" style="51" customWidth="1"/>
     <col min="7" max="7" width="22.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="179.125" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="189.5" style="38" customWidth="1"/>
     <col min="9" max="9" width="13.625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="19.625" style="2" hidden="1" customWidth="1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC739235-130D-4830-87C6-71A6548EBB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30236D1E-7ECC-4D69-B293-BEDFE1B89251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30236D1E-7ECC-4D69-B293-BEDFE1B89251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C9F4F-4402-4FC2-AE04-B7CF8713D4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="901">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2712,6 +2712,18 @@
   </si>
   <si>
     <t>Probe For Fully Auto analyser - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>AM/DOM/0013?2627</t>
+  </si>
+  <si>
+    <t>Om Logistics</t>
+  </si>
+  <si>
+    <t>Prism Biomedicals Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Sample Cups- Qty 400 Nos. / Cuvettes (60 in one set)- Qty 120 Nos.</t>
   </si>
 </sst>
 </file>
@@ -17819,6 +17831,9 @@
       <c r="D152" s="55">
         <v>46290</v>
       </c>
+      <c r="E152" s="10" t="s">
+        <v>898</v>
+      </c>
       <c r="F152" s="10" t="s">
         <v>161</v>
       </c>
@@ -17874,11 +17889,33 @@
       <c r="A154" s="27">
         <v>126</v>
       </c>
-      <c r="B154" s="45"/>
-      <c r="D154" s="45"/>
-      <c r="G154" s="45"/>
-      <c r="H154" s="45"/>
-      <c r="I154" s="29"/>
+      <c r="B154" s="55">
+        <v>46293</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>897</v>
+      </c>
+      <c r="D154" s="55">
+        <v>46293</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F154" s="10" t="s">
+        <v>899</v>
+      </c>
+      <c r="G154" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H154" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I154" s="29" t="s">
+        <v>900</v>
+      </c>
+      <c r="J154" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="155" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A155" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380C9F4F-4402-4FC2-AE04-B7CF8713D4ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478EAA9-3197-46F7-9C92-713469135191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="903">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2615,9 +2615,6 @@
     <t>Icon HealthCare Solutions</t>
   </si>
   <si>
-    <t>Cuvettes For BioE Lab fully Auto Analyser- Qty 100 Nos.  / Photometer Halogen Lamp Assy Bioelab FA 6V/10W - Qty 1 Nos.</t>
-  </si>
-  <si>
     <t>AM/DOM/0010/2627</t>
   </si>
   <si>
@@ -2724,6 +2721,15 @@
   </si>
   <si>
     <t>Sample Cups- Qty 400 Nos. / Cuvettes (60 in one set)- Qty 120 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Photometer Halogen Lamp Assy Bioelab FA 6V/10W - Qty 6 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuvettes For BioE Lab fully Auto Analyser- Qty 100 Nos.  </t>
+  </si>
+  <si>
+    <t>AM/PP/0036/2627</t>
   </si>
 </sst>
 </file>
@@ -9693,7 +9699,7 @@
         <v>46288</v>
       </c>
       <c r="C251" s="49" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D251" s="26">
         <v>46284</v>
@@ -9708,7 +9714,7 @@
         <v>48</v>
       </c>
       <c r="H251" s="36" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="I251" s="22" t="s">
         <v>50</v>
@@ -9722,7 +9728,7 @@
         <v>46288</v>
       </c>
       <c r="C252" s="49" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D252" s="26">
         <v>46286</v>
@@ -9731,13 +9737,13 @@
         <v>13</v>
       </c>
       <c r="F252" s="49" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G252" s="22" t="s">
         <v>48</v>
       </c>
       <c r="H252" s="36" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I252" s="22" t="s">
         <v>50</v>
@@ -9751,7 +9757,7 @@
         <v>46289</v>
       </c>
       <c r="C253" s="49" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D253" s="26">
         <v>46287</v>
@@ -9766,7 +9772,7 @@
         <v>48</v>
       </c>
       <c r="H253" s="36" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="I253" s="22" t="s">
         <v>50</v>
@@ -9780,7 +9786,7 @@
         <v>46290</v>
       </c>
       <c r="C254" s="49" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D254" s="26">
         <v>46282</v>
@@ -9795,10 +9801,10 @@
         <v>48</v>
       </c>
       <c r="H254" s="29" t="s">
+        <v>888</v>
+      </c>
+      <c r="I254" s="22" t="s">
         <v>889</v>
-      </c>
-      <c r="I254" s="22" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="255" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
@@ -17591,7 +17597,7 @@
         <v>48</v>
       </c>
       <c r="I144" s="29" t="s">
-        <v>864</v>
+        <v>901</v>
       </c>
       <c r="J144" s="10" t="s">
         <v>50</v>
@@ -17605,7 +17611,7 @@
         <v>46287</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D145" s="55">
         <v>46287</v>
@@ -17620,7 +17626,7 @@
         <v>48</v>
       </c>
       <c r="I145" s="29" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J145" s="10" t="s">
         <v>50</v>
@@ -17643,7 +17649,7 @@
         <v>102</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G146" s="45" t="s">
         <v>47</v>
@@ -17652,7 +17658,7 @@
         <v>48</v>
       </c>
       <c r="I146" s="29" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J146" s="10" t="s">
         <v>50</v>
@@ -17675,7 +17681,7 @@
         <v>102</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G147" s="45" t="s">
         <v>47</v>
@@ -17684,7 +17690,7 @@
         <v>48</v>
       </c>
       <c r="I147" s="29" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J147" s="10" t="s">
         <v>129</v>
@@ -17716,7 +17722,7 @@
         <v>210</v>
       </c>
       <c r="I148" s="29" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J148" s="10" t="s">
         <v>50</v>
@@ -17736,7 +17742,7 @@
         <v>46287</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>799</v>
@@ -17748,7 +17754,7 @@
         <v>48</v>
       </c>
       <c r="I149" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="J149" s="10" t="s">
         <v>50</v>
@@ -17759,10 +17765,10 @@
         <v>122</v>
       </c>
       <c r="B150" s="45" t="s">
+        <v>878</v>
+      </c>
+      <c r="C150" s="10" t="s">
         <v>879</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>880</v>
       </c>
       <c r="D150" s="55">
         <v>46288</v>
@@ -17771,7 +17777,7 @@
         <v>13</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G150" s="45" t="s">
         <v>47</v>
@@ -17780,7 +17786,7 @@
         <v>48</v>
       </c>
       <c r="I150" s="29" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="J150" s="10" t="s">
         <v>50</v>
@@ -17794,13 +17800,13 @@
         <v>46291</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D151" s="55">
         <v>46289</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>65</v>
@@ -17812,7 +17818,7 @@
         <v>48</v>
       </c>
       <c r="I151" s="29" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="J151" s="10" t="s">
         <v>50</v>
@@ -17823,16 +17829,16 @@
         <v>124</v>
       </c>
       <c r="B152" s="45" t="s">
+        <v>890</v>
+      </c>
+      <c r="C152" s="10" t="s">
         <v>891</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>892</v>
       </c>
       <c r="D152" s="55">
         <v>46290</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F152" s="10" t="s">
         <v>161</v>
@@ -17844,13 +17850,13 @@
         <v>48</v>
       </c>
       <c r="I152" s="29" t="s">
+        <v>892</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="O152" s="10" t="s">
         <v>893</v>
-      </c>
-      <c r="J152" s="10" t="s">
-        <v>890</v>
-      </c>
-      <c r="O152" s="10" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="153" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
@@ -17861,7 +17867,7 @@
         <v>46291</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D153" s="55">
         <v>46291</v>
@@ -17879,7 +17885,7 @@
         <v>48</v>
       </c>
       <c r="I153" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J153" s="10" t="s">
         <v>50</v>
@@ -17893,16 +17899,16 @@
         <v>46293</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D154" s="55">
         <v>46293</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G154" s="45" t="s">
         <v>47</v>
@@ -17911,22 +17917,48 @@
         <v>48</v>
       </c>
       <c r="I154" s="29" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="J154" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="155" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A155" s="27"/>
-      <c r="B155" s="45"/>
-      <c r="D155" s="45"/>
-      <c r="G155" s="45"/>
-      <c r="H155" s="45"/>
-      <c r="I155" s="29"/>
+      <c r="A155" s="27">
+        <v>127</v>
+      </c>
+      <c r="B155" s="55">
+        <v>46293</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="D155" s="55">
+        <v>46293</v>
+      </c>
+      <c r="E155" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="G155" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H155" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I155" s="29" t="s">
+        <v>900</v>
+      </c>
+      <c r="J155" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="156" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A156" s="27"/>
+      <c r="A156" s="27">
+        <v>128</v>
+      </c>
       <c r="B156" s="45"/>
       <c r="D156" s="45"/>
       <c r="G156" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478EAA9-3197-46F7-9C92-713469135191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82B26BC-DB32-4E18-9B6D-9B3D1B0682EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="903">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="907">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2730,6 +2730,18 @@
   </si>
   <si>
     <t>AM/PP/0036/2627</t>
+  </si>
+  <si>
+    <t>porter</t>
+  </si>
+  <si>
+    <t>Petri Dish &amp; Urine Sample Bottle - Qty 10 Nos.</t>
+  </si>
+  <si>
+    <t>Challan No. PTW/26-27/018</t>
+  </si>
+  <si>
+    <t>Heatasink For Lamp RD-BTS-SAA-064 - Qty 4 Nos.</t>
   </si>
 </sst>
 </file>
@@ -9808,9 +9820,33 @@
       </c>
     </row>
     <row r="255" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C255" s="49"/>
-      <c r="F255" s="49"/>
-      <c r="H255" s="36"/>
+      <c r="A255" s="22">
+        <v>197</v>
+      </c>
+      <c r="B255" s="26">
+        <v>46293</v>
+      </c>
+      <c r="C255" s="49" t="s">
+        <v>905</v>
+      </c>
+      <c r="D255" s="26">
+        <v>46293</v>
+      </c>
+      <c r="E255" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F255" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="G255" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H255" s="36" t="s">
+        <v>906</v>
+      </c>
+      <c r="I255" s="22" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="256" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C256" s="49"/>
@@ -17710,7 +17746,7 @@
         <v>46287</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>486</v>
+        <v>134</v>
       </c>
       <c r="F148" s="10" t="s">
         <v>473</v>
@@ -17959,11 +17995,33 @@
       <c r="A156" s="27">
         <v>128</v>
       </c>
-      <c r="B156" s="45"/>
-      <c r="D156" s="45"/>
-      <c r="G156" s="45"/>
-      <c r="H156" s="45"/>
-      <c r="I156" s="29"/>
+      <c r="B156" s="55">
+        <v>46294</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D156" s="55">
+        <v>46294</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>903</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="G156" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H156" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I156" s="29" t="s">
+        <v>904</v>
+      </c>
+      <c r="J156" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A157" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82B26BC-DB32-4E18-9B6D-9B3D1B0682EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05425326-59CD-4CF0-AF33-B286B645C0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="907">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="915">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2742,6 +2742,30 @@
   </si>
   <si>
     <t>Heatasink For Lamp RD-BTS-SAA-064 - Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>DC0072</t>
+  </si>
+  <si>
+    <t>DC0073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioSci HealthCare </t>
+  </si>
+  <si>
+    <t>BioSci 50 power Supply PCB(Rtn)-Qty 8 Nos. / Nano Pi PCB (Rtn)- Qty 1 Nos. / Photometer PCB (Rtn) -Qty 3 Nos. &amp; SanDisk Micro Card 16 GB-1</t>
+  </si>
+  <si>
+    <t>BioSci Health Care ( Ravi Sir)</t>
+  </si>
+  <si>
+    <t>4 Nos. of Invoice For The Month OF September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35x24x9cm </t>
+  </si>
+  <si>
+    <t>Nano Pi PCB - Qty 7 Nos.</t>
   </si>
 </sst>
 </file>
@@ -18024,28 +18048,91 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="27"/>
-      <c r="B157" s="45"/>
-      <c r="D157" s="45"/>
-      <c r="G157" s="45"/>
-      <c r="H157" s="45"/>
-      <c r="I157" s="29"/>
+      <c r="A157" s="27">
+        <v>129</v>
+      </c>
+      <c r="B157" s="55">
+        <v>46294</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>907</v>
+      </c>
+      <c r="D157" s="55">
+        <v>46294</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="F157" s="10" t="s">
+        <v>909</v>
+      </c>
+      <c r="G157" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H157" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I157" s="29" t="s">
+        <v>910</v>
+      </c>
+      <c r="J157" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O157" s="10" t="s">
+        <v>913</v>
+      </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="27"/>
-      <c r="B158" s="45"/>
-      <c r="D158" s="45"/>
-      <c r="G158" s="45"/>
-      <c r="H158" s="45"/>
-      <c r="I158" s="29"/>
+      <c r="B158" s="55"/>
+      <c r="D158" s="55"/>
+      <c r="F158" s="10" t="s">
+        <v>911</v>
+      </c>
+      <c r="G158" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H158" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="I158" s="29" t="s">
+        <v>912</v>
+      </c>
+      <c r="J158" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="159" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A159" s="27"/>
-      <c r="B159" s="45"/>
-      <c r="D159" s="45"/>
-      <c r="G159" s="45"/>
-      <c r="H159" s="45"/>
-      <c r="I159" s="29"/>
+      <c r="A159" s="27">
+        <v>130</v>
+      </c>
+      <c r="B159" s="55">
+        <v>46294</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="D159" s="55">
+        <v>46294</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="G159" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="H159" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I159" s="29" t="s">
+        <v>914</v>
+      </c>
+      <c r="J159" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="160" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A160" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05425326-59CD-4CF0-AF33-B286B645C0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4A4967-A908-4748-A1B4-DFA47F0DCA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2240" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="917">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2766,6 +2766,12 @@
   </si>
   <si>
     <t>Nano Pi PCB - Qty 7 Nos.</t>
+  </si>
+  <si>
+    <t>Akshat Biomedical (7733832686)</t>
+  </si>
+  <si>
+    <t>Cuvette - Qty 320 (8 pckt -Per Pckt 40 Nos.)</t>
   </si>
 </sst>
 </file>
@@ -9873,9 +9879,30 @@
       </c>
     </row>
     <row r="256" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C256" s="49"/>
-      <c r="F256" s="49"/>
-      <c r="H256" s="36"/>
+      <c r="A256" s="22">
+        <v>198</v>
+      </c>
+      <c r="B256" s="26">
+        <v>46295</v>
+      </c>
+      <c r="C256" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D256" s="26">
+        <v>46295</v>
+      </c>
+      <c r="E256" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F256" s="49" t="s">
+        <v>915</v>
+      </c>
+      <c r="H256" s="36" t="s">
+        <v>916</v>
+      </c>
+      <c r="I256" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="257" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C257" s="49"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4A4967-A908-4748-A1B4-DFA47F0DCA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364C61DC-673D-4FB1-8DBD-3B88488001C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="918">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2772,6 +2772,9 @@
   </si>
   <si>
     <t>Cuvette - Qty 320 (8 pckt -Per Pckt 40 Nos.)</t>
+  </si>
+  <si>
+    <t>Sample Lamp - Qty 1 Nos.</t>
   </si>
 </sst>
 </file>
@@ -18162,12 +18165,36 @@
       </c>
     </row>
     <row r="160" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A160" s="27"/>
-      <c r="B160" s="45"/>
-      <c r="D160" s="45"/>
-      <c r="G160" s="45"/>
-      <c r="H160" s="45"/>
-      <c r="I160" s="29"/>
+      <c r="A160" s="27">
+        <v>131</v>
+      </c>
+      <c r="B160" s="55">
+        <v>46295</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D160" s="55">
+        <v>46295</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="10" t="s">
+        <v>863</v>
+      </c>
+      <c r="G160" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H160" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I160" s="29" t="s">
+        <v>917</v>
+      </c>
+      <c r="J160" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="161" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A161" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364C61DC-673D-4FB1-8DBD-3B88488001C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9464E733-A4EF-4E34-8266-86B08DFE8A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="918">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2771,10 +2771,10 @@
     <t>Akshat Biomedical (7733832686)</t>
   </si>
   <si>
-    <t>Cuvette - Qty 320 (8 pckt -Per Pckt 40 Nos.)</t>
-  </si>
-  <si>
     <t>Sample Lamp - Qty 1 Nos.</t>
+  </si>
+  <si>
+    <t>Cuvette - Qty 300 (7 pckt -Per Pckt 40 Nos.) &amp; (1 Pckt 20 Nos.) = 5 Sets</t>
   </si>
 </sst>
 </file>
@@ -9900,89 +9900,95 @@
       <c r="F256" s="49" t="s">
         <v>915</v>
       </c>
+      <c r="G256" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="H256" s="36" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I256" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="257" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A257" s="22">
+        <v>199</v>
+      </c>
       <c r="C257" s="49"/>
       <c r="F257" s="49"/>
       <c r="H257" s="36"/>
     </row>
-    <row r="258" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="258" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C258" s="49"/>
       <c r="F258" s="49"/>
       <c r="H258" s="36"/>
     </row>
-    <row r="259" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="259" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C259" s="49"/>
       <c r="F259" s="49"/>
       <c r="H259" s="36"/>
     </row>
-    <row r="260" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="260" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C260" s="49"/>
       <c r="F260" s="49"/>
       <c r="H260" s="36"/>
     </row>
-    <row r="261" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="261" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C261" s="49"/>
       <c r="F261" s="49"/>
       <c r="H261" s="36"/>
     </row>
-    <row r="262" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="262" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C262" s="49"/>
       <c r="F262" s="49"/>
       <c r="H262" s="36"/>
     </row>
-    <row r="263" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="263" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C263" s="49"/>
       <c r="F263" s="49"/>
       <c r="H263" s="36"/>
     </row>
-    <row r="264" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="264" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C264" s="49"/>
       <c r="F264" s="49"/>
       <c r="H264" s="36"/>
     </row>
-    <row r="265" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="265" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C265" s="49"/>
       <c r="F265" s="49"/>
       <c r="H265" s="36"/>
     </row>
-    <row r="266" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="266" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C266" s="49"/>
       <c r="F266" s="49"/>
       <c r="H266" s="36"/>
     </row>
-    <row r="267" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="267" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C267" s="49"/>
       <c r="F267" s="49"/>
       <c r="H267" s="36"/>
     </row>
-    <row r="268" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="268" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C268" s="49"/>
       <c r="F268" s="49"/>
       <c r="H268" s="36"/>
     </row>
-    <row r="269" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="269" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C269" s="49"/>
       <c r="F269" s="49"/>
       <c r="H269" s="36"/>
     </row>
-    <row r="270" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="270" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C270" s="49"/>
       <c r="F270" s="49"/>
       <c r="H270" s="36"/>
     </row>
-    <row r="271" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="271" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C271" s="49"/>
       <c r="F271" s="49"/>
       <c r="H271" s="36"/>
     </row>
-    <row r="272" spans="3:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="272" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C272" s="49"/>
       <c r="F272" s="49"/>
       <c r="H272" s="36"/>
@@ -18190,7 +18196,7 @@
         <v>48</v>
       </c>
       <c r="I160" s="29" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="J160" s="10" t="s">
         <v>50</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9464E733-A4EF-4E34-8266-86B08DFE8A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA315C-96F6-496E-A9A5-501C9B9FCC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="922">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2775,6 +2775,18 @@
   </si>
   <si>
     <t>Cuvette - Qty 300 (7 pckt -Per Pckt 40 Nos.) &amp; (1 Pckt 20 Nos.) = 5 Sets</t>
+  </si>
+  <si>
+    <t>28x26x20cm</t>
+  </si>
+  <si>
+    <t>RGT Tray - 28 Podsition &amp; 40 Position With Sample Bottle With Cap</t>
+  </si>
+  <si>
+    <t>Cuvette - 2 Set -Qty 120 Nos.</t>
+  </si>
+  <si>
+    <t>Heat Skin - Qty 5 Nos.</t>
   </si>
 </sst>
 </file>
@@ -18202,31 +18214,106 @@
         <v>50</v>
       </c>
     </row>
-    <row r="161" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A161" s="27"/>
-      <c r="B161" s="45"/>
-      <c r="D161" s="45"/>
-      <c r="G161" s="45"/>
-      <c r="H161" s="45"/>
-      <c r="I161" s="29"/>
-    </row>
-    <row r="162" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A162" s="27"/>
-      <c r="B162" s="45"/>
-      <c r="D162" s="45"/>
-      <c r="G162" s="45"/>
-      <c r="H162" s="45"/>
-      <c r="I162" s="29"/>
-    </row>
-    <row r="163" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A163" s="27"/>
-      <c r="B163" s="45"/>
-      <c r="D163" s="45"/>
-      <c r="G163" s="45"/>
-      <c r="H163" s="45"/>
-      <c r="I163" s="29"/>
-    </row>
-    <row r="164" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="161" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A161" s="27">
+        <v>132</v>
+      </c>
+      <c r="B161" s="55">
+        <v>46296</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D161" s="55">
+        <v>46296</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="G161" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H161" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I161" s="29" t="s">
+        <v>919</v>
+      </c>
+      <c r="J161" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="O161" s="10" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A162" s="27">
+        <v>133</v>
+      </c>
+      <c r="B162" s="55">
+        <v>46296</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D162" s="55">
+        <v>46296</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F162" s="10" t="s">
+        <v>799</v>
+      </c>
+      <c r="G162" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H162" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I162" s="29" t="s">
+        <v>920</v>
+      </c>
+      <c r="J162" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A163" s="27">
+        <v>134</v>
+      </c>
+      <c r="B163" s="55">
+        <v>46296</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D163" s="55">
+        <v>46296</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="G163" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H163" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="I163" s="29" t="s">
+        <v>921</v>
+      </c>
+      <c r="J163" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A164" s="27"/>
       <c r="B164" s="45"/>
       <c r="D164" s="45"/>
@@ -18234,7 +18321,7 @@
       <c r="H164" s="45"/>
       <c r="I164" s="29"/>
     </row>
-    <row r="165" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="165" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A165" s="27"/>
       <c r="B165" s="45"/>
       <c r="D165" s="45"/>
@@ -18242,7 +18329,7 @@
       <c r="H165" s="45"/>
       <c r="I165" s="29"/>
     </row>
-    <row r="166" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="166" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A166" s="27"/>
       <c r="B166" s="45"/>
       <c r="D166" s="45"/>
@@ -18250,7 +18337,7 @@
       <c r="H166" s="45"/>
       <c r="I166" s="29"/>
     </row>
-    <row r="167" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A167" s="27"/>
       <c r="B167" s="45"/>
       <c r="D167" s="45"/>
@@ -18258,7 +18345,7 @@
       <c r="H167" s="45"/>
       <c r="I167" s="29"/>
     </row>
-    <row r="168" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="27"/>
       <c r="B168" s="45"/>
       <c r="D168" s="45"/>
@@ -18266,7 +18353,7 @@
       <c r="H168" s="45"/>
       <c r="I168" s="29"/>
     </row>
-    <row r="169" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="27"/>
       <c r="B169" s="45"/>
       <c r="D169" s="45"/>
@@ -18274,7 +18361,7 @@
       <c r="H169" s="45"/>
       <c r="I169" s="29"/>
     </row>
-    <row r="170" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="170" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A170" s="27"/>
       <c r="B170" s="45"/>
       <c r="D170" s="45"/>
@@ -18282,7 +18369,7 @@
       <c r="H170" s="45"/>
       <c r="I170" s="29"/>
     </row>
-    <row r="171" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A171" s="27"/>
       <c r="B171" s="45"/>
       <c r="D171" s="45"/>
@@ -18290,7 +18377,7 @@
       <c r="H171" s="45"/>
       <c r="I171" s="29"/>
     </row>
-    <row r="172" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A172" s="27"/>
       <c r="B172" s="45"/>
       <c r="D172" s="45"/>
@@ -18298,7 +18385,7 @@
       <c r="H172" s="45"/>
       <c r="I172" s="29"/>
     </row>
-    <row r="173" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A173" s="27"/>
       <c r="B173" s="45"/>
       <c r="D173" s="45"/>
@@ -18306,7 +18393,7 @@
       <c r="H173" s="45"/>
       <c r="I173" s="29"/>
     </row>
-    <row r="174" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="174" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A174" s="27"/>
       <c r="B174" s="45"/>
       <c r="D174" s="45"/>
@@ -18314,7 +18401,7 @@
       <c r="H174" s="45"/>
       <c r="I174" s="29"/>
     </row>
-    <row r="175" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="175" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A175" s="27"/>
       <c r="B175" s="45"/>
       <c r="D175" s="45"/>
@@ -18322,7 +18409,7 @@
       <c r="H175" s="45"/>
       <c r="I175" s="29"/>
     </row>
-    <row r="176" spans="1:9" s="10" customFormat="1" ht="24.75" customHeight="1">
+    <row r="176" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A176" s="27"/>
       <c r="B176" s="45"/>
       <c r="D176" s="45"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA315C-96F6-496E-A9A5-501C9B9FCC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE0D82D-0905-4DB5-9174-C2C84FC4CE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="923">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2787,6 +2787,9 @@
   </si>
   <si>
     <t>Heat Skin - Qty 5 Nos.</t>
+  </si>
+  <si>
+    <t>26-27-ABPL/384</t>
   </si>
 </sst>
 </file>
@@ -9901,10 +9904,10 @@
         <v>46295</v>
       </c>
       <c r="C256" s="49" t="s">
-        <v>40</v>
+        <v>922</v>
       </c>
       <c r="D256" s="26">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="E256" s="22" t="s">
         <v>37</v>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE0D82D-0905-4DB5-9174-C2C84FC4CE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE55378-4449-43C0-90B5-0AFECE23BA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="928">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2790,6 +2790,21 @@
   </si>
   <si>
     <t>26-27-ABPL/384</t>
+  </si>
+  <si>
+    <t>AM/PP/0037/2627</t>
+  </si>
+  <si>
+    <t>Vedich Biotech</t>
+  </si>
+  <si>
+    <t>Cuvettes For Bioelab Fully Auto Analyser - Qty 100 Nos</t>
+  </si>
+  <si>
+    <t>Cuvettes For Bioelab Fully Auto Analyser - Qty 300 Nos ( Per Box 100 Nos)</t>
+  </si>
+  <si>
+    <t>AWB#90678633931</t>
   </si>
 </sst>
 </file>
@@ -9925,85 +9940,109 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="257" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="A257" s="22">
         <v>199</v>
       </c>
-      <c r="C257" s="49"/>
-      <c r="F257" s="49"/>
-      <c r="H257" s="36"/>
-    </row>
-    <row r="258" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="B257" s="26">
+        <v>46296</v>
+      </c>
+      <c r="C257" s="49" t="s">
+        <v>927</v>
+      </c>
+      <c r="D257" s="26">
+        <v>46293</v>
+      </c>
+      <c r="E257" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F257" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G257" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H257" s="29" t="s">
+        <v>926</v>
+      </c>
+      <c r="I257" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A258" s="22">
+        <v>200</v>
+      </c>
       <c r="C258" s="49"/>
       <c r="F258" s="49"/>
       <c r="H258" s="36"/>
     </row>
-    <row r="259" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="259" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C259" s="49"/>
       <c r="F259" s="49"/>
       <c r="H259" s="36"/>
     </row>
-    <row r="260" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="260" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C260" s="49"/>
       <c r="F260" s="49"/>
       <c r="H260" s="36"/>
     </row>
-    <row r="261" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="261" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C261" s="49"/>
       <c r="F261" s="49"/>
       <c r="H261" s="36"/>
     </row>
-    <row r="262" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="262" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C262" s="49"/>
       <c r="F262" s="49"/>
       <c r="H262" s="36"/>
     </row>
-    <row r="263" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="263" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C263" s="49"/>
       <c r="F263" s="49"/>
       <c r="H263" s="36"/>
     </row>
-    <row r="264" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="264" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C264" s="49"/>
       <c r="F264" s="49"/>
       <c r="H264" s="36"/>
     </row>
-    <row r="265" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="265" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C265" s="49"/>
       <c r="F265" s="49"/>
       <c r="H265" s="36"/>
     </row>
-    <row r="266" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="266" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C266" s="49"/>
       <c r="F266" s="49"/>
       <c r="H266" s="36"/>
     </row>
-    <row r="267" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="267" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C267" s="49"/>
       <c r="F267" s="49"/>
       <c r="H267" s="36"/>
     </row>
-    <row r="268" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="268" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C268" s="49"/>
       <c r="F268" s="49"/>
       <c r="H268" s="36"/>
     </row>
-    <row r="269" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="269" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C269" s="49"/>
       <c r="F269" s="49"/>
       <c r="H269" s="36"/>
     </row>
-    <row r="270" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="270" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C270" s="49"/>
       <c r="F270" s="49"/>
       <c r="H270" s="36"/>
     </row>
-    <row r="271" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="271" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C271" s="49"/>
       <c r="F271" s="49"/>
       <c r="H271" s="36"/>
     </row>
-    <row r="272" spans="1:8" s="22" customFormat="1" ht="22.5" customHeight="1">
+    <row r="272" spans="1:9" s="22" customFormat="1" ht="22.5" customHeight="1">
       <c r="C272" s="49"/>
       <c r="F272" s="49"/>
       <c r="H272" s="36"/>
@@ -18317,12 +18356,36 @@
       </c>
     </row>
     <row r="164" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A164" s="27"/>
-      <c r="B164" s="45"/>
-      <c r="D164" s="45"/>
-      <c r="G164" s="45"/>
-      <c r="H164" s="45"/>
-      <c r="I164" s="29"/>
+      <c r="A164" s="27">
+        <v>135</v>
+      </c>
+      <c r="B164" s="55">
+        <v>46297</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="D164" s="55">
+        <v>46295</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="G164" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H164" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I164" s="29" t="s">
+        <v>925</v>
+      </c>
+      <c r="J164" s="10" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="165" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A165" s="27"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DDEDCC-0116-46CE-953E-E289FA1C1CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654111C0-B916-47C1-9821-ED7815238C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="937">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2796,6 +2796,42 @@
   </si>
   <si>
     <t xml:space="preserve">All in 1box        </t>
+  </si>
+  <si>
+    <t>014/2627</t>
+  </si>
+  <si>
+    <t>Trident Plastics</t>
+  </si>
+  <si>
+    <t>15 ml HDPE Brown Bottle With Brown Caps- Qty 4 Box ( Per Box 1500) /  40 ml HDPE Brown Bottle With Brown Caps- Qty 20 Box ( Per Box 500)</t>
+  </si>
+  <si>
+    <t>41 Boxes</t>
+  </si>
+  <si>
+    <t>40 ml HDPE Brown Bottle With White Caps- Qty 10 Box ( Per Box 500) / 15 ml HDPE Brown bottle With White Caps- Qty 7 Box Per Box</t>
+  </si>
+  <si>
+    <t>AM/DOM/0014/2627</t>
+  </si>
+  <si>
+    <t>System Pack Bottles BioElab R1- Qty 5000 Nos</t>
+  </si>
+  <si>
+    <t>10 Box</t>
+  </si>
+  <si>
+    <t>23 Box</t>
+  </si>
+  <si>
+    <t>System pack Bottles With Caps 40ml Brown Bottle Brown Caps- Qty 9500- 19 Box</t>
+  </si>
+  <si>
+    <t>System pack Bottles With Caps 15ml Brown Bottle Brown Caps- Qty  6000- 4 Box</t>
+  </si>
+  <si>
+    <t>AM/DOM/0015/2627</t>
   </si>
 </sst>
 </file>
@@ -3300,32 +3336,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3342,7 +3393,37 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3360,62 +3441,17 @@
     <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3717,21 +3753,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3764,10 +3800,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3880,46 +3916,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="64"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="64"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="64"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4013,117 +4049,117 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="63"/>
+      <c r="I12" s="68"/>
     </row>
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="63"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="63"/>
+      <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="64"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="64"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="64"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="65">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="68" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="65">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A16" s="63"/>
-      <c r="B16" s="66"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="63"/>
+      <c r="A16" s="68"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="63"/>
+      <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="64"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="64"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="64"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4242,25 +4278,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="65">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="65">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="68" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4271,13 +4307,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="64"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="64"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4402,46 +4438,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="65">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="65">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="68" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="64"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="64"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4499,101 +4535,101 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="65">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="68" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="65">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="68" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A33" s="63"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="63"/>
+      <c r="A33" s="68"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="I33" s="63"/>
+      <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="64"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="64"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="64"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="65">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="65">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="68" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="64"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="64"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="64"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4709,117 +4745,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="68" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="65">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="68" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="64"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="65">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="68" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="65">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="68" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="64"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="64"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="65">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="68" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="65">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="68" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4830,13 +4866,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="64"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="64"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4845,42 +4881,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="65">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="68">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="65">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="68" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="64"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="67"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="64"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="63"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="64"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5063,50 +5099,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="65">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="68" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="65">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="68" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="64"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="64"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="64"/>
-      <c r="J56" s="64"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5405,72 +5441,72 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="65">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="68" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="65">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="68" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A68" s="63"/>
-      <c r="B68" s="66"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="69"/>
-      <c r="G68" s="63"/>
+      <c r="A68" s="68"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="69"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="I68" s="63"/>
+      <c r="I68" s="68"/>
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A69" s="63"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="66"/>
-      <c r="E69" s="63"/>
-      <c r="F69" s="69"/>
-      <c r="G69" s="63"/>
+      <c r="A69" s="68"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="I69" s="63"/>
+      <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="64"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="70"/>
-      <c r="G70" s="64"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="64"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5699,83 +5735,83 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="65">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="68" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="65">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="68" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A80" s="63"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="69"/>
-      <c r="G80" s="63"/>
+      <c r="A80" s="68"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="I80" s="63"/>
+      <c r="I80" s="68"/>
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A81" s="63"/>
-      <c r="B81" s="66"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="66"/>
-      <c r="E81" s="63"/>
-      <c r="F81" s="69"/>
-      <c r="G81" s="63"/>
+      <c r="A81" s="68"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="70"/>
+      <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="I81" s="63"/>
+      <c r="I81" s="68"/>
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A82" s="63"/>
-      <c r="B82" s="66"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="66"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="69"/>
-      <c r="G82" s="63"/>
+      <c r="A82" s="68"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="I82" s="63"/>
+      <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="64"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="70"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="64"/>
-      <c r="F83" s="70"/>
-      <c r="G83" s="64"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="64"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5807,22 +5843,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="65">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="68" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="65">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="68" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5830,57 +5866,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="64"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="70"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="64"/>
-      <c r="F86" s="70"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="65">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="68" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="65">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="68" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="64"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="70"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="64"/>
-      <c r="F88" s="70"/>
-      <c r="G88" s="64"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="64"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5912,72 +5948,72 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="65">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="68">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="65">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="68" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A91" s="63"/>
-      <c r="B91" s="66"/>
-      <c r="C91" s="69"/>
-      <c r="D91" s="66"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="69"/>
-      <c r="G91" s="63"/>
+      <c r="A91" s="68"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="69"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="I91" s="63"/>
+      <c r="I91" s="68"/>
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A92" s="63"/>
-      <c r="B92" s="66"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="66"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="69"/>
-      <c r="G92" s="63"/>
+      <c r="A92" s="68"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
       </c>
-      <c r="I92" s="63"/>
+      <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="64"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="70"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="64"/>
-      <c r="F93" s="70"/>
-      <c r="G93" s="64"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="64"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6458,87 +6494,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="65">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="65">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="68" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="85" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A112" s="63"/>
-      <c r="B112" s="66"/>
+      <c r="A112" s="68"/>
+      <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="66"/>
-      <c r="E112" s="63"/>
-      <c r="F112" s="69"/>
-      <c r="G112" s="63"/>
+      <c r="D112" s="69"/>
+      <c r="E112" s="68"/>
+      <c r="F112" s="70"/>
+      <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="95"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A113" s="63"/>
-      <c r="B113" s="66"/>
+      <c r="A113" s="68"/>
+      <c r="B113" s="69"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="66"/>
-      <c r="E113" s="63"/>
-      <c r="F113" s="69"/>
-      <c r="G113" s="63"/>
+      <c r="D113" s="69"/>
+      <c r="E113" s="68"/>
+      <c r="F113" s="70"/>
+      <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="95"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A114" s="63"/>
-      <c r="B114" s="66"/>
+      <c r="A114" s="68"/>
+      <c r="B114" s="69"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="66"/>
-      <c r="E114" s="63"/>
-      <c r="F114" s="69"/>
-      <c r="G114" s="63"/>
+      <c r="D114" s="69"/>
+      <c r="E114" s="68"/>
+      <c r="F114" s="70"/>
+      <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="95"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="64"/>
-      <c r="B115" s="67"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="64"/>
-      <c r="F115" s="70"/>
-      <c r="G115" s="64"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="67"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="86"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7121,92 +7157,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="65">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="68" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="65">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="68" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="64"/>
-      <c r="B137" s="67"/>
-      <c r="C137" s="70"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="64"/>
-      <c r="F137" s="70"/>
-      <c r="G137" s="64"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
+      <c r="C137" s="67"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
+      <c r="F137" s="67"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="64"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="65">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="68" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="65">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="68" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="64"/>
-      <c r="B139" s="67"/>
-      <c r="C139" s="70"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="64"/>
-      <c r="F139" s="70"/>
-      <c r="G139" s="64"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="64"/>
-      <c r="J139" s="64"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7529,46 +7565,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="65">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="68" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="65">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="68" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="64"/>
-      <c r="B151" s="67"/>
-      <c r="C151" s="70"/>
-      <c r="D151" s="67"/>
-      <c r="E151" s="64"/>
-      <c r="F151" s="70"/>
-      <c r="G151" s="64"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
+      <c r="F151" s="67"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="64"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7597,72 +7633,72 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="65">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="68" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="65">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="68" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A154" s="63"/>
-      <c r="B154" s="66"/>
-      <c r="C154" s="69"/>
-      <c r="D154" s="66"/>
-      <c r="E154" s="63"/>
-      <c r="F154" s="69"/>
-      <c r="G154" s="63"/>
+      <c r="A154" s="68"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="69"/>
+      <c r="E154" s="68"/>
+      <c r="F154" s="70"/>
+      <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="I154" s="63"/>
+      <c r="I154" s="68"/>
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A155" s="63"/>
-      <c r="B155" s="66"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="66"/>
-      <c r="E155" s="63"/>
-      <c r="F155" s="69"/>
-      <c r="G155" s="63"/>
+      <c r="A155" s="68"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="69"/>
+      <c r="E155" s="68"/>
+      <c r="F155" s="70"/>
+      <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="I155" s="63"/>
+      <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="64"/>
-      <c r="B156" s="67"/>
-      <c r="C156" s="70"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="64"/>
-      <c r="F156" s="70"/>
-      <c r="G156" s="64"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="67"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="64"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7723,85 +7759,85 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="65">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="68" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="65">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="68" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A160" s="63"/>
-      <c r="B160" s="66"/>
-      <c r="C160" s="69"/>
-      <c r="D160" s="66"/>
-      <c r="E160" s="63"/>
-      <c r="F160" s="69"/>
-      <c r="G160" s="63"/>
+      <c r="A160" s="68"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="69"/>
+      <c r="E160" s="68"/>
+      <c r="F160" s="70"/>
+      <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="I160" s="63"/>
+      <c r="I160" s="68"/>
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A161" s="63"/>
-      <c r="B161" s="66"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="66"/>
-      <c r="E161" s="63"/>
-      <c r="F161" s="69"/>
-      <c r="G161" s="63"/>
+      <c r="A161" s="68"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="69"/>
+      <c r="E161" s="68"/>
+      <c r="F161" s="70"/>
+      <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="I161" s="63"/>
+      <c r="I161" s="68"/>
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A162" s="63"/>
-      <c r="B162" s="66"/>
-      <c r="C162" s="69"/>
-      <c r="D162" s="66"/>
-      <c r="E162" s="63"/>
-      <c r="F162" s="69"/>
-      <c r="G162" s="63"/>
+      <c r="A162" s="68"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="70"/>
+      <c r="D162" s="69"/>
+      <c r="E162" s="68"/>
+      <c r="F162" s="70"/>
+      <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="I162" s="63"/>
+      <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="64"/>
-      <c r="B163" s="67"/>
-      <c r="C163" s="70"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="64"/>
-      <c r="F163" s="70"/>
-      <c r="G163" s="64"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
+      <c r="F163" s="67"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="64"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8091,46 +8127,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="65">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="68" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="100">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="68" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="64"/>
-      <c r="B175" s="67"/>
-      <c r="C175" s="70"/>
-      <c r="D175" s="99"/>
-      <c r="E175" s="64"/>
-      <c r="F175" s="70"/>
-      <c r="G175" s="64"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="67"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="64"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8272,127 +8308,127 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="65">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="68" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="65">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="85" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A182" s="63"/>
-      <c r="B182" s="66"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="66"/>
-      <c r="E182" s="63"/>
-      <c r="F182" s="95"/>
-      <c r="G182" s="63"/>
+      <c r="A182" s="68"/>
+      <c r="B182" s="69"/>
+      <c r="C182" s="70"/>
+      <c r="D182" s="69"/>
+      <c r="E182" s="68"/>
+      <c r="F182" s="72"/>
+      <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
       </c>
-      <c r="I182" s="63"/>
+      <c r="I182" s="68"/>
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A183" s="63"/>
-      <c r="B183" s="66"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="66"/>
-      <c r="E183" s="63"/>
-      <c r="F183" s="95"/>
-      <c r="G183" s="63"/>
+      <c r="A183" s="68"/>
+      <c r="B183" s="69"/>
+      <c r="C183" s="70"/>
+      <c r="D183" s="69"/>
+      <c r="E183" s="68"/>
+      <c r="F183" s="72"/>
+      <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
       </c>
-      <c r="I183" s="63"/>
+      <c r="I183" s="68"/>
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A184" s="63"/>
-      <c r="B184" s="66"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="66"/>
-      <c r="E184" s="63"/>
-      <c r="F184" s="95"/>
-      <c r="G184" s="63"/>
+      <c r="A184" s="68"/>
+      <c r="B184" s="69"/>
+      <c r="C184" s="70"/>
+      <c r="D184" s="69"/>
+      <c r="E184" s="68"/>
+      <c r="F184" s="72"/>
+      <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="I184" s="63"/>
+      <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="64"/>
-      <c r="B185" s="67"/>
-      <c r="C185" s="70"/>
-      <c r="D185" s="67"/>
-      <c r="E185" s="64"/>
-      <c r="F185" s="86"/>
-      <c r="G185" s="64"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
+      <c r="C185" s="67"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="64"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="65">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="68" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="65">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="68" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="64"/>
-      <c r="B187" s="67"/>
-      <c r="C187" s="70"/>
-      <c r="D187" s="67"/>
-      <c r="E187" s="64"/>
-      <c r="F187" s="70"/>
-      <c r="G187" s="64"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
+      <c r="F187" s="67"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="64"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9060,31 +9096,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="65">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="68" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="65">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="68" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9092,43 +9128,43 @@
       </c>
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A212" s="63"/>
-      <c r="B212" s="66"/>
-      <c r="C212" s="69"/>
-      <c r="D212" s="66"/>
-      <c r="E212" s="63"/>
-      <c r="F212" s="69"/>
-      <c r="G212" s="63"/>
+      <c r="A212" s="68"/>
+      <c r="B212" s="69"/>
+      <c r="C212" s="70"/>
+      <c r="D212" s="69"/>
+      <c r="E212" s="68"/>
+      <c r="F212" s="70"/>
+      <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
       </c>
-      <c r="I212" s="63"/>
+      <c r="I212" s="68"/>
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A213" s="63"/>
-      <c r="B213" s="66"/>
-      <c r="C213" s="69"/>
-      <c r="D213" s="66"/>
-      <c r="E213" s="63"/>
-      <c r="F213" s="69"/>
-      <c r="G213" s="63"/>
+      <c r="A213" s="68"/>
+      <c r="B213" s="69"/>
+      <c r="C213" s="70"/>
+      <c r="D213" s="69"/>
+      <c r="E213" s="68"/>
+      <c r="F213" s="70"/>
+      <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
       </c>
-      <c r="I213" s="63"/>
+      <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="64"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="70"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="64"/>
-      <c r="F214" s="70"/>
-      <c r="G214" s="64"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
+      <c r="C214" s="67"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
+      <c r="F214" s="67"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="64"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9395,46 +9431,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="65">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="68" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="65">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="68" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="64"/>
-      <c r="B225" s="67"/>
-      <c r="C225" s="70"/>
-      <c r="D225" s="67"/>
-      <c r="E225" s="64"/>
-      <c r="F225" s="70"/>
-      <c r="G225" s="64"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
+      <c r="C225" s="67"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
+      <c r="F225" s="67"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="64"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9466,88 +9502,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="65">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="68" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="65">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="68" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="64"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="70"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="64"/>
-      <c r="F228" s="70"/>
-      <c r="G228" s="64"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
+      <c r="C228" s="67"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
+      <c r="F228" s="67"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="64"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="65">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="68" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="65">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="68" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="64"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="70"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="64"/>
-      <c r="F230" s="70"/>
-      <c r="G230" s="64"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
+      <c r="C230" s="67"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
+      <c r="F230" s="67"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="64"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9608,46 +9644,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="65">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="68" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="65">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="68" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="64"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="70"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="64"/>
-      <c r="F234" s="70"/>
-      <c r="G234" s="64"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
+      <c r="F234" s="67"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="64"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10287,85 +10323,108 @@
         <v>170</v>
       </c>
     </row>
-    <row r="257" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A257" s="21">
         <v>200</v>
       </c>
-      <c r="C257" s="46"/>
-      <c r="F257" s="46"/>
-      <c r="H257" s="34"/>
-    </row>
-    <row r="258" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+      <c r="B257" s="25">
+        <v>46300</v>
+      </c>
+      <c r="C257" s="46" t="s">
+        <v>925</v>
+      </c>
+      <c r="D257" s="25">
+        <v>46294</v>
+      </c>
+      <c r="E257" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F257" s="46" t="s">
+        <v>926</v>
+      </c>
+      <c r="G257" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H257" s="34" t="s">
+        <v>927</v>
+      </c>
+      <c r="I257" s="21" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C258" s="46"/>
       <c r="F258" s="46"/>
-      <c r="H258" s="34"/>
-    </row>
-    <row r="259" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+      <c r="H258" s="34" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C259" s="46"/>
       <c r="F259" s="46"/>
       <c r="H259" s="34"/>
     </row>
-    <row r="260" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="260" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C260" s="46"/>
       <c r="F260" s="46"/>
       <c r="H260" s="34"/>
     </row>
-    <row r="261" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="261" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C261" s="46"/>
       <c r="F261" s="46"/>
       <c r="H261" s="34"/>
     </row>
-    <row r="262" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C262" s="46"/>
       <c r="F262" s="46"/>
       <c r="H262" s="34"/>
     </row>
-    <row r="263" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C263" s="46"/>
       <c r="F263" s="46"/>
       <c r="H263" s="34"/>
     </row>
-    <row r="264" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C264" s="46"/>
       <c r="F264" s="46"/>
       <c r="H264" s="34"/>
     </row>
-    <row r="265" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="265" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C265" s="46"/>
       <c r="F265" s="46"/>
       <c r="H265" s="34"/>
     </row>
-    <row r="266" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="266" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C266" s="46"/>
       <c r="F266" s="46"/>
       <c r="H266" s="34"/>
     </row>
-    <row r="267" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="267" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C267" s="46"/>
       <c r="F267" s="46"/>
       <c r="H267" s="34"/>
     </row>
-    <row r="268" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="268" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C268" s="46"/>
       <c r="F268" s="46"/>
       <c r="H268" s="34"/>
     </row>
-    <row r="269" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="269" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C269" s="46"/>
       <c r="F269" s="46"/>
       <c r="H269" s="34"/>
     </row>
-    <row r="270" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="270" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C270" s="46"/>
       <c r="F270" s="46"/>
       <c r="H270" s="34"/>
     </row>
-    <row r="271" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="271" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C271" s="46"/>
       <c r="F271" s="46"/>
       <c r="H271" s="34"/>
     </row>
-    <row r="272" spans="1:8" s="21" customFormat="1" ht="22.5" customHeight="1">
+    <row r="272" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C272" s="46"/>
       <c r="F272" s="46"/>
       <c r="H272" s="34"/>
@@ -13922,6 +13981,232 @@
     </row>
   </sheetData>
   <mergeCells count="248">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -13944,232 +14229,6 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14201,23 +14260,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="94"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="83"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14285,28 +14344,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="96">
+      <c r="B4" s="84">
         <v>46098</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="96">
+      <c r="D4" s="84">
         <v>46098</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="85" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14326,14 +14385,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14351,14 +14410,14 @@
       </c>
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14376,14 +14435,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="64"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14494,50 +14553,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="90">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="85" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="90">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="85" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="85" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="68">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="64"/>
-      <c r="B12" s="91"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="70"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14572,110 +14631,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="78">
+      <c r="A14" s="93">
         <v>7</v>
       </c>
-      <c r="B14" s="80">
+      <c r="B14" s="95">
         <v>46105</v>
       </c>
-      <c r="C14" s="82" t="s">
+      <c r="C14" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="80">
+      <c r="D14" s="95">
         <v>46105</v>
       </c>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="G14" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="76" t="s">
+      <c r="J14" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="87"/>
-      <c r="B15" s="88"/>
-      <c r="C15" s="89"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
+      <c r="A15" s="97"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="84"/>
+      <c r="J15" s="91"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="79"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="77"/>
+      <c r="J16" s="92"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="78">
+      <c r="A17" s="93">
         <v>8</v>
       </c>
-      <c r="B17" s="80">
+      <c r="B17" s="95">
         <v>46105</v>
       </c>
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="80">
+      <c r="D17" s="95">
         <v>46105</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="76" t="s">
+      <c r="G17" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="76" t="s">
+      <c r="H17" s="90" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="76" t="s">
+      <c r="J17" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="79"/>
-      <c r="B18" s="81"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="77"/>
+      <c r="J18" s="92"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -14998,50 +15057,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="78">
+      <c r="A29" s="93">
         <v>19</v>
       </c>
-      <c r="B29" s="80">
+      <c r="B29" s="95">
         <v>46121</v>
       </c>
-      <c r="C29" s="82" t="s">
+      <c r="C29" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="80">
+      <c r="D29" s="95">
         <v>46121</v>
       </c>
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="82" t="s">
+      <c r="F29" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="76" t="s">
+      <c r="G29" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="76" t="s">
+      <c r="H29" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="76" t="s">
+      <c r="J29" s="90" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="79"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+      <c r="A30" s="94"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="77"/>
+      <c r="J30" s="92"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15134,74 +15193,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="78">
+      <c r="A34" s="93">
         <v>23</v>
       </c>
-      <c r="B34" s="80">
+      <c r="B34" s="95">
         <v>46128</v>
       </c>
-      <c r="C34" s="82" t="s">
+      <c r="C34" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="80">
+      <c r="D34" s="95">
         <v>46128</v>
       </c>
-      <c r="E34" s="82" t="s">
+      <c r="E34" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="82" t="s">
+      <c r="F34" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="76" t="s">
+      <c r="G34" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="76" t="s">
+      <c r="H34" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="76" t="s">
+      <c r="J34" s="90" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="79"/>
-      <c r="B35" s="81"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="A35" s="94"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="89"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="92"/>
+      <c r="H35" s="92"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="77"/>
+      <c r="J35" s="92"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="78">
+      <c r="A36" s="93">
         <v>24</v>
       </c>
-      <c r="B36" s="80">
+      <c r="B36" s="95">
         <v>46132</v>
       </c>
-      <c r="C36" s="82" t="s">
+      <c r="C36" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="80">
+      <c r="D36" s="95">
         <v>46129</v>
       </c>
-      <c r="E36" s="82" t="s">
+      <c r="E36" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="82" t="s">
+      <c r="F36" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="76" t="s">
+      <c r="G36" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="76" t="s">
+      <c r="H36" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15212,14 +15271,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="79"/>
-      <c r="B37" s="81"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
+      <c r="A37" s="94"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="89"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="89"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15322,50 +15381,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="78">
+      <c r="A41" s="93">
         <v>28</v>
       </c>
-      <c r="B41" s="80">
+      <c r="B41" s="95">
         <v>46139</v>
       </c>
-      <c r="C41" s="82" t="s">
+      <c r="C41" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="80">
+      <c r="D41" s="95">
         <v>46139</v>
       </c>
-      <c r="E41" s="82" t="s">
+      <c r="E41" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="82" t="s">
+      <c r="F41" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="76" t="s">
+      <c r="G41" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="76" t="s">
+      <c r="H41" s="90" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="76" t="s">
+      <c r="J41" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="79"/>
-      <c r="B42" s="81"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
+      <c r="A42" s="94"/>
+      <c r="B42" s="96"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="89"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="92"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="77"/>
+      <c r="J42" s="92"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15496,28 +15555,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="78">
+      <c r="A47" s="93">
         <v>33</v>
       </c>
-      <c r="B47" s="80">
+      <c r="B47" s="95">
         <v>46149</v>
       </c>
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="87" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="80">
+      <c r="D47" s="95">
         <v>46148</v>
       </c>
-      <c r="E47" s="82" t="s">
+      <c r="E47" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="82" t="s">
+      <c r="F47" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="76" t="s">
+      <c r="G47" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="76" t="s">
+      <c r="H47" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15528,14 +15587,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="79"/>
-      <c r="B48" s="81"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
+      <c r="A48" s="94"/>
+      <c r="B48" s="96"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="96"/>
+      <c r="E48" s="89"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="92"/>
+      <c r="H48" s="92"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15544,28 +15603,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="78">
+      <c r="A49" s="93">
         <v>34</v>
       </c>
-      <c r="B49" s="80">
+      <c r="B49" s="95">
         <v>46149</v>
       </c>
-      <c r="C49" s="82" t="s">
+      <c r="C49" s="87" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="80">
+      <c r="D49" s="95">
         <v>46148</v>
       </c>
-      <c r="E49" s="82" t="s">
+      <c r="E49" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="82" t="s">
+      <c r="F49" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="76" t="s">
+      <c r="G49" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="76" t="s">
+      <c r="H49" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15576,14 +15635,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="79"/>
-      <c r="B50" s="81"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="77"/>
+      <c r="A50" s="94"/>
+      <c r="B50" s="96"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="89"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="92"/>
+      <c r="H50" s="92"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -15880,50 +15939,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="78">
+      <c r="A60" s="93">
         <v>44</v>
       </c>
-      <c r="B60" s="80">
+      <c r="B60" s="95">
         <v>46169</v>
       </c>
-      <c r="C60" s="82" t="s">
+      <c r="C60" s="87" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="80">
+      <c r="D60" s="95">
         <v>46169</v>
       </c>
-      <c r="E60" s="82" t="s">
+      <c r="E60" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="82" t="s">
+      <c r="F60" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="76" t="s">
+      <c r="G60" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="76" t="s">
+      <c r="H60" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="76" t="s">
+      <c r="J60" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="79"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="83"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="83"/>
-      <c r="F61" s="83"/>
-      <c r="G61" s="77"/>
-      <c r="H61" s="77"/>
+      <c r="A61" s="94"/>
+      <c r="B61" s="96"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="96"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="92"/>
+      <c r="H61" s="92"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="77"/>
+      <c r="J61" s="92"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16243,50 +16302,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="78">
+      <c r="A72" s="93">
         <v>55</v>
       </c>
-      <c r="B72" s="80">
+      <c r="B72" s="95">
         <v>46192</v>
       </c>
-      <c r="C72" s="82" t="s">
+      <c r="C72" s="87" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="80">
+      <c r="D72" s="95">
         <v>46191</v>
       </c>
-      <c r="E72" s="82" t="s">
+      <c r="E72" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="82" t="s">
+      <c r="F72" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="76" t="s">
+      <c r="G72" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="76" t="s">
+      <c r="H72" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="76" t="s">
+      <c r="J72" s="90" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="79"/>
-      <c r="B73" s="81"/>
-      <c r="C73" s="83"/>
-      <c r="D73" s="81"/>
-      <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="77"/>
-      <c r="H73" s="77"/>
+      <c r="A73" s="94"/>
+      <c r="B73" s="96"/>
+      <c r="C73" s="89"/>
+      <c r="D73" s="96"/>
+      <c r="E73" s="89"/>
+      <c r="F73" s="89"/>
+      <c r="G73" s="92"/>
+      <c r="H73" s="92"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="77"/>
+      <c r="J73" s="92"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16481,184 +16540,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="78">
+      <c r="A80" s="93">
         <v>62</v>
       </c>
-      <c r="B80" s="80">
+      <c r="B80" s="95">
         <v>46200</v>
       </c>
-      <c r="C80" s="82" t="s">
+      <c r="C80" s="87" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="80">
+      <c r="D80" s="95">
         <v>46200</v>
       </c>
-      <c r="E80" s="82" t="s">
+      <c r="E80" s="87" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="82" t="s">
+      <c r="F80" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="76" t="s">
+      <c r="G80" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="76" t="s">
+      <c r="H80" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="76" t="s">
+      <c r="J80" s="90" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="87"/>
-      <c r="B81" s="88"/>
-      <c r="C81" s="89"/>
-      <c r="D81" s="88"/>
-      <c r="E81" s="89"/>
-      <c r="F81" s="89"/>
-      <c r="G81" s="84"/>
-      <c r="H81" s="84"/>
+      <c r="A81" s="97"/>
+      <c r="B81" s="98"/>
+      <c r="C81" s="88"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="88"/>
+      <c r="F81" s="88"/>
+      <c r="G81" s="91"/>
+      <c r="H81" s="91"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="84"/>
+      <c r="J81" s="91"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="87"/>
-      <c r="B82" s="88"/>
-      <c r="C82" s="89"/>
-      <c r="D82" s="88"/>
-      <c r="E82" s="89"/>
-      <c r="F82" s="89"/>
-      <c r="G82" s="84"/>
-      <c r="H82" s="84"/>
+      <c r="A82" s="97"/>
+      <c r="B82" s="98"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="98"/>
+      <c r="E82" s="88"/>
+      <c r="F82" s="88"/>
+      <c r="G82" s="91"/>
+      <c r="H82" s="91"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="84"/>
+      <c r="J82" s="91"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="87"/>
-      <c r="B83" s="88"/>
-      <c r="C83" s="89"/>
-      <c r="D83" s="88"/>
-      <c r="E83" s="89"/>
-      <c r="F83" s="89"/>
-      <c r="G83" s="84"/>
-      <c r="H83" s="84"/>
+      <c r="A83" s="97"/>
+      <c r="B83" s="98"/>
+      <c r="C83" s="88"/>
+      <c r="D83" s="98"/>
+      <c r="E83" s="88"/>
+      <c r="F83" s="88"/>
+      <c r="G83" s="91"/>
+      <c r="H83" s="91"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="84"/>
+      <c r="J83" s="91"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="79"/>
-      <c r="B84" s="81"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="81"/>
-      <c r="E84" s="83"/>
-      <c r="F84" s="83"/>
-      <c r="G84" s="77"/>
-      <c r="H84" s="77"/>
+      <c r="A84" s="94"/>
+      <c r="B84" s="96"/>
+      <c r="C84" s="89"/>
+      <c r="D84" s="96"/>
+      <c r="E84" s="89"/>
+      <c r="F84" s="89"/>
+      <c r="G84" s="92"/>
+      <c r="H84" s="92"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="77"/>
+      <c r="J84" s="92"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="78">
+      <c r="A85" s="93">
         <v>63</v>
       </c>
-      <c r="B85" s="80">
+      <c r="B85" s="95">
         <v>46204</v>
       </c>
-      <c r="C85" s="82" t="s">
+      <c r="C85" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="80">
+      <c r="D85" s="95">
         <v>46204</v>
       </c>
-      <c r="E85" s="82" t="s">
+      <c r="E85" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="82" t="s">
+      <c r="F85" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="76" t="s">
+      <c r="G85" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="76" t="s">
+      <c r="H85" s="90" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="76" t="s">
+      <c r="J85" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="79"/>
-      <c r="B86" s="81"/>
-      <c r="C86" s="83"/>
-      <c r="D86" s="81"/>
-      <c r="E86" s="83"/>
-      <c r="F86" s="83"/>
-      <c r="G86" s="77"/>
-      <c r="H86" s="77"/>
+      <c r="A86" s="94"/>
+      <c r="B86" s="96"/>
+      <c r="C86" s="89"/>
+      <c r="D86" s="96"/>
+      <c r="E86" s="89"/>
+      <c r="F86" s="89"/>
+      <c r="G86" s="92"/>
+      <c r="H86" s="92"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="77"/>
+      <c r="J86" s="92"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="78">
+      <c r="A87" s="93">
         <v>64</v>
       </c>
-      <c r="B87" s="80">
+      <c r="B87" s="95">
         <v>46210</v>
       </c>
-      <c r="C87" s="82" t="s">
+      <c r="C87" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="80">
+      <c r="D87" s="95">
         <v>46210</v>
       </c>
-      <c r="E87" s="82" t="s">
+      <c r="E87" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="82" t="s">
+      <c r="F87" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="76" t="s">
+      <c r="G87" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="76" t="s">
+      <c r="H87" s="90" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="76" t="s">
+      <c r="J87" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="79"/>
-      <c r="B88" s="81"/>
-      <c r="C88" s="83"/>
-      <c r="D88" s="81"/>
-      <c r="E88" s="83"/>
-      <c r="F88" s="83"/>
-      <c r="G88" s="77"/>
-      <c r="H88" s="77"/>
+      <c r="A88" s="94"/>
+      <c r="B88" s="96"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="96"/>
+      <c r="E88" s="89"/>
+      <c r="F88" s="89"/>
+      <c r="G88" s="92"/>
+      <c r="H88" s="92"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="77"/>
+      <c r="J88" s="92"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17264,64 +17323,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="78">
+      <c r="A108" s="93">
         <v>84</v>
       </c>
-      <c r="B108" s="80">
+      <c r="B108" s="95">
         <v>46231</v>
       </c>
-      <c r="C108" s="82" t="s">
+      <c r="C108" s="87" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="80">
+      <c r="D108" s="95">
         <v>46231</v>
       </c>
-      <c r="E108" s="82" t="s">
+      <c r="E108" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="82" t="s">
+      <c r="F108" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="76" t="s">
+      <c r="G108" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="76" t="s">
+      <c r="H108" s="90" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="76" t="s">
+      <c r="J108" s="90" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="87"/>
-      <c r="B109" s="88"/>
-      <c r="C109" s="89"/>
-      <c r="D109" s="88"/>
-      <c r="E109" s="89"/>
-      <c r="F109" s="89"/>
-      <c r="G109" s="84"/>
-      <c r="H109" s="84"/>
+      <c r="A109" s="97"/>
+      <c r="B109" s="98"/>
+      <c r="C109" s="88"/>
+      <c r="D109" s="98"/>
+      <c r="E109" s="88"/>
+      <c r="F109" s="88"/>
+      <c r="G109" s="91"/>
+      <c r="H109" s="91"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="84"/>
+      <c r="J109" s="91"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="79"/>
-      <c r="B110" s="81"/>
-      <c r="C110" s="83"/>
-      <c r="D110" s="81"/>
-      <c r="E110" s="83"/>
-      <c r="F110" s="83"/>
-      <c r="G110" s="77"/>
-      <c r="H110" s="77"/>
+      <c r="A110" s="94"/>
+      <c r="B110" s="96"/>
+      <c r="C110" s="89"/>
+      <c r="D110" s="96"/>
+      <c r="E110" s="89"/>
+      <c r="F110" s="89"/>
+      <c r="G110" s="92"/>
+      <c r="H110" s="92"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="77"/>
+      <c r="J110" s="92"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17740,50 +17799,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="78">
+      <c r="A124" s="93">
         <v>98</v>
       </c>
-      <c r="B124" s="80">
+      <c r="B124" s="95">
         <v>46263</v>
       </c>
-      <c r="C124" s="82" t="s">
+      <c r="C124" s="87" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="80">
+      <c r="D124" s="95">
         <v>46260</v>
       </c>
-      <c r="E124" s="82" t="s">
+      <c r="E124" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="82" t="s">
+      <c r="F124" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="76" t="s">
+      <c r="G124" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="76" t="s">
+      <c r="H124" s="90" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="76" t="s">
+      <c r="J124" s="90" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="79"/>
-      <c r="B125" s="81"/>
-      <c r="C125" s="83"/>
-      <c r="D125" s="81"/>
-      <c r="E125" s="83"/>
-      <c r="F125" s="83"/>
-      <c r="G125" s="77"/>
-      <c r="H125" s="77"/>
+      <c r="A125" s="94"/>
+      <c r="B125" s="96"/>
+      <c r="C125" s="89"/>
+      <c r="D125" s="96"/>
+      <c r="E125" s="89"/>
+      <c r="F125" s="89"/>
+      <c r="G125" s="92"/>
+      <c r="H125" s="92"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="77"/>
+      <c r="J125" s="92"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -18791,19 +18850,19 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="78">
+      <c r="A157" s="93">
         <v>129</v>
       </c>
-      <c r="B157" s="80">
+      <c r="B157" s="95">
         <v>46294</v>
       </c>
-      <c r="C157" s="82" t="s">
+      <c r="C157" s="87" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="80">
+      <c r="D157" s="95">
         <v>46294</v>
       </c>
-      <c r="E157" s="82" t="s">
+      <c r="E157" s="87" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
@@ -18826,11 +18885,11 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="79"/>
-      <c r="B158" s="81"/>
-      <c r="C158" s="83"/>
-      <c r="D158" s="81"/>
-      <c r="E158" s="83"/>
+      <c r="A158" s="94"/>
+      <c r="B158" s="96"/>
+      <c r="C158" s="89"/>
+      <c r="D158" s="96"/>
+      <c r="E158" s="89"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
@@ -19075,22 +19134,68 @@
       </c>
     </row>
     <row r="166" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A166" s="26"/>
-      <c r="B166" s="43"/>
-      <c r="D166" s="43"/>
-      <c r="G166" s="43"/>
-      <c r="H166" s="43"/>
-      <c r="I166" s="28"/>
-      <c r="J166" s="43"/>
+      <c r="A166" s="26">
+        <v>137</v>
+      </c>
+      <c r="B166" s="52">
+        <v>46300</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="D166" s="52">
+        <v>46295</v>
+      </c>
+      <c r="E166" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F166" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G166" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H166" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I166" s="28" t="s">
+        <v>931</v>
+      </c>
+      <c r="J166" s="43" t="s">
+        <v>932</v>
+      </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="26"/>
-      <c r="B167" s="43"/>
-      <c r="D167" s="43"/>
-      <c r="G167" s="43"/>
-      <c r="H167" s="43"/>
-      <c r="I167" s="28"/>
-      <c r="J167" s="43"/>
+      <c r="A167" s="26">
+        <v>138</v>
+      </c>
+      <c r="B167" s="52">
+        <v>46300</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="D167" s="52">
+        <v>46295</v>
+      </c>
+      <c r="E167" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="G167" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H167" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I167" s="28" t="s">
+        <v>934</v>
+      </c>
+      <c r="J167" s="43" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="26"/>
@@ -19098,11 +19203,15 @@
       <c r="D168" s="43"/>
       <c r="G168" s="43"/>
       <c r="H168" s="43"/>
-      <c r="I168" s="28"/>
+      <c r="I168" s="28" t="s">
+        <v>935</v>
+      </c>
       <c r="J168" s="43"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A169" s="26"/>
+      <c r="A169" s="26">
+        <v>139</v>
+      </c>
       <c r="B169" s="43"/>
       <c r="D169" s="43"/>
       <c r="G169" s="43"/>
@@ -26429,28 +26538,115 @@
     </row>
   </sheetData>
   <mergeCells count="155">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
     <mergeCell ref="J108:J110"/>
     <mergeCell ref="J124:J125"/>
     <mergeCell ref="A80:A84"/>
@@ -26475,115 +26671,28 @@
     <mergeCell ref="C108:C110"/>
     <mergeCell ref="D108:D110"/>
     <mergeCell ref="E108:E110"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654111C0-B916-47C1-9821-ED7815238C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4948C3A8-6413-4E6C-A88B-690B03FA1959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2315" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="940">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2832,6 +2832,15 @@
   </si>
   <si>
     <t>AM/DOM/0015/2627</t>
+  </si>
+  <si>
+    <t>Challan No. 1721</t>
+  </si>
+  <si>
+    <t>Mapel mould &amp; Dies (India) Pvt Ltd</t>
+  </si>
+  <si>
+    <t>Outer Cover- Qty 2 Nos. / Flpwcell- Qty 2 Nos. / Switch - Qty 2 Nos.</t>
   </si>
 </sst>
 </file>
@@ -3336,13 +3345,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3351,31 +3357,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3393,37 +3387,22 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3441,16 +3420,46 @@
     <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3753,21 +3762,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3800,10 +3809,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3916,46 +3925,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="68">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="70"/>
       <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="G8" s="64"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="64"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4049,117 +4058,117 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="68">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="68"/>
+      <c r="I12" s="63"/>
     </row>
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A13" s="68"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="69"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="68"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="63"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="68"/>
+      <c r="I13" s="63"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="64"/>
       <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="64"/>
       <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="G14" s="64"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="64"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="68">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="68">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A16" s="68"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="69"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="68"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="63"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="68"/>
+      <c r="I16" s="63"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
+      <c r="A17" s="64"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="64"/>
       <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="G17" s="64"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="64"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4278,25 +4287,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="68">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="68">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4307,13 +4316,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="70"/>
       <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="G23" s="64"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4438,46 +4447,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="68">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="68">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="65" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="70"/>
       <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="64"/>
       <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="G29" s="64"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="64"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4535,101 +4544,101 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="68">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="65" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="68">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="65" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A33" s="68"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
+      <c r="C33" s="66"/>
       <c r="D33" s="69"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="68"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="63"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="I33" s="68"/>
+      <c r="I33" s="63"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="70"/>
       <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="64"/>
       <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="G34" s="64"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="64"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="68">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="68">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="65" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
+      <c r="A36" s="64"/>
+      <c r="B36" s="70"/>
       <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="64"/>
       <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="G36" s="64"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="64"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4745,117 +4754,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="68">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="65" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
       <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="64"/>
       <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="G42" s="64"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="68">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="68">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="70"/>
       <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="64"/>
       <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="G44" s="64"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="64"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="68">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="68">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4866,13 +4875,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="70"/>
       <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="64"/>
       <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="G46" s="64"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4881,42 +4890,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="68">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="65">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="68">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
+      <c r="D48" s="70"/>
       <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="G48" s="64"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="64"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5099,50 +5108,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="68">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="65" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="68">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="65" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="70"/>
       <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="64"/>
       <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="G56" s="64"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="64"/>
+      <c r="J56" s="64"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5441,72 +5450,72 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="68">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="65" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="68">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A68" s="68"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
+      <c r="C68" s="66"/>
       <c r="D68" s="69"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
-      <c r="G68" s="68"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="63"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="I68" s="68"/>
+      <c r="I68" s="63"/>
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A69" s="68"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
+      <c r="C69" s="66"/>
       <c r="D69" s="69"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
-      <c r="G69" s="68"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="63"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="I69" s="68"/>
+      <c r="I69" s="63"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="70"/>
       <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="64"/>
       <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="G70" s="64"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="64"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5735,83 +5744,83 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="68">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="65" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="68">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A80" s="68"/>
+      <c r="A80" s="63"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
+      <c r="C80" s="66"/>
       <c r="D80" s="69"/>
-      <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
-      <c r="G80" s="68"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="63"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="I80" s="68"/>
+      <c r="I80" s="63"/>
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A81" s="68"/>
+      <c r="A81" s="63"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
+      <c r="C81" s="66"/>
       <c r="D81" s="69"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
-      <c r="G81" s="68"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="66"/>
+      <c r="G81" s="63"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="I81" s="68"/>
+      <c r="I81" s="63"/>
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A82" s="68"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
+      <c r="C82" s="66"/>
       <c r="D82" s="69"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
-      <c r="G82" s="68"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="63"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="I82" s="68"/>
+      <c r="I82" s="63"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
+      <c r="A83" s="64"/>
+      <c r="B83" s="70"/>
       <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="64"/>
       <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="G83" s="64"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="64"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5843,22 +5852,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="68">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="65" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="68">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="65" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5866,57 +5875,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
+      <c r="A86" s="64"/>
+      <c r="B86" s="70"/>
       <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="64"/>
       <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="68">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="65" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="68">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="65" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
+      <c r="A88" s="64"/>
+      <c r="B88" s="70"/>
       <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
+      <c r="D88" s="70"/>
+      <c r="E88" s="64"/>
       <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="G88" s="64"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="64"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5948,72 +5957,72 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="68">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="65">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="68">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="65" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A91" s="68"/>
+      <c r="A91" s="63"/>
       <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
+      <c r="C91" s="66"/>
       <c r="D91" s="69"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
-      <c r="G91" s="68"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="66"/>
+      <c r="G91" s="63"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="I91" s="68"/>
+      <c r="I91" s="63"/>
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A92" s="68"/>
+      <c r="A92" s="63"/>
       <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
+      <c r="C92" s="66"/>
       <c r="D92" s="69"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
-      <c r="G92" s="68"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="66"/>
+      <c r="G92" s="63"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
       </c>
-      <c r="I92" s="68"/>
+      <c r="I92" s="63"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
+      <c r="A93" s="64"/>
+      <c r="B93" s="70"/>
       <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="64"/>
       <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="G93" s="64"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="64"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6494,87 +6503,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="68">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="68">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A112" s="68"/>
+      <c r="A112" s="63"/>
       <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
       <c r="D112" s="69"/>
-      <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
-      <c r="G112" s="68"/>
+      <c r="E112" s="63"/>
+      <c r="F112" s="66"/>
+      <c r="G112" s="63"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A113" s="68"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="69"/>
       <c r="C113" s="46"/>
       <c r="D113" s="69"/>
-      <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
-      <c r="G113" s="68"/>
+      <c r="E113" s="63"/>
+      <c r="F113" s="66"/>
+      <c r="G113" s="63"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A114" s="68"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="69"/>
       <c r="C114" s="46"/>
       <c r="D114" s="69"/>
-      <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
-      <c r="G114" s="68"/>
+      <c r="E114" s="63"/>
+      <c r="F114" s="66"/>
+      <c r="G114" s="63"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="64"/>
+      <c r="B115" s="70"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
+      <c r="D115" s="70"/>
+      <c r="E115" s="64"/>
       <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="G115" s="64"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7157,92 +7166,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="68">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="65" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="68">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
+      <c r="A137" s="64"/>
+      <c r="B137" s="70"/>
       <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
+      <c r="D137" s="70"/>
+      <c r="E137" s="64"/>
       <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="G137" s="64"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="64"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="68">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="65" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="68">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="65" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
+      <c r="A139" s="64"/>
+      <c r="B139" s="70"/>
       <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
+      <c r="D139" s="70"/>
+      <c r="E139" s="64"/>
       <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="G139" s="64"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="64"/>
+      <c r="J139" s="64"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7565,46 +7574,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="68">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="65" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="68">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
+      <c r="A151" s="64"/>
+      <c r="B151" s="70"/>
       <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
+      <c r="D151" s="70"/>
+      <c r="E151" s="64"/>
       <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="G151" s="64"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="64"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7633,72 +7642,72 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="68">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="65" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="68">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A154" s="68"/>
+      <c r="A154" s="63"/>
       <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
+      <c r="C154" s="66"/>
       <c r="D154" s="69"/>
-      <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
-      <c r="G154" s="68"/>
+      <c r="E154" s="63"/>
+      <c r="F154" s="66"/>
+      <c r="G154" s="63"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="I154" s="68"/>
+      <c r="I154" s="63"/>
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A155" s="68"/>
+      <c r="A155" s="63"/>
       <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
+      <c r="C155" s="66"/>
       <c r="D155" s="69"/>
-      <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
-      <c r="G155" s="68"/>
+      <c r="E155" s="63"/>
+      <c r="F155" s="66"/>
+      <c r="G155" s="63"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="I155" s="68"/>
+      <c r="I155" s="63"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
+      <c r="A156" s="64"/>
+      <c r="B156" s="70"/>
       <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
+      <c r="D156" s="70"/>
+      <c r="E156" s="64"/>
       <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="G156" s="64"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="64"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7759,85 +7768,85 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="68">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="65" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="68">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A160" s="68"/>
+      <c r="A160" s="63"/>
       <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
+      <c r="C160" s="66"/>
       <c r="D160" s="69"/>
-      <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
-      <c r="G160" s="68"/>
+      <c r="E160" s="63"/>
+      <c r="F160" s="66"/>
+      <c r="G160" s="63"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="I160" s="68"/>
+      <c r="I160" s="63"/>
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A161" s="68"/>
+      <c r="A161" s="63"/>
       <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
+      <c r="C161" s="66"/>
       <c r="D161" s="69"/>
-      <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
-      <c r="G161" s="68"/>
+      <c r="E161" s="63"/>
+      <c r="F161" s="66"/>
+      <c r="G161" s="63"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="I161" s="68"/>
+      <c r="I161" s="63"/>
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A162" s="68"/>
+      <c r="A162" s="63"/>
       <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
+      <c r="C162" s="66"/>
       <c r="D162" s="69"/>
-      <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
-      <c r="G162" s="68"/>
+      <c r="E162" s="63"/>
+      <c r="F162" s="66"/>
+      <c r="G162" s="63"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="I162" s="68"/>
+      <c r="I162" s="63"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
+      <c r="A163" s="64"/>
+      <c r="B163" s="70"/>
       <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
+      <c r="D163" s="70"/>
+      <c r="E163" s="64"/>
       <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="G163" s="64"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="64"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8127,46 +8136,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="68">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="65" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="65" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
+      <c r="A175" s="64"/>
+      <c r="B175" s="70"/>
       <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="64"/>
       <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="G175" s="64"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="64"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8308,127 +8317,127 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="68">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="65" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="68">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A182" s="68"/>
+      <c r="A182" s="63"/>
       <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
+      <c r="C182" s="66"/>
       <c r="D182" s="69"/>
-      <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
-      <c r="G182" s="68"/>
+      <c r="E182" s="63"/>
+      <c r="F182" s="77"/>
+      <c r="G182" s="63"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
       </c>
-      <c r="I182" s="68"/>
+      <c r="I182" s="63"/>
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A183" s="68"/>
+      <c r="A183" s="63"/>
       <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
+      <c r="C183" s="66"/>
       <c r="D183" s="69"/>
-      <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
-      <c r="G183" s="68"/>
+      <c r="E183" s="63"/>
+      <c r="F183" s="77"/>
+      <c r="G183" s="63"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
       </c>
-      <c r="I183" s="68"/>
+      <c r="I183" s="63"/>
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A184" s="68"/>
+      <c r="A184" s="63"/>
       <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
+      <c r="C184" s="66"/>
       <c r="D184" s="69"/>
-      <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
-      <c r="G184" s="68"/>
+      <c r="E184" s="63"/>
+      <c r="F184" s="77"/>
+      <c r="G184" s="63"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="I184" s="68"/>
+      <c r="I184" s="63"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
+      <c r="A185" s="64"/>
+      <c r="B185" s="70"/>
       <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="D185" s="70"/>
+      <c r="E185" s="64"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="64"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="64"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="68">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="65" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="68">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="65" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
+      <c r="A187" s="64"/>
+      <c r="B187" s="70"/>
       <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
+      <c r="D187" s="70"/>
+      <c r="E187" s="64"/>
       <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="G187" s="64"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="64"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9096,31 +9105,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="68">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="65" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="68">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="65" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9128,43 +9137,43 @@
       </c>
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A212" s="68"/>
+      <c r="A212" s="63"/>
       <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
+      <c r="C212" s="66"/>
       <c r="D212" s="69"/>
-      <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
-      <c r="G212" s="68"/>
+      <c r="E212" s="63"/>
+      <c r="F212" s="66"/>
+      <c r="G212" s="63"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
       </c>
-      <c r="I212" s="68"/>
+      <c r="I212" s="63"/>
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A213" s="68"/>
+      <c r="A213" s="63"/>
       <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
+      <c r="C213" s="66"/>
       <c r="D213" s="69"/>
-      <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
-      <c r="G213" s="68"/>
+      <c r="E213" s="63"/>
+      <c r="F213" s="66"/>
+      <c r="G213" s="63"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
       </c>
-      <c r="I213" s="68"/>
+      <c r="I213" s="63"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
+      <c r="A214" s="64"/>
+      <c r="B214" s="70"/>
       <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
+      <c r="D214" s="70"/>
+      <c r="E214" s="64"/>
       <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="G214" s="64"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="64"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9431,46 +9440,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="68">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="65" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="68">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="65" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
+      <c r="A225" s="64"/>
+      <c r="B225" s="70"/>
       <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
+      <c r="D225" s="70"/>
+      <c r="E225" s="64"/>
       <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="G225" s="64"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="64"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9502,88 +9511,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="68">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="65" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="68">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
+      <c r="A228" s="64"/>
+      <c r="B228" s="70"/>
       <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
+      <c r="D228" s="70"/>
+      <c r="E228" s="64"/>
       <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="G228" s="64"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="64"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="68">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="65" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="68">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="65" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
+      <c r="A230" s="64"/>
+      <c r="B230" s="70"/>
       <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
+      <c r="D230" s="70"/>
+      <c r="E230" s="64"/>
       <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="G230" s="64"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="64"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9644,46 +9653,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="68">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="65" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="68">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="65" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
+      <c r="A234" s="64"/>
+      <c r="B234" s="70"/>
       <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
+      <c r="D234" s="70"/>
+      <c r="E234" s="64"/>
       <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="G234" s="64"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="64"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10360,9 +10369,33 @@
       </c>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C259" s="46"/>
-      <c r="F259" s="46"/>
-      <c r="H259" s="34"/>
+      <c r="A259" s="21">
+        <v>201</v>
+      </c>
+      <c r="B259" s="25">
+        <v>46300</v>
+      </c>
+      <c r="C259" s="46" t="s">
+        <v>937</v>
+      </c>
+      <c r="D259" s="25">
+        <v>46300</v>
+      </c>
+      <c r="E259" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F259" s="46" t="s">
+        <v>938</v>
+      </c>
+      <c r="G259" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="H259" s="34" t="s">
+        <v>939</v>
+      </c>
+      <c r="I259" s="21" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="260" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C260" s="46"/>
@@ -13981,232 +14014,6 @@
     </row>
   </sheetData>
   <mergeCells count="248">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -14229,6 +14036,232 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14260,23 +14293,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="83"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14344,28 +14377,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="62">
         <v>1</v>
       </c>
-      <c r="B4" s="84">
+      <c r="B4" s="98">
         <v>46098</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="84">
+      <c r="D4" s="98">
         <v>46098</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="65" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14385,14 +14418,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A5" s="68"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="85"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14410,14 +14443,14 @@
       </c>
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A6" s="68"/>
-      <c r="B6" s="85"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="A6" s="63"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14435,12 +14468,12 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
@@ -14553,44 +14586,44 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="64">
+      <c r="A11" s="62">
         <v>5</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="93">
         <v>46102</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <v>46095</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="65" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="65">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
       <c r="G12" s="67"/>
       <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
@@ -14631,16 +14664,16 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="93">
+      <c r="A14" s="83">
         <v>7</v>
       </c>
-      <c r="B14" s="95">
+      <c r="B14" s="85">
         <v>46105</v>
       </c>
       <c r="C14" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="95">
+      <c r="D14" s="85">
         <v>46105</v>
       </c>
       <c r="E14" s="87" t="s">
@@ -14649,58 +14682,58 @@
       <c r="F14" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="90" t="s">
+      <c r="G14" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="90" t="s">
+      <c r="H14" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="90" t="s">
+      <c r="J14" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="97"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="91"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="96"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="89"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="92"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="93">
+      <c r="A17" s="83">
         <v>8</v>
       </c>
-      <c r="B17" s="95">
+      <c r="B17" s="85">
         <v>46105</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="95">
+      <c r="D17" s="85">
         <v>46105</v>
       </c>
       <c r="E17" s="87" t="s">
@@ -14709,32 +14742,32 @@
       <c r="F17" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="90" t="s">
+      <c r="G17" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="90" t="s">
+      <c r="H17" s="81" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="90" t="s">
+      <c r="J17" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="94"/>
-      <c r="B18" s="96"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="89"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="92"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15057,16 +15090,16 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="93">
+      <c r="A29" s="83">
         <v>19</v>
       </c>
-      <c r="B29" s="95">
+      <c r="B29" s="85">
         <v>46121</v>
       </c>
       <c r="C29" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="95">
+      <c r="D29" s="85">
         <v>46121</v>
       </c>
       <c r="E29" s="87" t="s">
@@ -15075,32 +15108,32 @@
       <c r="F29" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="90" t="s">
+      <c r="G29" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="90" t="s">
+      <c r="H29" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="90" t="s">
+      <c r="J29" s="81" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="94"/>
-      <c r="B30" s="96"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="92"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="92"/>
+      <c r="J30" s="82"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15193,16 +15226,16 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="93">
+      <c r="A34" s="83">
         <v>23</v>
       </c>
-      <c r="B34" s="95">
+      <c r="B34" s="85">
         <v>46128</v>
       </c>
       <c r="C34" s="87" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="95">
+      <c r="D34" s="85">
         <v>46128</v>
       </c>
       <c r="E34" s="87" t="s">
@@ -15211,44 +15244,44 @@
       <c r="F34" s="87" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="90" t="s">
+      <c r="G34" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="90" t="s">
+      <c r="H34" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="90" t="s">
+      <c r="J34" s="81" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="94"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="92"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="92"/>
+      <c r="J35" s="82"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="93">
+      <c r="A36" s="83">
         <v>24</v>
       </c>
-      <c r="B36" s="95">
+      <c r="B36" s="85">
         <v>46132</v>
       </c>
       <c r="C36" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="95">
+      <c r="D36" s="85">
         <v>46129</v>
       </c>
       <c r="E36" s="87" t="s">
@@ -15257,10 +15290,10 @@
       <c r="F36" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="90" t="s">
+      <c r="G36" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="90" t="s">
+      <c r="H36" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15271,14 +15304,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="94"/>
-      <c r="B37" s="96"/>
-      <c r="C37" s="89"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
+      <c r="A37" s="84"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15381,16 +15414,16 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="93">
+      <c r="A41" s="83">
         <v>28</v>
       </c>
-      <c r="B41" s="95">
+      <c r="B41" s="85">
         <v>46139</v>
       </c>
       <c r="C41" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="95">
+      <c r="D41" s="85">
         <v>46139</v>
       </c>
       <c r="E41" s="87" t="s">
@@ -15399,32 +15432,32 @@
       <c r="F41" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="90" t="s">
+      <c r="G41" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="90" t="s">
+      <c r="H41" s="81" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="90" t="s">
+      <c r="J41" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="94"/>
-      <c r="B42" s="96"/>
-      <c r="C42" s="89"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="92"/>
+      <c r="A42" s="84"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="88"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="92"/>
+      <c r="J42" s="82"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15555,16 +15588,16 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="93">
+      <c r="A47" s="83">
         <v>33</v>
       </c>
-      <c r="B47" s="95">
+      <c r="B47" s="85">
         <v>46149</v>
       </c>
       <c r="C47" s="87" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="95">
+      <c r="D47" s="85">
         <v>46148</v>
       </c>
       <c r="E47" s="87" t="s">
@@ -15573,10 +15606,10 @@
       <c r="F47" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="90" t="s">
+      <c r="G47" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="90" t="s">
+      <c r="H47" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15587,14 +15620,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="94"/>
-      <c r="B48" s="96"/>
-      <c r="C48" s="89"/>
-      <c r="D48" s="96"/>
-      <c r="E48" s="89"/>
-      <c r="F48" s="89"/>
-      <c r="G48" s="92"/>
-      <c r="H48" s="92"/>
+      <c r="A48" s="84"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="88"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="88"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="82"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15603,16 +15636,16 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="93">
+      <c r="A49" s="83">
         <v>34</v>
       </c>
-      <c r="B49" s="95">
+      <c r="B49" s="85">
         <v>46149</v>
       </c>
       <c r="C49" s="87" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="95">
+      <c r="D49" s="85">
         <v>46148</v>
       </c>
       <c r="E49" s="87" t="s">
@@ -15621,10 +15654,10 @@
       <c r="F49" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="90" t="s">
+      <c r="G49" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="90" t="s">
+      <c r="H49" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15635,14 +15668,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="94"/>
-      <c r="B50" s="96"/>
-      <c r="C50" s="89"/>
-      <c r="D50" s="96"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="92"/>
-      <c r="H50" s="92"/>
+      <c r="A50" s="84"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="88"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="88"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="82"/>
+      <c r="H50" s="82"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -15939,16 +15972,16 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="93">
+      <c r="A60" s="83">
         <v>44</v>
       </c>
-      <c r="B60" s="95">
+      <c r="B60" s="85">
         <v>46169</v>
       </c>
       <c r="C60" s="87" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="95">
+      <c r="D60" s="85">
         <v>46169</v>
       </c>
       <c r="E60" s="87" t="s">
@@ -15957,32 +15990,32 @@
       <c r="F60" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="90" t="s">
+      <c r="G60" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="90" t="s">
+      <c r="H60" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="90" t="s">
+      <c r="J60" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="94"/>
-      <c r="B61" s="96"/>
-      <c r="C61" s="89"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
-      <c r="G61" s="92"/>
-      <c r="H61" s="92"/>
+      <c r="A61" s="84"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="88"/>
+      <c r="F61" s="88"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="82"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="92"/>
+      <c r="J61" s="82"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16302,16 +16335,16 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="93">
+      <c r="A72" s="83">
         <v>55</v>
       </c>
-      <c r="B72" s="95">
+      <c r="B72" s="85">
         <v>46192</v>
       </c>
       <c r="C72" s="87" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="95">
+      <c r="D72" s="85">
         <v>46191</v>
       </c>
       <c r="E72" s="87" t="s">
@@ -16320,32 +16353,32 @@
       <c r="F72" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="90" t="s">
+      <c r="G72" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="90" t="s">
+      <c r="H72" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="90" t="s">
+      <c r="J72" s="81" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="94"/>
-      <c r="B73" s="96"/>
-      <c r="C73" s="89"/>
-      <c r="D73" s="96"/>
-      <c r="E73" s="89"/>
-      <c r="F73" s="89"/>
-      <c r="G73" s="92"/>
-      <c r="H73" s="92"/>
+      <c r="A73" s="84"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="88"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="88"/>
+      <c r="F73" s="88"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="92"/>
+      <c r="J73" s="82"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16540,16 +16573,16 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="93">
+      <c r="A80" s="83">
         <v>62</v>
       </c>
-      <c r="B80" s="95">
+      <c r="B80" s="85">
         <v>46200</v>
       </c>
       <c r="C80" s="87" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="95">
+      <c r="D80" s="85">
         <v>46200</v>
       </c>
       <c r="E80" s="87" t="s">
@@ -16558,86 +16591,86 @@
       <c r="F80" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="90" t="s">
+      <c r="G80" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="90" t="s">
+      <c r="H80" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="90" t="s">
+      <c r="J80" s="81" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="97"/>
-      <c r="B81" s="98"/>
-      <c r="C81" s="88"/>
-      <c r="D81" s="98"/>
-      <c r="E81" s="88"/>
-      <c r="F81" s="88"/>
-      <c r="G81" s="91"/>
-      <c r="H81" s="91"/>
+      <c r="A81" s="89"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="90"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="91"/>
+      <c r="J81" s="92"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="97"/>
-      <c r="B82" s="98"/>
-      <c r="C82" s="88"/>
-      <c r="D82" s="98"/>
-      <c r="E82" s="88"/>
-      <c r="F82" s="88"/>
-      <c r="G82" s="91"/>
-      <c r="H82" s="91"/>
+      <c r="A82" s="89"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="91"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="91"/>
+      <c r="J82" s="92"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="97"/>
-      <c r="B83" s="98"/>
-      <c r="C83" s="88"/>
-      <c r="D83" s="98"/>
-      <c r="E83" s="88"/>
-      <c r="F83" s="88"/>
-      <c r="G83" s="91"/>
-      <c r="H83" s="91"/>
+      <c r="A83" s="89"/>
+      <c r="B83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="90"/>
+      <c r="E83" s="91"/>
+      <c r="F83" s="91"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="91"/>
+      <c r="J83" s="92"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="94"/>
-      <c r="B84" s="96"/>
-      <c r="C84" s="89"/>
-      <c r="D84" s="96"/>
-      <c r="E84" s="89"/>
-      <c r="F84" s="89"/>
-      <c r="G84" s="92"/>
-      <c r="H84" s="92"/>
+      <c r="A84" s="84"/>
+      <c r="B84" s="86"/>
+      <c r="C84" s="88"/>
+      <c r="D84" s="86"/>
+      <c r="E84" s="88"/>
+      <c r="F84" s="88"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="82"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="92"/>
+      <c r="J84" s="82"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="93">
+      <c r="A85" s="83">
         <v>63</v>
       </c>
-      <c r="B85" s="95">
+      <c r="B85" s="85">
         <v>46204</v>
       </c>
       <c r="C85" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="95">
+      <c r="D85" s="85">
         <v>46204</v>
       </c>
       <c r="E85" s="87" t="s">
@@ -16646,44 +16679,44 @@
       <c r="F85" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="90" t="s">
+      <c r="G85" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="90" t="s">
+      <c r="H85" s="81" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="90" t="s">
+      <c r="J85" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="94"/>
-      <c r="B86" s="96"/>
-      <c r="C86" s="89"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="89"/>
-      <c r="F86" s="89"/>
-      <c r="G86" s="92"/>
-      <c r="H86" s="92"/>
+      <c r="A86" s="84"/>
+      <c r="B86" s="86"/>
+      <c r="C86" s="88"/>
+      <c r="D86" s="86"/>
+      <c r="E86" s="88"/>
+      <c r="F86" s="88"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="92"/>
+      <c r="J86" s="82"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="93">
+      <c r="A87" s="83">
         <v>64</v>
       </c>
-      <c r="B87" s="95">
+      <c r="B87" s="85">
         <v>46210</v>
       </c>
       <c r="C87" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="95">
+      <c r="D87" s="85">
         <v>46210</v>
       </c>
       <c r="E87" s="87" t="s">
@@ -16692,32 +16725,32 @@
       <c r="F87" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="90" t="s">
+      <c r="G87" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="90" t="s">
+      <c r="H87" s="81" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="90" t="s">
+      <c r="J87" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="94"/>
-      <c r="B88" s="96"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="96"/>
-      <c r="E88" s="89"/>
-      <c r="F88" s="89"/>
-      <c r="G88" s="92"/>
-      <c r="H88" s="92"/>
+      <c r="A88" s="84"/>
+      <c r="B88" s="86"/>
+      <c r="C88" s="88"/>
+      <c r="D88" s="86"/>
+      <c r="E88" s="88"/>
+      <c r="F88" s="88"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="92"/>
+      <c r="J88" s="82"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17323,16 +17356,16 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="93">
+      <c r="A108" s="83">
         <v>84</v>
       </c>
-      <c r="B108" s="95">
+      <c r="B108" s="85">
         <v>46231</v>
       </c>
       <c r="C108" s="87" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="95">
+      <c r="D108" s="85">
         <v>46231</v>
       </c>
       <c r="E108" s="87" t="s">
@@ -17341,46 +17374,46 @@
       <c r="F108" s="87" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="90" t="s">
+      <c r="G108" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="90" t="s">
+      <c r="H108" s="81" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="90" t="s">
+      <c r="J108" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="97"/>
-      <c r="B109" s="98"/>
-      <c r="C109" s="88"/>
-      <c r="D109" s="98"/>
-      <c r="E109" s="88"/>
-      <c r="F109" s="88"/>
-      <c r="G109" s="91"/>
-      <c r="H109" s="91"/>
+      <c r="A109" s="89"/>
+      <c r="B109" s="90"/>
+      <c r="C109" s="91"/>
+      <c r="D109" s="90"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="92"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="91"/>
+      <c r="J109" s="92"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="94"/>
-      <c r="B110" s="96"/>
-      <c r="C110" s="89"/>
-      <c r="D110" s="96"/>
-      <c r="E110" s="89"/>
-      <c r="F110" s="89"/>
-      <c r="G110" s="92"/>
-      <c r="H110" s="92"/>
+      <c r="A110" s="84"/>
+      <c r="B110" s="86"/>
+      <c r="C110" s="88"/>
+      <c r="D110" s="86"/>
+      <c r="E110" s="88"/>
+      <c r="F110" s="88"/>
+      <c r="G110" s="82"/>
+      <c r="H110" s="82"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="92"/>
+      <c r="J110" s="82"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17799,16 +17832,16 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="93">
+      <c r="A124" s="83">
         <v>98</v>
       </c>
-      <c r="B124" s="95">
+      <c r="B124" s="85">
         <v>46263</v>
       </c>
       <c r="C124" s="87" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="95">
+      <c r="D124" s="85">
         <v>46260</v>
       </c>
       <c r="E124" s="87" t="s">
@@ -17817,32 +17850,32 @@
       <c r="F124" s="87" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="90" t="s">
+      <c r="G124" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="90" t="s">
+      <c r="H124" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="90" t="s">
+      <c r="J124" s="81" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="94"/>
-      <c r="B125" s="96"/>
-      <c r="C125" s="89"/>
-      <c r="D125" s="96"/>
-      <c r="E125" s="89"/>
-      <c r="F125" s="89"/>
-      <c r="G125" s="92"/>
-      <c r="H125" s="92"/>
+      <c r="A125" s="84"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="88"/>
+      <c r="D125" s="86"/>
+      <c r="E125" s="88"/>
+      <c r="F125" s="88"/>
+      <c r="G125" s="82"/>
+      <c r="H125" s="82"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="92"/>
+      <c r="J125" s="82"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -18850,16 +18883,16 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="93">
+      <c r="A157" s="83">
         <v>129</v>
       </c>
-      <c r="B157" s="95">
+      <c r="B157" s="85">
         <v>46294</v>
       </c>
       <c r="C157" s="87" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="95">
+      <c r="D157" s="85">
         <v>46294</v>
       </c>
       <c r="E157" s="87" t="s">
@@ -18885,11 +18918,11 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="94"/>
-      <c r="B158" s="96"/>
-      <c r="C158" s="89"/>
-      <c r="D158" s="96"/>
-      <c r="E158" s="89"/>
+      <c r="A158" s="84"/>
+      <c r="B158" s="86"/>
+      <c r="C158" s="88"/>
+      <c r="D158" s="86"/>
+      <c r="E158" s="88"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
@@ -26538,112 +26571,31 @@
     </row>
   </sheetData>
   <mergeCells count="155">
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="E124:E125"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="J14:J16"/>
     <mergeCell ref="H17:H18"/>
@@ -26668,31 +26620,112 @@
     <mergeCell ref="H124:H125"/>
     <mergeCell ref="A108:A110"/>
     <mergeCell ref="B108:B110"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4948C3A8-6413-4E6C-A88B-690B03FA1959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA63CF59-C126-419E-947D-470626E3AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="940">
   <si>
     <t>Sr No.</t>
   </si>
@@ -3345,10 +3345,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3357,19 +3360,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3387,33 +3402,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3426,23 +3414,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3460,6 +3436,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3762,21 +3762,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3809,10 +3809,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3925,46 +3925,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="65" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="64"/>
-      <c r="B8" s="70"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
       <c r="C8" s="67"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
       <c r="F8" s="67"/>
-      <c r="G8" s="64"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="64"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4058,117 +4058,117 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="68">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="65" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="63"/>
+      <c r="I12" s="68"/>
     </row>
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="66"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="70"/>
       <c r="D13" s="69"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="63"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="I13" s="63"/>
+      <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="64"/>
-      <c r="B14" s="64"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="67"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="64"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
       <c r="F14" s="67"/>
-      <c r="G14" s="64"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="64"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="68">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="65" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A16" s="63"/>
+      <c r="A16" s="68"/>
       <c r="B16" s="69"/>
-      <c r="C16" s="66"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="69"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="63"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="63"/>
+      <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="64"/>
-      <c r="B17" s="70"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
       <c r="C17" s="67"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="64"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
       <c r="F17" s="67"/>
-      <c r="G17" s="64"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="64"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4287,25 +4287,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="68">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="65" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4316,13 +4316,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="64"/>
-      <c r="B23" s="70"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
       <c r="C23" s="67"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="64"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
       <c r="F23" s="67"/>
-      <c r="G23" s="64"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4447,46 +4447,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="68">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="68">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="65" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="70"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
       <c r="C29" s="67"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="64"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
       <c r="F29" s="67"/>
-      <c r="G29" s="64"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="64"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4544,101 +4544,101 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="68">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="65" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="68">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="65" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A33" s="63"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="69"/>
-      <c r="C33" s="66"/>
+      <c r="C33" s="70"/>
       <c r="D33" s="69"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="63"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="I33" s="63"/>
+      <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="64"/>
-      <c r="B34" s="70"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
       <c r="C34" s="67"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="64"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
       <c r="F34" s="67"/>
-      <c r="G34" s="64"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="64"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="68">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="68">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="65" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="64"/>
-      <c r="B36" s="70"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
       <c r="C36" s="67"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="64"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
       <c r="F36" s="67"/>
-      <c r="G36" s="64"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="64"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4754,117 +4754,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="65" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="68">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="65" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="64"/>
-      <c r="B42" s="64"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
       <c r="C42" s="67"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="64"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
       <c r="F42" s="67"/>
-      <c r="G42" s="64"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="68">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="65" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="68">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="65" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="64"/>
-      <c r="B44" s="70"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
       <c r="C44" s="67"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="64"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
       <c r="F44" s="67"/>
-      <c r="G44" s="64"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="68">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="65" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="68">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="65" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4875,13 +4875,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="64"/>
-      <c r="B46" s="70"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
       <c r="C46" s="67"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="64"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
       <c r="F46" s="67"/>
-      <c r="G46" s="64"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4890,42 +4890,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="68">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="65">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="68">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="65" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="64"/>
-      <c r="B48" s="70"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
       <c r="C48" s="67"/>
-      <c r="D48" s="70"/>
+      <c r="D48" s="63"/>
       <c r="F48" s="67"/>
-      <c r="G48" s="64"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="64"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5108,50 +5108,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="68">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="65" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="65" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="64"/>
-      <c r="B56" s="70"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
       <c r="C56" s="67"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="64"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
       <c r="F56" s="67"/>
-      <c r="G56" s="64"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="64"/>
-      <c r="J56" s="64"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5450,72 +5450,72 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="68">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="68">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="65" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A68" s="63"/>
+      <c r="A68" s="68"/>
       <c r="B68" s="69"/>
-      <c r="C68" s="66"/>
+      <c r="C68" s="70"/>
       <c r="D68" s="69"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="66"/>
-      <c r="G68" s="63"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="I68" s="63"/>
+      <c r="I68" s="68"/>
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A69" s="63"/>
+      <c r="A69" s="68"/>
       <c r="B69" s="69"/>
-      <c r="C69" s="66"/>
+      <c r="C69" s="70"/>
       <c r="D69" s="69"/>
-      <c r="E69" s="63"/>
-      <c r="F69" s="66"/>
-      <c r="G69" s="63"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="I69" s="63"/>
+      <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="64"/>
-      <c r="B70" s="70"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
       <c r="C70" s="67"/>
-      <c r="D70" s="70"/>
-      <c r="E70" s="64"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
       <c r="F70" s="67"/>
-      <c r="G70" s="64"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="64"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5744,83 +5744,83 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="68">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="65" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="68">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="65" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A80" s="63"/>
+      <c r="A80" s="68"/>
       <c r="B80" s="69"/>
-      <c r="C80" s="66"/>
+      <c r="C80" s="70"/>
       <c r="D80" s="69"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="63"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="70"/>
+      <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="I80" s="63"/>
+      <c r="I80" s="68"/>
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A81" s="63"/>
+      <c r="A81" s="68"/>
       <c r="B81" s="69"/>
-      <c r="C81" s="66"/>
+      <c r="C81" s="70"/>
       <c r="D81" s="69"/>
-      <c r="E81" s="63"/>
-      <c r="F81" s="66"/>
-      <c r="G81" s="63"/>
+      <c r="E81" s="68"/>
+      <c r="F81" s="70"/>
+      <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="I81" s="63"/>
+      <c r="I81" s="68"/>
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A82" s="63"/>
+      <c r="A82" s="68"/>
       <c r="B82" s="69"/>
-      <c r="C82" s="66"/>
+      <c r="C82" s="70"/>
       <c r="D82" s="69"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="66"/>
-      <c r="G82" s="63"/>
+      <c r="E82" s="68"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
       </c>
-      <c r="I82" s="63"/>
+      <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="64"/>
-      <c r="B83" s="70"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
       <c r="C83" s="67"/>
-      <c r="D83" s="70"/>
-      <c r="E83" s="64"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
       <c r="F83" s="67"/>
-      <c r="G83" s="64"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="64"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="68">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="65" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="68">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="65" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5875,57 +5875,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="64"/>
-      <c r="B86" s="70"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
       <c r="C86" s="67"/>
-      <c r="D86" s="70"/>
-      <c r="E86" s="64"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
       <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="68">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="65" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="68">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="65" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="64"/>
-      <c r="B88" s="70"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
       <c r="C88" s="67"/>
-      <c r="D88" s="70"/>
-      <c r="E88" s="64"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
       <c r="F88" s="67"/>
-      <c r="G88" s="64"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="64"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5957,72 +5957,72 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="68">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="65">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="68">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="65" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A91" s="63"/>
+      <c r="A91" s="68"/>
       <c r="B91" s="69"/>
-      <c r="C91" s="66"/>
+      <c r="C91" s="70"/>
       <c r="D91" s="69"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="66"/>
-      <c r="G91" s="63"/>
+      <c r="E91" s="68"/>
+      <c r="F91" s="70"/>
+      <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="I91" s="63"/>
+      <c r="I91" s="68"/>
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A92" s="63"/>
+      <c r="A92" s="68"/>
       <c r="B92" s="69"/>
-      <c r="C92" s="66"/>
+      <c r="C92" s="70"/>
       <c r="D92" s="69"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="66"/>
-      <c r="G92" s="63"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="70"/>
+      <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
       </c>
-      <c r="I92" s="63"/>
+      <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="64"/>
-      <c r="B93" s="70"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
       <c r="C93" s="67"/>
-      <c r="D93" s="70"/>
-      <c r="E93" s="64"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
       <c r="F93" s="67"/>
-      <c r="G93" s="64"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="64"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6503,87 +6503,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="68">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="68">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="65" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="76" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A112" s="63"/>
+      <c r="A112" s="68"/>
       <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
       <c r="D112" s="69"/>
-      <c r="E112" s="63"/>
-      <c r="F112" s="66"/>
-      <c r="G112" s="63"/>
+      <c r="E112" s="68"/>
+      <c r="F112" s="70"/>
+      <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="77"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A113" s="63"/>
+      <c r="A113" s="68"/>
       <c r="B113" s="69"/>
       <c r="C113" s="46"/>
       <c r="D113" s="69"/>
-      <c r="E113" s="63"/>
-      <c r="F113" s="66"/>
-      <c r="G113" s="63"/>
+      <c r="E113" s="68"/>
+      <c r="F113" s="70"/>
+      <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="77"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A114" s="63"/>
+      <c r="A114" s="68"/>
       <c r="B114" s="69"/>
       <c r="C114" s="46"/>
       <c r="D114" s="69"/>
-      <c r="E114" s="63"/>
-      <c r="F114" s="66"/>
-      <c r="G114" s="63"/>
+      <c r="E114" s="68"/>
+      <c r="F114" s="70"/>
+      <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="77"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="64"/>
-      <c r="B115" s="70"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="70"/>
-      <c r="E115" s="64"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
       <c r="F115" s="67"/>
-      <c r="G115" s="64"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="78"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7166,92 +7166,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="68">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="65" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="68">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="65" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="64"/>
-      <c r="B137" s="70"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
       <c r="C137" s="67"/>
-      <c r="D137" s="70"/>
-      <c r="E137" s="64"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
       <c r="F137" s="67"/>
-      <c r="G137" s="64"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="64"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="68">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="65" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="68">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="65" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="64"/>
-      <c r="B139" s="70"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
       <c r="C139" s="67"/>
-      <c r="D139" s="70"/>
-      <c r="E139" s="64"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
       <c r="F139" s="67"/>
-      <c r="G139" s="64"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="64"/>
-      <c r="J139" s="64"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7574,46 +7574,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="68">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="65" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="68">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="65" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="64"/>
-      <c r="B151" s="70"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
       <c r="C151" s="67"/>
-      <c r="D151" s="70"/>
-      <c r="E151" s="64"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
       <c r="F151" s="67"/>
-      <c r="G151" s="64"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="64"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7642,72 +7642,72 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="68">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="65" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="68">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="65" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A154" s="63"/>
+      <c r="A154" s="68"/>
       <c r="B154" s="69"/>
-      <c r="C154" s="66"/>
+      <c r="C154" s="70"/>
       <c r="D154" s="69"/>
-      <c r="E154" s="63"/>
-      <c r="F154" s="66"/>
-      <c r="G154" s="63"/>
+      <c r="E154" s="68"/>
+      <c r="F154" s="70"/>
+      <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="I154" s="63"/>
+      <c r="I154" s="68"/>
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A155" s="63"/>
+      <c r="A155" s="68"/>
       <c r="B155" s="69"/>
-      <c r="C155" s="66"/>
+      <c r="C155" s="70"/>
       <c r="D155" s="69"/>
-      <c r="E155" s="63"/>
-      <c r="F155" s="66"/>
-      <c r="G155" s="63"/>
+      <c r="E155" s="68"/>
+      <c r="F155" s="70"/>
+      <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="I155" s="63"/>
+      <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="64"/>
-      <c r="B156" s="70"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
       <c r="C156" s="67"/>
-      <c r="D156" s="70"/>
-      <c r="E156" s="64"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
       <c r="F156" s="67"/>
-      <c r="G156" s="64"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="64"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7768,85 +7768,85 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="68">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="65" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="68">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="65" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A160" s="63"/>
+      <c r="A160" s="68"/>
       <c r="B160" s="69"/>
-      <c r="C160" s="66"/>
+      <c r="C160" s="70"/>
       <c r="D160" s="69"/>
-      <c r="E160" s="63"/>
-      <c r="F160" s="66"/>
-      <c r="G160" s="63"/>
+      <c r="E160" s="68"/>
+      <c r="F160" s="70"/>
+      <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="I160" s="63"/>
+      <c r="I160" s="68"/>
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A161" s="63"/>
+      <c r="A161" s="68"/>
       <c r="B161" s="69"/>
-      <c r="C161" s="66"/>
+      <c r="C161" s="70"/>
       <c r="D161" s="69"/>
-      <c r="E161" s="63"/>
-      <c r="F161" s="66"/>
-      <c r="G161" s="63"/>
+      <c r="E161" s="68"/>
+      <c r="F161" s="70"/>
+      <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="I161" s="63"/>
+      <c r="I161" s="68"/>
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A162" s="63"/>
+      <c r="A162" s="68"/>
       <c r="B162" s="69"/>
-      <c r="C162" s="66"/>
+      <c r="C162" s="70"/>
       <c r="D162" s="69"/>
-      <c r="E162" s="63"/>
-      <c r="F162" s="66"/>
-      <c r="G162" s="63"/>
+      <c r="E162" s="68"/>
+      <c r="F162" s="70"/>
+      <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="I162" s="63"/>
+      <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="64"/>
-      <c r="B163" s="70"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
       <c r="C163" s="67"/>
-      <c r="D163" s="70"/>
-      <c r="E163" s="64"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
       <c r="F163" s="67"/>
-      <c r="G163" s="64"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="64"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8136,46 +8136,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="68">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="65" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="79">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="65" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="64"/>
-      <c r="B175" s="70"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
       <c r="C175" s="67"/>
-      <c r="D175" s="80"/>
-      <c r="E175" s="64"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
       <c r="F175" s="67"/>
-      <c r="G175" s="64"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="64"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8317,127 +8317,127 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="68">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="65" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="68">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="76" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A182" s="63"/>
+      <c r="A182" s="68"/>
       <c r="B182" s="69"/>
-      <c r="C182" s="66"/>
+      <c r="C182" s="70"/>
       <c r="D182" s="69"/>
-      <c r="E182" s="63"/>
-      <c r="F182" s="77"/>
-      <c r="G182" s="63"/>
+      <c r="E182" s="68"/>
+      <c r="F182" s="72"/>
+      <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
       </c>
-      <c r="I182" s="63"/>
+      <c r="I182" s="68"/>
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A183" s="63"/>
+      <c r="A183" s="68"/>
       <c r="B183" s="69"/>
-      <c r="C183" s="66"/>
+      <c r="C183" s="70"/>
       <c r="D183" s="69"/>
-      <c r="E183" s="63"/>
-      <c r="F183" s="77"/>
-      <c r="G183" s="63"/>
+      <c r="E183" s="68"/>
+      <c r="F183" s="72"/>
+      <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
       </c>
-      <c r="I183" s="63"/>
+      <c r="I183" s="68"/>
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A184" s="63"/>
+      <c r="A184" s="68"/>
       <c r="B184" s="69"/>
-      <c r="C184" s="66"/>
+      <c r="C184" s="70"/>
       <c r="D184" s="69"/>
-      <c r="E184" s="63"/>
-      <c r="F184" s="77"/>
-      <c r="G184" s="63"/>
+      <c r="E184" s="68"/>
+      <c r="F184" s="72"/>
+      <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="I184" s="63"/>
+      <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="64"/>
-      <c r="B185" s="70"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
       <c r="C185" s="67"/>
-      <c r="D185" s="70"/>
-      <c r="E185" s="64"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="64"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="64"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="68">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="65" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="68">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="65" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="64"/>
-      <c r="B187" s="70"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
       <c r="C187" s="67"/>
-      <c r="D187" s="70"/>
-      <c r="E187" s="64"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
       <c r="F187" s="67"/>
-      <c r="G187" s="64"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="64"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9105,31 +9105,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="68">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="65" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="68">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="65" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9137,43 +9137,43 @@
       </c>
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A212" s="63"/>
+      <c r="A212" s="68"/>
       <c r="B212" s="69"/>
-      <c r="C212" s="66"/>
+      <c r="C212" s="70"/>
       <c r="D212" s="69"/>
-      <c r="E212" s="63"/>
-      <c r="F212" s="66"/>
-      <c r="G212" s="63"/>
+      <c r="E212" s="68"/>
+      <c r="F212" s="70"/>
+      <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
       </c>
-      <c r="I212" s="63"/>
+      <c r="I212" s="68"/>
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A213" s="63"/>
+      <c r="A213" s="68"/>
       <c r="B213" s="69"/>
-      <c r="C213" s="66"/>
+      <c r="C213" s="70"/>
       <c r="D213" s="69"/>
-      <c r="E213" s="63"/>
-      <c r="F213" s="66"/>
-      <c r="G213" s="63"/>
+      <c r="E213" s="68"/>
+      <c r="F213" s="70"/>
+      <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
       </c>
-      <c r="I213" s="63"/>
+      <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="64"/>
-      <c r="B214" s="70"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
       <c r="C214" s="67"/>
-      <c r="D214" s="70"/>
-      <c r="E214" s="64"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
       <c r="F214" s="67"/>
-      <c r="G214" s="64"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="64"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9440,46 +9440,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="68">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="65" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="68">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="65" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="64"/>
-      <c r="B225" s="70"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
       <c r="C225" s="67"/>
-      <c r="D225" s="70"/>
-      <c r="E225" s="64"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
       <c r="F225" s="67"/>
-      <c r="G225" s="64"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="64"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9511,88 +9511,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="68">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="65" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="68">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="65" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="64"/>
-      <c r="B228" s="70"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
       <c r="C228" s="67"/>
-      <c r="D228" s="70"/>
-      <c r="E228" s="64"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
       <c r="F228" s="67"/>
-      <c r="G228" s="64"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="64"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="68">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="65" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="68">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="65" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="64"/>
-      <c r="B230" s="70"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
       <c r="C230" s="67"/>
-      <c r="D230" s="70"/>
-      <c r="E230" s="64"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
       <c r="F230" s="67"/>
-      <c r="G230" s="64"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="64"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9653,46 +9653,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="68">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="65" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="68">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="65" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="64"/>
-      <c r="B234" s="70"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
       <c r="C234" s="67"/>
-      <c r="D234" s="70"/>
-      <c r="E234" s="64"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
       <c r="F234" s="67"/>
-      <c r="G234" s="64"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="64"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10333,40 +10333,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="21">
+      <c r="A257" s="64">
         <v>200</v>
       </c>
-      <c r="B257" s="25">
+      <c r="B257" s="62">
         <v>46300</v>
       </c>
-      <c r="C257" s="46" t="s">
+      <c r="C257" s="66" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="25">
+      <c r="D257" s="62">
         <v>46294</v>
       </c>
-      <c r="E257" s="21" t="s">
+      <c r="E257" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="46" t="s">
+      <c r="F257" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="21" t="s">
+      <c r="G257" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="21" t="s">
+      <c r="I257" s="64" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C258" s="46"/>
-      <c r="F258" s="46"/>
+      <c r="A258" s="65"/>
+      <c r="B258" s="63"/>
+      <c r="C258" s="67"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="65"/>
+      <c r="F258" s="67"/>
+      <c r="G258" s="65"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
+      <c r="I258" s="65"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -14013,7 +14019,241 @@
       <c r="H982" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="248">
+  <mergeCells count="256">
+    <mergeCell ref="G257:G258"/>
+    <mergeCell ref="I257:I258"/>
+    <mergeCell ref="F257:F258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="A257:A258"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -14036,232 +14276,6 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14293,23 +14307,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14377,28 +14391,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="90">
         <v>46098</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="90">
         <v>46098</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="65" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="65" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14418,14 +14432,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14443,14 +14457,14 @@
       </c>
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14468,12 +14482,12 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="64"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
@@ -14586,44 +14600,44 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="65" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="65">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="64"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
       <c r="G12" s="67"/>
       <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
@@ -14664,110 +14678,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="83">
+      <c r="A14" s="85">
         <v>7</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="81">
         <v>46105</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="81">
         <v>46105</v>
       </c>
-      <c r="E14" s="87" t="s">
+      <c r="E14" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="87" t="s">
+      <c r="F14" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="81" t="s">
+      <c r="H14" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="81" t="s">
+      <c r="J14" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="A15" s="98"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="96"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
+      <c r="A16" s="86"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="82"/>
+      <c r="J16" s="97"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="83">
+      <c r="A17" s="85">
         <v>8</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="81">
         <v>46105</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="81">
         <v>46105</v>
       </c>
-      <c r="E17" s="87" t="s">
+      <c r="E17" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="87" t="s">
+      <c r="F17" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="81" t="s">
+      <c r="G17" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="81" t="s">
+      <c r="H17" s="95" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="81" t="s">
+      <c r="J17" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="84"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
+      <c r="A18" s="86"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="82"/>
+      <c r="J18" s="97"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15090,50 +15104,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="83">
+      <c r="A29" s="85">
         <v>19</v>
       </c>
-      <c r="B29" s="85">
+      <c r="B29" s="81">
         <v>46121</v>
       </c>
-      <c r="C29" s="87" t="s">
+      <c r="C29" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="85">
+      <c r="D29" s="81">
         <v>46121</v>
       </c>
-      <c r="E29" s="87" t="s">
+      <c r="E29" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="87" t="s">
+      <c r="F29" s="83" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="81" t="s">
+      <c r="G29" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="81" t="s">
+      <c r="H29" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="81" t="s">
+      <c r="J29" s="95" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="84"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
+      <c r="A30" s="86"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="82"/>
+      <c r="J30" s="97"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15226,74 +15240,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="83">
+      <c r="A34" s="85">
         <v>23</v>
       </c>
-      <c r="B34" s="85">
+      <c r="B34" s="81">
         <v>46128</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="85">
+      <c r="D34" s="81">
         <v>46128</v>
       </c>
-      <c r="E34" s="87" t="s">
+      <c r="E34" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="87" t="s">
+      <c r="F34" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="81" t="s">
+      <c r="G34" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="81" t="s">
+      <c r="H34" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="81" t="s">
+      <c r="J34" s="95" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="84"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
+      <c r="A35" s="86"/>
+      <c r="B35" s="82"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="97"/>
+      <c r="H35" s="97"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="82"/>
+      <c r="J35" s="97"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="83">
+      <c r="A36" s="85">
         <v>24</v>
       </c>
-      <c r="B36" s="85">
+      <c r="B36" s="81">
         <v>46132</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="85">
+      <c r="D36" s="81">
         <v>46129</v>
       </c>
-      <c r="E36" s="87" t="s">
+      <c r="E36" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="87" t="s">
+      <c r="F36" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="81" t="s">
+      <c r="G36" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="81" t="s">
+      <c r="H36" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15304,14 +15318,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="84"/>
-      <c r="B37" s="86"/>
-      <c r="C37" s="88"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
+      <c r="A37" s="86"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="97"/>
+      <c r="H37" s="97"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15414,50 +15428,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="83">
+      <c r="A41" s="85">
         <v>28</v>
       </c>
-      <c r="B41" s="85">
+      <c r="B41" s="81">
         <v>46139</v>
       </c>
-      <c r="C41" s="87" t="s">
+      <c r="C41" s="83" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="85">
+      <c r="D41" s="81">
         <v>46139</v>
       </c>
-      <c r="E41" s="87" t="s">
+      <c r="E41" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="87" t="s">
+      <c r="F41" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="81" t="s">
+      <c r="G41" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="81" t="s">
+      <c r="H41" s="95" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="81" t="s">
+      <c r="J41" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="84"/>
-      <c r="B42" s="86"/>
-      <c r="C42" s="88"/>
-      <c r="D42" s="86"/>
-      <c r="E42" s="88"/>
-      <c r="F42" s="88"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="82"/>
+      <c r="A42" s="86"/>
+      <c r="B42" s="82"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="97"/>
+      <c r="H42" s="97"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="82"/>
+      <c r="J42" s="97"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15588,28 +15602,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="83">
+      <c r="A47" s="85">
         <v>33</v>
       </c>
-      <c r="B47" s="85">
+      <c r="B47" s="81">
         <v>46149</v>
       </c>
-      <c r="C47" s="87" t="s">
+      <c r="C47" s="83" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="85">
+      <c r="D47" s="81">
         <v>46148</v>
       </c>
-      <c r="E47" s="87" t="s">
+      <c r="E47" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="87" t="s">
+      <c r="F47" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="81" t="s">
+      <c r="G47" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="81" t="s">
+      <c r="H47" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15620,14 +15634,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="84"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="88"/>
-      <c r="D48" s="86"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
+      <c r="A48" s="86"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="97"/>
+      <c r="H48" s="97"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15636,28 +15650,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="83">
+      <c r="A49" s="85">
         <v>34</v>
       </c>
-      <c r="B49" s="85">
+      <c r="B49" s="81">
         <v>46149</v>
       </c>
-      <c r="C49" s="87" t="s">
+      <c r="C49" s="83" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="85">
+      <c r="D49" s="81">
         <v>46148</v>
       </c>
-      <c r="E49" s="87" t="s">
+      <c r="E49" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="87" t="s">
+      <c r="F49" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="81" t="s">
+      <c r="G49" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="81" t="s">
+      <c r="H49" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15668,14 +15682,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="84"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="88"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
+      <c r="A50" s="86"/>
+      <c r="B50" s="82"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="97"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -15972,50 +15986,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="83">
+      <c r="A60" s="85">
         <v>44</v>
       </c>
-      <c r="B60" s="85">
+      <c r="B60" s="81">
         <v>46169</v>
       </c>
-      <c r="C60" s="87" t="s">
+      <c r="C60" s="83" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="85">
+      <c r="D60" s="81">
         <v>46169</v>
       </c>
-      <c r="E60" s="87" t="s">
+      <c r="E60" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="87" t="s">
+      <c r="F60" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="81" t="s">
+      <c r="G60" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="81" t="s">
+      <c r="H60" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="81" t="s">
+      <c r="J60" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="84"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="88"/>
-      <c r="D61" s="86"/>
-      <c r="E61" s="88"/>
-      <c r="F61" s="88"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="82"/>
+      <c r="A61" s="86"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="84"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="84"/>
+      <c r="F61" s="84"/>
+      <c r="G61" s="97"/>
+      <c r="H61" s="97"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="82"/>
+      <c r="J61" s="97"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16335,50 +16349,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="83">
+      <c r="A72" s="85">
         <v>55</v>
       </c>
-      <c r="B72" s="85">
+      <c r="B72" s="81">
         <v>46192</v>
       </c>
-      <c r="C72" s="87" t="s">
+      <c r="C72" s="83" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="85">
+      <c r="D72" s="81">
         <v>46191</v>
       </c>
-      <c r="E72" s="87" t="s">
+      <c r="E72" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="87" t="s">
+      <c r="F72" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="81" t="s">
+      <c r="G72" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="81" t="s">
+      <c r="H72" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="81" t="s">
+      <c r="J72" s="95" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="84"/>
-      <c r="B73" s="86"/>
-      <c r="C73" s="88"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="88"/>
-      <c r="F73" s="88"/>
-      <c r="G73" s="82"/>
-      <c r="H73" s="82"/>
+      <c r="A73" s="86"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="84"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="84"/>
+      <c r="F73" s="84"/>
+      <c r="G73" s="97"/>
+      <c r="H73" s="97"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="82"/>
+      <c r="J73" s="97"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16573,184 +16587,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="83">
+      <c r="A80" s="85">
         <v>62</v>
       </c>
-      <c r="B80" s="85">
+      <c r="B80" s="81">
         <v>46200</v>
       </c>
-      <c r="C80" s="87" t="s">
+      <c r="C80" s="83" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="85">
+      <c r="D80" s="81">
         <v>46200</v>
       </c>
-      <c r="E80" s="87" t="s">
+      <c r="E80" s="83" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="87" t="s">
+      <c r="F80" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="81" t="s">
+      <c r="G80" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="81" t="s">
+      <c r="H80" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="81" t="s">
+      <c r="J80" s="95" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="89"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="90"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
+      <c r="A81" s="98"/>
+      <c r="B81" s="94"/>
+      <c r="C81" s="93"/>
+      <c r="D81" s="94"/>
+      <c r="E81" s="93"/>
+      <c r="F81" s="93"/>
+      <c r="G81" s="96"/>
+      <c r="H81" s="96"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="92"/>
+      <c r="J81" s="96"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="89"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="92"/>
-      <c r="H82" s="92"/>
+      <c r="A82" s="98"/>
+      <c r="B82" s="94"/>
+      <c r="C82" s="93"/>
+      <c r="D82" s="94"/>
+      <c r="E82" s="93"/>
+      <c r="F82" s="93"/>
+      <c r="G82" s="96"/>
+      <c r="H82" s="96"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="92"/>
+      <c r="J82" s="96"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="89"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="90"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
+      <c r="A83" s="98"/>
+      <c r="B83" s="94"/>
+      <c r="C83" s="93"/>
+      <c r="D83" s="94"/>
+      <c r="E83" s="93"/>
+      <c r="F83" s="93"/>
+      <c r="G83" s="96"/>
+      <c r="H83" s="96"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="96"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="84"/>
-      <c r="B84" s="86"/>
-      <c r="C84" s="88"/>
-      <c r="D84" s="86"/>
-      <c r="E84" s="88"/>
-      <c r="F84" s="88"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
+      <c r="A84" s="86"/>
+      <c r="B84" s="82"/>
+      <c r="C84" s="84"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="84"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="97"/>
+      <c r="H84" s="97"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="82"/>
+      <c r="J84" s="97"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="83">
+      <c r="A85" s="85">
         <v>63</v>
       </c>
-      <c r="B85" s="85">
+      <c r="B85" s="81">
         <v>46204</v>
       </c>
-      <c r="C85" s="87" t="s">
+      <c r="C85" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="85">
+      <c r="D85" s="81">
         <v>46204</v>
       </c>
-      <c r="E85" s="87" t="s">
+      <c r="E85" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="87" t="s">
+      <c r="F85" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="81" t="s">
+      <c r="G85" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="81" t="s">
+      <c r="H85" s="95" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="81" t="s">
+      <c r="J85" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="84"/>
-      <c r="B86" s="86"/>
-      <c r="C86" s="88"/>
-      <c r="D86" s="86"/>
-      <c r="E86" s="88"/>
-      <c r="F86" s="88"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
+      <c r="A86" s="86"/>
+      <c r="B86" s="82"/>
+      <c r="C86" s="84"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="84"/>
+      <c r="F86" s="84"/>
+      <c r="G86" s="97"/>
+      <c r="H86" s="97"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="82"/>
+      <c r="J86" s="97"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="83">
+      <c r="A87" s="85">
         <v>64</v>
       </c>
-      <c r="B87" s="85">
+      <c r="B87" s="81">
         <v>46210</v>
       </c>
-      <c r="C87" s="87" t="s">
+      <c r="C87" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="85">
+      <c r="D87" s="81">
         <v>46210</v>
       </c>
-      <c r="E87" s="87" t="s">
+      <c r="E87" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="87" t="s">
+      <c r="F87" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="81" t="s">
+      <c r="G87" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="81" t="s">
+      <c r="H87" s="95" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="81" t="s">
+      <c r="J87" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="84"/>
-      <c r="B88" s="86"/>
-      <c r="C88" s="88"/>
-      <c r="D88" s="86"/>
-      <c r="E88" s="88"/>
-      <c r="F88" s="88"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
+      <c r="A88" s="86"/>
+      <c r="B88" s="82"/>
+      <c r="C88" s="84"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="84"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="97"/>
+      <c r="H88" s="97"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="82"/>
+      <c r="J88" s="97"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17356,64 +17370,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="83">
+      <c r="A108" s="85">
         <v>84</v>
       </c>
-      <c r="B108" s="85">
+      <c r="B108" s="81">
         <v>46231</v>
       </c>
-      <c r="C108" s="87" t="s">
+      <c r="C108" s="83" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="85">
+      <c r="D108" s="81">
         <v>46231</v>
       </c>
-      <c r="E108" s="87" t="s">
+      <c r="E108" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="87" t="s">
+      <c r="F108" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="81" t="s">
+      <c r="G108" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="81" t="s">
+      <c r="H108" s="95" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="81" t="s">
+      <c r="J108" s="95" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="89"/>
-      <c r="B109" s="90"/>
-      <c r="C109" s="91"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="91"/>
-      <c r="F109" s="91"/>
-      <c r="G109" s="92"/>
-      <c r="H109" s="92"/>
+      <c r="A109" s="98"/>
+      <c r="B109" s="94"/>
+      <c r="C109" s="93"/>
+      <c r="D109" s="94"/>
+      <c r="E109" s="93"/>
+      <c r="F109" s="93"/>
+      <c r="G109" s="96"/>
+      <c r="H109" s="96"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="92"/>
+      <c r="J109" s="96"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="84"/>
-      <c r="B110" s="86"/>
-      <c r="C110" s="88"/>
-      <c r="D110" s="86"/>
-      <c r="E110" s="88"/>
-      <c r="F110" s="88"/>
-      <c r="G110" s="82"/>
-      <c r="H110" s="82"/>
+      <c r="A110" s="86"/>
+      <c r="B110" s="82"/>
+      <c r="C110" s="84"/>
+      <c r="D110" s="82"/>
+      <c r="E110" s="84"/>
+      <c r="F110" s="84"/>
+      <c r="G110" s="97"/>
+      <c r="H110" s="97"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="82"/>
+      <c r="J110" s="97"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17832,50 +17846,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="83">
+      <c r="A124" s="85">
         <v>98</v>
       </c>
-      <c r="B124" s="85">
+      <c r="B124" s="81">
         <v>46263</v>
       </c>
-      <c r="C124" s="87" t="s">
+      <c r="C124" s="83" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="85">
+      <c r="D124" s="81">
         <v>46260</v>
       </c>
-      <c r="E124" s="87" t="s">
+      <c r="E124" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="87" t="s">
+      <c r="F124" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="81" t="s">
+      <c r="G124" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="81" t="s">
+      <c r="H124" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="81" t="s">
+      <c r="J124" s="95" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="84"/>
-      <c r="B125" s="86"/>
-      <c r="C125" s="88"/>
-      <c r="D125" s="86"/>
-      <c r="E125" s="88"/>
-      <c r="F125" s="88"/>
-      <c r="G125" s="82"/>
-      <c r="H125" s="82"/>
+      <c r="A125" s="86"/>
+      <c r="B125" s="82"/>
+      <c r="C125" s="84"/>
+      <c r="D125" s="82"/>
+      <c r="E125" s="84"/>
+      <c r="F125" s="84"/>
+      <c r="G125" s="97"/>
+      <c r="H125" s="97"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="82"/>
+      <c r="J125" s="97"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -18883,25 +18897,25 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="83">
+      <c r="A157" s="85">
         <v>129</v>
       </c>
-      <c r="B157" s="85">
+      <c r="B157" s="81">
         <v>46294</v>
       </c>
-      <c r="C157" s="87" t="s">
+      <c r="C157" s="83" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="85">
+      <c r="D157" s="81">
         <v>46294</v>
       </c>
-      <c r="E157" s="87" t="s">
+      <c r="E157" s="83" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="43" t="s">
+      <c r="G157" s="95" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -18918,17 +18932,15 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="84"/>
-      <c r="B158" s="86"/>
-      <c r="C158" s="88"/>
-      <c r="D158" s="86"/>
-      <c r="E158" s="88"/>
+      <c r="A158" s="86"/>
+      <c r="B158" s="82"/>
+      <c r="C158" s="84"/>
+      <c r="D158" s="82"/>
+      <c r="E158" s="84"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="43" t="s">
-        <v>124</v>
-      </c>
+      <c r="G158" s="97"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19199,47 +19211,50 @@
       </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="26">
+      <c r="A167" s="85">
         <v>138</v>
       </c>
-      <c r="B167" s="52">
+      <c r="B167" s="81">
         <v>46300</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C167" s="83" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="52">
+      <c r="D167" s="81">
         <v>46295</v>
       </c>
-      <c r="E167" s="10" t="s">
+      <c r="E167" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F167" s="10" t="s">
+      <c r="F167" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="43" t="s">
+      <c r="G167" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="43" t="s">
+      <c r="H167" s="95" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="43" t="s">
+      <c r="J167" s="95" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A168" s="26"/>
-      <c r="B168" s="43"/>
-      <c r="D168" s="43"/>
-      <c r="G168" s="43"/>
-      <c r="H168" s="43"/>
+      <c r="A168" s="86"/>
+      <c r="B168" s="82"/>
+      <c r="C168" s="84"/>
+      <c r="D168" s="82"/>
+      <c r="E168" s="84"/>
+      <c r="F168" s="84"/>
+      <c r="G168" s="97"/>
+      <c r="H168" s="97"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="43"/>
+      <c r="J168" s="97"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -26570,7 +26585,148 @@
       <c r="J982" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="155">
+  <mergeCells count="165">
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="C157:C158"/>
     <mergeCell ref="D157:D158"/>
@@ -26595,137 +26751,6 @@
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
     <mergeCell ref="D124:D125"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA63CF59-C126-419E-947D-470626E3AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DD2DC4-BEB0-43F8-AA30-941CE50227CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="943">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2841,6 +2841,15 @@
   </si>
   <si>
     <t>Outer Cover- Qty 2 Nos. / Flpwcell- Qty 2 Nos. / Switch - Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>HeatSkin- Qty 5 Nos.</t>
+  </si>
+  <si>
+    <t>AWB#90682916623</t>
+  </si>
+  <si>
+    <t>Photometer Halogen Lamp assy Bioelab FA 6V/10w- Qty 15 Nos. /  Bioelab SA 6V/10W - Qty 7 Nos.</t>
   </si>
 </sst>
 </file>
@@ -3345,12 +3354,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3363,28 +3366,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3402,10 +3396,31 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3414,11 +3429,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3436,30 +3469,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3762,21 +3771,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3809,10 +3818,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3925,46 +3934,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="66">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="63"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4058,30 +4067,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="66">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4092,10 +4101,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4103,54 +4112,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="63"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="66">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="66">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="69"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4158,17 +4167,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4287,25 +4296,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="66">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="66">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4316,13 +4325,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4447,46 +4456,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="66">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="66">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4544,41 +4553,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="66">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="66">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4586,59 +4595,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="66">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="66">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4754,117 +4763,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="66">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="63"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="66">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="63"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="66">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="66">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4875,13 +4884,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4890,42 +4899,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="66">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="64">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="66">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="63"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5108,50 +5117,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="66">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="66">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="63"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5450,41 +5459,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="66">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="66">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
+      <c r="F68" s="69"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5493,11 +5502,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
+      <c r="F69" s="69"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5505,17 +5514,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="63"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="63"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5744,39 +5753,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="66">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="66">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="69"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
+      <c r="F80" s="69"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5785,11 +5794,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5798,11 +5807,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
+      <c r="F82" s="69"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5810,17 +5819,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="63"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="63"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5852,22 +5861,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="66">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="66">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="64" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5875,57 +5884,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="67"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="65"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="66">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="66">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="A88" s="63"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="63"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="63"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5957,41 +5966,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="66">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="64">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="66">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6000,11 +6009,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
+      <c r="F92" s="69"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6012,17 +6021,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="65"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="63"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6503,87 +6512,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="66">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="66">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="69"/>
+      <c r="D113" s="70"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="69"/>
+      <c r="D114" s="70"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
+      <c r="F114" s="69"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="67"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="63"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7166,92 +7175,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="66">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="66">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="67"/>
+      <c r="C137" s="65"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="63"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="66">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="66">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="65"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="63"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7574,46 +7583,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="66">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="66">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
-      <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="A151" s="63"/>
+      <c r="B151" s="67"/>
+      <c r="C151" s="65"/>
+      <c r="D151" s="67"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="63"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="63"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7642,41 +7651,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="66">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="66">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
-      <c r="D154" s="69"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="70"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
+      <c r="F154" s="69"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7685,11 +7694,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
-      <c r="D155" s="69"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="70"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
+      <c r="F155" s="69"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7697,17 +7706,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
-      <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="A156" s="63"/>
+      <c r="B156" s="67"/>
+      <c r="C156" s="65"/>
+      <c r="D156" s="67"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="65"/>
+      <c r="G156" s="63"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="63"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7768,41 +7777,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="66">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="66">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="69"/>
+      <c r="B160" s="70"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="70"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
+      <c r="F160" s="69"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7811,11 +7820,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="69"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="70"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
+      <c r="F161" s="69"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7824,11 +7833,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="69"/>
+      <c r="B162" s="70"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="70"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
+      <c r="F162" s="69"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7836,17 +7845,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
-      <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="A163" s="63"/>
+      <c r="B163" s="67"/>
+      <c r="C163" s="65"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="65"/>
+      <c r="G163" s="63"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="63"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8136,46 +8145,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="66">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
-      <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="A175" s="63"/>
+      <c r="B175" s="67"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="63"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="63"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8317,41 +8326,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="66">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="64" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="66">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
-      <c r="D182" s="69"/>
+      <c r="B182" s="70"/>
+      <c r="C182" s="69"/>
+      <c r="D182" s="70"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
+      <c r="F182" s="77"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8360,11 +8369,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
-      <c r="D183" s="69"/>
+      <c r="B183" s="70"/>
+      <c r="C183" s="69"/>
+      <c r="D183" s="70"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
+      <c r="F183" s="77"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8373,11 +8382,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
-      <c r="D184" s="69"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="69"/>
+      <c r="D184" s="70"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
+      <c r="F184" s="77"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8385,59 +8394,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
-      <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="A185" s="63"/>
+      <c r="B185" s="67"/>
+      <c r="C185" s="65"/>
+      <c r="D185" s="67"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="63"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="63"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="66">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="64" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="66">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
-      <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
-      <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="A187" s="63"/>
+      <c r="B187" s="67"/>
+      <c r="C187" s="65"/>
+      <c r="D187" s="67"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="65"/>
+      <c r="G187" s="63"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="63"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9105,31 +9114,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="66">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="64" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="66">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9138,11 +9147,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
-      <c r="D212" s="69"/>
+      <c r="B212" s="70"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
+      <c r="F212" s="69"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9151,11 +9160,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
-      <c r="D213" s="69"/>
+      <c r="B213" s="70"/>
+      <c r="C213" s="69"/>
+      <c r="D213" s="70"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
+      <c r="F213" s="69"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9163,17 +9172,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
-      <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="67"/>
+      <c r="C214" s="65"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="65"/>
+      <c r="G214" s="63"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="63"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9440,46 +9449,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="66">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="64" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="66">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="64" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
-      <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
-      <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="67"/>
+      <c r="C225" s="65"/>
+      <c r="D225" s="67"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="63"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="63"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9511,88 +9520,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="66">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="66">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
-      <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="A228" s="63"/>
+      <c r="B228" s="67"/>
+      <c r="C228" s="65"/>
+      <c r="D228" s="67"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="65"/>
+      <c r="G228" s="63"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="63"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="66">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="66">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
-      <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="A230" s="63"/>
+      <c r="B230" s="67"/>
+      <c r="C230" s="65"/>
+      <c r="D230" s="67"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="65"/>
+      <c r="G230" s="63"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="63"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9653,46 +9662,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="66">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="64" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="66">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
-      <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="A234" s="63"/>
+      <c r="B234" s="67"/>
+      <c r="C234" s="65"/>
+      <c r="D234" s="67"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="65"/>
+      <c r="G234" s="63"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="63"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10333,46 +10342,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="64">
+      <c r="A257" s="62">
         <v>200</v>
       </c>
-      <c r="B257" s="62">
+      <c r="B257" s="66">
         <v>46300</v>
       </c>
-      <c r="C257" s="66" t="s">
+      <c r="C257" s="64" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="62">
+      <c r="D257" s="66">
         <v>46294</v>
       </c>
-      <c r="E257" s="64" t="s">
+      <c r="E257" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="66" t="s">
+      <c r="F257" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="64" t="s">
+      <c r="G257" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="64" t="s">
+      <c r="I257" s="62" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="63"/>
-      <c r="E258" s="65"/>
-      <c r="F258" s="67"/>
-      <c r="G258" s="65"/>
+      <c r="A258" s="63"/>
+      <c r="B258" s="67"/>
+      <c r="C258" s="65"/>
+      <c r="D258" s="67"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="65"/>
+      <c r="G258" s="63"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="65"/>
+      <c r="I258" s="63"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10404,16 +10413,67 @@
       </c>
     </row>
     <row r="260" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C260" s="46"/>
-      <c r="F260" s="46"/>
-      <c r="H260" s="34"/>
+      <c r="A260" s="21">
+        <v>202</v>
+      </c>
+      <c r="B260" s="25">
+        <v>46301</v>
+      </c>
+      <c r="C260" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D260" s="25">
+        <v>46301</v>
+      </c>
+      <c r="E260" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F260" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="G260" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="H260" s="34" t="s">
+        <v>940</v>
+      </c>
+      <c r="I260" s="21" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="261" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C261" s="46"/>
-      <c r="F261" s="46"/>
-      <c r="H261" s="34"/>
+      <c r="A261" s="21">
+        <v>203</v>
+      </c>
+      <c r="B261" s="25">
+        <v>46301</v>
+      </c>
+      <c r="C261" s="46" t="s">
+        <v>941</v>
+      </c>
+      <c r="D261" s="25">
+        <v>46296</v>
+      </c>
+      <c r="E261" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F261" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G261" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H261" s="34" t="s">
+        <v>942</v>
+      </c>
+      <c r="I261" s="21" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A262" s="21">
+        <v>204</v>
+      </c>
       <c r="C262" s="46"/>
       <c r="F262" s="46"/>
       <c r="H262" s="34"/>
@@ -14020,6 +14080,238 @@
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="I229:I230"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="F233:F234"/>
+    <mergeCell ref="G233:G234"/>
+    <mergeCell ref="I233:I234"/>
+    <mergeCell ref="G229:G230"/>
+    <mergeCell ref="F229:F230"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="G257:G258"/>
     <mergeCell ref="I257:I258"/>
     <mergeCell ref="F257:F258"/>
@@ -14044,238 +14336,6 @@
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="I227:I228"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="F233:F234"/>
-    <mergeCell ref="G233:G234"/>
-    <mergeCell ref="I233:I234"/>
-    <mergeCell ref="G229:G230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14307,23 +14367,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14391,28 +14451,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="62">
         <v>1</v>
       </c>
-      <c r="B4" s="90">
+      <c r="B4" s="98">
         <v>46098</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="98">
         <v>46098</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="64" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14433,13 +14493,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14458,13 +14518,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14482,14 +14542,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14600,50 +14660,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="64">
+      <c r="A11" s="62">
         <v>5</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="93">
         <v>46102</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <v>46095</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="64" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14678,110 +14738,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="85">
+      <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="81">
+      <c r="B14" s="87">
         <v>46105</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="87">
         <v>46105</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="95" t="s">
+      <c r="G14" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="95" t="s">
+      <c r="H14" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="95" t="s">
+      <c r="J14" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="98"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="93"/>
-      <c r="F15" s="93"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="96"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="86"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="97"/>
-      <c r="H16" s="97"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="97"/>
+      <c r="J16" s="84"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="85">
+      <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="81">
+      <c r="B17" s="87">
         <v>46105</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="87">
         <v>46105</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="95" t="s">
+      <c r="H17" s="83" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="95" t="s">
+      <c r="J17" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="86"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="97"/>
+      <c r="J18" s="84"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15104,50 +15164,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="85">
+      <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="81">
+      <c r="B29" s="87">
         <v>46121</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="81">
+      <c r="D29" s="87">
         <v>46121</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="95" t="s">
+      <c r="G29" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="95" t="s">
+      <c r="H29" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="95" t="s">
+      <c r="J29" s="83" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="86"/>
-      <c r="B30" s="82"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="97"/>
+      <c r="J30" s="84"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15240,74 +15300,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="85">
+      <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="81">
+      <c r="B34" s="87">
         <v>46128</v>
       </c>
-      <c r="C34" s="83" t="s">
+      <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="81">
+      <c r="D34" s="87">
         <v>46128</v>
       </c>
-      <c r="E34" s="83" t="s">
+      <c r="E34" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="83" t="s">
+      <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="95" t="s">
+      <c r="G34" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="95" t="s">
+      <c r="H34" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="95" t="s">
+      <c r="J34" s="83" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="86"/>
-      <c r="B35" s="82"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="97"/>
-      <c r="H35" s="97"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="88"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="97"/>
+      <c r="J35" s="84"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="85">
+      <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="81">
+      <c r="B36" s="87">
         <v>46132</v>
       </c>
-      <c r="C36" s="83" t="s">
+      <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="81">
+      <c r="D36" s="87">
         <v>46129</v>
       </c>
-      <c r="E36" s="83" t="s">
+      <c r="E36" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="83" t="s">
+      <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="95" t="s">
+      <c r="G36" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="95" t="s">
+      <c r="H36" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15318,14 +15378,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="86"/>
-      <c r="B37" s="82"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="82"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="97"/>
-      <c r="H37" s="97"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="88"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15428,50 +15488,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="85">
+      <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="81">
+      <c r="B41" s="87">
         <v>46139</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="81">
+      <c r="D41" s="87">
         <v>46139</v>
       </c>
-      <c r="E41" s="83" t="s">
+      <c r="E41" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="95" t="s">
+      <c r="G41" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="95" t="s">
+      <c r="H41" s="83" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="95" t="s">
+      <c r="J41" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="86"/>
-      <c r="B42" s="82"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="97"/>
+      <c r="A42" s="82"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="88"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="86"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="97"/>
+      <c r="J42" s="84"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15602,28 +15662,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="85">
+      <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="81">
+      <c r="B47" s="87">
         <v>46149</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="81">
+      <c r="D47" s="87">
         <v>46148</v>
       </c>
-      <c r="E47" s="83" t="s">
+      <c r="E47" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="83" t="s">
+      <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="95" t="s">
+      <c r="G47" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="95" t="s">
+      <c r="H47" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15634,14 +15694,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="86"/>
-      <c r="B48" s="82"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="82"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="97"/>
-      <c r="H48" s="97"/>
+      <c r="A48" s="82"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="88"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15650,28 +15710,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="85">
+      <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="81">
+      <c r="B49" s="87">
         <v>46149</v>
       </c>
-      <c r="C49" s="83" t="s">
+      <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="81">
+      <c r="D49" s="87">
         <v>46148</v>
       </c>
-      <c r="E49" s="83" t="s">
+      <c r="E49" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="83" t="s">
+      <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="95" t="s">
+      <c r="G49" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="95" t="s">
+      <c r="H49" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15682,14 +15742,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="86"/>
-      <c r="B50" s="82"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="82"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="97"/>
-      <c r="H50" s="97"/>
+      <c r="A50" s="82"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -15986,50 +16046,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="85">
+      <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="81">
+      <c r="B60" s="87">
         <v>46169</v>
       </c>
-      <c r="C60" s="83" t="s">
+      <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="81">
+      <c r="D60" s="87">
         <v>46169</v>
       </c>
-      <c r="E60" s="83" t="s">
+      <c r="E60" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="83" t="s">
+      <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="95" t="s">
+      <c r="G60" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="95" t="s">
+      <c r="H60" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="95" t="s">
+      <c r="J60" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="86"/>
-      <c r="B61" s="82"/>
-      <c r="C61" s="84"/>
-      <c r="D61" s="82"/>
-      <c r="E61" s="84"/>
-      <c r="F61" s="84"/>
-      <c r="G61" s="97"/>
-      <c r="H61" s="97"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="88"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="88"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="84"/>
+      <c r="H61" s="84"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="97"/>
+      <c r="J61" s="84"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16349,50 +16409,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="85">
+      <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="81">
+      <c r="B72" s="87">
         <v>46192</v>
       </c>
-      <c r="C72" s="83" t="s">
+      <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="81">
+      <c r="D72" s="87">
         <v>46191</v>
       </c>
-      <c r="E72" s="83" t="s">
+      <c r="E72" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="83" t="s">
+      <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="95" t="s">
+      <c r="G72" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="95" t="s">
+      <c r="H72" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="95" t="s">
+      <c r="J72" s="83" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="86"/>
-      <c r="B73" s="82"/>
-      <c r="C73" s="84"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="84"/>
-      <c r="F73" s="84"/>
-      <c r="G73" s="97"/>
-      <c r="H73" s="97"/>
+      <c r="A73" s="82"/>
+      <c r="B73" s="88"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="88"/>
+      <c r="E73" s="86"/>
+      <c r="F73" s="86"/>
+      <c r="G73" s="84"/>
+      <c r="H73" s="84"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="97"/>
+      <c r="J73" s="84"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16587,184 +16647,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="85">
+      <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="81">
+      <c r="B80" s="87">
         <v>46200</v>
       </c>
-      <c r="C80" s="83" t="s">
+      <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="81">
+      <c r="D80" s="87">
         <v>46200</v>
       </c>
-      <c r="E80" s="83" t="s">
+      <c r="E80" s="85" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="83" t="s">
+      <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="95" t="s">
+      <c r="G80" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="95" t="s">
+      <c r="H80" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="95" t="s">
+      <c r="J80" s="83" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="98"/>
-      <c r="B81" s="94"/>
-      <c r="C81" s="93"/>
-      <c r="D81" s="94"/>
-      <c r="E81" s="93"/>
-      <c r="F81" s="93"/>
-      <c r="G81" s="96"/>
-      <c r="H81" s="96"/>
+      <c r="A81" s="89"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="90"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="96"/>
+      <c r="J81" s="92"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="98"/>
-      <c r="B82" s="94"/>
-      <c r="C82" s="93"/>
-      <c r="D82" s="94"/>
-      <c r="E82" s="93"/>
-      <c r="F82" s="93"/>
-      <c r="G82" s="96"/>
-      <c r="H82" s="96"/>
+      <c r="A82" s="89"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="91"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="96"/>
+      <c r="J82" s="92"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="98"/>
-      <c r="B83" s="94"/>
-      <c r="C83" s="93"/>
-      <c r="D83" s="94"/>
-      <c r="E83" s="93"/>
-      <c r="F83" s="93"/>
-      <c r="G83" s="96"/>
-      <c r="H83" s="96"/>
+      <c r="A83" s="89"/>
+      <c r="B83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="90"/>
+      <c r="E83" s="91"/>
+      <c r="F83" s="91"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="96"/>
+      <c r="J83" s="92"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="86"/>
-      <c r="B84" s="82"/>
-      <c r="C84" s="84"/>
-      <c r="D84" s="82"/>
-      <c r="E84" s="84"/>
-      <c r="F84" s="84"/>
-      <c r="G84" s="97"/>
-      <c r="H84" s="97"/>
+      <c r="A84" s="82"/>
+      <c r="B84" s="88"/>
+      <c r="C84" s="86"/>
+      <c r="D84" s="88"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="86"/>
+      <c r="G84" s="84"/>
+      <c r="H84" s="84"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="97"/>
+      <c r="J84" s="84"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="85">
+      <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="81">
+      <c r="B85" s="87">
         <v>46204</v>
       </c>
-      <c r="C85" s="83" t="s">
+      <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="81">
+      <c r="D85" s="87">
         <v>46204</v>
       </c>
-      <c r="E85" s="83" t="s">
+      <c r="E85" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="83" t="s">
+      <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="95" t="s">
+      <c r="G85" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="95" t="s">
+      <c r="H85" s="83" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="95" t="s">
+      <c r="J85" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="86"/>
-      <c r="B86" s="82"/>
-      <c r="C86" s="84"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="84"/>
-      <c r="G86" s="97"/>
-      <c r="H86" s="97"/>
+      <c r="A86" s="82"/>
+      <c r="B86" s="88"/>
+      <c r="C86" s="86"/>
+      <c r="D86" s="88"/>
+      <c r="E86" s="86"/>
+      <c r="F86" s="86"/>
+      <c r="G86" s="84"/>
+      <c r="H86" s="84"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="97"/>
+      <c r="J86" s="84"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="85">
+      <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="81">
+      <c r="B87" s="87">
         <v>46210</v>
       </c>
-      <c r="C87" s="83" t="s">
+      <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="81">
+      <c r="D87" s="87">
         <v>46210</v>
       </c>
-      <c r="E87" s="83" t="s">
+      <c r="E87" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="83" t="s">
+      <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="95" t="s">
+      <c r="G87" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="95" t="s">
+      <c r="H87" s="83" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="95" t="s">
+      <c r="J87" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="86"/>
-      <c r="B88" s="82"/>
-      <c r="C88" s="84"/>
-      <c r="D88" s="82"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="84"/>
-      <c r="G88" s="97"/>
-      <c r="H88" s="97"/>
+      <c r="A88" s="82"/>
+      <c r="B88" s="88"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="88"/>
+      <c r="E88" s="86"/>
+      <c r="F88" s="86"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="97"/>
+      <c r="J88" s="84"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17370,64 +17430,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="85">
+      <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="81">
+      <c r="B108" s="87">
         <v>46231</v>
       </c>
-      <c r="C108" s="83" t="s">
+      <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="81">
+      <c r="D108" s="87">
         <v>46231</v>
       </c>
-      <c r="E108" s="83" t="s">
+      <c r="E108" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="83" t="s">
+      <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="95" t="s">
+      <c r="G108" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="95" t="s">
+      <c r="H108" s="83" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="95" t="s">
+      <c r="J108" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="98"/>
-      <c r="B109" s="94"/>
-      <c r="C109" s="93"/>
-      <c r="D109" s="94"/>
-      <c r="E109" s="93"/>
-      <c r="F109" s="93"/>
-      <c r="G109" s="96"/>
-      <c r="H109" s="96"/>
+      <c r="A109" s="89"/>
+      <c r="B109" s="90"/>
+      <c r="C109" s="91"/>
+      <c r="D109" s="90"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="92"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="96"/>
+      <c r="J109" s="92"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="86"/>
-      <c r="B110" s="82"/>
-      <c r="C110" s="84"/>
-      <c r="D110" s="82"/>
-      <c r="E110" s="84"/>
-      <c r="F110" s="84"/>
-      <c r="G110" s="97"/>
-      <c r="H110" s="97"/>
+      <c r="A110" s="82"/>
+      <c r="B110" s="88"/>
+      <c r="C110" s="86"/>
+      <c r="D110" s="88"/>
+      <c r="E110" s="86"/>
+      <c r="F110" s="86"/>
+      <c r="G110" s="84"/>
+      <c r="H110" s="84"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="97"/>
+      <c r="J110" s="84"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17846,50 +17906,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="85">
+      <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="81">
+      <c r="B124" s="87">
         <v>46263</v>
       </c>
-      <c r="C124" s="83" t="s">
+      <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="81">
+      <c r="D124" s="87">
         <v>46260</v>
       </c>
-      <c r="E124" s="83" t="s">
+      <c r="E124" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="83" t="s">
+      <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="95" t="s">
+      <c r="G124" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="95" t="s">
+      <c r="H124" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="95" t="s">
+      <c r="J124" s="83" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="86"/>
-      <c r="B125" s="82"/>
-      <c r="C125" s="84"/>
-      <c r="D125" s="82"/>
-      <c r="E125" s="84"/>
-      <c r="F125" s="84"/>
-      <c r="G125" s="97"/>
-      <c r="H125" s="97"/>
+      <c r="A125" s="82"/>
+      <c r="B125" s="88"/>
+      <c r="C125" s="86"/>
+      <c r="D125" s="88"/>
+      <c r="E125" s="86"/>
+      <c r="F125" s="86"/>
+      <c r="G125" s="84"/>
+      <c r="H125" s="84"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="97"/>
+      <c r="J125" s="84"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -18897,25 +18957,25 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="85">
+      <c r="A157" s="81">
         <v>129</v>
       </c>
-      <c r="B157" s="81">
+      <c r="B157" s="87">
         <v>46294</v>
       </c>
-      <c r="C157" s="83" t="s">
+      <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="81">
+      <c r="D157" s="87">
         <v>46294</v>
       </c>
-      <c r="E157" s="83" t="s">
+      <c r="E157" s="85" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="95" t="s">
+      <c r="G157" s="83" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -18932,15 +18992,15 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="86"/>
-      <c r="B158" s="82"/>
-      <c r="C158" s="84"/>
-      <c r="D158" s="82"/>
-      <c r="E158" s="84"/>
+      <c r="A158" s="82"/>
+      <c r="B158" s="88"/>
+      <c r="C158" s="86"/>
+      <c r="D158" s="88"/>
+      <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="97"/>
+      <c r="G158" s="84"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19211,50 +19271,50 @@
       </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="85">
+      <c r="A167" s="81">
         <v>138</v>
       </c>
-      <c r="B167" s="81">
+      <c r="B167" s="87">
         <v>46300</v>
       </c>
-      <c r="C167" s="83" t="s">
+      <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="81">
+      <c r="D167" s="87">
         <v>46295</v>
       </c>
-      <c r="E167" s="83" t="s">
+      <c r="E167" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F167" s="83" t="s">
+      <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="95" t="s">
+      <c r="G167" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="95" t="s">
+      <c r="H167" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="95" t="s">
+      <c r="J167" s="83" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A168" s="86"/>
-      <c r="B168" s="82"/>
-      <c r="C168" s="84"/>
-      <c r="D168" s="82"/>
-      <c r="E168" s="84"/>
-      <c r="F168" s="84"/>
-      <c r="G168" s="97"/>
-      <c r="H168" s="97"/>
+      <c r="A168" s="82"/>
+      <c r="B168" s="88"/>
+      <c r="C168" s="86"/>
+      <c r="D168" s="88"/>
+      <c r="E168" s="86"/>
+      <c r="F168" s="86"/>
+      <c r="G168" s="84"/>
+      <c r="H168" s="84"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="97"/>
+      <c r="J168" s="84"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -26586,85 +26646,63 @@
     </row>
   </sheetData>
   <mergeCells count="165">
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="J17:J18"/>
@@ -26689,68 +26727,90 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="C157:C158"/>
     <mergeCell ref="D157:D158"/>
     <mergeCell ref="E157:E158"/>
     <mergeCell ref="A157:A158"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DD2DC4-BEB0-43F8-AA30-941CE50227CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145154BE-1A3B-4E1E-BB4D-5AA93C87A40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2843,13 +2843,13 @@
     <t>Outer Cover- Qty 2 Nos. / Flpwcell- Qty 2 Nos. / Switch - Qty 2 Nos.</t>
   </si>
   <si>
-    <t>HeatSkin- Qty 5 Nos.</t>
-  </si>
-  <si>
     <t>AWB#90682916623</t>
   </si>
   <si>
     <t>Photometer Halogen Lamp assy Bioelab FA 6V/10w- Qty 15 Nos. /  Bioelab SA 6V/10W - Qty 7 Nos.</t>
+  </si>
+  <si>
+    <t>HeatSkin- Qty 4 Nos.</t>
   </si>
 </sst>
 </file>
@@ -3354,6 +3354,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3366,19 +3372,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3396,31 +3411,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3428,30 +3428,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3469,6 +3445,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3771,21 +3771,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3818,10 +3818,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3934,46 +3934,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="63"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="63"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4067,30 +4067,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4101,10 +4101,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4112,54 +4112,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="63"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="63"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="66">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4167,17 +4167,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="63"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="63"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4296,25 +4296,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="66">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4325,13 +4325,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="63"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="63"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4456,46 +4456,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="66">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="63"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="63"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4553,41 +4553,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="66">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="70"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="69"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4595,59 +4595,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="63"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="66">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="63"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="63"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4763,117 +4763,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="66">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="64" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="63"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="63"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="66">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="64" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="63"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="63"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="66">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="66">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="64" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="63"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="63"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4899,42 +4899,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="66">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="66">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="63"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="67"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="63"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="63"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="63"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5117,50 +5117,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="66">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="66">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="63"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="63"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="63"/>
-      <c r="J56" s="63"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5459,41 +5459,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="66">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="66">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="64" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="70"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="69"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5502,11 +5502,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5514,17 +5514,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="63"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="63"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="63"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="63"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5753,39 +5753,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="66">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="66">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="64" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="70"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="69"/>
+      <c r="F80" s="70"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5794,11 +5794,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="70"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5807,11 +5807,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="70"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="69"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
+      <c r="F82" s="70"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5819,17 +5819,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="63"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="63"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="63"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5861,22 +5861,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="66">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="64" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="66">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="64" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5884,57 +5884,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="63"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="65"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="66">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="64" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="66">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="64" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="63"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="65"/>
-      <c r="G88" s="63"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="63"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5966,41 +5966,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="66">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="64">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="66">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="64" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="69"/>
-      <c r="D91" s="70"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="69"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6009,11 +6009,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="70"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="70"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="69"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="69"/>
+      <c r="F92" s="70"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6021,17 +6021,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="63"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="65"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="63"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="63"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6512,87 +6512,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="66">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="66">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="64" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="76" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="70"/>
+      <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="69"/>
+      <c r="F112" s="70"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="77"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="70"/>
+      <c r="B113" s="69"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="70"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="69"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="77"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="70"/>
+      <c r="B114" s="69"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="70"/>
+      <c r="D114" s="69"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="69"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="77"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="63"/>
-      <c r="B115" s="67"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="63"/>
-      <c r="F115" s="65"/>
-      <c r="G115" s="63"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="67"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="78"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7175,92 +7175,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="66">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="64" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="66">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="64" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="63"/>
-      <c r="B137" s="67"/>
-      <c r="C137" s="65"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="65"/>
-      <c r="G137" s="63"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
+      <c r="C137" s="67"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
+      <c r="F137" s="67"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="63"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="66">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="64" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="66">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="64" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="63"/>
-      <c r="B139" s="67"/>
-      <c r="C139" s="65"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="63"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="63"/>
-      <c r="J139" s="63"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7583,46 +7583,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="66">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="64" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="66">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="64" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="63"/>
-      <c r="B151" s="67"/>
-      <c r="C151" s="65"/>
-      <c r="D151" s="67"/>
-      <c r="E151" s="63"/>
-      <c r="F151" s="65"/>
-      <c r="G151" s="63"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
+      <c r="F151" s="67"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="63"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7651,41 +7651,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="66">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="64" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="66">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="64" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="69"/>
-      <c r="D154" s="70"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="69"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="69"/>
+      <c r="F154" s="70"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7694,11 +7694,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="70"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="70"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="69"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="69"/>
+      <c r="F155" s="70"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7706,17 +7706,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="63"/>
-      <c r="B156" s="67"/>
-      <c r="C156" s="65"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="63"/>
-      <c r="F156" s="65"/>
-      <c r="G156" s="63"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="67"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="63"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7777,41 +7777,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="66">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="64" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="66">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="64" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="70"/>
-      <c r="C160" s="69"/>
-      <c r="D160" s="70"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="69"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="69"/>
+      <c r="F160" s="70"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7820,11 +7820,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="70"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="70"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="69"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="69"/>
+      <c r="F161" s="70"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7833,11 +7833,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="70"/>
-      <c r="C162" s="69"/>
-      <c r="D162" s="70"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="70"/>
+      <c r="D162" s="69"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="69"/>
+      <c r="F162" s="70"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7845,17 +7845,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="63"/>
-      <c r="B163" s="67"/>
-      <c r="C163" s="65"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="65"/>
-      <c r="G163" s="63"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
+      <c r="F163" s="67"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="63"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8145,46 +8145,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="66">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="64" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="79">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="64" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="63"/>
-      <c r="B175" s="67"/>
-      <c r="C175" s="65"/>
-      <c r="D175" s="80"/>
-      <c r="E175" s="63"/>
-      <c r="F175" s="65"/>
-      <c r="G175" s="63"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="67"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="63"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8326,41 +8326,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="66">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="64" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="66">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="76" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="70"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="70"/>
+      <c r="B182" s="69"/>
+      <c r="C182" s="70"/>
+      <c r="D182" s="69"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="77"/>
+      <c r="F182" s="72"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8369,11 +8369,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="70"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="70"/>
+      <c r="B183" s="69"/>
+      <c r="C183" s="70"/>
+      <c r="D183" s="69"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="77"/>
+      <c r="F183" s="72"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8382,11 +8382,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="70"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="70"/>
+      <c r="B184" s="69"/>
+      <c r="C184" s="70"/>
+      <c r="D184" s="69"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="77"/>
+      <c r="F184" s="72"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8394,59 +8394,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="63"/>
-      <c r="B185" s="67"/>
-      <c r="C185" s="65"/>
-      <c r="D185" s="67"/>
-      <c r="E185" s="63"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="63"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
+      <c r="C185" s="67"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="63"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="66">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="64" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="66">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="64" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="63"/>
-      <c r="B187" s="67"/>
-      <c r="C187" s="65"/>
-      <c r="D187" s="67"/>
-      <c r="E187" s="63"/>
-      <c r="F187" s="65"/>
-      <c r="G187" s="63"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
+      <c r="F187" s="67"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="63"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9114,31 +9114,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="66">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="64" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="66">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="64" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9147,11 +9147,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="70"/>
-      <c r="C212" s="69"/>
-      <c r="D212" s="70"/>
+      <c r="B212" s="69"/>
+      <c r="C212" s="70"/>
+      <c r="D212" s="69"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="69"/>
+      <c r="F212" s="70"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9160,11 +9160,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="70"/>
-      <c r="C213" s="69"/>
-      <c r="D213" s="70"/>
+      <c r="B213" s="69"/>
+      <c r="C213" s="70"/>
+      <c r="D213" s="69"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="69"/>
+      <c r="F213" s="70"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9172,17 +9172,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="63"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="65"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="63"/>
-      <c r="F214" s="65"/>
-      <c r="G214" s="63"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
+      <c r="C214" s="67"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
+      <c r="F214" s="67"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="63"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9449,46 +9449,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="66">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="64" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="66">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="64" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="63"/>
-      <c r="B225" s="67"/>
-      <c r="C225" s="65"/>
-      <c r="D225" s="67"/>
-      <c r="E225" s="63"/>
-      <c r="F225" s="65"/>
-      <c r="G225" s="63"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
+      <c r="C225" s="67"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
+      <c r="F225" s="67"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="63"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9520,88 +9520,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="66">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="64" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="66">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="64" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="63"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="65"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="63"/>
-      <c r="F228" s="65"/>
-      <c r="G228" s="63"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
+      <c r="C228" s="67"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
+      <c r="F228" s="67"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="63"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="66">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="64" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="66">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="64" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="63"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="65"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="63"/>
-      <c r="F230" s="65"/>
-      <c r="G230" s="63"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
+      <c r="C230" s="67"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
+      <c r="F230" s="67"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="63"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9662,46 +9662,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="66">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="64" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="66">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="64" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="63"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="65"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="63"/>
-      <c r="F234" s="65"/>
-      <c r="G234" s="63"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
+      <c r="F234" s="67"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="63"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10342,46 +10342,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="62">
+      <c r="A257" s="64">
         <v>200</v>
       </c>
-      <c r="B257" s="66">
+      <c r="B257" s="62">
         <v>46300</v>
       </c>
-      <c r="C257" s="64" t="s">
+      <c r="C257" s="66" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="66">
+      <c r="D257" s="62">
         <v>46294</v>
       </c>
-      <c r="E257" s="62" t="s">
+      <c r="E257" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="64" t="s">
+      <c r="F257" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="62" t="s">
+      <c r="G257" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="62" t="s">
+      <c r="I257" s="64" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="63"/>
-      <c r="B258" s="67"/>
-      <c r="C258" s="65"/>
-      <c r="D258" s="67"/>
-      <c r="E258" s="63"/>
-      <c r="F258" s="65"/>
-      <c r="G258" s="63"/>
+      <c r="A258" s="65"/>
+      <c r="B258" s="63"/>
+      <c r="C258" s="67"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="65"/>
+      <c r="F258" s="67"/>
+      <c r="G258" s="65"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="63"/>
+      <c r="I258" s="65"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10435,7 +10435,7 @@
         <v>45</v>
       </c>
       <c r="H260" s="34" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="I260" s="21" t="s">
         <v>50</v>
@@ -10449,13 +10449,13 @@
         <v>46301</v>
       </c>
       <c r="C261" s="46" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D261" s="25">
         <v>46296</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="F261" s="46" t="s">
         <v>83</v>
@@ -10464,7 +10464,7 @@
         <v>48</v>
       </c>
       <c r="H261" s="34" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="I261" s="21" t="s">
         <v>50</v>
@@ -14080,238 +14080,6 @@
     </row>
   </sheetData>
   <mergeCells count="256">
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="I227:I228"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="F233:F234"/>
-    <mergeCell ref="G233:G234"/>
-    <mergeCell ref="I233:I234"/>
-    <mergeCell ref="G229:G230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
     <mergeCell ref="G257:G258"/>
     <mergeCell ref="I257:I258"/>
     <mergeCell ref="F257:F258"/>
@@ -14336,6 +14104,238 @@
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="I229:I230"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="F233:F234"/>
+    <mergeCell ref="G233:G234"/>
+    <mergeCell ref="I233:I234"/>
+    <mergeCell ref="G229:G230"/>
+    <mergeCell ref="F229:F230"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14367,23 +14367,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14451,28 +14451,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="90">
         <v>46098</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="90">
         <v>46098</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14493,13 +14493,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14518,13 +14518,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14542,14 +14542,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14660,50 +14660,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="64" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="65"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14741,13 +14741,13 @@
       <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="87">
+      <c r="B14" s="83">
         <v>46105</v>
       </c>
       <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="87">
+      <c r="D14" s="83">
         <v>46105</v>
       </c>
       <c r="E14" s="85" t="s">
@@ -14756,58 +14756,58 @@
       <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="83" t="s">
+      <c r="G14" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="83" t="s">
+      <c r="H14" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="83" t="s">
+      <c r="J14" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A16" s="82"/>
-      <c r="B16" s="88"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="86"/>
-      <c r="D16" s="88"/>
+      <c r="D16" s="84"/>
       <c r="E16" s="86"/>
       <c r="F16" s="86"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="84"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="87">
+      <c r="B17" s="83">
         <v>46105</v>
       </c>
       <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="87">
+      <c r="D17" s="83">
         <v>46105</v>
       </c>
       <c r="E17" s="85" t="s">
@@ -14816,32 +14816,32 @@
       <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="83" t="s">
+      <c r="J17" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A18" s="82"/>
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="86"/>
-      <c r="D18" s="88"/>
+      <c r="D18" s="84"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="84"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15167,13 +15167,13 @@
       <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="87">
+      <c r="B29" s="83">
         <v>46121</v>
       </c>
       <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="87">
+      <c r="D29" s="83">
         <v>46121</v>
       </c>
       <c r="E29" s="85" t="s">
@@ -15182,32 +15182,32 @@
       <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="83" t="s">
+      <c r="G29" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="83" t="s">
+      <c r="H29" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="93" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A30" s="82"/>
-      <c r="B30" s="88"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="86"/>
-      <c r="D30" s="88"/>
+      <c r="D30" s="84"/>
       <c r="E30" s="86"/>
       <c r="F30" s="86"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="84"/>
+      <c r="J30" s="95"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15303,13 +15303,13 @@
       <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="87">
+      <c r="B34" s="83">
         <v>46128</v>
       </c>
       <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="87">
+      <c r="D34" s="83">
         <v>46128</v>
       </c>
       <c r="E34" s="85" t="s">
@@ -15318,44 +15318,44 @@
       <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="83" t="s">
+      <c r="G34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="83" t="s">
+      <c r="H34" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="93" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A35" s="82"/>
-      <c r="B35" s="88"/>
+      <c r="B35" s="84"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="88"/>
+      <c r="D35" s="84"/>
       <c r="E35" s="86"/>
       <c r="F35" s="86"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="84"/>
+      <c r="J35" s="95"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="87">
+      <c r="B36" s="83">
         <v>46132</v>
       </c>
       <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="87">
+      <c r="D36" s="83">
         <v>46129</v>
       </c>
       <c r="E36" s="85" t="s">
@@ -15364,10 +15364,10 @@
       <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="83" t="s">
+      <c r="G36" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="83" t="s">
+      <c r="H36" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15379,13 +15379,13 @@
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A37" s="82"/>
-      <c r="B37" s="88"/>
+      <c r="B37" s="84"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="88"/>
+      <c r="D37" s="84"/>
       <c r="E37" s="86"/>
       <c r="F37" s="86"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15491,13 +15491,13 @@
       <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="87">
+      <c r="B41" s="83">
         <v>46139</v>
       </c>
       <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="87">
+      <c r="D41" s="83">
         <v>46139</v>
       </c>
       <c r="E41" s="85" t="s">
@@ -15506,32 +15506,32 @@
       <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="83" t="s">
+      <c r="G41" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="83" t="s">
+      <c r="H41" s="93" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="83" t="s">
+      <c r="J41" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A42" s="82"/>
-      <c r="B42" s="88"/>
+      <c r="B42" s="84"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="88"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="86"/>
       <c r="F42" s="86"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="84"/>
+      <c r="J42" s="95"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15665,13 +15665,13 @@
       <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="87">
+      <c r="B47" s="83">
         <v>46149</v>
       </c>
       <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="87">
+      <c r="D47" s="83">
         <v>46148</v>
       </c>
       <c r="E47" s="85" t="s">
@@ -15680,10 +15680,10 @@
       <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="83" t="s">
+      <c r="G47" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="83" t="s">
+      <c r="H47" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15695,13 +15695,13 @@
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A48" s="82"/>
-      <c r="B48" s="88"/>
+      <c r="B48" s="84"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="88"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="86"/>
       <c r="F48" s="86"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15713,13 +15713,13 @@
       <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="87">
+      <c r="B49" s="83">
         <v>46149</v>
       </c>
       <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="87">
+      <c r="D49" s="83">
         <v>46148</v>
       </c>
       <c r="E49" s="85" t="s">
@@ -15728,10 +15728,10 @@
       <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="83" t="s">
+      <c r="G49" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="83" t="s">
+      <c r="H49" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15743,13 +15743,13 @@
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A50" s="82"/>
-      <c r="B50" s="88"/>
+      <c r="B50" s="84"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="88"/>
+      <c r="D50" s="84"/>
       <c r="E50" s="86"/>
       <c r="F50" s="86"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16049,13 +16049,13 @@
       <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="87">
+      <c r="B60" s="83">
         <v>46169</v>
       </c>
       <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="87">
+      <c r="D60" s="83">
         <v>46169</v>
       </c>
       <c r="E60" s="85" t="s">
@@ -16064,32 +16064,32 @@
       <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="83" t="s">
+      <c r="G60" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="83" t="s">
+      <c r="H60" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="83" t="s">
+      <c r="J60" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A61" s="82"/>
-      <c r="B61" s="88"/>
+      <c r="B61" s="84"/>
       <c r="C61" s="86"/>
-      <c r="D61" s="88"/>
+      <c r="D61" s="84"/>
       <c r="E61" s="86"/>
       <c r="F61" s="86"/>
-      <c r="G61" s="84"/>
-      <c r="H61" s="84"/>
+      <c r="G61" s="95"/>
+      <c r="H61" s="95"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="84"/>
+      <c r="J61" s="95"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16412,13 +16412,13 @@
       <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="87">
+      <c r="B72" s="83">
         <v>46192</v>
       </c>
       <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="87">
+      <c r="D72" s="83">
         <v>46191</v>
       </c>
       <c r="E72" s="85" t="s">
@@ -16427,32 +16427,32 @@
       <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="83" t="s">
+      <c r="G72" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="83" t="s">
+      <c r="H72" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="83" t="s">
+      <c r="J72" s="93" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A73" s="82"/>
-      <c r="B73" s="88"/>
+      <c r="B73" s="84"/>
       <c r="C73" s="86"/>
-      <c r="D73" s="88"/>
+      <c r="D73" s="84"/>
       <c r="E73" s="86"/>
       <c r="F73" s="86"/>
-      <c r="G73" s="84"/>
-      <c r="H73" s="84"/>
+      <c r="G73" s="95"/>
+      <c r="H73" s="95"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="84"/>
+      <c r="J73" s="95"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16650,13 +16650,13 @@
       <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="87">
+      <c r="B80" s="83">
         <v>46200</v>
       </c>
       <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="87">
+      <c r="D80" s="83">
         <v>46200</v>
       </c>
       <c r="E80" s="85" t="s">
@@ -16665,86 +16665,86 @@
       <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="83" t="s">
+      <c r="G80" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="83" t="s">
+      <c r="H80" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="83" t="s">
+      <c r="J80" s="93" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="89"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="90"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
+      <c r="A81" s="96"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="92"/>
+      <c r="J81" s="94"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="89"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="92"/>
-      <c r="H82" s="92"/>
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="97"/>
+      <c r="E82" s="98"/>
+      <c r="F82" s="98"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="94"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="92"/>
+      <c r="J82" s="94"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="89"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="90"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
+      <c r="A83" s="96"/>
+      <c r="B83" s="97"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="98"/>
+      <c r="F83" s="98"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="94"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="94"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A84" s="82"/>
-      <c r="B84" s="88"/>
+      <c r="B84" s="84"/>
       <c r="C84" s="86"/>
-      <c r="D84" s="88"/>
+      <c r="D84" s="84"/>
       <c r="E84" s="86"/>
       <c r="F84" s="86"/>
-      <c r="G84" s="84"/>
-      <c r="H84" s="84"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="95"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="84"/>
+      <c r="J84" s="95"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="87">
+      <c r="B85" s="83">
         <v>46204</v>
       </c>
       <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="87">
+      <c r="D85" s="83">
         <v>46204</v>
       </c>
       <c r="E85" s="85" t="s">
@@ -16753,44 +16753,44 @@
       <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="83" t="s">
+      <c r="G85" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="83" t="s">
+      <c r="H85" s="93" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="83" t="s">
+      <c r="J85" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A86" s="82"/>
-      <c r="B86" s="88"/>
+      <c r="B86" s="84"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="88"/>
+      <c r="D86" s="84"/>
       <c r="E86" s="86"/>
       <c r="F86" s="86"/>
-      <c r="G86" s="84"/>
-      <c r="H86" s="84"/>
+      <c r="G86" s="95"/>
+      <c r="H86" s="95"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="84"/>
+      <c r="J86" s="95"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="87">
+      <c r="B87" s="83">
         <v>46210</v>
       </c>
       <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="87">
+      <c r="D87" s="83">
         <v>46210</v>
       </c>
       <c r="E87" s="85" t="s">
@@ -16799,32 +16799,32 @@
       <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="83" t="s">
+      <c r="G87" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="83" t="s">
+      <c r="H87" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="83" t="s">
+      <c r="J87" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A88" s="82"/>
-      <c r="B88" s="88"/>
+      <c r="B88" s="84"/>
       <c r="C88" s="86"/>
-      <c r="D88" s="88"/>
+      <c r="D88" s="84"/>
       <c r="E88" s="86"/>
       <c r="F88" s="86"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="95"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="84"/>
+      <c r="J88" s="95"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17433,13 +17433,13 @@
       <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="87">
+      <c r="B108" s="83">
         <v>46231</v>
       </c>
       <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="87">
+      <c r="D108" s="83">
         <v>46231</v>
       </c>
       <c r="E108" s="85" t="s">
@@ -17448,46 +17448,46 @@
       <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="83" t="s">
+      <c r="G108" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="83" t="s">
+      <c r="H108" s="93" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="83" t="s">
+      <c r="J108" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="89"/>
-      <c r="B109" s="90"/>
-      <c r="C109" s="91"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="91"/>
-      <c r="F109" s="91"/>
-      <c r="G109" s="92"/>
-      <c r="H109" s="92"/>
+      <c r="A109" s="96"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="97"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="94"/>
+      <c r="H109" s="94"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="92"/>
+      <c r="J109" s="94"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="82"/>
-      <c r="B110" s="88"/>
+      <c r="B110" s="84"/>
       <c r="C110" s="86"/>
-      <c r="D110" s="88"/>
+      <c r="D110" s="84"/>
       <c r="E110" s="86"/>
       <c r="F110" s="86"/>
-      <c r="G110" s="84"/>
-      <c r="H110" s="84"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="95"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="84"/>
+      <c r="J110" s="95"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17909,13 +17909,13 @@
       <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="87">
+      <c r="B124" s="83">
         <v>46263</v>
       </c>
       <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="87">
+      <c r="D124" s="83">
         <v>46260</v>
       </c>
       <c r="E124" s="85" t="s">
@@ -17924,32 +17924,32 @@
       <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="83" t="s">
+      <c r="G124" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="83" t="s">
+      <c r="H124" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="83" t="s">
+      <c r="J124" s="93" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="82"/>
-      <c r="B125" s="88"/>
+      <c r="B125" s="84"/>
       <c r="C125" s="86"/>
-      <c r="D125" s="88"/>
+      <c r="D125" s="84"/>
       <c r="E125" s="86"/>
       <c r="F125" s="86"/>
-      <c r="G125" s="84"/>
-      <c r="H125" s="84"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="84"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -18960,13 +18960,13 @@
       <c r="A157" s="81">
         <v>129</v>
       </c>
-      <c r="B157" s="87">
+      <c r="B157" s="83">
         <v>46294</v>
       </c>
       <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="87">
+      <c r="D157" s="83">
         <v>46294</v>
       </c>
       <c r="E157" s="85" t="s">
@@ -18975,7 +18975,7 @@
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="83" t="s">
+      <c r="G157" s="93" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -18993,14 +18993,14 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="82"/>
-      <c r="B158" s="88"/>
+      <c r="B158" s="84"/>
       <c r="C158" s="86"/>
-      <c r="D158" s="88"/>
+      <c r="D158" s="84"/>
       <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="84"/>
+      <c r="G158" s="95"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19274,13 +19274,13 @@
       <c r="A167" s="81">
         <v>138</v>
       </c>
-      <c r="B167" s="87">
+      <c r="B167" s="83">
         <v>46300</v>
       </c>
       <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="87">
+      <c r="D167" s="83">
         <v>46295</v>
       </c>
       <c r="E167" s="85" t="s">
@@ -19289,32 +19289,32 @@
       <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="83" t="s">
+      <c r="G167" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="83" t="s">
+      <c r="H167" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="83" t="s">
+      <c r="J167" s="93" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="82"/>
-      <c r="B168" s="88"/>
+      <c r="B168" s="84"/>
       <c r="C168" s="86"/>
-      <c r="D168" s="88"/>
+      <c r="D168" s="84"/>
       <c r="E168" s="86"/>
       <c r="F168" s="86"/>
-      <c r="G168" s="84"/>
-      <c r="H168" s="84"/>
+      <c r="G168" s="95"/>
+      <c r="H168" s="95"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="84"/>
+      <c r="J168" s="95"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -26646,6 +26646,147 @@
     </row>
   </sheetData>
   <mergeCells count="165">
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
@@ -26670,147 +26811,6 @@
     <mergeCell ref="C80:C84"/>
     <mergeCell ref="D80:D84"/>
     <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145154BE-1A3B-4E1E-BB4D-5AA93C87A40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75F9061-EF13-408F-8D58-9DD55942D2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -3354,12 +3354,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3372,28 +3366,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3411,11 +3396,38 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3423,11 +3435,23 @@
     <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3445,30 +3469,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3771,21 +3771,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3818,10 +3818,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3934,46 +3934,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="66">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="63"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4067,30 +4067,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="66">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4101,10 +4101,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4112,54 +4112,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="63"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="66">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="66">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="69"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4167,17 +4167,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4296,25 +4296,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="66">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="66">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4325,13 +4325,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4456,46 +4456,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="66">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="66">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4553,41 +4553,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="66">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="66">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4595,59 +4595,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="66">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="66">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4763,117 +4763,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="66">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="63"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="66">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="63"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="66">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="66">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4899,42 +4899,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="66">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="64">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="66">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="63"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5117,50 +5117,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="66">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="66">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="63"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5459,41 +5459,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="66">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="66">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
+      <c r="F68" s="69"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5502,11 +5502,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
+      <c r="F69" s="69"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5514,17 +5514,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="63"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="63"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5753,39 +5753,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="66">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="66">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="69"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
+      <c r="F80" s="69"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5794,11 +5794,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5807,11 +5807,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
+      <c r="F82" s="69"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5819,17 +5819,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="63"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="63"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5861,22 +5861,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="66">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="66">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="64" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5884,57 +5884,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="67"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="65"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="66">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="66">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="A88" s="63"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="63"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="63"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5966,41 +5966,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="66">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="64">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="66">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6009,11 +6009,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
+      <c r="F92" s="69"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6021,17 +6021,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="65"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="63"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6512,87 +6512,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="66">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="66">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="69"/>
+      <c r="D113" s="70"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="69"/>
+      <c r="D114" s="70"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
+      <c r="F114" s="69"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="67"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="63"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7175,92 +7175,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="66">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="66">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="67"/>
+      <c r="C137" s="65"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="63"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="66">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="66">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="65"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="63"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7583,46 +7583,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="66">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="66">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
-      <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="A151" s="63"/>
+      <c r="B151" s="67"/>
+      <c r="C151" s="65"/>
+      <c r="D151" s="67"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="63"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="63"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7651,41 +7651,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="66">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="66">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
-      <c r="D154" s="69"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="70"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
+      <c r="F154" s="69"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7694,11 +7694,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
-      <c r="D155" s="69"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="70"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
+      <c r="F155" s="69"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7706,17 +7706,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
-      <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="A156" s="63"/>
+      <c r="B156" s="67"/>
+      <c r="C156" s="65"/>
+      <c r="D156" s="67"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="65"/>
+      <c r="G156" s="63"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="63"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7777,41 +7777,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="66">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="66">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="69"/>
+      <c r="B160" s="70"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="70"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
+      <c r="F160" s="69"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7820,11 +7820,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="69"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="70"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
+      <c r="F161" s="69"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7833,11 +7833,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="69"/>
+      <c r="B162" s="70"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="70"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
+      <c r="F162" s="69"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7845,17 +7845,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
-      <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="A163" s="63"/>
+      <c r="B163" s="67"/>
+      <c r="C163" s="65"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="65"/>
+      <c r="G163" s="63"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="63"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8145,46 +8145,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="66">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
-      <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="A175" s="63"/>
+      <c r="B175" s="67"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="63"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="63"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8326,41 +8326,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="66">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="64" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="66">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
-      <c r="D182" s="69"/>
+      <c r="B182" s="70"/>
+      <c r="C182" s="69"/>
+      <c r="D182" s="70"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
+      <c r="F182" s="77"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8369,11 +8369,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
-      <c r="D183" s="69"/>
+      <c r="B183" s="70"/>
+      <c r="C183" s="69"/>
+      <c r="D183" s="70"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
+      <c r="F183" s="77"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8382,11 +8382,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
-      <c r="D184" s="69"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="69"/>
+      <c r="D184" s="70"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
+      <c r="F184" s="77"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8394,59 +8394,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
-      <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="A185" s="63"/>
+      <c r="B185" s="67"/>
+      <c r="C185" s="65"/>
+      <c r="D185" s="67"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="63"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="63"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="66">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="64" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="66">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
-      <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
-      <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="A187" s="63"/>
+      <c r="B187" s="67"/>
+      <c r="C187" s="65"/>
+      <c r="D187" s="67"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="65"/>
+      <c r="G187" s="63"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="63"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9114,31 +9114,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="66">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="64" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="66">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9147,11 +9147,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
-      <c r="D212" s="69"/>
+      <c r="B212" s="70"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
+      <c r="F212" s="69"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9160,11 +9160,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
-      <c r="D213" s="69"/>
+      <c r="B213" s="70"/>
+      <c r="C213" s="69"/>
+      <c r="D213" s="70"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
+      <c r="F213" s="69"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9172,17 +9172,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
-      <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="67"/>
+      <c r="C214" s="65"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="65"/>
+      <c r="G214" s="63"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="63"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9449,46 +9449,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="66">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="64" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="66">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="64" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
-      <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
-      <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="67"/>
+      <c r="C225" s="65"/>
+      <c r="D225" s="67"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="63"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="63"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9520,88 +9520,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="66">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="66">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
-      <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="A228" s="63"/>
+      <c r="B228" s="67"/>
+      <c r="C228" s="65"/>
+      <c r="D228" s="67"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="65"/>
+      <c r="G228" s="63"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="63"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="66">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="66">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
-      <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="A230" s="63"/>
+      <c r="B230" s="67"/>
+      <c r="C230" s="65"/>
+      <c r="D230" s="67"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="65"/>
+      <c r="G230" s="63"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="63"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9662,46 +9662,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="66">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="64" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="66">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
-      <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="A234" s="63"/>
+      <c r="B234" s="67"/>
+      <c r="C234" s="65"/>
+      <c r="D234" s="67"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="65"/>
+      <c r="G234" s="63"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="63"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10342,46 +10342,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="64">
+      <c r="A257" s="62">
         <v>200</v>
       </c>
-      <c r="B257" s="62">
+      <c r="B257" s="66">
         <v>46300</v>
       </c>
-      <c r="C257" s="66" t="s">
+      <c r="C257" s="64" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="62">
+      <c r="D257" s="66">
         <v>46294</v>
       </c>
-      <c r="E257" s="64" t="s">
+      <c r="E257" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="66" t="s">
+      <c r="F257" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="64" t="s">
+      <c r="G257" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="64" t="s">
+      <c r="I257" s="62" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="63"/>
-      <c r="E258" s="65"/>
-      <c r="F258" s="67"/>
-      <c r="G258" s="65"/>
+      <c r="A258" s="63"/>
+      <c r="B258" s="67"/>
+      <c r="C258" s="65"/>
+      <c r="D258" s="67"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="65"/>
+      <c r="G258" s="63"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="65"/>
+      <c r="I258" s="63"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -14080,6 +14080,238 @@
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="I229:I230"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="F233:F234"/>
+    <mergeCell ref="G233:G234"/>
+    <mergeCell ref="I233:I234"/>
+    <mergeCell ref="G229:G230"/>
+    <mergeCell ref="F229:F230"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="G257:G258"/>
     <mergeCell ref="I257:I258"/>
     <mergeCell ref="F257:F258"/>
@@ -14104,238 +14336,6 @@
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="I227:I228"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="F233:F234"/>
-    <mergeCell ref="G233:G234"/>
-    <mergeCell ref="I233:I234"/>
-    <mergeCell ref="G229:G230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14367,23 +14367,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14451,28 +14451,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="62">
         <v>1</v>
       </c>
-      <c r="B4" s="90">
+      <c r="B4" s="98">
         <v>46098</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="98">
         <v>46098</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="64" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14493,13 +14493,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14518,13 +14518,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14542,14 +14542,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14660,50 +14660,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="64">
+      <c r="A11" s="62">
         <v>5</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="93">
         <v>46102</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <v>46095</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="64" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14741,13 +14741,13 @@
       <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="83">
+      <c r="B14" s="87">
         <v>46105</v>
       </c>
       <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="87">
         <v>46105</v>
       </c>
       <c r="E14" s="85" t="s">
@@ -14756,58 +14756,58 @@
       <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="93" t="s">
+      <c r="H14" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="93" t="s">
+      <c r="J14" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="94"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A16" s="82"/>
-      <c r="B16" s="84"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="86"/>
-      <c r="D16" s="84"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="86"/>
       <c r="F16" s="86"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="95"/>
+      <c r="J16" s="84"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="83">
+      <c r="B17" s="87">
         <v>46105</v>
       </c>
       <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="87">
         <v>46105</v>
       </c>
       <c r="E17" s="85" t="s">
@@ -14816,32 +14816,32 @@
       <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="93" t="s">
+      <c r="G17" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="83" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="93" t="s">
+      <c r="J17" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A18" s="82"/>
-      <c r="B18" s="84"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="86"/>
-      <c r="D18" s="84"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="95"/>
+      <c r="J18" s="84"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15167,13 +15167,13 @@
       <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="83">
+      <c r="B29" s="87">
         <v>46121</v>
       </c>
       <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="87">
         <v>46121</v>
       </c>
       <c r="E29" s="85" t="s">
@@ -15182,32 +15182,32 @@
       <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="93" t="s">
+      <c r="G29" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="93" t="s">
+      <c r="H29" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="93" t="s">
+      <c r="J29" s="83" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A30" s="82"/>
-      <c r="B30" s="84"/>
+      <c r="B30" s="88"/>
       <c r="C30" s="86"/>
-      <c r="D30" s="84"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="86"/>
       <c r="F30" s="86"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="95"/>
+      <c r="J30" s="84"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15303,13 +15303,13 @@
       <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="83">
+      <c r="B34" s="87">
         <v>46128</v>
       </c>
       <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="83">
+      <c r="D34" s="87">
         <v>46128</v>
       </c>
       <c r="E34" s="85" t="s">
@@ -15318,44 +15318,44 @@
       <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="93" t="s">
+      <c r="G34" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="93" t="s">
+      <c r="H34" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="93" t="s">
+      <c r="J34" s="83" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A35" s="82"/>
-      <c r="B35" s="84"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="84"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="86"/>
       <c r="F35" s="86"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="95"/>
+      <c r="J35" s="84"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="83">
+      <c r="B36" s="87">
         <v>46132</v>
       </c>
       <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="87">
         <v>46129</v>
       </c>
       <c r="E36" s="85" t="s">
@@ -15364,10 +15364,10 @@
       <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="93" t="s">
+      <c r="G36" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="93" t="s">
+      <c r="H36" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15379,13 +15379,13 @@
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A37" s="82"/>
-      <c r="B37" s="84"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="84"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="86"/>
       <c r="F37" s="86"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15491,13 +15491,13 @@
       <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="83">
+      <c r="B41" s="87">
         <v>46139</v>
       </c>
       <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="83">
+      <c r="D41" s="87">
         <v>46139</v>
       </c>
       <c r="E41" s="85" t="s">
@@ -15506,32 +15506,32 @@
       <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="93" t="s">
+      <c r="G41" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="93" t="s">
+      <c r="H41" s="83" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="93" t="s">
+      <c r="J41" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A42" s="82"/>
-      <c r="B42" s="84"/>
+      <c r="B42" s="88"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="84"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="86"/>
       <c r="F42" s="86"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="95"/>
+      <c r="J42" s="84"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15665,13 +15665,13 @@
       <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="83">
+      <c r="B47" s="87">
         <v>46149</v>
       </c>
       <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="83">
+      <c r="D47" s="87">
         <v>46148</v>
       </c>
       <c r="E47" s="85" t="s">
@@ -15680,10 +15680,10 @@
       <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="93" t="s">
+      <c r="G47" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="93" t="s">
+      <c r="H47" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15695,13 +15695,13 @@
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A48" s="82"/>
-      <c r="B48" s="84"/>
+      <c r="B48" s="88"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="84"/>
+      <c r="D48" s="88"/>
       <c r="E48" s="86"/>
       <c r="F48" s="86"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="95"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15713,13 +15713,13 @@
       <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="83">
+      <c r="B49" s="87">
         <v>46149</v>
       </c>
       <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="83">
+      <c r="D49" s="87">
         <v>46148</v>
       </c>
       <c r="E49" s="85" t="s">
@@ -15728,10 +15728,10 @@
       <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="93" t="s">
+      <c r="G49" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="93" t="s">
+      <c r="H49" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15743,13 +15743,13 @@
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A50" s="82"/>
-      <c r="B50" s="84"/>
+      <c r="B50" s="88"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="84"/>
+      <c r="D50" s="88"/>
       <c r="E50" s="86"/>
       <c r="F50" s="86"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="95"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16049,13 +16049,13 @@
       <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="83">
+      <c r="B60" s="87">
         <v>46169</v>
       </c>
       <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="83">
+      <c r="D60" s="87">
         <v>46169</v>
       </c>
       <c r="E60" s="85" t="s">
@@ -16064,32 +16064,32 @@
       <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="93" t="s">
+      <c r="G60" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="93" t="s">
+      <c r="H60" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="93" t="s">
+      <c r="J60" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A61" s="82"/>
-      <c r="B61" s="84"/>
+      <c r="B61" s="88"/>
       <c r="C61" s="86"/>
-      <c r="D61" s="84"/>
+      <c r="D61" s="88"/>
       <c r="E61" s="86"/>
       <c r="F61" s="86"/>
-      <c r="G61" s="95"/>
-      <c r="H61" s="95"/>
+      <c r="G61" s="84"/>
+      <c r="H61" s="84"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="95"/>
+      <c r="J61" s="84"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16412,13 +16412,13 @@
       <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="83">
+      <c r="B72" s="87">
         <v>46192</v>
       </c>
       <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="83">
+      <c r="D72" s="87">
         <v>46191</v>
       </c>
       <c r="E72" s="85" t="s">
@@ -16427,32 +16427,32 @@
       <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="93" t="s">
+      <c r="G72" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="93" t="s">
+      <c r="H72" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="93" t="s">
+      <c r="J72" s="83" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A73" s="82"/>
-      <c r="B73" s="84"/>
+      <c r="B73" s="88"/>
       <c r="C73" s="86"/>
-      <c r="D73" s="84"/>
+      <c r="D73" s="88"/>
       <c r="E73" s="86"/>
       <c r="F73" s="86"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
+      <c r="G73" s="84"/>
+      <c r="H73" s="84"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="95"/>
+      <c r="J73" s="84"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16650,13 +16650,13 @@
       <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="83">
+      <c r="B80" s="87">
         <v>46200</v>
       </c>
       <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="83">
+      <c r="D80" s="87">
         <v>46200</v>
       </c>
       <c r="E80" s="85" t="s">
@@ -16665,86 +16665,86 @@
       <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="93" t="s">
+      <c r="G80" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="93" t="s">
+      <c r="H80" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="93" t="s">
+      <c r="J80" s="83" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="96"/>
-      <c r="B81" s="97"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
+      <c r="A81" s="89"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="90"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="94"/>
+      <c r="J81" s="92"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="96"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="98"/>
-      <c r="D82" s="97"/>
-      <c r="E82" s="98"/>
-      <c r="F82" s="98"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="94"/>
+      <c r="A82" s="89"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="91"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="94"/>
+      <c r="J82" s="92"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="96"/>
-      <c r="B83" s="97"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="97"/>
-      <c r="E83" s="98"/>
-      <c r="F83" s="98"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="94"/>
+      <c r="A83" s="89"/>
+      <c r="B83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="90"/>
+      <c r="E83" s="91"/>
+      <c r="F83" s="91"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="94"/>
+      <c r="J83" s="92"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A84" s="82"/>
-      <c r="B84" s="84"/>
+      <c r="B84" s="88"/>
       <c r="C84" s="86"/>
-      <c r="D84" s="84"/>
+      <c r="D84" s="88"/>
       <c r="E84" s="86"/>
       <c r="F84" s="86"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="95"/>
+      <c r="G84" s="84"/>
+      <c r="H84" s="84"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="95"/>
+      <c r="J84" s="84"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="83">
+      <c r="B85" s="87">
         <v>46204</v>
       </c>
       <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="83">
+      <c r="D85" s="87">
         <v>46204</v>
       </c>
       <c r="E85" s="85" t="s">
@@ -16753,44 +16753,44 @@
       <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="93" t="s">
+      <c r="G85" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="93" t="s">
+      <c r="H85" s="83" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="93" t="s">
+      <c r="J85" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A86" s="82"/>
-      <c r="B86" s="84"/>
+      <c r="B86" s="88"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="84"/>
+      <c r="D86" s="88"/>
       <c r="E86" s="86"/>
       <c r="F86" s="86"/>
-      <c r="G86" s="95"/>
-      <c r="H86" s="95"/>
+      <c r="G86" s="84"/>
+      <c r="H86" s="84"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="95"/>
+      <c r="J86" s="84"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="83">
+      <c r="B87" s="87">
         <v>46210</v>
       </c>
       <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="83">
+      <c r="D87" s="87">
         <v>46210</v>
       </c>
       <c r="E87" s="85" t="s">
@@ -16799,32 +16799,32 @@
       <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="93" t="s">
+      <c r="G87" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="93" t="s">
+      <c r="H87" s="83" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="93" t="s">
+      <c r="J87" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A88" s="82"/>
-      <c r="B88" s="84"/>
+      <c r="B88" s="88"/>
       <c r="C88" s="86"/>
-      <c r="D88" s="84"/>
+      <c r="D88" s="88"/>
       <c r="E88" s="86"/>
       <c r="F88" s="86"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="95"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="95"/>
+      <c r="J88" s="84"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17433,13 +17433,13 @@
       <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="83">
+      <c r="B108" s="87">
         <v>46231</v>
       </c>
       <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="83">
+      <c r="D108" s="87">
         <v>46231</v>
       </c>
       <c r="E108" s="85" t="s">
@@ -17448,46 +17448,46 @@
       <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="93" t="s">
+      <c r="G108" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="93" t="s">
+      <c r="H108" s="83" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="93" t="s">
+      <c r="J108" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="96"/>
-      <c r="B109" s="97"/>
-      <c r="C109" s="98"/>
-      <c r="D109" s="97"/>
-      <c r="E109" s="98"/>
-      <c r="F109" s="98"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="94"/>
+      <c r="A109" s="89"/>
+      <c r="B109" s="90"/>
+      <c r="C109" s="91"/>
+      <c r="D109" s="90"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="92"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="94"/>
+      <c r="J109" s="92"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="82"/>
-      <c r="B110" s="84"/>
+      <c r="B110" s="88"/>
       <c r="C110" s="86"/>
-      <c r="D110" s="84"/>
+      <c r="D110" s="88"/>
       <c r="E110" s="86"/>
       <c r="F110" s="86"/>
-      <c r="G110" s="95"/>
-      <c r="H110" s="95"/>
+      <c r="G110" s="84"/>
+      <c r="H110" s="84"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="95"/>
+      <c r="J110" s="84"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17909,13 +17909,13 @@
       <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="83">
+      <c r="B124" s="87">
         <v>46263</v>
       </c>
       <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="83">
+      <c r="D124" s="87">
         <v>46260</v>
       </c>
       <c r="E124" s="85" t="s">
@@ -17924,32 +17924,32 @@
       <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="93" t="s">
+      <c r="G124" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="93" t="s">
+      <c r="H124" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="93" t="s">
+      <c r="J124" s="83" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="82"/>
-      <c r="B125" s="84"/>
+      <c r="B125" s="88"/>
       <c r="C125" s="86"/>
-      <c r="D125" s="84"/>
+      <c r="D125" s="88"/>
       <c r="E125" s="86"/>
       <c r="F125" s="86"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
+      <c r="G125" s="84"/>
+      <c r="H125" s="84"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="95"/>
+      <c r="J125" s="84"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -17984,7 +17984,9 @@
       </c>
     </row>
     <row r="127" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A127" s="26"/>
+      <c r="A127" s="26">
+        <v>100</v>
+      </c>
       <c r="B127" s="52">
         <v>46265</v>
       </c>
@@ -18015,7 +18017,7 @@
     </row>
     <row r="128" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A128" s="26">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B128" s="52">
         <v>46265</v>
@@ -18047,7 +18049,7 @@
     </row>
     <row r="129" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A129" s="26">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B129" s="52">
         <v>46267</v>
@@ -18079,7 +18081,7 @@
     </row>
     <row r="130" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A130" s="26">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B130" s="52">
         <v>46267</v>
@@ -18111,7 +18113,7 @@
     </row>
     <row r="131" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A131" s="26">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B131" s="52">
         <v>46268</v>
@@ -18140,7 +18142,7 @@
     </row>
     <row r="132" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A132" s="26">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B132" s="52">
         <v>46268</v>
@@ -18172,7 +18174,7 @@
     </row>
     <row r="133" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A133" s="26">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B133" s="52">
         <v>46268</v>
@@ -18204,7 +18206,7 @@
     </row>
     <row r="134" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A134" s="26">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B134" s="52">
         <v>46269</v>
@@ -18236,7 +18238,7 @@
     </row>
     <row r="135" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A135" s="26">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B135" s="43" t="s">
         <v>803</v>
@@ -18268,7 +18270,7 @@
     </row>
     <row r="136" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A136" s="26">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B136" s="52">
         <v>46272</v>
@@ -18300,7 +18302,7 @@
     </row>
     <row r="137" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A137" s="26">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B137" s="52">
         <v>46273</v>
@@ -18335,7 +18337,7 @@
     </row>
     <row r="138" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A138" s="26">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B138" s="52">
         <v>46276</v>
@@ -18370,7 +18372,7 @@
     </row>
     <row r="139" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A139" s="26">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B139" s="52">
         <v>46276</v>
@@ -18405,7 +18407,7 @@
     </row>
     <row r="140" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A140" s="26">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B140" s="52">
         <v>46280</v>
@@ -18440,7 +18442,7 @@
     </row>
     <row r="141" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A141" s="26">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B141" s="52">
         <v>46281</v>
@@ -18475,7 +18477,7 @@
     </row>
     <row r="142" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A142" s="26">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B142" s="52">
         <v>46282</v>
@@ -18510,7 +18512,7 @@
     </row>
     <row r="143" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A143" s="26">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B143" s="52">
         <v>46283</v>
@@ -18542,7 +18544,7 @@
     </row>
     <row r="144" spans="1:14" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A144" s="26">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B144" s="52">
         <v>46286</v>
@@ -18574,7 +18576,7 @@
     </row>
     <row r="145" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A145" s="26">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B145" s="52">
         <v>46287</v>
@@ -18603,7 +18605,7 @@
     </row>
     <row r="146" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A146" s="26">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B146" s="52">
         <v>46287</v>
@@ -18635,7 +18637,7 @@
     </row>
     <row r="147" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A147" s="26">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B147" s="52">
         <v>46287</v>
@@ -18667,7 +18669,7 @@
     </row>
     <row r="148" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A148" s="26">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B148" s="52">
         <v>46287</v>
@@ -18699,7 +18701,7 @@
     </row>
     <row r="149" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A149" s="26">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B149" s="52">
         <v>46287</v>
@@ -18731,7 +18733,7 @@
     </row>
     <row r="150" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A150" s="26">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B150" s="43" t="s">
         <v>872</v>
@@ -18763,7 +18765,7 @@
     </row>
     <row r="151" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A151" s="26">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B151" s="52">
         <v>46291</v>
@@ -18795,7 +18797,7 @@
     </row>
     <row r="152" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A152" s="26">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B152" s="43" t="s">
         <v>884</v>
@@ -18830,7 +18832,7 @@
     </row>
     <row r="153" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A153" s="26">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B153" s="52">
         <v>46291</v>
@@ -18862,7 +18864,7 @@
     </row>
     <row r="154" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A154" s="26">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B154" s="52">
         <v>46293</v>
@@ -18894,7 +18896,7 @@
     </row>
     <row r="155" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A155" s="26">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B155" s="52">
         <v>46293</v>
@@ -18926,7 +18928,7 @@
     </row>
     <row r="156" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A156" s="26">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B156" s="52">
         <v>46294</v>
@@ -18958,15 +18960,15 @@
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A157" s="81">
-        <v>129</v>
-      </c>
-      <c r="B157" s="83">
+        <v>130</v>
+      </c>
+      <c r="B157" s="87">
         <v>46294</v>
       </c>
       <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="83">
+      <c r="D157" s="87">
         <v>46294</v>
       </c>
       <c r="E157" s="85" t="s">
@@ -18975,7 +18977,7 @@
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="93" t="s">
+      <c r="G157" s="83" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -18993,14 +18995,14 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="82"/>
-      <c r="B158" s="84"/>
+      <c r="B158" s="88"/>
       <c r="C158" s="86"/>
-      <c r="D158" s="84"/>
+      <c r="D158" s="88"/>
       <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="95"/>
+      <c r="G158" s="84"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19013,7 +19015,7 @@
     </row>
     <row r="159" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A159" s="26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B159" s="52">
         <v>46294</v>
@@ -19045,7 +19047,7 @@
     </row>
     <row r="160" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A160" s="26">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B160" s="52">
         <v>46295</v>
@@ -19077,7 +19079,7 @@
     </row>
     <row r="161" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A161" s="26">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B161" s="52">
         <v>46296</v>
@@ -19112,7 +19114,7 @@
     </row>
     <row r="162" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A162" s="26">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B162" s="52">
         <v>46296</v>
@@ -19144,7 +19146,7 @@
     </row>
     <row r="163" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A163" s="26">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B163" s="52">
         <v>46296</v>
@@ -19176,7 +19178,7 @@
     </row>
     <row r="164" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A164" s="26">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B164" s="52">
         <v>46297</v>
@@ -19208,7 +19210,7 @@
     </row>
     <row r="165" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A165" s="26">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B165" s="52">
         <v>46297</v>
@@ -19240,7 +19242,7 @@
     </row>
     <row r="166" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A166" s="26">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B166" s="52">
         <v>46300</v>
@@ -19272,15 +19274,15 @@
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A167" s="81">
-        <v>138</v>
-      </c>
-      <c r="B167" s="83">
+        <v>139</v>
+      </c>
+      <c r="B167" s="87">
         <v>46300</v>
       </c>
       <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="83">
+      <c r="D167" s="87">
         <v>46295</v>
       </c>
       <c r="E167" s="85" t="s">
@@ -19289,36 +19291,36 @@
       <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="93" t="s">
+      <c r="G167" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="93" t="s">
+      <c r="H167" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="93" t="s">
+      <c r="J167" s="83" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="82"/>
-      <c r="B168" s="84"/>
+      <c r="B168" s="88"/>
       <c r="C168" s="86"/>
-      <c r="D168" s="84"/>
+      <c r="D168" s="88"/>
       <c r="E168" s="86"/>
       <c r="F168" s="86"/>
-      <c r="G168" s="95"/>
-      <c r="H168" s="95"/>
+      <c r="G168" s="84"/>
+      <c r="H168" s="84"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="95"/>
+      <c r="J168" s="84"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B169" s="43"/>
       <c r="D169" s="43"/>
@@ -26646,90 +26648,63 @@
     </row>
   </sheetData>
   <mergeCells count="165">
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="J17:J18"/>
@@ -26754,63 +26729,90 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75F9061-EF13-408F-8D58-9DD55942D2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C714CCC-E4E7-49D5-B23A-D4D4D0C461F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="953">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2850,6 +2850,36 @@
   </si>
   <si>
     <t>HeatSkin- Qty 4 Nos.</t>
+  </si>
+  <si>
+    <t>AM/DOM/0016/2627</t>
+  </si>
+  <si>
+    <t>System Pack Bottle With Cap 20ml (Brown Bottle Blue Cap)- Qty 3000</t>
+  </si>
+  <si>
+    <t>60 Box</t>
+  </si>
+  <si>
+    <t>70ml System Pack Natural White Bottle With White Cap- Qty 20000- 40 Box</t>
+  </si>
+  <si>
+    <t>20ml System Pack Natural White Bottle With Red Cap- qty 20000- 20 Box</t>
+  </si>
+  <si>
+    <t>AM/PP/0040/2627</t>
+  </si>
+  <si>
+    <t>017/2627</t>
+  </si>
+  <si>
+    <t>20ml Natural Trans Bottle With Red Cap-Qty 20000- 20 Box / 70ml Natural Trans Bottle With White Cap - Qty 20000- 40 Box</t>
+  </si>
+  <si>
+    <t>20ml  Natural Trans Brown Bottle With Blue Cap - Qty 3000 Nos.- 3 Box</t>
+  </si>
+  <si>
+    <t>63 Box</t>
   </si>
 </sst>
 </file>
@@ -3354,6 +3384,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3366,19 +3402,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3396,31 +3441,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3428,30 +3458,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3469,6 +3475,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3771,21 +3801,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3818,10 +3848,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3934,46 +3964,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="63"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="63"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4067,30 +4097,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4101,10 +4131,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4112,54 +4142,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="63"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="63"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="66">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4167,17 +4197,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="63"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="63"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4296,25 +4326,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="66">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4325,13 +4355,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="63"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="63"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4456,46 +4486,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="66">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="63"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="63"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4553,41 +4583,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="66">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="70"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="69"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4595,59 +4625,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="63"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="66">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="63"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="63"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4763,117 +4793,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="66">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="64" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="63"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="63"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="66">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="64" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="63"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="63"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="66">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="66">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="64" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4884,13 +4914,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="63"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="63"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4899,42 +4929,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="66">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="66">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="63"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="67"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="63"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="63"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="63"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5117,50 +5147,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="66">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="66">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="63"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="63"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="63"/>
-      <c r="J56" s="63"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5459,41 +5489,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="66">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="66">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="64" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="70"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="69"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5502,11 +5532,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5514,17 +5544,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="63"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="63"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="63"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="63"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5753,39 +5783,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="66">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="66">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="64" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="70"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="69"/>
+      <c r="F80" s="70"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5794,11 +5824,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="70"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5807,11 +5837,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="70"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="69"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
+      <c r="F82" s="70"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5819,17 +5849,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="63"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="63"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="63"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5861,22 +5891,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="66">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="64" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="66">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="64" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5884,57 +5914,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="63"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="65"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="66">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="64" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="66">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="64" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="63"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="65"/>
-      <c r="G88" s="63"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="63"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5966,41 +5996,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="66">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="64">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="66">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="64" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="69"/>
-      <c r="D91" s="70"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="69"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6009,11 +6039,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="70"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="70"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="69"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="69"/>
+      <c r="F92" s="70"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6021,17 +6051,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="63"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="65"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="63"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="63"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6512,87 +6542,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="66">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="66">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="64" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="76" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="70"/>
+      <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="69"/>
+      <c r="F112" s="70"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="77"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="70"/>
+      <c r="B113" s="69"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="70"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="69"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="77"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="70"/>
+      <c r="B114" s="69"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="70"/>
+      <c r="D114" s="69"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="69"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="77"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="63"/>
-      <c r="B115" s="67"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="63"/>
-      <c r="F115" s="65"/>
-      <c r="G115" s="63"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="67"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="78"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7175,92 +7205,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="66">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="64" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="66">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="64" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="63"/>
-      <c r="B137" s="67"/>
-      <c r="C137" s="65"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="65"/>
-      <c r="G137" s="63"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
+      <c r="C137" s="67"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
+      <c r="F137" s="67"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="63"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="66">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="64" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="66">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="64" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="63"/>
-      <c r="B139" s="67"/>
-      <c r="C139" s="65"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="63"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="63"/>
-      <c r="J139" s="63"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7583,46 +7613,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="66">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="64" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="66">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="64" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="63"/>
-      <c r="B151" s="67"/>
-      <c r="C151" s="65"/>
-      <c r="D151" s="67"/>
-      <c r="E151" s="63"/>
-      <c r="F151" s="65"/>
-      <c r="G151" s="63"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
+      <c r="F151" s="67"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="63"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7651,41 +7681,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="66">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="64" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="66">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="64" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="69"/>
-      <c r="D154" s="70"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="69"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="69"/>
+      <c r="F154" s="70"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7694,11 +7724,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="70"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="70"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="69"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="69"/>
+      <c r="F155" s="70"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7706,17 +7736,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="63"/>
-      <c r="B156" s="67"/>
-      <c r="C156" s="65"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="63"/>
-      <c r="F156" s="65"/>
-      <c r="G156" s="63"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="67"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="63"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7777,41 +7807,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="66">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="64" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="66">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="64" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="70"/>
-      <c r="C160" s="69"/>
-      <c r="D160" s="70"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="69"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="69"/>
+      <c r="F160" s="70"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7820,11 +7850,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="70"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="70"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="69"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="69"/>
+      <c r="F161" s="70"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7833,11 +7863,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="70"/>
-      <c r="C162" s="69"/>
-      <c r="D162" s="70"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="70"/>
+      <c r="D162" s="69"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="69"/>
+      <c r="F162" s="70"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7845,17 +7875,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="63"/>
-      <c r="B163" s="67"/>
-      <c r="C163" s="65"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="65"/>
-      <c r="G163" s="63"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
+      <c r="F163" s="67"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="63"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8145,46 +8175,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="66">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="64" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="79">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="64" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="63"/>
-      <c r="B175" s="67"/>
-      <c r="C175" s="65"/>
-      <c r="D175" s="80"/>
-      <c r="E175" s="63"/>
-      <c r="F175" s="65"/>
-      <c r="G175" s="63"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="67"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="63"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8326,41 +8356,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="66">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="64" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="66">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="76" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="70"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="70"/>
+      <c r="B182" s="69"/>
+      <c r="C182" s="70"/>
+      <c r="D182" s="69"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="77"/>
+      <c r="F182" s="72"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8369,11 +8399,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="70"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="70"/>
+      <c r="B183" s="69"/>
+      <c r="C183" s="70"/>
+      <c r="D183" s="69"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="77"/>
+      <c r="F183" s="72"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8382,11 +8412,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="70"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="70"/>
+      <c r="B184" s="69"/>
+      <c r="C184" s="70"/>
+      <c r="D184" s="69"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="77"/>
+      <c r="F184" s="72"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8394,59 +8424,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="63"/>
-      <c r="B185" s="67"/>
-      <c r="C185" s="65"/>
-      <c r="D185" s="67"/>
-      <c r="E185" s="63"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="63"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
+      <c r="C185" s="67"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="63"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="66">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="64" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="66">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="64" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="63"/>
-      <c r="B187" s="67"/>
-      <c r="C187" s="65"/>
-      <c r="D187" s="67"/>
-      <c r="E187" s="63"/>
-      <c r="F187" s="65"/>
-      <c r="G187" s="63"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
+      <c r="F187" s="67"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="63"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9114,31 +9144,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="66">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="64" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="66">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="64" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9147,11 +9177,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="70"/>
-      <c r="C212" s="69"/>
-      <c r="D212" s="70"/>
+      <c r="B212" s="69"/>
+      <c r="C212" s="70"/>
+      <c r="D212" s="69"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="69"/>
+      <c r="F212" s="70"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9160,11 +9190,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="70"/>
-      <c r="C213" s="69"/>
-      <c r="D213" s="70"/>
+      <c r="B213" s="69"/>
+      <c r="C213" s="70"/>
+      <c r="D213" s="69"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="69"/>
+      <c r="F213" s="70"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9172,17 +9202,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="63"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="65"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="63"/>
-      <c r="F214" s="65"/>
-      <c r="G214" s="63"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
+      <c r="C214" s="67"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
+      <c r="F214" s="67"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="63"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9449,46 +9479,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="66">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="64" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="66">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="64" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="63"/>
-      <c r="B225" s="67"/>
-      <c r="C225" s="65"/>
-      <c r="D225" s="67"/>
-      <c r="E225" s="63"/>
-      <c r="F225" s="65"/>
-      <c r="G225" s="63"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
+      <c r="C225" s="67"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
+      <c r="F225" s="67"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="63"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9520,88 +9550,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="66">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="64" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="66">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="64" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="63"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="65"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="63"/>
-      <c r="F228" s="65"/>
-      <c r="G228" s="63"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
+      <c r="C228" s="67"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
+      <c r="F228" s="67"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="63"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="66">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="64" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="66">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="64" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="63"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="65"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="63"/>
-      <c r="F230" s="65"/>
-      <c r="G230" s="63"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
+      <c r="C230" s="67"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
+      <c r="F230" s="67"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="63"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9662,46 +9692,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="66">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="64" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="66">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="64" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="63"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="65"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="63"/>
-      <c r="F234" s="65"/>
-      <c r="G234" s="63"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
+      <c r="F234" s="67"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="63"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10342,46 +10372,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="62">
+      <c r="A257" s="64">
         <v>200</v>
       </c>
-      <c r="B257" s="66">
+      <c r="B257" s="62">
         <v>46300</v>
       </c>
-      <c r="C257" s="64" t="s">
+      <c r="C257" s="66" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="66">
+      <c r="D257" s="62">
         <v>46294</v>
       </c>
-      <c r="E257" s="62" t="s">
+      <c r="E257" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="64" t="s">
+      <c r="F257" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="62" t="s">
+      <c r="G257" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="62" t="s">
+      <c r="I257" s="64" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="63"/>
-      <c r="B258" s="67"/>
-      <c r="C258" s="65"/>
-      <c r="D258" s="67"/>
-      <c r="E258" s="63"/>
-      <c r="F258" s="65"/>
-      <c r="G258" s="63"/>
+      <c r="A258" s="65"/>
+      <c r="B258" s="63"/>
+      <c r="C258" s="67"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="65"/>
+      <c r="F258" s="67"/>
+      <c r="G258" s="65"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="63"/>
+      <c r="I258" s="65"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10474,14 +10504,37 @@
       <c r="A262" s="21">
         <v>204</v>
       </c>
-      <c r="C262" s="46"/>
-      <c r="F262" s="46"/>
-      <c r="H262" s="34"/>
+      <c r="B262" s="25">
+        <v>46301</v>
+      </c>
+      <c r="C262" s="46" t="s">
+        <v>949</v>
+      </c>
+      <c r="D262" s="25">
+        <v>46301</v>
+      </c>
+      <c r="E262" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="F262" s="46" t="s">
+        <v>926</v>
+      </c>
+      <c r="G262" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H262" s="34" t="s">
+        <v>950</v>
+      </c>
+      <c r="I262" s="21" t="s">
+        <v>952</v>
+      </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C263" s="46"/>
       <c r="F263" s="46"/>
-      <c r="H263" s="34"/>
+      <c r="H263" s="34" t="s">
+        <v>951</v>
+      </c>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C264" s="46"/>
@@ -14080,238 +14133,6 @@
     </row>
   </sheetData>
   <mergeCells count="256">
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="I227:I228"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="F233:F234"/>
-    <mergeCell ref="G233:G234"/>
-    <mergeCell ref="I233:I234"/>
-    <mergeCell ref="G229:G230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
     <mergeCell ref="G257:G258"/>
     <mergeCell ref="I257:I258"/>
     <mergeCell ref="F257:F258"/>
@@ -14336,6 +14157,238 @@
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="I229:I230"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="F233:F234"/>
+    <mergeCell ref="G233:G234"/>
+    <mergeCell ref="I233:I234"/>
+    <mergeCell ref="G229:G230"/>
+    <mergeCell ref="F229:F230"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14367,23 +14420,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14451,28 +14504,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="90">
         <v>46098</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="90">
         <v>46098</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14493,13 +14546,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14518,13 +14571,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14542,14 +14595,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14660,50 +14713,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="64" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="65"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14741,13 +14794,13 @@
       <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="87">
+      <c r="B14" s="83">
         <v>46105</v>
       </c>
       <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="87">
+      <c r="D14" s="83">
         <v>46105</v>
       </c>
       <c r="E14" s="85" t="s">
@@ -14756,58 +14809,58 @@
       <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="83" t="s">
+      <c r="G14" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="83" t="s">
+      <c r="H14" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="83" t="s">
+      <c r="J14" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A16" s="82"/>
-      <c r="B16" s="88"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="86"/>
-      <c r="D16" s="88"/>
+      <c r="D16" s="84"/>
       <c r="E16" s="86"/>
       <c r="F16" s="86"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="84"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="87">
+      <c r="B17" s="83">
         <v>46105</v>
       </c>
       <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="87">
+      <c r="D17" s="83">
         <v>46105</v>
       </c>
       <c r="E17" s="85" t="s">
@@ -14816,32 +14869,32 @@
       <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="83" t="s">
+      <c r="J17" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A18" s="82"/>
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="86"/>
-      <c r="D18" s="88"/>
+      <c r="D18" s="84"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="84"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15167,13 +15220,13 @@
       <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="87">
+      <c r="B29" s="83">
         <v>46121</v>
       </c>
       <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="87">
+      <c r="D29" s="83">
         <v>46121</v>
       </c>
       <c r="E29" s="85" t="s">
@@ -15182,32 +15235,32 @@
       <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="83" t="s">
+      <c r="G29" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="83" t="s">
+      <c r="H29" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="93" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A30" s="82"/>
-      <c r="B30" s="88"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="86"/>
-      <c r="D30" s="88"/>
+      <c r="D30" s="84"/>
       <c r="E30" s="86"/>
       <c r="F30" s="86"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="84"/>
+      <c r="J30" s="95"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15303,13 +15356,13 @@
       <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="87">
+      <c r="B34" s="83">
         <v>46128</v>
       </c>
       <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="87">
+      <c r="D34" s="83">
         <v>46128</v>
       </c>
       <c r="E34" s="85" t="s">
@@ -15318,44 +15371,44 @@
       <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="83" t="s">
+      <c r="G34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="83" t="s">
+      <c r="H34" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="93" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A35" s="82"/>
-      <c r="B35" s="88"/>
+      <c r="B35" s="84"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="88"/>
+      <c r="D35" s="84"/>
       <c r="E35" s="86"/>
       <c r="F35" s="86"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="84"/>
+      <c r="J35" s="95"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="87">
+      <c r="B36" s="83">
         <v>46132</v>
       </c>
       <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="87">
+      <c r="D36" s="83">
         <v>46129</v>
       </c>
       <c r="E36" s="85" t="s">
@@ -15364,10 +15417,10 @@
       <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="83" t="s">
+      <c r="G36" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="83" t="s">
+      <c r="H36" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15379,13 +15432,13 @@
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A37" s="82"/>
-      <c r="B37" s="88"/>
+      <c r="B37" s="84"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="88"/>
+      <c r="D37" s="84"/>
       <c r="E37" s="86"/>
       <c r="F37" s="86"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15491,13 +15544,13 @@
       <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="87">
+      <c r="B41" s="83">
         <v>46139</v>
       </c>
       <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="87">
+      <c r="D41" s="83">
         <v>46139</v>
       </c>
       <c r="E41" s="85" t="s">
@@ -15506,32 +15559,32 @@
       <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="83" t="s">
+      <c r="G41" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="83" t="s">
+      <c r="H41" s="93" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="83" t="s">
+      <c r="J41" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A42" s="82"/>
-      <c r="B42" s="88"/>
+      <c r="B42" s="84"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="88"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="86"/>
       <c r="F42" s="86"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="84"/>
+      <c r="J42" s="95"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15665,13 +15718,13 @@
       <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="87">
+      <c r="B47" s="83">
         <v>46149</v>
       </c>
       <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="87">
+      <c r="D47" s="83">
         <v>46148</v>
       </c>
       <c r="E47" s="85" t="s">
@@ -15680,10 +15733,10 @@
       <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="83" t="s">
+      <c r="G47" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="83" t="s">
+      <c r="H47" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15695,13 +15748,13 @@
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A48" s="82"/>
-      <c r="B48" s="88"/>
+      <c r="B48" s="84"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="88"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="86"/>
       <c r="F48" s="86"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15713,13 +15766,13 @@
       <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="87">
+      <c r="B49" s="83">
         <v>46149</v>
       </c>
       <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="87">
+      <c r="D49" s="83">
         <v>46148</v>
       </c>
       <c r="E49" s="85" t="s">
@@ -15728,10 +15781,10 @@
       <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="83" t="s">
+      <c r="G49" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="83" t="s">
+      <c r="H49" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15743,13 +15796,13 @@
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A50" s="82"/>
-      <c r="B50" s="88"/>
+      <c r="B50" s="84"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="88"/>
+      <c r="D50" s="84"/>
       <c r="E50" s="86"/>
       <c r="F50" s="86"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16049,13 +16102,13 @@
       <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="87">
+      <c r="B60" s="83">
         <v>46169</v>
       </c>
       <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="87">
+      <c r="D60" s="83">
         <v>46169</v>
       </c>
       <c r="E60" s="85" t="s">
@@ -16064,32 +16117,32 @@
       <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="83" t="s">
+      <c r="G60" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="83" t="s">
+      <c r="H60" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="83" t="s">
+      <c r="J60" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A61" s="82"/>
-      <c r="B61" s="88"/>
+      <c r="B61" s="84"/>
       <c r="C61" s="86"/>
-      <c r="D61" s="88"/>
+      <c r="D61" s="84"/>
       <c r="E61" s="86"/>
       <c r="F61" s="86"/>
-      <c r="G61" s="84"/>
-      <c r="H61" s="84"/>
+      <c r="G61" s="95"/>
+      <c r="H61" s="95"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="84"/>
+      <c r="J61" s="95"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16412,13 +16465,13 @@
       <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="87">
+      <c r="B72" s="83">
         <v>46192</v>
       </c>
       <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="87">
+      <c r="D72" s="83">
         <v>46191</v>
       </c>
       <c r="E72" s="85" t="s">
@@ -16427,32 +16480,32 @@
       <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="83" t="s">
+      <c r="G72" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="83" t="s">
+      <c r="H72" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="83" t="s">
+      <c r="J72" s="93" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A73" s="82"/>
-      <c r="B73" s="88"/>
+      <c r="B73" s="84"/>
       <c r="C73" s="86"/>
-      <c r="D73" s="88"/>
+      <c r="D73" s="84"/>
       <c r="E73" s="86"/>
       <c r="F73" s="86"/>
-      <c r="G73" s="84"/>
-      <c r="H73" s="84"/>
+      <c r="G73" s="95"/>
+      <c r="H73" s="95"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="84"/>
+      <c r="J73" s="95"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16650,13 +16703,13 @@
       <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="87">
+      <c r="B80" s="83">
         <v>46200</v>
       </c>
       <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="87">
+      <c r="D80" s="83">
         <v>46200</v>
       </c>
       <c r="E80" s="85" t="s">
@@ -16665,86 +16718,86 @@
       <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="83" t="s">
+      <c r="G80" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="83" t="s">
+      <c r="H80" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="83" t="s">
+      <c r="J80" s="93" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="89"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="90"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
+      <c r="A81" s="96"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="92"/>
+      <c r="J81" s="94"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="89"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="92"/>
-      <c r="H82" s="92"/>
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="97"/>
+      <c r="E82" s="98"/>
+      <c r="F82" s="98"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="94"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="92"/>
+      <c r="J82" s="94"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="89"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="90"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
+      <c r="A83" s="96"/>
+      <c r="B83" s="97"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="98"/>
+      <c r="F83" s="98"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="94"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="94"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A84" s="82"/>
-      <c r="B84" s="88"/>
+      <c r="B84" s="84"/>
       <c r="C84" s="86"/>
-      <c r="D84" s="88"/>
+      <c r="D84" s="84"/>
       <c r="E84" s="86"/>
       <c r="F84" s="86"/>
-      <c r="G84" s="84"/>
-      <c r="H84" s="84"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="95"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="84"/>
+      <c r="J84" s="95"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="87">
+      <c r="B85" s="83">
         <v>46204</v>
       </c>
       <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="87">
+      <c r="D85" s="83">
         <v>46204</v>
       </c>
       <c r="E85" s="85" t="s">
@@ -16753,44 +16806,44 @@
       <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="83" t="s">
+      <c r="G85" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="83" t="s">
+      <c r="H85" s="93" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="83" t="s">
+      <c r="J85" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A86" s="82"/>
-      <c r="B86" s="88"/>
+      <c r="B86" s="84"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="88"/>
+      <c r="D86" s="84"/>
       <c r="E86" s="86"/>
       <c r="F86" s="86"/>
-      <c r="G86" s="84"/>
-      <c r="H86" s="84"/>
+      <c r="G86" s="95"/>
+      <c r="H86" s="95"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="84"/>
+      <c r="J86" s="95"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="87">
+      <c r="B87" s="83">
         <v>46210</v>
       </c>
       <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="87">
+      <c r="D87" s="83">
         <v>46210</v>
       </c>
       <c r="E87" s="85" t="s">
@@ -16799,32 +16852,32 @@
       <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="83" t="s">
+      <c r="G87" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="83" t="s">
+      <c r="H87" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="83" t="s">
+      <c r="J87" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A88" s="82"/>
-      <c r="B88" s="88"/>
+      <c r="B88" s="84"/>
       <c r="C88" s="86"/>
-      <c r="D88" s="88"/>
+      <c r="D88" s="84"/>
       <c r="E88" s="86"/>
       <c r="F88" s="86"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="95"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="84"/>
+      <c r="J88" s="95"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17433,13 +17486,13 @@
       <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="87">
+      <c r="B108" s="83">
         <v>46231</v>
       </c>
       <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="87">
+      <c r="D108" s="83">
         <v>46231</v>
       </c>
       <c r="E108" s="85" t="s">
@@ -17448,46 +17501,46 @@
       <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="83" t="s">
+      <c r="G108" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="83" t="s">
+      <c r="H108" s="93" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="83" t="s">
+      <c r="J108" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="89"/>
-      <c r="B109" s="90"/>
-      <c r="C109" s="91"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="91"/>
-      <c r="F109" s="91"/>
-      <c r="G109" s="92"/>
-      <c r="H109" s="92"/>
+      <c r="A109" s="96"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="97"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="94"/>
+      <c r="H109" s="94"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="92"/>
+      <c r="J109" s="94"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="82"/>
-      <c r="B110" s="88"/>
+      <c r="B110" s="84"/>
       <c r="C110" s="86"/>
-      <c r="D110" s="88"/>
+      <c r="D110" s="84"/>
       <c r="E110" s="86"/>
       <c r="F110" s="86"/>
-      <c r="G110" s="84"/>
-      <c r="H110" s="84"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="95"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="84"/>
+      <c r="J110" s="95"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17909,13 +17962,13 @@
       <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="87">
+      <c r="B124" s="83">
         <v>46263</v>
       </c>
       <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="87">
+      <c r="D124" s="83">
         <v>46260</v>
       </c>
       <c r="E124" s="85" t="s">
@@ -17924,32 +17977,32 @@
       <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="83" t="s">
+      <c r="G124" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="83" t="s">
+      <c r="H124" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="83" t="s">
+      <c r="J124" s="93" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="82"/>
-      <c r="B125" s="88"/>
+      <c r="B125" s="84"/>
       <c r="C125" s="86"/>
-      <c r="D125" s="88"/>
+      <c r="D125" s="84"/>
       <c r="E125" s="86"/>
       <c r="F125" s="86"/>
-      <c r="G125" s="84"/>
-      <c r="H125" s="84"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="84"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -18962,13 +19015,13 @@
       <c r="A157" s="81">
         <v>130</v>
       </c>
-      <c r="B157" s="87">
+      <c r="B157" s="83">
         <v>46294</v>
       </c>
       <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="87">
+      <c r="D157" s="83">
         <v>46294</v>
       </c>
       <c r="E157" s="85" t="s">
@@ -18977,7 +19030,7 @@
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="83" t="s">
+      <c r="G157" s="93" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -18995,14 +19048,14 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="82"/>
-      <c r="B158" s="88"/>
+      <c r="B158" s="84"/>
       <c r="C158" s="86"/>
-      <c r="D158" s="88"/>
+      <c r="D158" s="84"/>
       <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="84"/>
+      <c r="G158" s="95"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19276,13 +19329,13 @@
       <c r="A167" s="81">
         <v>139</v>
       </c>
-      <c r="B167" s="87">
+      <c r="B167" s="83">
         <v>46300</v>
       </c>
       <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="87">
+      <c r="D167" s="83">
         <v>46295</v>
       </c>
       <c r="E167" s="85" t="s">
@@ -19291,61 +19344,126 @@
       <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="83" t="s">
+      <c r="G167" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="83" t="s">
+      <c r="H167" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="83" t="s">
+      <c r="J167" s="93" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="82"/>
-      <c r="B168" s="88"/>
+      <c r="B168" s="84"/>
       <c r="C168" s="86"/>
-      <c r="D168" s="88"/>
+      <c r="D168" s="84"/>
       <c r="E168" s="86"/>
       <c r="F168" s="86"/>
-      <c r="G168" s="84"/>
-      <c r="H168" s="84"/>
+      <c r="G168" s="95"/>
+      <c r="H168" s="95"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="84"/>
+      <c r="J168" s="95"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
         <v>140</v>
       </c>
-      <c r="B169" s="43"/>
-      <c r="D169" s="43"/>
-      <c r="G169" s="43"/>
-      <c r="H169" s="43"/>
-      <c r="I169" s="28"/>
+      <c r="B169" s="52">
+        <v>46301</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D169" s="52">
+        <v>46301</v>
+      </c>
+      <c r="E169" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G169" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H169" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="I169" s="34" t="s">
+        <v>942</v>
+      </c>
       <c r="J169" s="43"/>
     </row>
     <row r="170" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A170" s="26"/>
-      <c r="B170" s="43"/>
-      <c r="D170" s="43"/>
-      <c r="G170" s="43"/>
-      <c r="H170" s="43"/>
-      <c r="I170" s="28"/>
-      <c r="J170" s="43"/>
+      <c r="A170" s="26">
+        <v>141</v>
+      </c>
+      <c r="B170" s="52">
+        <v>46301</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>943</v>
+      </c>
+      <c r="D170" s="52">
+        <v>46301</v>
+      </c>
+      <c r="E170" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F170" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="G170" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H170" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I170" s="28" t="s">
+        <v>944</v>
+      </c>
+      <c r="J170" s="43" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A171" s="26"/>
-      <c r="B171" s="43"/>
-      <c r="D171" s="43"/>
-      <c r="G171" s="43"/>
-      <c r="H171" s="43"/>
-      <c r="I171" s="28"/>
-      <c r="J171" s="43"/>
+      <c r="A171" s="26">
+        <v>142</v>
+      </c>
+      <c r="B171" s="52">
+        <v>46301</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>948</v>
+      </c>
+      <c r="D171" s="52">
+        <v>46301</v>
+      </c>
+      <c r="E171" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F171" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G171" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H171" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I171" s="28" t="s">
+        <v>946</v>
+      </c>
+      <c r="J171" s="43" t="s">
+        <v>945</v>
+      </c>
     </row>
     <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A172" s="26"/>
@@ -19353,11 +19471,15 @@
       <c r="D172" s="43"/>
       <c r="G172" s="43"/>
       <c r="H172" s="43"/>
-      <c r="I172" s="28"/>
+      <c r="I172" s="28" t="s">
+        <v>947</v>
+      </c>
       <c r="J172" s="43"/>
     </row>
     <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A173" s="26"/>
+      <c r="A173" s="26">
+        <v>143</v>
+      </c>
       <c r="B173" s="43"/>
       <c r="D173" s="43"/>
       <c r="G173" s="43"/>
@@ -26648,6 +26770,147 @@
     </row>
   </sheetData>
   <mergeCells count="165">
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
@@ -26672,147 +26935,6 @@
     <mergeCell ref="C80:C84"/>
     <mergeCell ref="D80:D84"/>
     <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C714CCC-E4E7-49D5-B23A-D4D4D0C461F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2D2759-3311-4697-8C98-187183D03F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="957">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2880,6 +2880,18 @@
   </si>
   <si>
     <t>63 Box</t>
+  </si>
+  <si>
+    <t>Niraj Patil</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Photometer Halogen Lamp Assy Bioelab FA 6V/10W - Qty 5 Nos. /Dryer Chip - Qty 10 Nos./Cuvette one Set - Qty 60 Nos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP Semi Auto Analyser </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Oct 2026</t>
   </si>
 </sst>
 </file>
@@ -3384,12 +3396,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3402,28 +3408,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3441,11 +3438,38 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3453,11 +3477,23 @@
     <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3475,30 +3511,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3801,21 +3813,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3848,10 +3860,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3964,46 +3976,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="66">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="63"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4097,30 +4109,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="66">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4131,10 +4143,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4142,54 +4154,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="63"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="66">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="66">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="69"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4197,17 +4209,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4326,25 +4338,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="66">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="66">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4355,13 +4367,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4486,46 +4498,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="66">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="66">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4583,41 +4595,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="66">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="66">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4625,59 +4637,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="66">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="66">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4793,117 +4805,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="66">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="63"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="66">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="63"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="66">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="66">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4914,13 +4926,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4929,42 +4941,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="66">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="64">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="66">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="63"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5147,50 +5159,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="66">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="66">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="63"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5489,41 +5501,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="66">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="66">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
+      <c r="F68" s="69"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5532,11 +5544,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
+      <c r="F69" s="69"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5544,17 +5556,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="63"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="63"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5783,39 +5795,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="66">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="66">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="69"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
+      <c r="F80" s="69"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5824,11 +5836,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5837,11 +5849,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
+      <c r="F82" s="69"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5849,17 +5861,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="63"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="63"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5891,22 +5903,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="66">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="66">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="64" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5914,57 +5926,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="67"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="65"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="66">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="66">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="A88" s="63"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="63"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="63"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -5996,41 +6008,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="66">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="64">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="66">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6039,11 +6051,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
+      <c r="F92" s="69"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6051,17 +6063,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="65"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="63"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6542,87 +6554,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="66">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="66">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="69"/>
+      <c r="D113" s="70"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="69"/>
+      <c r="D114" s="70"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
+      <c r="F114" s="69"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="67"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="63"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7205,92 +7217,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="66">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="66">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="67"/>
+      <c r="C137" s="65"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="63"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="66">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="66">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="65"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="63"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7613,46 +7625,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="66">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="66">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
-      <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="A151" s="63"/>
+      <c r="B151" s="67"/>
+      <c r="C151" s="65"/>
+      <c r="D151" s="67"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="63"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="63"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7681,41 +7693,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="66">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="66">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
-      <c r="D154" s="69"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="70"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
+      <c r="F154" s="69"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7724,11 +7736,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
-      <c r="D155" s="69"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="70"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
+      <c r="F155" s="69"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7736,17 +7748,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
-      <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="A156" s="63"/>
+      <c r="B156" s="67"/>
+      <c r="C156" s="65"/>
+      <c r="D156" s="67"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="65"/>
+      <c r="G156" s="63"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="63"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7807,41 +7819,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="66">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="66">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="69"/>
+      <c r="B160" s="70"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="70"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
+      <c r="F160" s="69"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7850,11 +7862,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="69"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="70"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
+      <c r="F161" s="69"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7863,11 +7875,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="69"/>
+      <c r="B162" s="70"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="70"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
+      <c r="F162" s="69"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7875,17 +7887,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
-      <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="A163" s="63"/>
+      <c r="B163" s="67"/>
+      <c r="C163" s="65"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="65"/>
+      <c r="G163" s="63"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="63"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8175,46 +8187,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="66">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
-      <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="A175" s="63"/>
+      <c r="B175" s="67"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="63"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="63"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8356,41 +8368,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="66">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="64" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="66">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
-      <c r="D182" s="69"/>
+      <c r="B182" s="70"/>
+      <c r="C182" s="69"/>
+      <c r="D182" s="70"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
+      <c r="F182" s="77"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8399,11 +8411,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
-      <c r="D183" s="69"/>
+      <c r="B183" s="70"/>
+      <c r="C183" s="69"/>
+      <c r="D183" s="70"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
+      <c r="F183" s="77"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8412,11 +8424,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
-      <c r="D184" s="69"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="69"/>
+      <c r="D184" s="70"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
+      <c r="F184" s="77"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8424,59 +8436,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
-      <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="A185" s="63"/>
+      <c r="B185" s="67"/>
+      <c r="C185" s="65"/>
+      <c r="D185" s="67"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="63"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="63"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="66">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="64" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="66">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
-      <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
-      <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="A187" s="63"/>
+      <c r="B187" s="67"/>
+      <c r="C187" s="65"/>
+      <c r="D187" s="67"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="65"/>
+      <c r="G187" s="63"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="63"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9144,31 +9156,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="66">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="64" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="66">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9177,11 +9189,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
-      <c r="D212" s="69"/>
+      <c r="B212" s="70"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
+      <c r="F212" s="69"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9190,11 +9202,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
-      <c r="D213" s="69"/>
+      <c r="B213" s="70"/>
+      <c r="C213" s="69"/>
+      <c r="D213" s="70"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
+      <c r="F213" s="69"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9202,17 +9214,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
-      <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="67"/>
+      <c r="C214" s="65"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="65"/>
+      <c r="G214" s="63"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="63"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9479,46 +9491,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="66">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="64" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="66">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="64" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
-      <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
-      <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="67"/>
+      <c r="C225" s="65"/>
+      <c r="D225" s="67"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="63"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="63"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9550,88 +9562,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="66">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="66">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
-      <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="A228" s="63"/>
+      <c r="B228" s="67"/>
+      <c r="C228" s="65"/>
+      <c r="D228" s="67"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="65"/>
+      <c r="G228" s="63"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="63"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="66">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="66">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
-      <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="A230" s="63"/>
+      <c r="B230" s="67"/>
+      <c r="C230" s="65"/>
+      <c r="D230" s="67"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="65"/>
+      <c r="G230" s="63"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="63"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9692,46 +9704,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="66">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="64" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="66">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
-      <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="A234" s="63"/>
+      <c r="B234" s="67"/>
+      <c r="C234" s="65"/>
+      <c r="D234" s="67"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="65"/>
+      <c r="G234" s="63"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="63"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10372,46 +10384,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="64">
+      <c r="A257" s="62">
         <v>200</v>
       </c>
-      <c r="B257" s="62">
+      <c r="B257" s="66">
         <v>46300</v>
       </c>
-      <c r="C257" s="66" t="s">
+      <c r="C257" s="64" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="62">
+      <c r="D257" s="66">
         <v>46294</v>
       </c>
-      <c r="E257" s="64" t="s">
+      <c r="E257" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="66" t="s">
+      <c r="F257" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="64" t="s">
+      <c r="G257" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="64" t="s">
+      <c r="I257" s="62" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="63"/>
-      <c r="E258" s="65"/>
-      <c r="F258" s="67"/>
-      <c r="G258" s="65"/>
+      <c r="A258" s="63"/>
+      <c r="B258" s="67"/>
+      <c r="C258" s="65"/>
+      <c r="D258" s="67"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="65"/>
+      <c r="G258" s="63"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="65"/>
+      <c r="I258" s="63"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -14133,6 +14145,238 @@
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="I229:I230"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="F233:F234"/>
+    <mergeCell ref="G233:G234"/>
+    <mergeCell ref="I233:I234"/>
+    <mergeCell ref="G229:G230"/>
+    <mergeCell ref="F229:F230"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
     <mergeCell ref="G257:G258"/>
     <mergeCell ref="I257:I258"/>
     <mergeCell ref="F257:F258"/>
@@ -14157,238 +14401,6 @@
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="I227:I228"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="F233:F234"/>
-    <mergeCell ref="G233:G234"/>
-    <mergeCell ref="I233:I234"/>
-    <mergeCell ref="G229:G230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14420,23 +14432,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14504,28 +14516,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="62">
         <v>1</v>
       </c>
-      <c r="B4" s="90">
+      <c r="B4" s="98">
         <v>46098</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="98">
         <v>46098</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="64" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14546,13 +14558,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14571,13 +14583,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14595,14 +14607,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14713,50 +14725,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="64">
+      <c r="A11" s="62">
         <v>5</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="93">
         <v>46102</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <v>46095</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="64" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14794,13 +14806,13 @@
       <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="83">
+      <c r="B14" s="87">
         <v>46105</v>
       </c>
       <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="87">
         <v>46105</v>
       </c>
       <c r="E14" s="85" t="s">
@@ -14809,58 +14821,58 @@
       <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="93" t="s">
+      <c r="H14" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="93" t="s">
+      <c r="J14" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="94"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A16" s="82"/>
-      <c r="B16" s="84"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="86"/>
-      <c r="D16" s="84"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="86"/>
       <c r="F16" s="86"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="95"/>
+      <c r="J16" s="84"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="83">
+      <c r="B17" s="87">
         <v>46105</v>
       </c>
       <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="87">
         <v>46105</v>
       </c>
       <c r="E17" s="85" t="s">
@@ -14869,32 +14881,32 @@
       <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="93" t="s">
+      <c r="G17" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="83" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="93" t="s">
+      <c r="J17" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A18" s="82"/>
-      <c r="B18" s="84"/>
+      <c r="B18" s="88"/>
       <c r="C18" s="86"/>
-      <c r="D18" s="84"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="95"/>
+      <c r="J18" s="84"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15220,13 +15232,13 @@
       <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="83">
+      <c r="B29" s="87">
         <v>46121</v>
       </c>
       <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="87">
         <v>46121</v>
       </c>
       <c r="E29" s="85" t="s">
@@ -15235,32 +15247,32 @@
       <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="93" t="s">
+      <c r="G29" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="93" t="s">
+      <c r="H29" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="93" t="s">
+      <c r="J29" s="83" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A30" s="82"/>
-      <c r="B30" s="84"/>
+      <c r="B30" s="88"/>
       <c r="C30" s="86"/>
-      <c r="D30" s="84"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="86"/>
       <c r="F30" s="86"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="95"/>
+      <c r="J30" s="84"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15356,13 +15368,13 @@
       <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="83">
+      <c r="B34" s="87">
         <v>46128</v>
       </c>
       <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="83">
+      <c r="D34" s="87">
         <v>46128</v>
       </c>
       <c r="E34" s="85" t="s">
@@ -15371,44 +15383,44 @@
       <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="93" t="s">
+      <c r="G34" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="93" t="s">
+      <c r="H34" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="93" t="s">
+      <c r="J34" s="83" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A35" s="82"/>
-      <c r="B35" s="84"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="84"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="86"/>
       <c r="F35" s="86"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="95"/>
+      <c r="J35" s="84"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="83">
+      <c r="B36" s="87">
         <v>46132</v>
       </c>
       <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="87">
         <v>46129</v>
       </c>
       <c r="E36" s="85" t="s">
@@ -15417,10 +15429,10 @@
       <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="93" t="s">
+      <c r="G36" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="93" t="s">
+      <c r="H36" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15432,13 +15444,13 @@
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A37" s="82"/>
-      <c r="B37" s="84"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="84"/>
+      <c r="D37" s="88"/>
       <c r="E37" s="86"/>
       <c r="F37" s="86"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15544,13 +15556,13 @@
       <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="83">
+      <c r="B41" s="87">
         <v>46139</v>
       </c>
       <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="83">
+      <c r="D41" s="87">
         <v>46139</v>
       </c>
       <c r="E41" s="85" t="s">
@@ -15559,32 +15571,32 @@
       <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="93" t="s">
+      <c r="G41" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="93" t="s">
+      <c r="H41" s="83" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="93" t="s">
+      <c r="J41" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A42" s="82"/>
-      <c r="B42" s="84"/>
+      <c r="B42" s="88"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="84"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="86"/>
       <c r="F42" s="86"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="95"/>
+      <c r="J42" s="84"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15718,13 +15730,13 @@
       <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="83">
+      <c r="B47" s="87">
         <v>46149</v>
       </c>
       <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="83">
+      <c r="D47" s="87">
         <v>46148</v>
       </c>
       <c r="E47" s="85" t="s">
@@ -15733,10 +15745,10 @@
       <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="93" t="s">
+      <c r="G47" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="93" t="s">
+      <c r="H47" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15748,13 +15760,13 @@
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A48" s="82"/>
-      <c r="B48" s="84"/>
+      <c r="B48" s="88"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="84"/>
+      <c r="D48" s="88"/>
       <c r="E48" s="86"/>
       <c r="F48" s="86"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="95"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15766,13 +15778,13 @@
       <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="83">
+      <c r="B49" s="87">
         <v>46149</v>
       </c>
       <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="83">
+      <c r="D49" s="87">
         <v>46148</v>
       </c>
       <c r="E49" s="85" t="s">
@@ -15781,10 +15793,10 @@
       <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="93" t="s">
+      <c r="G49" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="93" t="s">
+      <c r="H49" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15796,13 +15808,13 @@
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A50" s="82"/>
-      <c r="B50" s="84"/>
+      <c r="B50" s="88"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="84"/>
+      <c r="D50" s="88"/>
       <c r="E50" s="86"/>
       <c r="F50" s="86"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="95"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16102,13 +16114,13 @@
       <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="83">
+      <c r="B60" s="87">
         <v>46169</v>
       </c>
       <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="83">
+      <c r="D60" s="87">
         <v>46169</v>
       </c>
       <c r="E60" s="85" t="s">
@@ -16117,32 +16129,32 @@
       <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="93" t="s">
+      <c r="G60" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="93" t="s">
+      <c r="H60" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="93" t="s">
+      <c r="J60" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A61" s="82"/>
-      <c r="B61" s="84"/>
+      <c r="B61" s="88"/>
       <c r="C61" s="86"/>
-      <c r="D61" s="84"/>
+      <c r="D61" s="88"/>
       <c r="E61" s="86"/>
       <c r="F61" s="86"/>
-      <c r="G61" s="95"/>
-      <c r="H61" s="95"/>
+      <c r="G61" s="84"/>
+      <c r="H61" s="84"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="95"/>
+      <c r="J61" s="84"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16465,13 +16477,13 @@
       <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="83">
+      <c r="B72" s="87">
         <v>46192</v>
       </c>
       <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="83">
+      <c r="D72" s="87">
         <v>46191</v>
       </c>
       <c r="E72" s="85" t="s">
@@ -16480,32 +16492,32 @@
       <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="93" t="s">
+      <c r="G72" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="93" t="s">
+      <c r="H72" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="93" t="s">
+      <c r="J72" s="83" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A73" s="82"/>
-      <c r="B73" s="84"/>
+      <c r="B73" s="88"/>
       <c r="C73" s="86"/>
-      <c r="D73" s="84"/>
+      <c r="D73" s="88"/>
       <c r="E73" s="86"/>
       <c r="F73" s="86"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
+      <c r="G73" s="84"/>
+      <c r="H73" s="84"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="95"/>
+      <c r="J73" s="84"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16703,13 +16715,13 @@
       <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="83">
+      <c r="B80" s="87">
         <v>46200</v>
       </c>
       <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="83">
+      <c r="D80" s="87">
         <v>46200</v>
       </c>
       <c r="E80" s="85" t="s">
@@ -16718,86 +16730,86 @@
       <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="93" t="s">
+      <c r="G80" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="93" t="s">
+      <c r="H80" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="93" t="s">
+      <c r="J80" s="83" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="96"/>
-      <c r="B81" s="97"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
+      <c r="A81" s="89"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="90"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="94"/>
+      <c r="J81" s="92"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="96"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="98"/>
-      <c r="D82" s="97"/>
-      <c r="E82" s="98"/>
-      <c r="F82" s="98"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="94"/>
+      <c r="A82" s="89"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="91"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="94"/>
+      <c r="J82" s="92"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="96"/>
-      <c r="B83" s="97"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="97"/>
-      <c r="E83" s="98"/>
-      <c r="F83" s="98"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="94"/>
+      <c r="A83" s="89"/>
+      <c r="B83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="90"/>
+      <c r="E83" s="91"/>
+      <c r="F83" s="91"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="94"/>
+      <c r="J83" s="92"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A84" s="82"/>
-      <c r="B84" s="84"/>
+      <c r="B84" s="88"/>
       <c r="C84" s="86"/>
-      <c r="D84" s="84"/>
+      <c r="D84" s="88"/>
       <c r="E84" s="86"/>
       <c r="F84" s="86"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="95"/>
+      <c r="G84" s="84"/>
+      <c r="H84" s="84"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="95"/>
+      <c r="J84" s="84"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="83">
+      <c r="B85" s="87">
         <v>46204</v>
       </c>
       <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="83">
+      <c r="D85" s="87">
         <v>46204</v>
       </c>
       <c r="E85" s="85" t="s">
@@ -16806,44 +16818,44 @@
       <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="93" t="s">
+      <c r="G85" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="93" t="s">
+      <c r="H85" s="83" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="93" t="s">
+      <c r="J85" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A86" s="82"/>
-      <c r="B86" s="84"/>
+      <c r="B86" s="88"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="84"/>
+      <c r="D86" s="88"/>
       <c r="E86" s="86"/>
       <c r="F86" s="86"/>
-      <c r="G86" s="95"/>
-      <c r="H86" s="95"/>
+      <c r="G86" s="84"/>
+      <c r="H86" s="84"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="95"/>
+      <c r="J86" s="84"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="83">
+      <c r="B87" s="87">
         <v>46210</v>
       </c>
       <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="83">
+      <c r="D87" s="87">
         <v>46210</v>
       </c>
       <c r="E87" s="85" t="s">
@@ -16852,32 +16864,32 @@
       <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="93" t="s">
+      <c r="G87" s="83" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="93" t="s">
+      <c r="H87" s="83" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="93" t="s">
+      <c r="J87" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A88" s="82"/>
-      <c r="B88" s="84"/>
+      <c r="B88" s="88"/>
       <c r="C88" s="86"/>
-      <c r="D88" s="84"/>
+      <c r="D88" s="88"/>
       <c r="E88" s="86"/>
       <c r="F88" s="86"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="95"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="95"/>
+      <c r="J88" s="84"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17486,13 +17498,13 @@
       <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="83">
+      <c r="B108" s="87">
         <v>46231</v>
       </c>
       <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="83">
+      <c r="D108" s="87">
         <v>46231</v>
       </c>
       <c r="E108" s="85" t="s">
@@ -17501,46 +17513,46 @@
       <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="93" t="s">
+      <c r="G108" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="93" t="s">
+      <c r="H108" s="83" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="93" t="s">
+      <c r="J108" s="83" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="96"/>
-      <c r="B109" s="97"/>
-      <c r="C109" s="98"/>
-      <c r="D109" s="97"/>
-      <c r="E109" s="98"/>
-      <c r="F109" s="98"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="94"/>
+      <c r="A109" s="89"/>
+      <c r="B109" s="90"/>
+      <c r="C109" s="91"/>
+      <c r="D109" s="90"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="92"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="94"/>
+      <c r="J109" s="92"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="82"/>
-      <c r="B110" s="84"/>
+      <c r="B110" s="88"/>
       <c r="C110" s="86"/>
-      <c r="D110" s="84"/>
+      <c r="D110" s="88"/>
       <c r="E110" s="86"/>
       <c r="F110" s="86"/>
-      <c r="G110" s="95"/>
-      <c r="H110" s="95"/>
+      <c r="G110" s="84"/>
+      <c r="H110" s="84"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="95"/>
+      <c r="J110" s="84"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17962,13 +17974,13 @@
       <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="83">
+      <c r="B124" s="87">
         <v>46263</v>
       </c>
       <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="83">
+      <c r="D124" s="87">
         <v>46260</v>
       </c>
       <c r="E124" s="85" t="s">
@@ -17977,32 +17989,32 @@
       <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="93" t="s">
+      <c r="G124" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="93" t="s">
+      <c r="H124" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="93" t="s">
+      <c r="J124" s="83" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="82"/>
-      <c r="B125" s="84"/>
+      <c r="B125" s="88"/>
       <c r="C125" s="86"/>
-      <c r="D125" s="84"/>
+      <c r="D125" s="88"/>
       <c r="E125" s="86"/>
       <c r="F125" s="86"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
+      <c r="G125" s="84"/>
+      <c r="H125" s="84"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="95"/>
+      <c r="J125" s="84"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -19015,13 +19027,13 @@
       <c r="A157" s="81">
         <v>130</v>
       </c>
-      <c r="B157" s="83">
+      <c r="B157" s="87">
         <v>46294</v>
       </c>
       <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="83">
+      <c r="D157" s="87">
         <v>46294</v>
       </c>
       <c r="E157" s="85" t="s">
@@ -19030,7 +19042,7 @@
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="93" t="s">
+      <c r="G157" s="83" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -19048,14 +19060,14 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="82"/>
-      <c r="B158" s="84"/>
+      <c r="B158" s="88"/>
       <c r="C158" s="86"/>
-      <c r="D158" s="84"/>
+      <c r="D158" s="88"/>
       <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="95"/>
+      <c r="G158" s="84"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19329,13 +19341,13 @@
       <c r="A167" s="81">
         <v>139</v>
       </c>
-      <c r="B167" s="83">
+      <c r="B167" s="87">
         <v>46300</v>
       </c>
       <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="83">
+      <c r="D167" s="87">
         <v>46295</v>
       </c>
       <c r="E167" s="85" t="s">
@@ -19344,32 +19356,32 @@
       <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="93" t="s">
+      <c r="G167" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="93" t="s">
+      <c r="H167" s="83" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="93" t="s">
+      <c r="J167" s="83" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="82"/>
-      <c r="B168" s="84"/>
+      <c r="B168" s="88"/>
       <c r="C168" s="86"/>
-      <c r="D168" s="84"/>
+      <c r="D168" s="88"/>
       <c r="E168" s="86"/>
       <c r="F168" s="86"/>
-      <c r="G168" s="95"/>
-      <c r="H168" s="95"/>
+      <c r="G168" s="84"/>
+      <c r="H168" s="84"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="95"/>
+      <c r="J168" s="84"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -19480,24 +19492,68 @@
       <c r="A173" s="26">
         <v>143</v>
       </c>
-      <c r="B173" s="43"/>
-      <c r="D173" s="43"/>
-      <c r="G173" s="43"/>
-      <c r="H173" s="43"/>
-      <c r="I173" s="28"/>
-      <c r="J173" s="43"/>
+      <c r="B173" s="52">
+        <v>46303</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D173" s="52" t="s">
+        <v>956</v>
+      </c>
+      <c r="E173" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>953</v>
+      </c>
+      <c r="G173" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H173" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I173" s="28" t="s">
+        <v>954</v>
+      </c>
+      <c r="J173" s="43" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="174" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A174" s="26"/>
-      <c r="B174" s="43"/>
+      <c r="A174" s="26">
+        <v>144</v>
+      </c>
+      <c r="B174" s="52">
+        <v>46303</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>40</v>
+      </c>
       <c r="D174" s="43"/>
-      <c r="G174" s="43"/>
-      <c r="H174" s="43"/>
-      <c r="I174" s="28"/>
-      <c r="J174" s="43"/>
+      <c r="E174" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F174" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="G174" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H174" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="I174" s="28" t="s">
+        <v>955</v>
+      </c>
+      <c r="J174" s="43" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="175" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A175" s="26"/>
+      <c r="A175" s="26">
+        <v>145</v>
+      </c>
       <c r="B175" s="43"/>
       <c r="D175" s="43"/>
       <c r="G175" s="43"/>
@@ -26770,90 +26826,63 @@
     </row>
   </sheetData>
   <mergeCells count="165">
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="J17:J18"/>
@@ -26878,63 +26907,90 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2D2759-3311-4697-8C98-187183D03F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF8EF3A-589A-4A90-A393-9A476918AFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">JP Semi Auto Analyser </t>
   </si>
   <si>
-    <t xml:space="preserve"> Oct 2026</t>
+    <t>HeatSkin- Qty 3Nos.</t>
   </si>
 </sst>
 </file>
@@ -3396,6 +3396,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3408,19 +3414,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3438,31 +3453,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3470,30 +3470,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3511,6 +3487,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3813,21 +3813,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3860,10 +3860,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3976,46 +3976,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="63"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="63"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4109,30 +4109,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4143,10 +4143,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4154,54 +4154,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="63"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="63"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="66">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4209,17 +4209,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="63"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="63"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4338,25 +4338,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="66">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4367,13 +4367,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="63"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="63"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4498,46 +4498,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="66">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="63"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="63"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4595,41 +4595,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="66">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="70"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="69"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4637,59 +4637,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="63"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="66">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="63"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="63"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4805,117 +4805,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="66">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="64" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="63"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="63"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="66">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="64" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="63"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="63"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="66">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="66">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="64" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4926,13 +4926,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="63"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="63"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4941,42 +4941,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="66">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="66">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="63"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="67"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="63"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="63"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="63"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5159,50 +5159,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="66">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="66">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="63"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="63"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="63"/>
-      <c r="J56" s="63"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5501,41 +5501,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="66">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="66">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="64" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="70"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="69"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5544,11 +5544,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5556,17 +5556,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="63"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="63"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="63"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="63"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5795,39 +5795,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="66">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="66">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="64" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="70"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="69"/>
+      <c r="F80" s="70"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5836,11 +5836,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="70"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5849,11 +5849,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="70"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="69"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
+      <c r="F82" s="70"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5861,17 +5861,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="63"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="63"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="63"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5903,22 +5903,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="66">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="64" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="66">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="64" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5926,57 +5926,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="63"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="65"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="66">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="64" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="66">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="64" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="63"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="65"/>
-      <c r="G88" s="63"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="63"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -6008,41 +6008,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="66">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="64">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="66">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="64" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="69"/>
-      <c r="D91" s="70"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="69"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6051,11 +6051,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="70"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="70"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="69"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="69"/>
+      <c r="F92" s="70"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6063,17 +6063,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="63"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="65"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="63"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="63"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6554,87 +6554,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="66">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="66">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="64" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="76" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="70"/>
+      <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="69"/>
+      <c r="F112" s="70"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="77"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="70"/>
+      <c r="B113" s="69"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="70"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="69"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="77"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="70"/>
+      <c r="B114" s="69"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="70"/>
+      <c r="D114" s="69"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="69"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="77"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="63"/>
-      <c r="B115" s="67"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="63"/>
-      <c r="F115" s="65"/>
-      <c r="G115" s="63"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="67"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="78"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7217,92 +7217,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="66">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="64" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="66">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="64" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="63"/>
-      <c r="B137" s="67"/>
-      <c r="C137" s="65"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="65"/>
-      <c r="G137" s="63"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
+      <c r="C137" s="67"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
+      <c r="F137" s="67"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="63"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="66">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="64" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="66">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="64" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="63"/>
-      <c r="B139" s="67"/>
-      <c r="C139" s="65"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="63"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="63"/>
-      <c r="J139" s="63"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7625,46 +7625,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="66">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="64" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="66">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="64" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="63"/>
-      <c r="B151" s="67"/>
-      <c r="C151" s="65"/>
-      <c r="D151" s="67"/>
-      <c r="E151" s="63"/>
-      <c r="F151" s="65"/>
-      <c r="G151" s="63"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
+      <c r="F151" s="67"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="63"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7693,41 +7693,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="66">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="64" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="66">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="64" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="69"/>
-      <c r="D154" s="70"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="69"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="69"/>
+      <c r="F154" s="70"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7736,11 +7736,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="70"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="70"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="69"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="69"/>
+      <c r="F155" s="70"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7748,17 +7748,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="63"/>
-      <c r="B156" s="67"/>
-      <c r="C156" s="65"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="63"/>
-      <c r="F156" s="65"/>
-      <c r="G156" s="63"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="67"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="63"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7819,41 +7819,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="66">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="64" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="66">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="64" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="70"/>
-      <c r="C160" s="69"/>
-      <c r="D160" s="70"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="69"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="69"/>
+      <c r="F160" s="70"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7862,11 +7862,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="70"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="70"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="69"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="69"/>
+      <c r="F161" s="70"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7875,11 +7875,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="70"/>
-      <c r="C162" s="69"/>
-      <c r="D162" s="70"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="70"/>
+      <c r="D162" s="69"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="69"/>
+      <c r="F162" s="70"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7887,17 +7887,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="63"/>
-      <c r="B163" s="67"/>
-      <c r="C163" s="65"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="65"/>
-      <c r="G163" s="63"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
+      <c r="F163" s="67"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="63"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8187,46 +8187,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="66">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="64" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="79">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="64" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="63"/>
-      <c r="B175" s="67"/>
-      <c r="C175" s="65"/>
-      <c r="D175" s="80"/>
-      <c r="E175" s="63"/>
-      <c r="F175" s="65"/>
-      <c r="G175" s="63"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="67"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="63"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8368,41 +8368,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="66">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="64" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="66">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="76" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="70"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="70"/>
+      <c r="B182" s="69"/>
+      <c r="C182" s="70"/>
+      <c r="D182" s="69"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="77"/>
+      <c r="F182" s="72"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8411,11 +8411,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="70"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="70"/>
+      <c r="B183" s="69"/>
+      <c r="C183" s="70"/>
+      <c r="D183" s="69"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="77"/>
+      <c r="F183" s="72"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8424,11 +8424,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="70"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="70"/>
+      <c r="B184" s="69"/>
+      <c r="C184" s="70"/>
+      <c r="D184" s="69"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="77"/>
+      <c r="F184" s="72"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8436,59 +8436,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="63"/>
-      <c r="B185" s="67"/>
-      <c r="C185" s="65"/>
-      <c r="D185" s="67"/>
-      <c r="E185" s="63"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="63"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
+      <c r="C185" s="67"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="63"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="66">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="64" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="66">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="64" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="63"/>
-      <c r="B187" s="67"/>
-      <c r="C187" s="65"/>
-      <c r="D187" s="67"/>
-      <c r="E187" s="63"/>
-      <c r="F187" s="65"/>
-      <c r="G187" s="63"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
+      <c r="F187" s="67"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="63"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9156,31 +9156,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="66">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="64" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="66">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="64" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9189,11 +9189,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="70"/>
-      <c r="C212" s="69"/>
-      <c r="D212" s="70"/>
+      <c r="B212" s="69"/>
+      <c r="C212" s="70"/>
+      <c r="D212" s="69"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="69"/>
+      <c r="F212" s="70"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9202,11 +9202,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="70"/>
-      <c r="C213" s="69"/>
-      <c r="D213" s="70"/>
+      <c r="B213" s="69"/>
+      <c r="C213" s="70"/>
+      <c r="D213" s="69"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="69"/>
+      <c r="F213" s="70"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9214,17 +9214,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="63"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="65"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="63"/>
-      <c r="F214" s="65"/>
-      <c r="G214" s="63"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
+      <c r="C214" s="67"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
+      <c r="F214" s="67"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="63"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9491,46 +9491,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="66">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="64" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="66">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="64" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="63"/>
-      <c r="B225" s="67"/>
-      <c r="C225" s="65"/>
-      <c r="D225" s="67"/>
-      <c r="E225" s="63"/>
-      <c r="F225" s="65"/>
-      <c r="G225" s="63"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
+      <c r="C225" s="67"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
+      <c r="F225" s="67"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="63"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9562,88 +9562,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="66">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="64" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="66">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="64" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="63"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="65"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="63"/>
-      <c r="F228" s="65"/>
-      <c r="G228" s="63"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
+      <c r="C228" s="67"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
+      <c r="F228" s="67"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="63"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="66">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="64" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="66">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="64" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="63"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="65"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="63"/>
-      <c r="F230" s="65"/>
-      <c r="G230" s="63"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
+      <c r="C230" s="67"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
+      <c r="F230" s="67"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="63"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9704,46 +9704,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="66">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="64" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="66">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="64" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="63"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="65"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="63"/>
-      <c r="F234" s="65"/>
-      <c r="G234" s="63"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
+      <c r="F234" s="67"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="63"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10384,46 +10384,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="62">
+      <c r="A257" s="64">
         <v>200</v>
       </c>
-      <c r="B257" s="66">
+      <c r="B257" s="62">
         <v>46300</v>
       </c>
-      <c r="C257" s="64" t="s">
+      <c r="C257" s="66" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="66">
+      <c r="D257" s="62">
         <v>46294</v>
       </c>
-      <c r="E257" s="62" t="s">
+      <c r="E257" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="64" t="s">
+      <c r="F257" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="62" t="s">
+      <c r="G257" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="62" t="s">
+      <c r="I257" s="64" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="63"/>
-      <c r="B258" s="67"/>
-      <c r="C258" s="65"/>
-      <c r="D258" s="67"/>
-      <c r="E258" s="63"/>
-      <c r="F258" s="65"/>
-      <c r="G258" s="63"/>
+      <c r="A258" s="65"/>
+      <c r="B258" s="63"/>
+      <c r="C258" s="67"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="65"/>
+      <c r="F258" s="67"/>
+      <c r="G258" s="65"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="63"/>
+      <c r="I258" s="65"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10513,40 +10513,46 @@
       </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A262" s="21">
+      <c r="A262" s="64">
         <v>204</v>
       </c>
-      <c r="B262" s="25">
+      <c r="B262" s="62">
         <v>46301</v>
       </c>
-      <c r="C262" s="46" t="s">
+      <c r="C262" s="66" t="s">
         <v>949</v>
       </c>
-      <c r="D262" s="25">
+      <c r="D262" s="62">
         <v>46301</v>
       </c>
-      <c r="E262" s="21" t="s">
+      <c r="E262" s="64" t="s">
         <v>308</v>
       </c>
-      <c r="F262" s="46" t="s">
+      <c r="F262" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G262" s="21" t="s">
+      <c r="G262" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H262" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="I262" s="21" t="s">
+      <c r="I262" s="64" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="C263" s="46"/>
-      <c r="F263" s="46"/>
+      <c r="A263" s="65"/>
+      <c r="B263" s="63"/>
+      <c r="C263" s="67"/>
+      <c r="D263" s="63"/>
+      <c r="E263" s="65"/>
+      <c r="F263" s="67"/>
+      <c r="G263" s="65"/>
       <c r="H263" s="34" t="s">
         <v>951</v>
       </c>
+      <c r="I263" s="65"/>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="C264" s="46"/>
@@ -14144,239 +14150,15 @@
       <c r="H982" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="256">
-    <mergeCell ref="B229:B230"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="I227:I228"/>
-    <mergeCell ref="I229:I230"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="C233:C234"/>
-    <mergeCell ref="D233:D234"/>
-    <mergeCell ref="E233:E234"/>
-    <mergeCell ref="F233:F234"/>
-    <mergeCell ref="G233:G234"/>
-    <mergeCell ref="I233:I234"/>
-    <mergeCell ref="G229:G230"/>
-    <mergeCell ref="F229:F230"/>
-    <mergeCell ref="E229:E230"/>
-    <mergeCell ref="D229:D230"/>
-    <mergeCell ref="C229:C230"/>
-    <mergeCell ref="E227:E228"/>
-    <mergeCell ref="D227:D228"/>
-    <mergeCell ref="C227:C228"/>
-    <mergeCell ref="B227:B228"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
+  <mergeCells count="264">
+    <mergeCell ref="I262:I263"/>
+    <mergeCell ref="G262:G263"/>
+    <mergeCell ref="F262:F263"/>
+    <mergeCell ref="E262:E263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A262:A263"/>
     <mergeCell ref="G257:G258"/>
     <mergeCell ref="I257:I258"/>
     <mergeCell ref="F257:F258"/>
@@ -14401,6 +14183,238 @@
     <mergeCell ref="E15:E17"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="B229:B230"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="I227:I228"/>
+    <mergeCell ref="I229:I230"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
+    <mergeCell ref="E233:E234"/>
+    <mergeCell ref="F233:F234"/>
+    <mergeCell ref="G233:G234"/>
+    <mergeCell ref="I233:I234"/>
+    <mergeCell ref="G229:G230"/>
+    <mergeCell ref="F229:F230"/>
+    <mergeCell ref="E229:E230"/>
+    <mergeCell ref="D229:D230"/>
+    <mergeCell ref="C229:C230"/>
+    <mergeCell ref="E227:E228"/>
+    <mergeCell ref="D227:D228"/>
+    <mergeCell ref="C227:C228"/>
+    <mergeCell ref="B227:B228"/>
+    <mergeCell ref="A227:A228"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14432,23 +14446,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14516,28 +14530,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="90">
         <v>46098</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="90">
         <v>46098</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14558,13 +14572,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14583,13 +14597,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14607,14 +14621,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14725,50 +14739,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="64" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="65"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14806,13 +14820,13 @@
       <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="87">
+      <c r="B14" s="83">
         <v>46105</v>
       </c>
       <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="87">
+      <c r="D14" s="83">
         <v>46105</v>
       </c>
       <c r="E14" s="85" t="s">
@@ -14821,58 +14835,58 @@
       <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="83" t="s">
+      <c r="G14" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="83" t="s">
+      <c r="H14" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="83" t="s">
+      <c r="J14" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A16" s="82"/>
-      <c r="B16" s="88"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="86"/>
-      <c r="D16" s="88"/>
+      <c r="D16" s="84"/>
       <c r="E16" s="86"/>
       <c r="F16" s="86"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="84"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="87">
+      <c r="B17" s="83">
         <v>46105</v>
       </c>
       <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="87">
+      <c r="D17" s="83">
         <v>46105</v>
       </c>
       <c r="E17" s="85" t="s">
@@ -14881,32 +14895,32 @@
       <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="83" t="s">
+      <c r="H17" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="83" t="s">
+      <c r="J17" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A18" s="82"/>
-      <c r="B18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="86"/>
-      <c r="D18" s="88"/>
+      <c r="D18" s="84"/>
       <c r="E18" s="86"/>
       <c r="F18" s="86"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="84"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15232,13 +15246,13 @@
       <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="87">
+      <c r="B29" s="83">
         <v>46121</v>
       </c>
       <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="87">
+      <c r="D29" s="83">
         <v>46121</v>
       </c>
       <c r="E29" s="85" t="s">
@@ -15247,32 +15261,32 @@
       <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="83" t="s">
+      <c r="G29" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="83" t="s">
+      <c r="H29" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="J29" s="93" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A30" s="82"/>
-      <c r="B30" s="88"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="86"/>
-      <c r="D30" s="88"/>
+      <c r="D30" s="84"/>
       <c r="E30" s="86"/>
       <c r="F30" s="86"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="84"/>
+      <c r="J30" s="95"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15368,13 +15382,13 @@
       <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="87">
+      <c r="B34" s="83">
         <v>46128</v>
       </c>
       <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="87">
+      <c r="D34" s="83">
         <v>46128</v>
       </c>
       <c r="E34" s="85" t="s">
@@ -15383,44 +15397,44 @@
       <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="83" t="s">
+      <c r="G34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="83" t="s">
+      <c r="H34" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="83" t="s">
+      <c r="J34" s="93" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A35" s="82"/>
-      <c r="B35" s="88"/>
+      <c r="B35" s="84"/>
       <c r="C35" s="86"/>
-      <c r="D35" s="88"/>
+      <c r="D35" s="84"/>
       <c r="E35" s="86"/>
       <c r="F35" s="86"/>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="84"/>
+      <c r="J35" s="95"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="87">
+      <c r="B36" s="83">
         <v>46132</v>
       </c>
       <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="87">
+      <c r="D36" s="83">
         <v>46129</v>
       </c>
       <c r="E36" s="85" t="s">
@@ -15429,10 +15443,10 @@
       <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="83" t="s">
+      <c r="G36" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="83" t="s">
+      <c r="H36" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15444,13 +15458,13 @@
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A37" s="82"/>
-      <c r="B37" s="88"/>
+      <c r="B37" s="84"/>
       <c r="C37" s="86"/>
-      <c r="D37" s="88"/>
+      <c r="D37" s="84"/>
       <c r="E37" s="86"/>
       <c r="F37" s="86"/>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15556,13 +15570,13 @@
       <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="87">
+      <c r="B41" s="83">
         <v>46139</v>
       </c>
       <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="87">
+      <c r="D41" s="83">
         <v>46139</v>
       </c>
       <c r="E41" s="85" t="s">
@@ -15571,32 +15585,32 @@
       <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="83" t="s">
+      <c r="G41" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="83" t="s">
+      <c r="H41" s="93" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="83" t="s">
+      <c r="J41" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A42" s="82"/>
-      <c r="B42" s="88"/>
+      <c r="B42" s="84"/>
       <c r="C42" s="86"/>
-      <c r="D42" s="88"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="86"/>
       <c r="F42" s="86"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="84"/>
+      <c r="J42" s="95"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15730,13 +15744,13 @@
       <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="87">
+      <c r="B47" s="83">
         <v>46149</v>
       </c>
       <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="87">
+      <c r="D47" s="83">
         <v>46148</v>
       </c>
       <c r="E47" s="85" t="s">
@@ -15745,10 +15759,10 @@
       <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="83" t="s">
+      <c r="G47" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="83" t="s">
+      <c r="H47" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15760,13 +15774,13 @@
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A48" s="82"/>
-      <c r="B48" s="88"/>
+      <c r="B48" s="84"/>
       <c r="C48" s="86"/>
-      <c r="D48" s="88"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="86"/>
       <c r="F48" s="86"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15778,13 +15792,13 @@
       <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="87">
+      <c r="B49" s="83">
         <v>46149</v>
       </c>
       <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="87">
+      <c r="D49" s="83">
         <v>46148</v>
       </c>
       <c r="E49" s="85" t="s">
@@ -15793,10 +15807,10 @@
       <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="83" t="s">
+      <c r="G49" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="83" t="s">
+      <c r="H49" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15808,13 +15822,13 @@
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A50" s="82"/>
-      <c r="B50" s="88"/>
+      <c r="B50" s="84"/>
       <c r="C50" s="86"/>
-      <c r="D50" s="88"/>
+      <c r="D50" s="84"/>
       <c r="E50" s="86"/>
       <c r="F50" s="86"/>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16114,13 +16128,13 @@
       <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="87">
+      <c r="B60" s="83">
         <v>46169</v>
       </c>
       <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="87">
+      <c r="D60" s="83">
         <v>46169</v>
       </c>
       <c r="E60" s="85" t="s">
@@ -16129,32 +16143,32 @@
       <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="83" t="s">
+      <c r="G60" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="83" t="s">
+      <c r="H60" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="83" t="s">
+      <c r="J60" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A61" s="82"/>
-      <c r="B61" s="88"/>
+      <c r="B61" s="84"/>
       <c r="C61" s="86"/>
-      <c r="D61" s="88"/>
+      <c r="D61" s="84"/>
       <c r="E61" s="86"/>
       <c r="F61" s="86"/>
-      <c r="G61" s="84"/>
-      <c r="H61" s="84"/>
+      <c r="G61" s="95"/>
+      <c r="H61" s="95"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="84"/>
+      <c r="J61" s="95"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16477,13 +16491,13 @@
       <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="87">
+      <c r="B72" s="83">
         <v>46192</v>
       </c>
       <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="87">
+      <c r="D72" s="83">
         <v>46191</v>
       </c>
       <c r="E72" s="85" t="s">
@@ -16492,32 +16506,32 @@
       <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="83" t="s">
+      <c r="G72" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="83" t="s">
+      <c r="H72" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="83" t="s">
+      <c r="J72" s="93" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A73" s="82"/>
-      <c r="B73" s="88"/>
+      <c r="B73" s="84"/>
       <c r="C73" s="86"/>
-      <c r="D73" s="88"/>
+      <c r="D73" s="84"/>
       <c r="E73" s="86"/>
       <c r="F73" s="86"/>
-      <c r="G73" s="84"/>
-      <c r="H73" s="84"/>
+      <c r="G73" s="95"/>
+      <c r="H73" s="95"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="84"/>
+      <c r="J73" s="95"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16715,13 +16729,13 @@
       <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="87">
+      <c r="B80" s="83">
         <v>46200</v>
       </c>
       <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="87">
+      <c r="D80" s="83">
         <v>46200</v>
       </c>
       <c r="E80" s="85" t="s">
@@ -16730,86 +16744,86 @@
       <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="83" t="s">
+      <c r="G80" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="83" t="s">
+      <c r="H80" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="83" t="s">
+      <c r="J80" s="93" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="89"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="90"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
+      <c r="A81" s="96"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="92"/>
+      <c r="J81" s="94"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="89"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="92"/>
-      <c r="H82" s="92"/>
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="97"/>
+      <c r="E82" s="98"/>
+      <c r="F82" s="98"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="94"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="92"/>
+      <c r="J82" s="94"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="89"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="90"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
+      <c r="A83" s="96"/>
+      <c r="B83" s="97"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="98"/>
+      <c r="F83" s="98"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="94"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="94"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A84" s="82"/>
-      <c r="B84" s="88"/>
+      <c r="B84" s="84"/>
       <c r="C84" s="86"/>
-      <c r="D84" s="88"/>
+      <c r="D84" s="84"/>
       <c r="E84" s="86"/>
       <c r="F84" s="86"/>
-      <c r="G84" s="84"/>
-      <c r="H84" s="84"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="95"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="84"/>
+      <c r="J84" s="95"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="87">
+      <c r="B85" s="83">
         <v>46204</v>
       </c>
       <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="87">
+      <c r="D85" s="83">
         <v>46204</v>
       </c>
       <c r="E85" s="85" t="s">
@@ -16818,44 +16832,44 @@
       <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="83" t="s">
+      <c r="G85" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="83" t="s">
+      <c r="H85" s="93" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="83" t="s">
+      <c r="J85" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A86" s="82"/>
-      <c r="B86" s="88"/>
+      <c r="B86" s="84"/>
       <c r="C86" s="86"/>
-      <c r="D86" s="88"/>
+      <c r="D86" s="84"/>
       <c r="E86" s="86"/>
       <c r="F86" s="86"/>
-      <c r="G86" s="84"/>
-      <c r="H86" s="84"/>
+      <c r="G86" s="95"/>
+      <c r="H86" s="95"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="84"/>
+      <c r="J86" s="95"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="87">
+      <c r="B87" s="83">
         <v>46210</v>
       </c>
       <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="87">
+      <c r="D87" s="83">
         <v>46210</v>
       </c>
       <c r="E87" s="85" t="s">
@@ -16864,32 +16878,32 @@
       <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="83" t="s">
+      <c r="G87" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="83" t="s">
+      <c r="H87" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="83" t="s">
+      <c r="J87" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A88" s="82"/>
-      <c r="B88" s="88"/>
+      <c r="B88" s="84"/>
       <c r="C88" s="86"/>
-      <c r="D88" s="88"/>
+      <c r="D88" s="84"/>
       <c r="E88" s="86"/>
       <c r="F88" s="86"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="95"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="84"/>
+      <c r="J88" s="95"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17498,13 +17512,13 @@
       <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="87">
+      <c r="B108" s="83">
         <v>46231</v>
       </c>
       <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="87">
+      <c r="D108" s="83">
         <v>46231</v>
       </c>
       <c r="E108" s="85" t="s">
@@ -17513,46 +17527,46 @@
       <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="83" t="s">
+      <c r="G108" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="83" t="s">
+      <c r="H108" s="93" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="83" t="s">
+      <c r="J108" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="89"/>
-      <c r="B109" s="90"/>
-      <c r="C109" s="91"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="91"/>
-      <c r="F109" s="91"/>
-      <c r="G109" s="92"/>
-      <c r="H109" s="92"/>
+      <c r="A109" s="96"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="97"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="94"/>
+      <c r="H109" s="94"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="92"/>
+      <c r="J109" s="94"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A110" s="82"/>
-      <c r="B110" s="88"/>
+      <c r="B110" s="84"/>
       <c r="C110" s="86"/>
-      <c r="D110" s="88"/>
+      <c r="D110" s="84"/>
       <c r="E110" s="86"/>
       <c r="F110" s="86"/>
-      <c r="G110" s="84"/>
-      <c r="H110" s="84"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="95"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="84"/>
+      <c r="J110" s="95"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17974,13 +17988,13 @@
       <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="87">
+      <c r="B124" s="83">
         <v>46263</v>
       </c>
       <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="87">
+      <c r="D124" s="83">
         <v>46260</v>
       </c>
       <c r="E124" s="85" t="s">
@@ -17989,32 +18003,32 @@
       <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="83" t="s">
+      <c r="G124" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="83" t="s">
+      <c r="H124" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="83" t="s">
+      <c r="J124" s="93" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A125" s="82"/>
-      <c r="B125" s="88"/>
+      <c r="B125" s="84"/>
       <c r="C125" s="86"/>
-      <c r="D125" s="88"/>
+      <c r="D125" s="84"/>
       <c r="E125" s="86"/>
       <c r="F125" s="86"/>
-      <c r="G125" s="84"/>
-      <c r="H125" s="84"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="84"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -19027,13 +19041,13 @@
       <c r="A157" s="81">
         <v>130</v>
       </c>
-      <c r="B157" s="87">
+      <c r="B157" s="83">
         <v>46294</v>
       </c>
       <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="87">
+      <c r="D157" s="83">
         <v>46294</v>
       </c>
       <c r="E157" s="85" t="s">
@@ -19042,7 +19056,7 @@
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="83" t="s">
+      <c r="G157" s="93" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -19060,14 +19074,14 @@
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A158" s="82"/>
-      <c r="B158" s="88"/>
+      <c r="B158" s="84"/>
       <c r="C158" s="86"/>
-      <c r="D158" s="88"/>
+      <c r="D158" s="84"/>
       <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="84"/>
+      <c r="G158" s="95"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19341,13 +19355,13 @@
       <c r="A167" s="81">
         <v>139</v>
       </c>
-      <c r="B167" s="87">
+      <c r="B167" s="83">
         <v>46300</v>
       </c>
       <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="87">
+      <c r="D167" s="83">
         <v>46295</v>
       </c>
       <c r="E167" s="85" t="s">
@@ -19356,32 +19370,32 @@
       <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="83" t="s">
+      <c r="G167" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="83" t="s">
+      <c r="H167" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="83" t="s">
+      <c r="J167" s="93" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A168" s="82"/>
-      <c r="B168" s="88"/>
+      <c r="B168" s="84"/>
       <c r="C168" s="86"/>
-      <c r="D168" s="88"/>
+      <c r="D168" s="84"/>
       <c r="E168" s="86"/>
       <c r="F168" s="86"/>
-      <c r="G168" s="84"/>
-      <c r="H168" s="84"/>
+      <c r="G168" s="95"/>
+      <c r="H168" s="95"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="84"/>
+      <c r="J168" s="95"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -19409,9 +19423,11 @@
         <v>209</v>
       </c>
       <c r="I169" s="34" t="s">
-        <v>942</v>
-      </c>
-      <c r="J169" s="43"/>
+        <v>956</v>
+      </c>
+      <c r="J169" s="43" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="170" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A170" s="26">
@@ -19446,47 +19462,50 @@
       </c>
     </row>
     <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A171" s="26">
+      <c r="A171" s="81">
         <v>142</v>
       </c>
-      <c r="B171" s="52">
+      <c r="B171" s="83">
         <v>46301</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C171" s="85" t="s">
         <v>948</v>
       </c>
-      <c r="D171" s="52">
+      <c r="D171" s="83">
         <v>46301</v>
       </c>
-      <c r="E171" s="10" t="s">
+      <c r="E171" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F171" s="10" t="s">
+      <c r="F171" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="G171" s="43" t="s">
+      <c r="G171" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H171" s="43" t="s">
+      <c r="H171" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I171" s="28" t="s">
         <v>946</v>
       </c>
-      <c r="J171" s="43" t="s">
+      <c r="J171" s="93" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A172" s="26"/>
-      <c r="B172" s="43"/>
-      <c r="D172" s="43"/>
-      <c r="G172" s="43"/>
-      <c r="H172" s="43"/>
+      <c r="A172" s="82"/>
+      <c r="B172" s="84"/>
+      <c r="C172" s="86"/>
+      <c r="D172" s="84"/>
+      <c r="E172" s="86"/>
+      <c r="F172" s="86"/>
+      <c r="G172" s="95"/>
+      <c r="H172" s="95"/>
       <c r="I172" s="28" t="s">
         <v>947</v>
       </c>
-      <c r="J172" s="43"/>
+      <c r="J172" s="95"/>
     </row>
     <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A173" s="26">
@@ -19498,8 +19517,8 @@
       <c r="C173" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D173" s="52" t="s">
-        <v>956</v>
+      <c r="D173" s="52">
+        <v>46303</v>
       </c>
       <c r="E173" s="10" t="s">
         <v>13</v>
@@ -19530,7 +19549,9 @@
       <c r="C174" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D174" s="43"/>
+      <c r="D174" s="52">
+        <v>46303</v>
+      </c>
       <c r="E174" s="10" t="s">
         <v>102</v>
       </c>
@@ -26825,7 +26846,157 @@
       <c r="J982" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="174">
+    <mergeCell ref="J171:J172"/>
+    <mergeCell ref="H171:H172"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="F171:F172"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
@@ -26850,147 +27021,6 @@
     <mergeCell ref="C80:C84"/>
     <mergeCell ref="D80:D84"/>
     <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF8EF3A-589A-4A90-A393-9A476918AFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCC995A-FFAF-4DDF-9CD0-927BBEF00D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3396,12 +3396,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3414,28 +3408,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3453,11 +3438,32 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3466,10 +3472,28 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3487,30 +3511,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3813,21 +3813,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3860,10 +3860,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3976,46 +3976,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="66">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="63"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4109,30 +4109,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="66">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4143,10 +4143,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4154,54 +4154,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="63"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="66">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="66">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="69"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4209,17 +4209,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4338,25 +4338,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="66">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="66">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4367,13 +4367,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4498,46 +4498,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="66">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="66">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4595,41 +4595,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="66">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="66">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4637,59 +4637,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="66">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="66">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4805,117 +4805,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="66">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="63"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="66">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="63"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="66">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="66">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4926,13 +4926,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4941,42 +4941,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="66">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="64">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="66">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="63"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5159,50 +5159,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="66">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="66">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="63"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5501,41 +5501,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="66">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="66">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
+      <c r="F68" s="69"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5544,11 +5544,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
+      <c r="F69" s="69"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5556,17 +5556,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="63"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="63"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5795,39 +5795,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="66">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="66">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="69"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
+      <c r="F80" s="69"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5836,11 +5836,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5849,11 +5849,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
+      <c r="F82" s="69"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5861,17 +5861,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="63"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="63"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5903,22 +5903,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="66">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="66">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="64" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5926,57 +5926,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="67"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="65"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="66">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="66">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="A88" s="63"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="63"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="63"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -6008,41 +6008,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="66">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="64">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="66">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6051,11 +6051,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
+      <c r="F92" s="69"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6063,17 +6063,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="65"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="63"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6554,87 +6554,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="66">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="66">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="69"/>
+      <c r="D113" s="70"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="69"/>
+      <c r="D114" s="70"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
+      <c r="F114" s="69"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="67"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="63"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7217,92 +7217,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="66">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="66">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="67"/>
+      <c r="C137" s="65"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="63"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="66">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="66">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="65"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="63"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7625,46 +7625,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="66">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="66">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
-      <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="A151" s="63"/>
+      <c r="B151" s="67"/>
+      <c r="C151" s="65"/>
+      <c r="D151" s="67"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="63"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="63"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7693,41 +7693,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="66">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="66">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
-      <c r="D154" s="69"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="70"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
+      <c r="F154" s="69"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7736,11 +7736,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
-      <c r="D155" s="69"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="70"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
+      <c r="F155" s="69"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7748,17 +7748,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
-      <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="A156" s="63"/>
+      <c r="B156" s="67"/>
+      <c r="C156" s="65"/>
+      <c r="D156" s="67"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="65"/>
+      <c r="G156" s="63"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="63"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7819,41 +7819,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="66">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="66">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="69"/>
+      <c r="B160" s="70"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="70"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
+      <c r="F160" s="69"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7862,11 +7862,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="69"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="70"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
+      <c r="F161" s="69"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7875,11 +7875,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="69"/>
+      <c r="B162" s="70"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="70"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
+      <c r="F162" s="69"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7887,17 +7887,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
-      <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="A163" s="63"/>
+      <c r="B163" s="67"/>
+      <c r="C163" s="65"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="65"/>
+      <c r="G163" s="63"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="63"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8187,46 +8187,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="66">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
-      <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="A175" s="63"/>
+      <c r="B175" s="67"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="63"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="63"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8368,41 +8368,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="66">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="64" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="66">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
-      <c r="D182" s="69"/>
+      <c r="B182" s="70"/>
+      <c r="C182" s="69"/>
+      <c r="D182" s="70"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
+      <c r="F182" s="77"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8411,11 +8411,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
-      <c r="D183" s="69"/>
+      <c r="B183" s="70"/>
+      <c r="C183" s="69"/>
+      <c r="D183" s="70"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
+      <c r="F183" s="77"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8424,11 +8424,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
-      <c r="D184" s="69"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="69"/>
+      <c r="D184" s="70"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
+      <c r="F184" s="77"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8436,59 +8436,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
-      <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="A185" s="63"/>
+      <c r="B185" s="67"/>
+      <c r="C185" s="65"/>
+      <c r="D185" s="67"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="63"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="63"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="66">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="64" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="66">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
-      <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
-      <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="A187" s="63"/>
+      <c r="B187" s="67"/>
+      <c r="C187" s="65"/>
+      <c r="D187" s="67"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="65"/>
+      <c r="G187" s="63"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="63"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9156,31 +9156,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="66">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="64" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="66">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9189,11 +9189,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
-      <c r="D212" s="69"/>
+      <c r="B212" s="70"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
+      <c r="F212" s="69"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9202,11 +9202,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
-      <c r="D213" s="69"/>
+      <c r="B213" s="70"/>
+      <c r="C213" s="69"/>
+      <c r="D213" s="70"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
+      <c r="F213" s="69"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9214,17 +9214,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
-      <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="67"/>
+      <c r="C214" s="65"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="65"/>
+      <c r="G214" s="63"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="63"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9491,46 +9491,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="66">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="64" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="66">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="64" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
-      <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
-      <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="67"/>
+      <c r="C225" s="65"/>
+      <c r="D225" s="67"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="63"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="63"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9562,88 +9562,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="66">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="66">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
-      <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="A228" s="63"/>
+      <c r="B228" s="67"/>
+      <c r="C228" s="65"/>
+      <c r="D228" s="67"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="65"/>
+      <c r="G228" s="63"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="63"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="66">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="66">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
-      <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="A230" s="63"/>
+      <c r="B230" s="67"/>
+      <c r="C230" s="65"/>
+      <c r="D230" s="67"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="65"/>
+      <c r="G230" s="63"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="63"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9704,46 +9704,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="66">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="64" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="66">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
-      <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="A234" s="63"/>
+      <c r="B234" s="67"/>
+      <c r="C234" s="65"/>
+      <c r="D234" s="67"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="65"/>
+      <c r="G234" s="63"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="63"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10384,46 +10384,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="64">
+      <c r="A257" s="62">
         <v>200</v>
       </c>
-      <c r="B257" s="62">
+      <c r="B257" s="66">
         <v>46300</v>
       </c>
-      <c r="C257" s="66" t="s">
+      <c r="C257" s="64" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="62">
+      <c r="D257" s="66">
         <v>46294</v>
       </c>
-      <c r="E257" s="64" t="s">
+      <c r="E257" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="66" t="s">
+      <c r="F257" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="64" t="s">
+      <c r="G257" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="64" t="s">
+      <c r="I257" s="62" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="63"/>
-      <c r="E258" s="65"/>
-      <c r="F258" s="67"/>
-      <c r="G258" s="65"/>
+      <c r="A258" s="63"/>
+      <c r="B258" s="67"/>
+      <c r="C258" s="65"/>
+      <c r="D258" s="67"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="65"/>
+      <c r="G258" s="63"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="65"/>
+      <c r="I258" s="63"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10513,48 +10513,51 @@
       </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A262" s="64">
+      <c r="A262" s="62">
         <v>204</v>
       </c>
-      <c r="B262" s="62">
+      <c r="B262" s="66">
         <v>46301</v>
       </c>
-      <c r="C262" s="66" t="s">
+      <c r="C262" s="64" t="s">
         <v>949</v>
       </c>
-      <c r="D262" s="62">
+      <c r="D262" s="66">
         <v>46301</v>
       </c>
-      <c r="E262" s="64" t="s">
+      <c r="E262" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="F262" s="66" t="s">
+      <c r="F262" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G262" s="64" t="s">
+      <c r="G262" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H262" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="I262" s="64" t="s">
+      <c r="I262" s="62" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A263" s="65"/>
-      <c r="B263" s="63"/>
-      <c r="C263" s="67"/>
-      <c r="D263" s="63"/>
-      <c r="E263" s="65"/>
-      <c r="F263" s="67"/>
-      <c r="G263" s="65"/>
+      <c r="A263" s="63"/>
+      <c r="B263" s="67"/>
+      <c r="C263" s="65"/>
+      <c r="D263" s="67"/>
+      <c r="E263" s="63"/>
+      <c r="F263" s="65"/>
+      <c r="G263" s="63"/>
       <c r="H263" s="34" t="s">
         <v>951</v>
       </c>
-      <c r="I263" s="65"/>
+      <c r="I263" s="63"/>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A264" s="21">
+        <v>205</v>
+      </c>
       <c r="C264" s="46"/>
       <c r="F264" s="46"/>
       <c r="H264" s="34"/>
@@ -14151,248 +14154,6 @@
     </row>
   </sheetData>
   <mergeCells count="264">
-    <mergeCell ref="I262:I263"/>
-    <mergeCell ref="G262:G263"/>
-    <mergeCell ref="F262:F263"/>
-    <mergeCell ref="E262:E263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="G257:G258"/>
-    <mergeCell ref="I257:I258"/>
-    <mergeCell ref="F257:F258"/>
-    <mergeCell ref="E257:E258"/>
-    <mergeCell ref="D257:D258"/>
-    <mergeCell ref="C257:C258"/>
-    <mergeCell ref="B257:B258"/>
-    <mergeCell ref="A257:A258"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -14415,6 +14176,248 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="I262:I263"/>
+    <mergeCell ref="G262:G263"/>
+    <mergeCell ref="F262:F263"/>
+    <mergeCell ref="E262:E263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="G257:G258"/>
+    <mergeCell ref="I257:I258"/>
+    <mergeCell ref="F257:F258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="A257:A258"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14446,23 +14449,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14530,28 +14533,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="62">
         <v>1</v>
       </c>
-      <c r="B4" s="90">
+      <c r="B4" s="98">
         <v>46098</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="98">
         <v>46098</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="64" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14572,13 +14575,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14597,13 +14600,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14621,14 +14624,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14739,50 +14742,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="64">
+      <c r="A11" s="62">
         <v>5</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="93">
         <v>46102</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <v>46095</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="64" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14817,110 +14820,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="81">
+      <c r="A14" s="87">
         <v>7</v>
       </c>
-      <c r="B14" s="83">
+      <c r="B14" s="85">
         <v>46105</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="85">
         <v>46105</v>
       </c>
-      <c r="E14" s="85" t="s">
+      <c r="E14" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="93" t="s">
+      <c r="H14" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="93" t="s">
+      <c r="J14" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="94"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="95"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="81">
+      <c r="A17" s="87">
         <v>8</v>
       </c>
-      <c r="B17" s="83">
+      <c r="B17" s="85">
         <v>46105</v>
       </c>
-      <c r="C17" s="85" t="s">
+      <c r="C17" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="85">
         <v>46105</v>
       </c>
-      <c r="E17" s="85" t="s">
+      <c r="E17" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="85" t="s">
+      <c r="F17" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="93" t="s">
+      <c r="G17" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="81" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="93" t="s">
+      <c r="J17" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="95"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15243,50 +15246,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="81">
+      <c r="A29" s="87">
         <v>19</v>
       </c>
-      <c r="B29" s="83">
+      <c r="B29" s="85">
         <v>46121</v>
       </c>
-      <c r="C29" s="85" t="s">
+      <c r="C29" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="85">
         <v>46121</v>
       </c>
-      <c r="E29" s="85" t="s">
+      <c r="E29" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="85" t="s">
+      <c r="F29" s="83" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="93" t="s">
+      <c r="G29" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="93" t="s">
+      <c r="H29" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="93" t="s">
+      <c r="J29" s="81" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="82"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="95"/>
+      <c r="J30" s="82"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15379,74 +15382,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="81">
+      <c r="A34" s="87">
         <v>23</v>
       </c>
-      <c r="B34" s="83">
+      <c r="B34" s="85">
         <v>46128</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="83">
+      <c r="D34" s="85">
         <v>46128</v>
       </c>
-      <c r="E34" s="85" t="s">
+      <c r="E34" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="93" t="s">
+      <c r="G34" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="93" t="s">
+      <c r="H34" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="93" t="s">
+      <c r="J34" s="81" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="82"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="95"/>
+      <c r="J35" s="82"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="81">
+      <c r="A36" s="87">
         <v>24</v>
       </c>
-      <c r="B36" s="83">
+      <c r="B36" s="85">
         <v>46132</v>
       </c>
-      <c r="C36" s="85" t="s">
+      <c r="C36" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="85">
         <v>46129</v>
       </c>
-      <c r="E36" s="85" t="s">
+      <c r="E36" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="85" t="s">
+      <c r="F36" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="93" t="s">
+      <c r="G36" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="93" t="s">
+      <c r="H36" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15457,14 +15460,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="82"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15567,50 +15570,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="81">
+      <c r="A41" s="87">
         <v>28</v>
       </c>
-      <c r="B41" s="83">
+      <c r="B41" s="85">
         <v>46139</v>
       </c>
-      <c r="C41" s="85" t="s">
+      <c r="C41" s="83" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="83">
+      <c r="D41" s="85">
         <v>46139</v>
       </c>
-      <c r="E41" s="85" t="s">
+      <c r="E41" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="85" t="s">
+      <c r="F41" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="93" t="s">
+      <c r="G41" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="93" t="s">
+      <c r="H41" s="81" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="93" t="s">
+      <c r="J41" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="82"/>
-      <c r="B42" s="84"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
+      <c r="A42" s="88"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="95"/>
+      <c r="J42" s="82"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15741,28 +15744,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="81">
+      <c r="A47" s="87">
         <v>33</v>
       </c>
-      <c r="B47" s="83">
+      <c r="B47" s="85">
         <v>46149</v>
       </c>
-      <c r="C47" s="85" t="s">
+      <c r="C47" s="83" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="83">
+      <c r="D47" s="85">
         <v>46148</v>
       </c>
-      <c r="E47" s="85" t="s">
+      <c r="E47" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="85" t="s">
+      <c r="F47" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="93" t="s">
+      <c r="G47" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="93" t="s">
+      <c r="H47" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15773,14 +15776,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="82"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="86"/>
-      <c r="F48" s="86"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="95"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="82"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15789,28 +15792,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="81">
+      <c r="A49" s="87">
         <v>34</v>
       </c>
-      <c r="B49" s="83">
+      <c r="B49" s="85">
         <v>46149</v>
       </c>
-      <c r="C49" s="85" t="s">
+      <c r="C49" s="83" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="83">
+      <c r="D49" s="85">
         <v>46148</v>
       </c>
-      <c r="E49" s="85" t="s">
+      <c r="E49" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="85" t="s">
+      <c r="F49" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="93" t="s">
+      <c r="G49" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="93" t="s">
+      <c r="H49" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15821,14 +15824,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="82"/>
-      <c r="B50" s="84"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="84"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="86"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="95"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="82"/>
+      <c r="H50" s="82"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16125,50 +16128,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="81">
+      <c r="A60" s="87">
         <v>44</v>
       </c>
-      <c r="B60" s="83">
+      <c r="B60" s="85">
         <v>46169</v>
       </c>
-      <c r="C60" s="85" t="s">
+      <c r="C60" s="83" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="83">
+      <c r="D60" s="85">
         <v>46169</v>
       </c>
-      <c r="E60" s="85" t="s">
+      <c r="E60" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="85" t="s">
+      <c r="F60" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="93" t="s">
+      <c r="G60" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="93" t="s">
+      <c r="H60" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="93" t="s">
+      <c r="J60" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="82"/>
-      <c r="B61" s="84"/>
-      <c r="C61" s="86"/>
-      <c r="D61" s="84"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="95"/>
-      <c r="H61" s="95"/>
+      <c r="A61" s="88"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="84"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="84"/>
+      <c r="F61" s="84"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="82"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="95"/>
+      <c r="J61" s="82"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16488,50 +16491,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="81">
+      <c r="A72" s="87">
         <v>55</v>
       </c>
-      <c r="B72" s="83">
+      <c r="B72" s="85">
         <v>46192</v>
       </c>
-      <c r="C72" s="85" t="s">
+      <c r="C72" s="83" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="83">
+      <c r="D72" s="85">
         <v>46191</v>
       </c>
-      <c r="E72" s="85" t="s">
+      <c r="E72" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="85" t="s">
+      <c r="F72" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="93" t="s">
+      <c r="G72" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="93" t="s">
+      <c r="H72" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="93" t="s">
+      <c r="J72" s="81" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="82"/>
-      <c r="B73" s="84"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="84"/>
-      <c r="E73" s="86"/>
-      <c r="F73" s="86"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
+      <c r="A73" s="88"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="84"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="84"/>
+      <c r="F73" s="84"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="95"/>
+      <c r="J73" s="82"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16726,184 +16729,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="81">
+      <c r="A80" s="87">
         <v>62</v>
       </c>
-      <c r="B80" s="83">
+      <c r="B80" s="85">
         <v>46200</v>
       </c>
-      <c r="C80" s="85" t="s">
+      <c r="C80" s="83" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="83">
+      <c r="D80" s="85">
         <v>46200</v>
       </c>
-      <c r="E80" s="85" t="s">
+      <c r="E80" s="83" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="85" t="s">
+      <c r="F80" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="93" t="s">
+      <c r="G80" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="93" t="s">
+      <c r="H80" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="93" t="s">
+      <c r="J80" s="81" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="96"/>
-      <c r="B81" s="97"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
+      <c r="A81" s="89"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="90"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="94"/>
+      <c r="J81" s="92"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="96"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="98"/>
-      <c r="D82" s="97"/>
-      <c r="E82" s="98"/>
-      <c r="F82" s="98"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="94"/>
+      <c r="A82" s="89"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="91"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="94"/>
+      <c r="J82" s="92"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="96"/>
-      <c r="B83" s="97"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="97"/>
-      <c r="E83" s="98"/>
-      <c r="F83" s="98"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="94"/>
+      <c r="A83" s="89"/>
+      <c r="B83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="90"/>
+      <c r="E83" s="91"/>
+      <c r="F83" s="91"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="94"/>
+      <c r="J83" s="92"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="82"/>
-      <c r="B84" s="84"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="84"/>
-      <c r="E84" s="86"/>
-      <c r="F84" s="86"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="95"/>
+      <c r="A84" s="88"/>
+      <c r="B84" s="86"/>
+      <c r="C84" s="84"/>
+      <c r="D84" s="86"/>
+      <c r="E84" s="84"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="82"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="95"/>
+      <c r="J84" s="82"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="81">
+      <c r="A85" s="87">
         <v>63</v>
       </c>
-      <c r="B85" s="83">
+      <c r="B85" s="85">
         <v>46204</v>
       </c>
-      <c r="C85" s="85" t="s">
+      <c r="C85" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="83">
+      <c r="D85" s="85">
         <v>46204</v>
       </c>
-      <c r="E85" s="85" t="s">
+      <c r="E85" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="85" t="s">
+      <c r="F85" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="93" t="s">
+      <c r="G85" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="93" t="s">
+      <c r="H85" s="81" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="93" t="s">
+      <c r="J85" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="82"/>
-      <c r="B86" s="84"/>
-      <c r="C86" s="86"/>
-      <c r="D86" s="84"/>
-      <c r="E86" s="86"/>
-      <c r="F86" s="86"/>
-      <c r="G86" s="95"/>
-      <c r="H86" s="95"/>
+      <c r="A86" s="88"/>
+      <c r="B86" s="86"/>
+      <c r="C86" s="84"/>
+      <c r="D86" s="86"/>
+      <c r="E86" s="84"/>
+      <c r="F86" s="84"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="95"/>
+      <c r="J86" s="82"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="81">
+      <c r="A87" s="87">
         <v>64</v>
       </c>
-      <c r="B87" s="83">
+      <c r="B87" s="85">
         <v>46210</v>
       </c>
-      <c r="C87" s="85" t="s">
+      <c r="C87" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="83">
+      <c r="D87" s="85">
         <v>46210</v>
       </c>
-      <c r="E87" s="85" t="s">
+      <c r="E87" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="85" t="s">
+      <c r="F87" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="93" t="s">
+      <c r="G87" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="93" t="s">
+      <c r="H87" s="81" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="93" t="s">
+      <c r="J87" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="82"/>
-      <c r="B88" s="84"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="84"/>
-      <c r="E88" s="86"/>
-      <c r="F88" s="86"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="95"/>
+      <c r="A88" s="88"/>
+      <c r="B88" s="86"/>
+      <c r="C88" s="84"/>
+      <c r="D88" s="86"/>
+      <c r="E88" s="84"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="95"/>
+      <c r="J88" s="82"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17509,64 +17512,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="81">
+      <c r="A108" s="87">
         <v>84</v>
       </c>
-      <c r="B108" s="83">
+      <c r="B108" s="85">
         <v>46231</v>
       </c>
-      <c r="C108" s="85" t="s">
+      <c r="C108" s="83" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="83">
+      <c r="D108" s="85">
         <v>46231</v>
       </c>
-      <c r="E108" s="85" t="s">
+      <c r="E108" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="85" t="s">
+      <c r="F108" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="93" t="s">
+      <c r="G108" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="93" t="s">
+      <c r="H108" s="81" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="93" t="s">
+      <c r="J108" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="96"/>
-      <c r="B109" s="97"/>
-      <c r="C109" s="98"/>
-      <c r="D109" s="97"/>
-      <c r="E109" s="98"/>
-      <c r="F109" s="98"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="94"/>
+      <c r="A109" s="89"/>
+      <c r="B109" s="90"/>
+      <c r="C109" s="91"/>
+      <c r="D109" s="90"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="92"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="94"/>
+      <c r="J109" s="92"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="82"/>
-      <c r="B110" s="84"/>
-      <c r="C110" s="86"/>
-      <c r="D110" s="84"/>
-      <c r="E110" s="86"/>
-      <c r="F110" s="86"/>
-      <c r="G110" s="95"/>
-      <c r="H110" s="95"/>
+      <c r="A110" s="88"/>
+      <c r="B110" s="86"/>
+      <c r="C110" s="84"/>
+      <c r="D110" s="86"/>
+      <c r="E110" s="84"/>
+      <c r="F110" s="84"/>
+      <c r="G110" s="82"/>
+      <c r="H110" s="82"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="95"/>
+      <c r="J110" s="82"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17985,50 +17988,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="81">
+      <c r="A124" s="87">
         <v>98</v>
       </c>
-      <c r="B124" s="83">
+      <c r="B124" s="85">
         <v>46263</v>
       </c>
-      <c r="C124" s="85" t="s">
+      <c r="C124" s="83" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="83">
+      <c r="D124" s="85">
         <v>46260</v>
       </c>
-      <c r="E124" s="85" t="s">
+      <c r="E124" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="85" t="s">
+      <c r="F124" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="93" t="s">
+      <c r="G124" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="93" t="s">
+      <c r="H124" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="93" t="s">
+      <c r="J124" s="81" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="82"/>
-      <c r="B125" s="84"/>
-      <c r="C125" s="86"/>
-      <c r="D125" s="84"/>
-      <c r="E125" s="86"/>
-      <c r="F125" s="86"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
+      <c r="A125" s="88"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="84"/>
+      <c r="D125" s="86"/>
+      <c r="E125" s="84"/>
+      <c r="F125" s="84"/>
+      <c r="G125" s="82"/>
+      <c r="H125" s="82"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="95"/>
+      <c r="J125" s="82"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -19038,25 +19041,25 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="81">
+      <c r="A157" s="87">
         <v>130</v>
       </c>
-      <c r="B157" s="83">
+      <c r="B157" s="85">
         <v>46294</v>
       </c>
-      <c r="C157" s="85" t="s">
+      <c r="C157" s="83" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="83">
+      <c r="D157" s="85">
         <v>46294</v>
       </c>
-      <c r="E157" s="85" t="s">
+      <c r="E157" s="83" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="93" t="s">
+      <c r="G157" s="81" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -19073,15 +19076,15 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="82"/>
-      <c r="B158" s="84"/>
-      <c r="C158" s="86"/>
-      <c r="D158" s="84"/>
-      <c r="E158" s="86"/>
+      <c r="A158" s="88"/>
+      <c r="B158" s="86"/>
+      <c r="C158" s="84"/>
+      <c r="D158" s="86"/>
+      <c r="E158" s="84"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="95"/>
+      <c r="G158" s="82"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19352,50 +19355,50 @@
       </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="81">
+      <c r="A167" s="87">
         <v>139</v>
       </c>
-      <c r="B167" s="83">
+      <c r="B167" s="85">
         <v>46300</v>
       </c>
-      <c r="C167" s="85" t="s">
+      <c r="C167" s="83" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="83">
+      <c r="D167" s="85">
         <v>46295</v>
       </c>
-      <c r="E167" s="85" t="s">
+      <c r="E167" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F167" s="85" t="s">
+      <c r="F167" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="93" t="s">
+      <c r="G167" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="93" t="s">
+      <c r="H167" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="93" t="s">
+      <c r="J167" s="81" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A168" s="82"/>
-      <c r="B168" s="84"/>
-      <c r="C168" s="86"/>
-      <c r="D168" s="84"/>
-      <c r="E168" s="86"/>
-      <c r="F168" s="86"/>
-      <c r="G168" s="95"/>
-      <c r="H168" s="95"/>
+      <c r="A168" s="88"/>
+      <c r="B168" s="86"/>
+      <c r="C168" s="84"/>
+      <c r="D168" s="86"/>
+      <c r="E168" s="84"/>
+      <c r="F168" s="84"/>
+      <c r="G168" s="82"/>
+      <c r="H168" s="82"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="95"/>
+      <c r="J168" s="82"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -19462,50 +19465,50 @@
       </c>
     </row>
     <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A171" s="81">
+      <c r="A171" s="87">
         <v>142</v>
       </c>
-      <c r="B171" s="83">
+      <c r="B171" s="85">
         <v>46301</v>
       </c>
-      <c r="C171" s="85" t="s">
+      <c r="C171" s="83" t="s">
         <v>948</v>
       </c>
-      <c r="D171" s="83">
+      <c r="D171" s="85">
         <v>46301</v>
       </c>
-      <c r="E171" s="85" t="s">
+      <c r="E171" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F171" s="85" t="s">
+      <c r="F171" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="G171" s="93" t="s">
+      <c r="G171" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H171" s="93" t="s">
+      <c r="H171" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I171" s="28" t="s">
         <v>946</v>
       </c>
-      <c r="J171" s="93" t="s">
+      <c r="J171" s="81" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A172" s="82"/>
-      <c r="B172" s="84"/>
-      <c r="C172" s="86"/>
-      <c r="D172" s="84"/>
-      <c r="E172" s="86"/>
-      <c r="F172" s="86"/>
-      <c r="G172" s="95"/>
-      <c r="H172" s="95"/>
+      <c r="A172" s="88"/>
+      <c r="B172" s="86"/>
+      <c r="C172" s="84"/>
+      <c r="D172" s="86"/>
+      <c r="E172" s="84"/>
+      <c r="F172" s="84"/>
+      <c r="G172" s="82"/>
+      <c r="H172" s="82"/>
       <c r="I172" s="28" t="s">
         <v>947</v>
       </c>
-      <c r="J172" s="95"/>
+      <c r="J172" s="82"/>
     </row>
     <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A173" s="26">
@@ -26847,99 +26850,63 @@
     </row>
   </sheetData>
   <mergeCells count="174">
-    <mergeCell ref="J171:J172"/>
-    <mergeCell ref="H171:H172"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="F171:F172"/>
-    <mergeCell ref="E171:E172"/>
-    <mergeCell ref="D171:D172"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="J17:J18"/>
@@ -26964,63 +26931,99 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J171:J172"/>
+    <mergeCell ref="H171:H172"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="F171:F172"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A171:A172"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCC995A-FFAF-4DDF-9CD0-927BBEF00D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FCA675-57EF-47A4-BB5A-279F887606E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="958">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2892,6 +2892,9 @@
   </si>
   <si>
     <t>HeatSkin- Qty 3Nos.</t>
+  </si>
+  <si>
+    <t>Hybec Lamp 12v - Qty 2 Pcs</t>
   </si>
 </sst>
 </file>
@@ -3396,6 +3399,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3408,19 +3417,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3438,32 +3456,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3472,28 +3469,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3511,6 +3490,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3813,21 +3816,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3860,10 +3863,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3976,46 +3979,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="63"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="63"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4109,30 +4112,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4143,10 +4146,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4154,54 +4157,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="63"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="63"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="66">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4209,17 +4212,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="63"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="63"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4338,25 +4341,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="66">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4367,13 +4370,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="63"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="63"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4498,46 +4501,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="66">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="63"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="63"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4595,41 +4598,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="66">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="70"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="69"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4637,59 +4640,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="63"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="66">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="63"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="63"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4805,117 +4808,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="66">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="64" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="63"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="63"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="66">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="64" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="63"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="63"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="66">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="66">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="64" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4926,13 +4929,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="63"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="63"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4941,42 +4944,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="66">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="66">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="63"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="67"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="63"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="63"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="63"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5159,50 +5162,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="66">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="66">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="63"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="63"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="63"/>
-      <c r="J56" s="63"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5501,41 +5504,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="66">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="66">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="64" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="70"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="69"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5544,11 +5547,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5556,17 +5559,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="63"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="63"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="63"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="63"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5795,39 +5798,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="66">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="66">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="64" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="70"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="69"/>
+      <c r="F80" s="70"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5836,11 +5839,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="70"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5849,11 +5852,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="70"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="69"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
+      <c r="F82" s="70"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5861,17 +5864,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="63"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="63"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="63"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5903,22 +5906,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="66">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="64" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="66">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="64" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5926,57 +5929,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="63"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="65"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="66">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="64" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="66">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="64" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="63"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="65"/>
-      <c r="G88" s="63"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="63"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -6008,41 +6011,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="66">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="64">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="66">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="64" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="69"/>
-      <c r="D91" s="70"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="69"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6051,11 +6054,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="70"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="70"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="69"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="69"/>
+      <c r="F92" s="70"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6063,17 +6066,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="63"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="65"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="63"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="63"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6554,87 +6557,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="66">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="66">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="64" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="76" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="70"/>
+      <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="69"/>
+      <c r="F112" s="70"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="77"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="70"/>
+      <c r="B113" s="69"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="70"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="69"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="77"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="70"/>
+      <c r="B114" s="69"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="70"/>
+      <c r="D114" s="69"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="69"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="77"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="63"/>
-      <c r="B115" s="67"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="63"/>
-      <c r="F115" s="65"/>
-      <c r="G115" s="63"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="67"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="78"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7217,92 +7220,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="66">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="64" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="66">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="64" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="63"/>
-      <c r="B137" s="67"/>
-      <c r="C137" s="65"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="65"/>
-      <c r="G137" s="63"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
+      <c r="C137" s="67"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
+      <c r="F137" s="67"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="63"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="66">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="64" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="66">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="64" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="63"/>
-      <c r="B139" s="67"/>
-      <c r="C139" s="65"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="63"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="63"/>
-      <c r="J139" s="63"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7625,46 +7628,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="66">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="64" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="66">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="64" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="63"/>
-      <c r="B151" s="67"/>
-      <c r="C151" s="65"/>
-      <c r="D151" s="67"/>
-      <c r="E151" s="63"/>
-      <c r="F151" s="65"/>
-      <c r="G151" s="63"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
+      <c r="F151" s="67"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="63"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7693,41 +7696,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="66">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="64" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="66">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="64" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="69"/>
-      <c r="D154" s="70"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="69"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="69"/>
+      <c r="F154" s="70"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7736,11 +7739,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="70"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="70"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="69"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="69"/>
+      <c r="F155" s="70"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7748,17 +7751,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="63"/>
-      <c r="B156" s="67"/>
-      <c r="C156" s="65"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="63"/>
-      <c r="F156" s="65"/>
-      <c r="G156" s="63"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="67"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="63"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7819,41 +7822,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="66">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="64" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="66">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="64" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="70"/>
-      <c r="C160" s="69"/>
-      <c r="D160" s="70"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="69"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="69"/>
+      <c r="F160" s="70"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7862,11 +7865,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="70"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="70"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="69"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="69"/>
+      <c r="F161" s="70"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7875,11 +7878,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="70"/>
-      <c r="C162" s="69"/>
-      <c r="D162" s="70"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="70"/>
+      <c r="D162" s="69"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="69"/>
+      <c r="F162" s="70"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7887,17 +7890,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="63"/>
-      <c r="B163" s="67"/>
-      <c r="C163" s="65"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="65"/>
-      <c r="G163" s="63"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
+      <c r="F163" s="67"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="63"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8187,46 +8190,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="66">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="64" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="79">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="64" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="63"/>
-      <c r="B175" s="67"/>
-      <c r="C175" s="65"/>
-      <c r="D175" s="80"/>
-      <c r="E175" s="63"/>
-      <c r="F175" s="65"/>
-      <c r="G175" s="63"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="67"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="63"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8368,41 +8371,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="66">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="64" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="66">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="76" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="70"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="70"/>
+      <c r="B182" s="69"/>
+      <c r="C182" s="70"/>
+      <c r="D182" s="69"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="77"/>
+      <c r="F182" s="72"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8411,11 +8414,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="70"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="70"/>
+      <c r="B183" s="69"/>
+      <c r="C183" s="70"/>
+      <c r="D183" s="69"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="77"/>
+      <c r="F183" s="72"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8424,11 +8427,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="70"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="70"/>
+      <c r="B184" s="69"/>
+      <c r="C184" s="70"/>
+      <c r="D184" s="69"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="77"/>
+      <c r="F184" s="72"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8436,59 +8439,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="63"/>
-      <c r="B185" s="67"/>
-      <c r="C185" s="65"/>
-      <c r="D185" s="67"/>
-      <c r="E185" s="63"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="63"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
+      <c r="C185" s="67"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="63"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="66">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="64" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="66">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="64" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="63"/>
-      <c r="B187" s="67"/>
-      <c r="C187" s="65"/>
-      <c r="D187" s="67"/>
-      <c r="E187" s="63"/>
-      <c r="F187" s="65"/>
-      <c r="G187" s="63"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
+      <c r="F187" s="67"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="63"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9156,31 +9159,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="66">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="64" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="66">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="64" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9189,11 +9192,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="70"/>
-      <c r="C212" s="69"/>
-      <c r="D212" s="70"/>
+      <c r="B212" s="69"/>
+      <c r="C212" s="70"/>
+      <c r="D212" s="69"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="69"/>
+      <c r="F212" s="70"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9202,11 +9205,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="70"/>
-      <c r="C213" s="69"/>
-      <c r="D213" s="70"/>
+      <c r="B213" s="69"/>
+      <c r="C213" s="70"/>
+      <c r="D213" s="69"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="69"/>
+      <c r="F213" s="70"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9214,17 +9217,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="63"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="65"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="63"/>
-      <c r="F214" s="65"/>
-      <c r="G214" s="63"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
+      <c r="C214" s="67"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
+      <c r="F214" s="67"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="63"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9491,46 +9494,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="66">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="64" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="66">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="64" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="63"/>
-      <c r="B225" s="67"/>
-      <c r="C225" s="65"/>
-      <c r="D225" s="67"/>
-      <c r="E225" s="63"/>
-      <c r="F225" s="65"/>
-      <c r="G225" s="63"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
+      <c r="C225" s="67"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
+      <c r="F225" s="67"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="63"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9562,88 +9565,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="66">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="64" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="66">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="64" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="63"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="65"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="63"/>
-      <c r="F228" s="65"/>
-      <c r="G228" s="63"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
+      <c r="C228" s="67"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
+      <c r="F228" s="67"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="63"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="66">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="64" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="66">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="64" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="63"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="65"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="63"/>
-      <c r="F230" s="65"/>
-      <c r="G230" s="63"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
+      <c r="C230" s="67"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
+      <c r="F230" s="67"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="63"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9704,46 +9707,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="66">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="64" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="66">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="64" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="63"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="65"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="63"/>
-      <c r="F234" s="65"/>
-      <c r="G234" s="63"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
+      <c r="F234" s="67"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="63"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10384,46 +10387,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="62">
+      <c r="A257" s="64">
         <v>200</v>
       </c>
-      <c r="B257" s="66">
+      <c r="B257" s="62">
         <v>46300</v>
       </c>
-      <c r="C257" s="64" t="s">
+      <c r="C257" s="66" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="66">
+      <c r="D257" s="62">
         <v>46294</v>
       </c>
-      <c r="E257" s="62" t="s">
+      <c r="E257" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="64" t="s">
+      <c r="F257" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="62" t="s">
+      <c r="G257" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="62" t="s">
+      <c r="I257" s="64" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="63"/>
-      <c r="B258" s="67"/>
-      <c r="C258" s="65"/>
-      <c r="D258" s="67"/>
-      <c r="E258" s="63"/>
-      <c r="F258" s="65"/>
-      <c r="G258" s="63"/>
+      <c r="A258" s="65"/>
+      <c r="B258" s="63"/>
+      <c r="C258" s="67"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="65"/>
+      <c r="F258" s="67"/>
+      <c r="G258" s="65"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="63"/>
+      <c r="I258" s="65"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10513,46 +10516,46 @@
       </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A262" s="62">
+      <c r="A262" s="64">
         <v>204</v>
       </c>
-      <c r="B262" s="66">
+      <c r="B262" s="62">
         <v>46301</v>
       </c>
-      <c r="C262" s="64" t="s">
+      <c r="C262" s="66" t="s">
         <v>949</v>
       </c>
-      <c r="D262" s="66">
+      <c r="D262" s="62">
         <v>46301</v>
       </c>
-      <c r="E262" s="62" t="s">
+      <c r="E262" s="64" t="s">
         <v>308</v>
       </c>
-      <c r="F262" s="64" t="s">
+      <c r="F262" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G262" s="62" t="s">
+      <c r="G262" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H262" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="I262" s="62" t="s">
+      <c r="I262" s="64" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A263" s="63"/>
-      <c r="B263" s="67"/>
-      <c r="C263" s="65"/>
-      <c r="D263" s="67"/>
-      <c r="E263" s="63"/>
-      <c r="F263" s="65"/>
-      <c r="G263" s="63"/>
+      <c r="A263" s="65"/>
+      <c r="B263" s="63"/>
+      <c r="C263" s="67"/>
+      <c r="D263" s="63"/>
+      <c r="E263" s="65"/>
+      <c r="F263" s="67"/>
+      <c r="G263" s="65"/>
       <c r="H263" s="34" t="s">
         <v>951</v>
       </c>
-      <c r="I263" s="63"/>
+      <c r="I263" s="65"/>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A264" s="21">
@@ -14154,6 +14157,248 @@
     </row>
   </sheetData>
   <mergeCells count="264">
+    <mergeCell ref="I262:I263"/>
+    <mergeCell ref="G262:G263"/>
+    <mergeCell ref="F262:F263"/>
+    <mergeCell ref="E262:E263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="G257:G258"/>
+    <mergeCell ref="I257:I258"/>
+    <mergeCell ref="F257:F258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="A257:A258"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -14176,248 +14421,6 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="I262:I263"/>
-    <mergeCell ref="G262:G263"/>
-    <mergeCell ref="F262:F263"/>
-    <mergeCell ref="E262:E263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="G257:G258"/>
-    <mergeCell ref="I257:I258"/>
-    <mergeCell ref="F257:F258"/>
-    <mergeCell ref="E257:E258"/>
-    <mergeCell ref="D257:D258"/>
-    <mergeCell ref="C257:C258"/>
-    <mergeCell ref="B257:B258"/>
-    <mergeCell ref="A257:A258"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14449,23 +14452,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14533,28 +14536,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="90">
         <v>46098</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="90">
         <v>46098</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14575,13 +14578,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14600,13 +14603,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14624,14 +14627,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14742,50 +14745,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="64" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="65"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14820,110 +14823,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="87">
+      <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="83">
         <v>46105</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="83">
         <v>46105</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="81" t="s">
+      <c r="H14" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="81" t="s">
+      <c r="J14" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="88"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="82"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="87">
+      <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="83">
         <v>46105</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="83">
         <v>46105</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="81" t="s">
+      <c r="G17" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="81" t="s">
+      <c r="H17" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="81" t="s">
+      <c r="J17" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="82"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15246,50 +15249,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="87">
+      <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="85">
+      <c r="B29" s="83">
         <v>46121</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="85">
+      <c r="D29" s="83">
         <v>46121</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="81" t="s">
+      <c r="G29" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="81" t="s">
+      <c r="H29" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="81" t="s">
+      <c r="J29" s="93" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="88"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="82"/>
+      <c r="J30" s="95"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15382,74 +15385,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="87">
+      <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="85">
+      <c r="B34" s="83">
         <v>46128</v>
       </c>
-      <c r="C34" s="83" t="s">
+      <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="85">
+      <c r="D34" s="83">
         <v>46128</v>
       </c>
-      <c r="E34" s="83" t="s">
+      <c r="E34" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="83" t="s">
+      <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="81" t="s">
+      <c r="G34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="81" t="s">
+      <c r="H34" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="81" t="s">
+      <c r="J34" s="93" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="88"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="82"/>
+      <c r="J35" s="95"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="87">
+      <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="85">
+      <c r="B36" s="83">
         <v>46132</v>
       </c>
-      <c r="C36" s="83" t="s">
+      <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="85">
+      <c r="D36" s="83">
         <v>46129</v>
       </c>
-      <c r="E36" s="83" t="s">
+      <c r="E36" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="83" t="s">
+      <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="81" t="s">
+      <c r="G36" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="81" t="s">
+      <c r="H36" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15460,14 +15463,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="88"/>
-      <c r="B37" s="86"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15570,50 +15573,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="87">
+      <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="85">
+      <c r="B41" s="83">
         <v>46139</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="85">
+      <c r="D41" s="83">
         <v>46139</v>
       </c>
-      <c r="E41" s="83" t="s">
+      <c r="E41" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="81" t="s">
+      <c r="G41" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="81" t="s">
+      <c r="H41" s="93" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="81" t="s">
+      <c r="J41" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="88"/>
-      <c r="B42" s="86"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="86"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="82"/>
+      <c r="A42" s="82"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="86"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="82"/>
+      <c r="J42" s="95"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15744,28 +15747,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="87">
+      <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="85">
+      <c r="B47" s="83">
         <v>46149</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="85">
+      <c r="D47" s="83">
         <v>46148</v>
       </c>
-      <c r="E47" s="83" t="s">
+      <c r="E47" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="83" t="s">
+      <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="81" t="s">
+      <c r="G47" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="81" t="s">
+      <c r="H47" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15776,14 +15779,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="88"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="86"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
+      <c r="A48" s="82"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15792,28 +15795,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="87">
+      <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="85">
+      <c r="B49" s="83">
         <v>46149</v>
       </c>
-      <c r="C49" s="83" t="s">
+      <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="85">
+      <c r="D49" s="83">
         <v>46148</v>
       </c>
-      <c r="E49" s="83" t="s">
+      <c r="E49" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="83" t="s">
+      <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="81" t="s">
+      <c r="G49" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="81" t="s">
+      <c r="H49" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15824,14 +15827,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="88"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
+      <c r="A50" s="82"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16128,50 +16131,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="87">
+      <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="85">
+      <c r="B60" s="83">
         <v>46169</v>
       </c>
-      <c r="C60" s="83" t="s">
+      <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="85">
+      <c r="D60" s="83">
         <v>46169</v>
       </c>
-      <c r="E60" s="83" t="s">
+      <c r="E60" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="83" t="s">
+      <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="81" t="s">
+      <c r="G60" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="81" t="s">
+      <c r="H60" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="81" t="s">
+      <c r="J60" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="88"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="84"/>
-      <c r="D61" s="86"/>
-      <c r="E61" s="84"/>
-      <c r="F61" s="84"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="82"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="84"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="84"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="95"/>
+      <c r="H61" s="95"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="82"/>
+      <c r="J61" s="95"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16491,50 +16494,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="87">
+      <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="85">
+      <c r="B72" s="83">
         <v>46192</v>
       </c>
-      <c r="C72" s="83" t="s">
+      <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="85">
+      <c r="D72" s="83">
         <v>46191</v>
       </c>
-      <c r="E72" s="83" t="s">
+      <c r="E72" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="83" t="s">
+      <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="81" t="s">
+      <c r="G72" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="81" t="s">
+      <c r="H72" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="81" t="s">
+      <c r="J72" s="93" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="88"/>
-      <c r="B73" s="86"/>
-      <c r="C73" s="84"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="84"/>
-      <c r="F73" s="84"/>
-      <c r="G73" s="82"/>
-      <c r="H73" s="82"/>
+      <c r="A73" s="82"/>
+      <c r="B73" s="84"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="84"/>
+      <c r="E73" s="86"/>
+      <c r="F73" s="86"/>
+      <c r="G73" s="95"/>
+      <c r="H73" s="95"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="82"/>
+      <c r="J73" s="95"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16729,184 +16732,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="87">
+      <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="85">
+      <c r="B80" s="83">
         <v>46200</v>
       </c>
-      <c r="C80" s="83" t="s">
+      <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="85">
+      <c r="D80" s="83">
         <v>46200</v>
       </c>
-      <c r="E80" s="83" t="s">
+      <c r="E80" s="85" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="83" t="s">
+      <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="81" t="s">
+      <c r="G80" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="81" t="s">
+      <c r="H80" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="81" t="s">
+      <c r="J80" s="93" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="89"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="90"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
+      <c r="A81" s="96"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="92"/>
+      <c r="J81" s="94"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="89"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="92"/>
-      <c r="H82" s="92"/>
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="97"/>
+      <c r="E82" s="98"/>
+      <c r="F82" s="98"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="94"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="92"/>
+      <c r="J82" s="94"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="89"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="90"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
+      <c r="A83" s="96"/>
+      <c r="B83" s="97"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="98"/>
+      <c r="F83" s="98"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="94"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="94"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="88"/>
-      <c r="B84" s="86"/>
-      <c r="C84" s="84"/>
-      <c r="D84" s="86"/>
-      <c r="E84" s="84"/>
-      <c r="F84" s="84"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
+      <c r="A84" s="82"/>
+      <c r="B84" s="84"/>
+      <c r="C84" s="86"/>
+      <c r="D84" s="84"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="86"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="95"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="82"/>
+      <c r="J84" s="95"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="87">
+      <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="85">
+      <c r="B85" s="83">
         <v>46204</v>
       </c>
-      <c r="C85" s="83" t="s">
+      <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="85">
+      <c r="D85" s="83">
         <v>46204</v>
       </c>
-      <c r="E85" s="83" t="s">
+      <c r="E85" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="83" t="s">
+      <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="81" t="s">
+      <c r="G85" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="81" t="s">
+      <c r="H85" s="93" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="81" t="s">
+      <c r="J85" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="88"/>
-      <c r="B86" s="86"/>
-      <c r="C86" s="84"/>
-      <c r="D86" s="86"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="84"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
+      <c r="A86" s="82"/>
+      <c r="B86" s="84"/>
+      <c r="C86" s="86"/>
+      <c r="D86" s="84"/>
+      <c r="E86" s="86"/>
+      <c r="F86" s="86"/>
+      <c r="G86" s="95"/>
+      <c r="H86" s="95"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="82"/>
+      <c r="J86" s="95"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="87">
+      <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="85">
+      <c r="B87" s="83">
         <v>46210</v>
       </c>
-      <c r="C87" s="83" t="s">
+      <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="85">
+      <c r="D87" s="83">
         <v>46210</v>
       </c>
-      <c r="E87" s="83" t="s">
+      <c r="E87" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="83" t="s">
+      <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="81" t="s">
+      <c r="G87" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="81" t="s">
+      <c r="H87" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="81" t="s">
+      <c r="J87" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="88"/>
-      <c r="B88" s="86"/>
-      <c r="C88" s="84"/>
-      <c r="D88" s="86"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="84"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
+      <c r="A88" s="82"/>
+      <c r="B88" s="84"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="84"/>
+      <c r="E88" s="86"/>
+      <c r="F88" s="86"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="95"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="82"/>
+      <c r="J88" s="95"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17512,64 +17515,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="87">
+      <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="85">
+      <c r="B108" s="83">
         <v>46231</v>
       </c>
-      <c r="C108" s="83" t="s">
+      <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="85">
+      <c r="D108" s="83">
         <v>46231</v>
       </c>
-      <c r="E108" s="83" t="s">
+      <c r="E108" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="83" t="s">
+      <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="81" t="s">
+      <c r="G108" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="81" t="s">
+      <c r="H108" s="93" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="81" t="s">
+      <c r="J108" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="89"/>
-      <c r="B109" s="90"/>
-      <c r="C109" s="91"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="91"/>
-      <c r="F109" s="91"/>
-      <c r="G109" s="92"/>
-      <c r="H109" s="92"/>
+      <c r="A109" s="96"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="97"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="94"/>
+      <c r="H109" s="94"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="92"/>
+      <c r="J109" s="94"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="88"/>
-      <c r="B110" s="86"/>
-      <c r="C110" s="84"/>
-      <c r="D110" s="86"/>
-      <c r="E110" s="84"/>
-      <c r="F110" s="84"/>
-      <c r="G110" s="82"/>
-      <c r="H110" s="82"/>
+      <c r="A110" s="82"/>
+      <c r="B110" s="84"/>
+      <c r="C110" s="86"/>
+      <c r="D110" s="84"/>
+      <c r="E110" s="86"/>
+      <c r="F110" s="86"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="95"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="82"/>
+      <c r="J110" s="95"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17988,50 +17991,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="87">
+      <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="85">
+      <c r="B124" s="83">
         <v>46263</v>
       </c>
-      <c r="C124" s="83" t="s">
+      <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="85">
+      <c r="D124" s="83">
         <v>46260</v>
       </c>
-      <c r="E124" s="83" t="s">
+      <c r="E124" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="83" t="s">
+      <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="81" t="s">
+      <c r="G124" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="81" t="s">
+      <c r="H124" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="81" t="s">
+      <c r="J124" s="93" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="88"/>
-      <c r="B125" s="86"/>
-      <c r="C125" s="84"/>
-      <c r="D125" s="86"/>
-      <c r="E125" s="84"/>
-      <c r="F125" s="84"/>
-      <c r="G125" s="82"/>
-      <c r="H125" s="82"/>
+      <c r="A125" s="82"/>
+      <c r="B125" s="84"/>
+      <c r="C125" s="86"/>
+      <c r="D125" s="84"/>
+      <c r="E125" s="86"/>
+      <c r="F125" s="86"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="82"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -19041,25 +19044,25 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="87">
+      <c r="A157" s="81">
         <v>130</v>
       </c>
-      <c r="B157" s="85">
+      <c r="B157" s="83">
         <v>46294</v>
       </c>
-      <c r="C157" s="83" t="s">
+      <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="85">
+      <c r="D157" s="83">
         <v>46294</v>
       </c>
-      <c r="E157" s="83" t="s">
+      <c r="E157" s="85" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="81" t="s">
+      <c r="G157" s="93" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -19076,15 +19079,15 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="88"/>
-      <c r="B158" s="86"/>
-      <c r="C158" s="84"/>
-      <c r="D158" s="86"/>
-      <c r="E158" s="84"/>
+      <c r="A158" s="82"/>
+      <c r="B158" s="84"/>
+      <c r="C158" s="86"/>
+      <c r="D158" s="84"/>
+      <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="82"/>
+      <c r="G158" s="95"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19355,50 +19358,50 @@
       </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="87">
+      <c r="A167" s="81">
         <v>139</v>
       </c>
-      <c r="B167" s="85">
+      <c r="B167" s="83">
         <v>46300</v>
       </c>
-      <c r="C167" s="83" t="s">
+      <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="85">
+      <c r="D167" s="83">
         <v>46295</v>
       </c>
-      <c r="E167" s="83" t="s">
+      <c r="E167" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F167" s="83" t="s">
+      <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="81" t="s">
+      <c r="G167" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="81" t="s">
+      <c r="H167" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="81" t="s">
+      <c r="J167" s="93" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A168" s="88"/>
-      <c r="B168" s="86"/>
-      <c r="C168" s="84"/>
-      <c r="D168" s="86"/>
-      <c r="E168" s="84"/>
-      <c r="F168" s="84"/>
-      <c r="G168" s="82"/>
-      <c r="H168" s="82"/>
+      <c r="A168" s="82"/>
+      <c r="B168" s="84"/>
+      <c r="C168" s="86"/>
+      <c r="D168" s="84"/>
+      <c r="E168" s="86"/>
+      <c r="F168" s="86"/>
+      <c r="G168" s="95"/>
+      <c r="H168" s="95"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="82"/>
+      <c r="J168" s="95"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -19465,50 +19468,50 @@
       </c>
     </row>
     <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A171" s="87">
+      <c r="A171" s="81">
         <v>142</v>
       </c>
-      <c r="B171" s="85">
+      <c r="B171" s="83">
         <v>46301</v>
       </c>
-      <c r="C171" s="83" t="s">
+      <c r="C171" s="85" t="s">
         <v>948</v>
       </c>
-      <c r="D171" s="85">
+      <c r="D171" s="83">
         <v>46301</v>
       </c>
-      <c r="E171" s="83" t="s">
+      <c r="E171" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F171" s="83" t="s">
+      <c r="F171" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="G171" s="81" t="s">
+      <c r="G171" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H171" s="81" t="s">
+      <c r="H171" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I171" s="28" t="s">
         <v>946</v>
       </c>
-      <c r="J171" s="81" t="s">
+      <c r="J171" s="93" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A172" s="88"/>
-      <c r="B172" s="86"/>
-      <c r="C172" s="84"/>
-      <c r="D172" s="86"/>
-      <c r="E172" s="84"/>
-      <c r="F172" s="84"/>
-      <c r="G172" s="82"/>
-      <c r="H172" s="82"/>
+      <c r="A172" s="82"/>
+      <c r="B172" s="84"/>
+      <c r="C172" s="86"/>
+      <c r="D172" s="84"/>
+      <c r="E172" s="86"/>
+      <c r="F172" s="86"/>
+      <c r="G172" s="95"/>
+      <c r="H172" s="95"/>
       <c r="I172" s="28" t="s">
         <v>947</v>
       </c>
-      <c r="J172" s="82"/>
+      <c r="J172" s="95"/>
     </row>
     <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A173" s="26">
@@ -19578,15 +19581,38 @@
       <c r="A175" s="26">
         <v>145</v>
       </c>
-      <c r="B175" s="43"/>
-      <c r="D175" s="43"/>
-      <c r="G175" s="43"/>
-      <c r="H175" s="43"/>
-      <c r="I175" s="28"/>
-      <c r="J175" s="43"/>
+      <c r="B175" s="52">
+        <v>46305</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D175" s="52">
+        <v>46305</v>
+      </c>
+      <c r="E175" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="G175" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H175" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I175" s="28" t="s">
+        <v>957</v>
+      </c>
+      <c r="J175" s="43" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="176" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A176" s="26"/>
+      <c r="A176" s="26">
+        <v>146</v>
+      </c>
       <c r="B176" s="43"/>
       <c r="D176" s="43"/>
       <c r="G176" s="43"/>
@@ -26850,6 +26876,156 @@
     </row>
   </sheetData>
   <mergeCells count="174">
+    <mergeCell ref="J171:J172"/>
+    <mergeCell ref="H171:H172"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="F171:F172"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
@@ -26874,156 +27050,6 @@
     <mergeCell ref="C80:C84"/>
     <mergeCell ref="D80:D84"/>
     <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="J171:J172"/>
-    <mergeCell ref="H171:H172"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="F171:F172"/>
-    <mergeCell ref="E171:E172"/>
-    <mergeCell ref="D171:D172"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A171:A172"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FCA675-57EF-47A4-BB5A-279F887606E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6515B973-BBA6-49EB-A764-26D12A5A5A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="961">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2895,6 +2895,15 @@
   </si>
   <si>
     <t>Hybec Lamp 12v - Qty 2 Pcs</t>
+  </si>
+  <si>
+    <t>Cuvettes For Bioelab Fully Auto Analyser - Qty 100 Nos / Photometer Halogen Lamp Assy  Bioelab FA 6V/10w- Qty 2 Nos.</t>
+  </si>
+  <si>
+    <t>Peerless Biotech Pvt Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Photometer Halogen Lamp Assy Bioelab SA 6V/10W - Qty 10Nos</t>
   </si>
 </sst>
 </file>
@@ -3399,12 +3408,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3417,28 +3420,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3456,11 +3450,32 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3469,10 +3484,28 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3490,30 +3523,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3816,21 +3825,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3863,10 +3872,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3979,46 +3988,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="66">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="63"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4112,30 +4121,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="66">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4146,10 +4155,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4157,54 +4166,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="63"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="66">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="66">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="69"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4212,17 +4221,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4341,25 +4350,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="66">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="66">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4370,13 +4379,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4501,46 +4510,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="66">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="66">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4598,41 +4607,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="66">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="66">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4640,59 +4649,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="66">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="66">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4808,117 +4817,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="66">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="63"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="66">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="63"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="66">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="66">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4929,13 +4938,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4944,42 +4953,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="66">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="64">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="66">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="63"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5162,50 +5171,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="66">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="66">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="63"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5504,41 +5513,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="66">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="66">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
+      <c r="F68" s="69"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5547,11 +5556,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
+      <c r="F69" s="69"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5559,17 +5568,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="63"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="63"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5798,39 +5807,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="66">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="66">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="69"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
+      <c r="F80" s="69"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5839,11 +5848,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5852,11 +5861,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
+      <c r="F82" s="69"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5864,17 +5873,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="63"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="63"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5906,22 +5915,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="66">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="66">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="64" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5929,57 +5938,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="67"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="65"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="66">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="66">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="A88" s="63"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="63"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="63"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -6011,41 +6020,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="66">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="64">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="66">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6054,11 +6063,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
+      <c r="F92" s="69"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6066,17 +6075,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="65"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="63"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6557,87 +6566,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="66">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="66">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="69"/>
+      <c r="D113" s="70"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="69"/>
+      <c r="D114" s="70"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
+      <c r="F114" s="69"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="67"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="63"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7220,92 +7229,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="66">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="66">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="67"/>
+      <c r="C137" s="65"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="63"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="66">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="66">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="65"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="63"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7628,46 +7637,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="66">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="66">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
-      <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="A151" s="63"/>
+      <c r="B151" s="67"/>
+      <c r="C151" s="65"/>
+      <c r="D151" s="67"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="63"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="63"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7696,41 +7705,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="66">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="66">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
-      <c r="D154" s="69"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="70"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
+      <c r="F154" s="69"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7739,11 +7748,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
-      <c r="D155" s="69"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="70"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
+      <c r="F155" s="69"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7751,17 +7760,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
-      <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="A156" s="63"/>
+      <c r="B156" s="67"/>
+      <c r="C156" s="65"/>
+      <c r="D156" s="67"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="65"/>
+      <c r="G156" s="63"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="63"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7822,41 +7831,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="66">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="66">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="69"/>
+      <c r="B160" s="70"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="70"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
+      <c r="F160" s="69"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7865,11 +7874,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="69"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="70"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
+      <c r="F161" s="69"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7878,11 +7887,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="69"/>
+      <c r="B162" s="70"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="70"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
+      <c r="F162" s="69"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7890,17 +7899,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
-      <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="A163" s="63"/>
+      <c r="B163" s="67"/>
+      <c r="C163" s="65"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="65"/>
+      <c r="G163" s="63"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="63"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8190,46 +8199,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="66">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
-      <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="A175" s="63"/>
+      <c r="B175" s="67"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="63"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="63"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8371,41 +8380,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="66">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="64" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="66">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
-      <c r="D182" s="69"/>
+      <c r="B182" s="70"/>
+      <c r="C182" s="69"/>
+      <c r="D182" s="70"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
+      <c r="F182" s="77"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8414,11 +8423,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
-      <c r="D183" s="69"/>
+      <c r="B183" s="70"/>
+      <c r="C183" s="69"/>
+      <c r="D183" s="70"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
+      <c r="F183" s="77"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8427,11 +8436,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
-      <c r="D184" s="69"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="69"/>
+      <c r="D184" s="70"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
+      <c r="F184" s="77"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8439,59 +8448,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
-      <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="A185" s="63"/>
+      <c r="B185" s="67"/>
+      <c r="C185" s="65"/>
+      <c r="D185" s="67"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="63"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="63"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="66">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="64" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="66">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
-      <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
-      <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="A187" s="63"/>
+      <c r="B187" s="67"/>
+      <c r="C187" s="65"/>
+      <c r="D187" s="67"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="65"/>
+      <c r="G187" s="63"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="63"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9159,31 +9168,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="66">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="64" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="66">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9192,11 +9201,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
-      <c r="D212" s="69"/>
+      <c r="B212" s="70"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
+      <c r="F212" s="69"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9205,11 +9214,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
-      <c r="D213" s="69"/>
+      <c r="B213" s="70"/>
+      <c r="C213" s="69"/>
+      <c r="D213" s="70"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
+      <c r="F213" s="69"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9217,17 +9226,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
-      <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="67"/>
+      <c r="C214" s="65"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="65"/>
+      <c r="G214" s="63"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="63"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9494,46 +9503,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="66">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="64" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="66">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="64" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
-      <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
-      <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="67"/>
+      <c r="C225" s="65"/>
+      <c r="D225" s="67"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="63"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="63"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9565,88 +9574,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="66">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="66">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
-      <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="A228" s="63"/>
+      <c r="B228" s="67"/>
+      <c r="C228" s="65"/>
+      <c r="D228" s="67"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="65"/>
+      <c r="G228" s="63"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="63"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="66">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="66">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
-      <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="A230" s="63"/>
+      <c r="B230" s="67"/>
+      <c r="C230" s="65"/>
+      <c r="D230" s="67"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="65"/>
+      <c r="G230" s="63"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="63"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9707,46 +9716,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="66">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="64" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="66">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
-      <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="A234" s="63"/>
+      <c r="B234" s="67"/>
+      <c r="C234" s="65"/>
+      <c r="D234" s="67"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="65"/>
+      <c r="G234" s="63"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="63"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10387,46 +10396,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="64">
+      <c r="A257" s="62">
         <v>200</v>
       </c>
-      <c r="B257" s="62">
+      <c r="B257" s="66">
         <v>46300</v>
       </c>
-      <c r="C257" s="66" t="s">
+      <c r="C257" s="64" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="62">
+      <c r="D257" s="66">
         <v>46294</v>
       </c>
-      <c r="E257" s="64" t="s">
+      <c r="E257" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="66" t="s">
+      <c r="F257" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="64" t="s">
+      <c r="G257" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="64" t="s">
+      <c r="I257" s="62" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="63"/>
-      <c r="E258" s="65"/>
-      <c r="F258" s="67"/>
-      <c r="G258" s="65"/>
+      <c r="A258" s="63"/>
+      <c r="B258" s="67"/>
+      <c r="C258" s="65"/>
+      <c r="D258" s="67"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="65"/>
+      <c r="G258" s="63"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="65"/>
+      <c r="I258" s="63"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10516,46 +10525,46 @@
       </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A262" s="64">
+      <c r="A262" s="62">
         <v>204</v>
       </c>
-      <c r="B262" s="62">
+      <c r="B262" s="66">
         <v>46301</v>
       </c>
-      <c r="C262" s="66" t="s">
+      <c r="C262" s="64" t="s">
         <v>949</v>
       </c>
-      <c r="D262" s="62">
+      <c r="D262" s="66">
         <v>46301</v>
       </c>
-      <c r="E262" s="64" t="s">
+      <c r="E262" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="F262" s="66" t="s">
+      <c r="F262" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G262" s="64" t="s">
+      <c r="G262" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H262" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="I262" s="64" t="s">
+      <c r="I262" s="62" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A263" s="65"/>
-      <c r="B263" s="63"/>
-      <c r="C263" s="67"/>
-      <c r="D263" s="63"/>
-      <c r="E263" s="65"/>
-      <c r="F263" s="67"/>
-      <c r="G263" s="65"/>
+      <c r="A263" s="63"/>
+      <c r="B263" s="67"/>
+      <c r="C263" s="65"/>
+      <c r="D263" s="67"/>
+      <c r="E263" s="63"/>
+      <c r="F263" s="65"/>
+      <c r="G263" s="63"/>
       <c r="H263" s="34" t="s">
         <v>951</v>
       </c>
-      <c r="I263" s="65"/>
+      <c r="I263" s="63"/>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A264" s="21">
@@ -14157,248 +14166,6 @@
     </row>
   </sheetData>
   <mergeCells count="264">
-    <mergeCell ref="I262:I263"/>
-    <mergeCell ref="G262:G263"/>
-    <mergeCell ref="F262:F263"/>
-    <mergeCell ref="E262:E263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="G257:G258"/>
-    <mergeCell ref="I257:I258"/>
-    <mergeCell ref="F257:F258"/>
-    <mergeCell ref="E257:E258"/>
-    <mergeCell ref="D257:D258"/>
-    <mergeCell ref="C257:C258"/>
-    <mergeCell ref="B257:B258"/>
-    <mergeCell ref="A257:A258"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -14421,6 +14188,248 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="I262:I263"/>
+    <mergeCell ref="G262:G263"/>
+    <mergeCell ref="F262:F263"/>
+    <mergeCell ref="E262:E263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="G257:G258"/>
+    <mergeCell ref="I257:I258"/>
+    <mergeCell ref="F257:F258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="A257:A258"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14452,23 +14461,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="97"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14536,28 +14545,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="64">
+      <c r="A4" s="62">
         <v>1</v>
       </c>
-      <c r="B4" s="90">
+      <c r="B4" s="98">
         <v>46098</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="98">
         <v>46098</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="64" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14578,13 +14587,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14603,13 +14612,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14627,14 +14636,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14745,50 +14754,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="64">
+      <c r="A11" s="62">
         <v>5</v>
       </c>
-      <c r="B11" s="99">
+      <c r="B11" s="93">
         <v>46102</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="93">
         <v>46095</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="64" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="67"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14823,110 +14832,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="81">
+      <c r="A14" s="87">
         <v>7</v>
       </c>
-      <c r="B14" s="83">
+      <c r="B14" s="85">
         <v>46105</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="83">
+      <c r="D14" s="85">
         <v>46105</v>
       </c>
-      <c r="E14" s="85" t="s">
+      <c r="E14" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="93" t="s">
+      <c r="G14" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="93" t="s">
+      <c r="H14" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="93" t="s">
+      <c r="J14" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="96"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
+      <c r="A15" s="89"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="94"/>
+      <c r="J15" s="92"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="82"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="84"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="95"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="81">
+      <c r="A17" s="87">
         <v>8</v>
       </c>
-      <c r="B17" s="83">
+      <c r="B17" s="85">
         <v>46105</v>
       </c>
-      <c r="C17" s="85" t="s">
+      <c r="C17" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="83">
+      <c r="D17" s="85">
         <v>46105</v>
       </c>
-      <c r="E17" s="85" t="s">
+      <c r="E17" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="85" t="s">
+      <c r="F17" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="93" t="s">
+      <c r="G17" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="81" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="93" t="s">
+      <c r="J17" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="82"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="95"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15249,50 +15258,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="81">
+      <c r="A29" s="87">
         <v>19</v>
       </c>
-      <c r="B29" s="83">
+      <c r="B29" s="85">
         <v>46121</v>
       </c>
-      <c r="C29" s="85" t="s">
+      <c r="C29" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="85">
         <v>46121</v>
       </c>
-      <c r="E29" s="85" t="s">
+      <c r="E29" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="85" t="s">
+      <c r="F29" s="83" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="93" t="s">
+      <c r="G29" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="93" t="s">
+      <c r="H29" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="93" t="s">
+      <c r="J29" s="81" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="82"/>
-      <c r="B30" s="84"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="95"/>
-      <c r="H30" s="95"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="95"/>
+      <c r="J30" s="82"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15385,74 +15394,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="81">
+      <c r="A34" s="87">
         <v>23</v>
       </c>
-      <c r="B34" s="83">
+      <c r="B34" s="85">
         <v>46128</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="83">
+      <c r="D34" s="85">
         <v>46128</v>
       </c>
-      <c r="E34" s="85" t="s">
+      <c r="E34" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="93" t="s">
+      <c r="G34" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="93" t="s">
+      <c r="H34" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="93" t="s">
+      <c r="J34" s="81" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="82"/>
-      <c r="B35" s="84"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="86"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="95"/>
+      <c r="J35" s="82"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="81">
+      <c r="A36" s="87">
         <v>24</v>
       </c>
-      <c r="B36" s="83">
+      <c r="B36" s="85">
         <v>46132</v>
       </c>
-      <c r="C36" s="85" t="s">
+      <c r="C36" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="83">
+      <c r="D36" s="85">
         <v>46129</v>
       </c>
-      <c r="E36" s="85" t="s">
+      <c r="E36" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="85" t="s">
+      <c r="F36" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="93" t="s">
+      <c r="G36" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="93" t="s">
+      <c r="H36" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15463,14 +15472,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="82"/>
-      <c r="B37" s="84"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15573,50 +15582,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="81">
+      <c r="A41" s="87">
         <v>28</v>
       </c>
-      <c r="B41" s="83">
+      <c r="B41" s="85">
         <v>46139</v>
       </c>
-      <c r="C41" s="85" t="s">
+      <c r="C41" s="83" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="83">
+      <c r="D41" s="85">
         <v>46139</v>
       </c>
-      <c r="E41" s="85" t="s">
+      <c r="E41" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="85" t="s">
+      <c r="F41" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="93" t="s">
+      <c r="G41" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="93" t="s">
+      <c r="H41" s="81" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="93" t="s">
+      <c r="J41" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="82"/>
-      <c r="B42" s="84"/>
-      <c r="C42" s="86"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
+      <c r="A42" s="88"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="82"/>
+      <c r="H42" s="82"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="95"/>
+      <c r="J42" s="82"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15747,28 +15756,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="81">
+      <c r="A47" s="87">
         <v>33</v>
       </c>
-      <c r="B47" s="83">
+      <c r="B47" s="85">
         <v>46149</v>
       </c>
-      <c r="C47" s="85" t="s">
+      <c r="C47" s="83" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="83">
+      <c r="D47" s="85">
         <v>46148</v>
       </c>
-      <c r="E47" s="85" t="s">
+      <c r="E47" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="85" t="s">
+      <c r="F47" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="93" t="s">
+      <c r="G47" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="93" t="s">
+      <c r="H47" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15779,14 +15788,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="82"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="86"/>
-      <c r="F48" s="86"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="95"/>
+      <c r="A48" s="88"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="82"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15795,28 +15804,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="81">
+      <c r="A49" s="87">
         <v>34</v>
       </c>
-      <c r="B49" s="83">
+      <c r="B49" s="85">
         <v>46149</v>
       </c>
-      <c r="C49" s="85" t="s">
+      <c r="C49" s="83" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="83">
+      <c r="D49" s="85">
         <v>46148</v>
       </c>
-      <c r="E49" s="85" t="s">
+      <c r="E49" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="85" t="s">
+      <c r="F49" s="83" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="93" t="s">
+      <c r="G49" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="93" t="s">
+      <c r="H49" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15827,14 +15836,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="82"/>
-      <c r="B50" s="84"/>
-      <c r="C50" s="86"/>
-      <c r="D50" s="84"/>
-      <c r="E50" s="86"/>
-      <c r="F50" s="86"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="95"/>
+      <c r="A50" s="88"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="82"/>
+      <c r="H50" s="82"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16131,50 +16140,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="81">
+      <c r="A60" s="87">
         <v>44</v>
       </c>
-      <c r="B60" s="83">
+      <c r="B60" s="85">
         <v>46169</v>
       </c>
-      <c r="C60" s="85" t="s">
+      <c r="C60" s="83" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="83">
+      <c r="D60" s="85">
         <v>46169</v>
       </c>
-      <c r="E60" s="85" t="s">
+      <c r="E60" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="85" t="s">
+      <c r="F60" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="93" t="s">
+      <c r="G60" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="93" t="s">
+      <c r="H60" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="93" t="s">
+      <c r="J60" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="82"/>
-      <c r="B61" s="84"/>
-      <c r="C61" s="86"/>
-      <c r="D61" s="84"/>
-      <c r="E61" s="86"/>
-      <c r="F61" s="86"/>
-      <c r="G61" s="95"/>
-      <c r="H61" s="95"/>
+      <c r="A61" s="88"/>
+      <c r="B61" s="86"/>
+      <c r="C61" s="84"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="84"/>
+      <c r="F61" s="84"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="82"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="95"/>
+      <c r="J61" s="82"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16494,50 +16503,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="81">
+      <c r="A72" s="87">
         <v>55</v>
       </c>
-      <c r="B72" s="83">
+      <c r="B72" s="85">
         <v>46192</v>
       </c>
-      <c r="C72" s="85" t="s">
+      <c r="C72" s="83" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="83">
+      <c r="D72" s="85">
         <v>46191</v>
       </c>
-      <c r="E72" s="85" t="s">
+      <c r="E72" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="85" t="s">
+      <c r="F72" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="93" t="s">
+      <c r="G72" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="93" t="s">
+      <c r="H72" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="93" t="s">
+      <c r="J72" s="81" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="82"/>
-      <c r="B73" s="84"/>
-      <c r="C73" s="86"/>
-      <c r="D73" s="84"/>
-      <c r="E73" s="86"/>
-      <c r="F73" s="86"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
+      <c r="A73" s="88"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="84"/>
+      <c r="D73" s="86"/>
+      <c r="E73" s="84"/>
+      <c r="F73" s="84"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="95"/>
+      <c r="J73" s="82"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16732,184 +16741,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="81">
+      <c r="A80" s="87">
         <v>62</v>
       </c>
-      <c r="B80" s="83">
+      <c r="B80" s="85">
         <v>46200</v>
       </c>
-      <c r="C80" s="85" t="s">
+      <c r="C80" s="83" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="83">
+      <c r="D80" s="85">
         <v>46200</v>
       </c>
-      <c r="E80" s="85" t="s">
+      <c r="E80" s="83" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="85" t="s">
+      <c r="F80" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="93" t="s">
+      <c r="G80" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="93" t="s">
+      <c r="H80" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="93" t="s">
+      <c r="J80" s="81" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="96"/>
-      <c r="B81" s="97"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
+      <c r="A81" s="89"/>
+      <c r="B81" s="90"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="90"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="94"/>
+      <c r="J81" s="92"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="96"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="98"/>
-      <c r="D82" s="97"/>
-      <c r="E82" s="98"/>
-      <c r="F82" s="98"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="94"/>
+      <c r="A82" s="89"/>
+      <c r="B82" s="90"/>
+      <c r="C82" s="91"/>
+      <c r="D82" s="90"/>
+      <c r="E82" s="91"/>
+      <c r="F82" s="91"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="94"/>
+      <c r="J82" s="92"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="96"/>
-      <c r="B83" s="97"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="97"/>
-      <c r="E83" s="98"/>
-      <c r="F83" s="98"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="94"/>
+      <c r="A83" s="89"/>
+      <c r="B83" s="90"/>
+      <c r="C83" s="91"/>
+      <c r="D83" s="90"/>
+      <c r="E83" s="91"/>
+      <c r="F83" s="91"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="94"/>
+      <c r="J83" s="92"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="82"/>
-      <c r="B84" s="84"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="84"/>
-      <c r="E84" s="86"/>
-      <c r="F84" s="86"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="95"/>
+      <c r="A84" s="88"/>
+      <c r="B84" s="86"/>
+      <c r="C84" s="84"/>
+      <c r="D84" s="86"/>
+      <c r="E84" s="84"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="82"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="95"/>
+      <c r="J84" s="82"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="81">
+      <c r="A85" s="87">
         <v>63</v>
       </c>
-      <c r="B85" s="83">
+      <c r="B85" s="85">
         <v>46204</v>
       </c>
-      <c r="C85" s="85" t="s">
+      <c r="C85" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="83">
+      <c r="D85" s="85">
         <v>46204</v>
       </c>
-      <c r="E85" s="85" t="s">
+      <c r="E85" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="85" t="s">
+      <c r="F85" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="93" t="s">
+      <c r="G85" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="93" t="s">
+      <c r="H85" s="81" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="93" t="s">
+      <c r="J85" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="82"/>
-      <c r="B86" s="84"/>
-      <c r="C86" s="86"/>
-      <c r="D86" s="84"/>
-      <c r="E86" s="86"/>
-      <c r="F86" s="86"/>
-      <c r="G86" s="95"/>
-      <c r="H86" s="95"/>
+      <c r="A86" s="88"/>
+      <c r="B86" s="86"/>
+      <c r="C86" s="84"/>
+      <c r="D86" s="86"/>
+      <c r="E86" s="84"/>
+      <c r="F86" s="84"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="95"/>
+      <c r="J86" s="82"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="81">
+      <c r="A87" s="87">
         <v>64</v>
       </c>
-      <c r="B87" s="83">
+      <c r="B87" s="85">
         <v>46210</v>
       </c>
-      <c r="C87" s="85" t="s">
+      <c r="C87" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="83">
+      <c r="D87" s="85">
         <v>46210</v>
       </c>
-      <c r="E87" s="85" t="s">
+      <c r="E87" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="85" t="s">
+      <c r="F87" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="93" t="s">
+      <c r="G87" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="93" t="s">
+      <c r="H87" s="81" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="93" t="s">
+      <c r="J87" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="82"/>
-      <c r="B88" s="84"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="84"/>
-      <c r="E88" s="86"/>
-      <c r="F88" s="86"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="95"/>
+      <c r="A88" s="88"/>
+      <c r="B88" s="86"/>
+      <c r="C88" s="84"/>
+      <c r="D88" s="86"/>
+      <c r="E88" s="84"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="95"/>
+      <c r="J88" s="82"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17515,64 +17524,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="81">
+      <c r="A108" s="87">
         <v>84</v>
       </c>
-      <c r="B108" s="83">
+      <c r="B108" s="85">
         <v>46231</v>
       </c>
-      <c r="C108" s="85" t="s">
+      <c r="C108" s="83" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="83">
+      <c r="D108" s="85">
         <v>46231</v>
       </c>
-      <c r="E108" s="85" t="s">
+      <c r="E108" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="85" t="s">
+      <c r="F108" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="93" t="s">
+      <c r="G108" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="93" t="s">
+      <c r="H108" s="81" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="93" t="s">
+      <c r="J108" s="81" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="96"/>
-      <c r="B109" s="97"/>
-      <c r="C109" s="98"/>
-      <c r="D109" s="97"/>
-      <c r="E109" s="98"/>
-      <c r="F109" s="98"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="94"/>
+      <c r="A109" s="89"/>
+      <c r="B109" s="90"/>
+      <c r="C109" s="91"/>
+      <c r="D109" s="90"/>
+      <c r="E109" s="91"/>
+      <c r="F109" s="91"/>
+      <c r="G109" s="92"/>
+      <c r="H109" s="92"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="94"/>
+      <c r="J109" s="92"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="82"/>
-      <c r="B110" s="84"/>
-      <c r="C110" s="86"/>
-      <c r="D110" s="84"/>
-      <c r="E110" s="86"/>
-      <c r="F110" s="86"/>
-      <c r="G110" s="95"/>
-      <c r="H110" s="95"/>
+      <c r="A110" s="88"/>
+      <c r="B110" s="86"/>
+      <c r="C110" s="84"/>
+      <c r="D110" s="86"/>
+      <c r="E110" s="84"/>
+      <c r="F110" s="84"/>
+      <c r="G110" s="82"/>
+      <c r="H110" s="82"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="95"/>
+      <c r="J110" s="82"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -17991,50 +18000,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="81">
+      <c r="A124" s="87">
         <v>98</v>
       </c>
-      <c r="B124" s="83">
+      <c r="B124" s="85">
         <v>46263</v>
       </c>
-      <c r="C124" s="85" t="s">
+      <c r="C124" s="83" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="83">
+      <c r="D124" s="85">
         <v>46260</v>
       </c>
-      <c r="E124" s="85" t="s">
+      <c r="E124" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="85" t="s">
+      <c r="F124" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="93" t="s">
+      <c r="G124" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="93" t="s">
+      <c r="H124" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="93" t="s">
+      <c r="J124" s="81" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="82"/>
-      <c r="B125" s="84"/>
-      <c r="C125" s="86"/>
-      <c r="D125" s="84"/>
-      <c r="E125" s="86"/>
-      <c r="F125" s="86"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="95"/>
+      <c r="A125" s="88"/>
+      <c r="B125" s="86"/>
+      <c r="C125" s="84"/>
+      <c r="D125" s="86"/>
+      <c r="E125" s="84"/>
+      <c r="F125" s="84"/>
+      <c r="G125" s="82"/>
+      <c r="H125" s="82"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="95"/>
+      <c r="J125" s="82"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -19044,25 +19053,25 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="81">
+      <c r="A157" s="87">
         <v>130</v>
       </c>
-      <c r="B157" s="83">
+      <c r="B157" s="85">
         <v>46294</v>
       </c>
-      <c r="C157" s="85" t="s">
+      <c r="C157" s="83" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="83">
+      <c r="D157" s="85">
         <v>46294</v>
       </c>
-      <c r="E157" s="85" t="s">
+      <c r="E157" s="83" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="93" t="s">
+      <c r="G157" s="81" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -19079,15 +19088,15 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="82"/>
-      <c r="B158" s="84"/>
-      <c r="C158" s="86"/>
-      <c r="D158" s="84"/>
-      <c r="E158" s="86"/>
+      <c r="A158" s="88"/>
+      <c r="B158" s="86"/>
+      <c r="C158" s="84"/>
+      <c r="D158" s="86"/>
+      <c r="E158" s="84"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="95"/>
+      <c r="G158" s="82"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19358,50 +19367,50 @@
       </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="81">
+      <c r="A167" s="87">
         <v>139</v>
       </c>
-      <c r="B167" s="83">
+      <c r="B167" s="85">
         <v>46300</v>
       </c>
-      <c r="C167" s="85" t="s">
+      <c r="C167" s="83" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="83">
+      <c r="D167" s="85">
         <v>46295</v>
       </c>
-      <c r="E167" s="85" t="s">
+      <c r="E167" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="F167" s="85" t="s">
+      <c r="F167" s="83" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="93" t="s">
+      <c r="G167" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="93" t="s">
+      <c r="H167" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="93" t="s">
+      <c r="J167" s="81" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A168" s="82"/>
-      <c r="B168" s="84"/>
-      <c r="C168" s="86"/>
-      <c r="D168" s="84"/>
-      <c r="E168" s="86"/>
-      <c r="F168" s="86"/>
-      <c r="G168" s="95"/>
-      <c r="H168" s="95"/>
+      <c r="A168" s="88"/>
+      <c r="B168" s="86"/>
+      <c r="C168" s="84"/>
+      <c r="D168" s="86"/>
+      <c r="E168" s="84"/>
+      <c r="F168" s="84"/>
+      <c r="G168" s="82"/>
+      <c r="H168" s="82"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="95"/>
+      <c r="J168" s="82"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -19468,50 +19477,50 @@
       </c>
     </row>
     <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A171" s="81">
+      <c r="A171" s="87">
         <v>142</v>
       </c>
-      <c r="B171" s="83">
+      <c r="B171" s="85">
         <v>46301</v>
       </c>
-      <c r="C171" s="85" t="s">
+      <c r="C171" s="83" t="s">
         <v>948</v>
       </c>
-      <c r="D171" s="83">
+      <c r="D171" s="85">
         <v>46301</v>
       </c>
-      <c r="E171" s="85" t="s">
+      <c r="E171" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="F171" s="85" t="s">
+      <c r="F171" s="83" t="s">
         <v>160</v>
       </c>
-      <c r="G171" s="93" t="s">
+      <c r="G171" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="H171" s="93" t="s">
+      <c r="H171" s="81" t="s">
         <v>48</v>
       </c>
       <c r="I171" s="28" t="s">
         <v>946</v>
       </c>
-      <c r="J171" s="93" t="s">
+      <c r="J171" s="81" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A172" s="82"/>
-      <c r="B172" s="84"/>
-      <c r="C172" s="86"/>
-      <c r="D172" s="84"/>
-      <c r="E172" s="86"/>
-      <c r="F172" s="86"/>
-      <c r="G172" s="95"/>
-      <c r="H172" s="95"/>
+      <c r="A172" s="88"/>
+      <c r="B172" s="86"/>
+      <c r="C172" s="84"/>
+      <c r="D172" s="86"/>
+      <c r="E172" s="84"/>
+      <c r="F172" s="84"/>
+      <c r="G172" s="82"/>
+      <c r="H172" s="82"/>
       <c r="I172" s="28" t="s">
         <v>947</v>
       </c>
-      <c r="J172" s="95"/>
+      <c r="J172" s="82"/>
     </row>
     <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A173" s="26">
@@ -19613,21 +19622,62 @@
       <c r="A176" s="26">
         <v>146</v>
       </c>
-      <c r="B176" s="43"/>
-      <c r="D176" s="43"/>
-      <c r="G176" s="43"/>
-      <c r="H176" s="43"/>
-      <c r="I176" s="28"/>
-      <c r="J176" s="43"/>
+      <c r="B176" s="52">
+        <v>46307</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D176" s="52">
+        <v>46307</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="10" t="s">
+        <v>959</v>
+      </c>
+      <c r="G176" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H176" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I176" s="28" t="s">
+        <v>958</v>
+      </c>
+      <c r="J176" s="43" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="177" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A177" s="26"/>
-      <c r="B177" s="43"/>
-      <c r="D177" s="43"/>
-      <c r="G177" s="43"/>
-      <c r="H177" s="43"/>
-      <c r="I177" s="28"/>
-      <c r="J177" s="43"/>
+      <c r="A177" s="26">
+        <v>147</v>
+      </c>
+      <c r="B177" s="52">
+        <v>46307</v>
+      </c>
+      <c r="D177" s="52">
+        <v>46307</v>
+      </c>
+      <c r="E177" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G177" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H177" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="I177" s="28" t="s">
+        <v>960</v>
+      </c>
+      <c r="J177" s="43" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="178" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A178" s="26"/>
@@ -26876,99 +26926,63 @@
     </row>
   </sheetData>
   <mergeCells count="174">
-    <mergeCell ref="J171:J172"/>
-    <mergeCell ref="H171:H172"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="F171:F172"/>
-    <mergeCell ref="E171:E172"/>
-    <mergeCell ref="D171:D172"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="D124:D125"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="H4:H7"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="E124:E125"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="J108:J110"/>
+    <mergeCell ref="J124:J125"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="D80:D84"/>
+    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="F17:F18"/>
     <mergeCell ref="J17:J18"/>
@@ -26993,63 +27007,99 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="C124:C125"/>
-    <mergeCell ref="D124:D125"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="H4:H7"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="E4:E7"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="E124:E125"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="J108:J110"/>
-    <mergeCell ref="J124:J125"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="D80:D84"/>
-    <mergeCell ref="E80:E84"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J171:J172"/>
+    <mergeCell ref="H171:H172"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="F171:F172"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A171:A172"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6515B973-BBA6-49EB-A764-26D12A5A5A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D21190-DEF6-4542-AE54-03CB92758CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="963">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2904,6 +2904,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Photometer Halogen Lamp Assy Bioelab SA 6V/10W - Qty 10Nos</t>
+  </si>
+  <si>
+    <t>AM/DOM/0017/2627</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -3408,6 +3414,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3420,19 +3432,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3450,32 +3471,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3484,28 +3484,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3523,6 +3505,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3825,21 +3831,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="76" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="73"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="78"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3872,10 +3878,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="75"/>
+      <c r="L2" s="80"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3988,46 +3994,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="62">
+      <c r="A7" s="64">
         <v>4</v>
       </c>
-      <c r="B7" s="66">
+      <c r="B7" s="62">
         <v>46099</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="D7" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="62" t="s">
+      <c r="E7" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="64" t="s">
+      <c r="F7" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="64" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="63"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="65"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="63"/>
+      <c r="I8" s="65"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4121,30 +4127,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="62" t="s">
+      <c r="I11" s="64" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="62">
+      <c r="A12" s="64">
         <v>8</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="62">
         <v>46104</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="64" t="s">
+      <c r="F12" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4155,10 +4161,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4166,54 +4172,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="63"/>
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="65"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="63"/>
+      <c r="I14" s="65"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="62">
+      <c r="A15" s="64">
         <v>9</v>
       </c>
-      <c r="B15" s="66">
+      <c r="B15" s="62">
         <v>46105</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="C15" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="62">
         <v>46104</v>
       </c>
-      <c r="E15" s="62" t="s">
+      <c r="E15" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="64" t="s">
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="62" t="s">
+      <c r="I15" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="69"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
+      <c r="F16" s="70"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4221,17 +4227,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="63"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="63"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="65"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="63"/>
+      <c r="I17" s="65"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4350,25 +4356,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="62">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="66">
+      <c r="B22" s="62">
         <v>46112</v>
       </c>
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="62">
         <v>46105</v>
       </c>
-      <c r="E22" s="62" t="s">
+      <c r="E22" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="64" t="s">
+      <c r="F22" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4379,13 +4385,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="63"/>
-      <c r="B23" s="67"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="63"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="65"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4510,46 +4516,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="62">
+      <c r="A28" s="64">
         <v>19</v>
       </c>
-      <c r="B28" s="66">
+      <c r="B28" s="62">
         <v>46121</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="66">
+      <c r="D28" s="62">
         <v>46120</v>
       </c>
-      <c r="E28" s="62" t="s">
+      <c r="E28" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="F28" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="62" t="s">
+      <c r="I28" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="63"/>
-      <c r="B29" s="67"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="63"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="65"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="63"/>
+      <c r="I29" s="65"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4607,41 +4613,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="62">
+      <c r="A32" s="64">
         <v>22</v>
       </c>
-      <c r="B32" s="66">
+      <c r="B32" s="62">
         <v>46122</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C32" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="62">
         <v>46120</v>
       </c>
-      <c r="E32" s="62" t="s">
+      <c r="E32" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="64" t="s">
+      <c r="F32" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="62" t="s">
+      <c r="I32" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="70"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="69"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="69"/>
+      <c r="F33" s="70"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4649,59 +4655,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="67"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="63"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="63"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="65"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="63"/>
+      <c r="I34" s="65"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="62">
+      <c r="A35" s="64">
         <v>23</v>
       </c>
-      <c r="B35" s="66">
+      <c r="B35" s="62">
         <v>46123</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="C35" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="66">
+      <c r="D35" s="62">
         <v>46121</v>
       </c>
-      <c r="E35" s="62" t="s">
+      <c r="E35" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="64" t="s">
+      <c r="F35" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="62" t="s">
+      <c r="I35" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="63"/>
-      <c r="B36" s="67"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="63"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="63"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4817,117 +4823,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="62">
+      <c r="A41" s="64">
         <v>28</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="64" t="s">
+      <c r="C41" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="66">
+      <c r="D41" s="62">
         <v>46123</v>
       </c>
-      <c r="E41" s="62" t="s">
+      <c r="E41" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="64" t="s">
+      <c r="F41" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="62" t="s">
+      <c r="I41" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="62" t="s">
+      <c r="J41" s="64" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="63"/>
-      <c r="B42" s="63"/>
-      <c r="C42" s="65"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="63"/>
+      <c r="A42" s="65"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="65"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="63"/>
-      <c r="J42" s="63"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="62">
+      <c r="A43" s="64">
         <v>29</v>
       </c>
-      <c r="B43" s="66">
+      <c r="B43" s="62">
         <v>46126</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="C43" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="66">
+      <c r="D43" s="62">
         <v>46122</v>
       </c>
-      <c r="E43" s="62" t="s">
+      <c r="E43" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="64" t="s">
+      <c r="F43" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="62" t="s">
+      <c r="J43" s="64" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="63"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="65"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="63"/>
+      <c r="A44" s="65"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="65"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="65"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="63"/>
-      <c r="J44" s="63"/>
+      <c r="I44" s="65"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="62">
+      <c r="A45" s="64">
         <v>30</v>
       </c>
-      <c r="B45" s="66">
+      <c r="B45" s="62">
         <v>46127</v>
       </c>
-      <c r="C45" s="64" t="s">
+      <c r="C45" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="66">
+      <c r="D45" s="62">
         <v>46125</v>
       </c>
-      <c r="E45" s="62" t="s">
+      <c r="E45" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="64" t="s">
+      <c r="F45" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4938,13 +4944,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="63"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="63"/>
+      <c r="A46" s="65"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="65"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4953,42 +4959,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="62">
+      <c r="A47" s="64">
         <v>31</v>
       </c>
-      <c r="B47" s="66">
+      <c r="B47" s="62">
         <v>46127</v>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="66">
         <v>360142</v>
       </c>
-      <c r="D47" s="66">
+      <c r="D47" s="62">
         <v>46120</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="64" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="63"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="67"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="63"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="63"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="65"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="63"/>
+      <c r="I48" s="65"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5171,50 +5177,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="62">
+      <c r="A55" s="64">
         <v>38</v>
       </c>
-      <c r="B55" s="66">
+      <c r="B55" s="62">
         <v>46137</v>
       </c>
-      <c r="C55" s="64" t="s">
+      <c r="C55" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="66">
+      <c r="D55" s="62">
         <v>46137</v>
       </c>
-      <c r="E55" s="62" t="s">
+      <c r="E55" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="66" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="62" t="s">
+      <c r="G55" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="62" t="s">
+      <c r="I55" s="64" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="62" t="s">
+      <c r="J55" s="64" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="63"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="63"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="65"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="63"/>
-      <c r="J56" s="63"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5513,41 +5519,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="62">
+      <c r="A67" s="64">
         <v>49</v>
       </c>
-      <c r="B67" s="66">
+      <c r="B67" s="62">
         <v>46146</v>
       </c>
-      <c r="C67" s="64" t="s">
+      <c r="C67" s="66" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="66">
+      <c r="D67" s="62">
         <v>46142</v>
       </c>
-      <c r="E67" s="62" t="s">
+      <c r="E67" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="64" t="s">
+      <c r="F67" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="62" t="s">
+      <c r="G67" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="62" t="s">
+      <c r="I67" s="64" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="69"/>
-      <c r="D68" s="70"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="69"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="69"/>
+      <c r="F68" s="70"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5556,11 +5562,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="70"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="69"/>
+      <c r="F69" s="70"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5568,17 +5574,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="63"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="63"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="63"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="67"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="67"/>
+      <c r="G70" s="65"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="63"/>
+      <c r="I70" s="65"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5807,39 +5813,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="62">
+      <c r="A79" s="64">
         <v>58</v>
       </c>
-      <c r="B79" s="66">
+      <c r="B79" s="62">
         <v>46148</v>
       </c>
-      <c r="C79" s="64" t="s">
+      <c r="C79" s="66" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="66">
+      <c r="D79" s="62">
         <v>46143</v>
       </c>
-      <c r="E79" s="62" t="s">
+      <c r="E79" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="64" t="s">
+      <c r="F79" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="62" t="s">
+      <c r="G79" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="62"/>
+      <c r="I79" s="64"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="70"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="70"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="69"/>
+      <c r="F80" s="70"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5848,11 +5854,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="70"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="70"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="69"/>
+      <c r="F81" s="70"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5861,11 +5867,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="70"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="70"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="69"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="69"/>
+      <c r="F82" s="70"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5873,17 +5879,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="63"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="67"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="63"/>
+      <c r="A83" s="65"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="67"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="67"/>
+      <c r="G83" s="65"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="63"/>
+      <c r="I83" s="65"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5915,22 +5921,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="62">
+      <c r="A85" s="64">
         <v>60</v>
       </c>
-      <c r="B85" s="66">
+      <c r="B85" s="62">
         <v>46149</v>
       </c>
-      <c r="C85" s="64" t="s">
+      <c r="C85" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="66">
+      <c r="D85" s="62">
         <v>46142</v>
       </c>
-      <c r="E85" s="62" t="s">
+      <c r="E85" s="64" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="64" t="s">
+      <c r="F85" s="66" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5938,57 +5944,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="63"/>
-      <c r="B86" s="67"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="65"/>
+      <c r="A86" s="65"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="65"/>
+      <c r="F86" s="67"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="62">
+      <c r="A87" s="64">
         <v>61</v>
       </c>
-      <c r="B87" s="66">
+      <c r="B87" s="62">
         <v>46149</v>
       </c>
-      <c r="C87" s="64" t="s">
+      <c r="C87" s="66" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="66">
+      <c r="D87" s="62">
         <v>46142</v>
       </c>
-      <c r="E87" s="62" t="s">
+      <c r="E87" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="64" t="s">
+      <c r="F87" s="66" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="62" t="s">
+      <c r="G87" s="64" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="62" t="s">
+      <c r="I87" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="63"/>
-      <c r="B88" s="67"/>
-      <c r="C88" s="65"/>
-      <c r="D88" s="67"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="65"/>
-      <c r="G88" s="63"/>
+      <c r="A88" s="65"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="67"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="65"/>
+      <c r="F88" s="67"/>
+      <c r="G88" s="65"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="63"/>
+      <c r="I88" s="65"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -6020,41 +6026,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="62">
+      <c r="A90" s="64">
         <v>63</v>
       </c>
-      <c r="B90" s="66">
+      <c r="B90" s="62">
         <v>46149</v>
       </c>
-      <c r="C90" s="64">
+      <c r="C90" s="66">
         <v>33</v>
       </c>
-      <c r="D90" s="66">
+      <c r="D90" s="62">
         <v>46140</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="64" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="64" t="s">
+      <c r="F90" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="62" t="s">
+      <c r="G90" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="62" t="s">
+      <c r="I90" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="69"/>
-      <c r="D91" s="70"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="70"/>
+      <c r="D91" s="69"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="69"/>
+      <c r="F91" s="70"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6063,11 +6069,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="70"/>
-      <c r="C92" s="69"/>
-      <c r="D92" s="70"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="69"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="69"/>
+      <c r="F92" s="70"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6075,17 +6081,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="63"/>
-      <c r="B93" s="67"/>
-      <c r="C93" s="65"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="65"/>
-      <c r="G93" s="63"/>
+      <c r="A93" s="65"/>
+      <c r="B93" s="63"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="65"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="65"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="63"/>
+      <c r="I93" s="65"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6566,87 +6572,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="62">
+      <c r="A111" s="64">
         <v>81</v>
       </c>
-      <c r="B111" s="66">
+      <c r="B111" s="62">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="66">
+      <c r="D111" s="62">
         <v>46164</v>
       </c>
-      <c r="E111" s="62" t="s">
+      <c r="E111" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="64" t="s">
+      <c r="F111" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="62" t="s">
+      <c r="G111" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="76" t="s">
+      <c r="I111" s="71" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="70"/>
+      <c r="B112" s="69"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="70"/>
+      <c r="D112" s="69"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="69"/>
+      <c r="F112" s="70"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="77"/>
+      <c r="I112" s="72"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="70"/>
+      <c r="B113" s="69"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="70"/>
+      <c r="D113" s="69"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="69"/>
+      <c r="F113" s="70"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="77"/>
+      <c r="I113" s="72"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="70"/>
+      <c r="B114" s="69"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="70"/>
+      <c r="D114" s="69"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="69"/>
+      <c r="F114" s="70"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="77"/>
+      <c r="I114" s="72"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="63"/>
-      <c r="B115" s="67"/>
+      <c r="A115" s="65"/>
+      <c r="B115" s="63"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="67"/>
-      <c r="E115" s="63"/>
-      <c r="F115" s="65"/>
-      <c r="G115" s="63"/>
+      <c r="D115" s="63"/>
+      <c r="E115" s="65"/>
+      <c r="F115" s="67"/>
+      <c r="G115" s="65"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="78"/>
+      <c r="I115" s="73"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7229,92 +7235,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="62">
+      <c r="A136" s="64">
         <v>102</v>
       </c>
-      <c r="B136" s="66">
+      <c r="B136" s="62">
         <v>46181</v>
       </c>
-      <c r="C136" s="64" t="s">
+      <c r="C136" s="66" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="66">
+      <c r="D136" s="62">
         <v>46177</v>
       </c>
-      <c r="E136" s="62" t="s">
+      <c r="E136" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="64" t="s">
+      <c r="F136" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="62" t="s">
+      <c r="G136" s="64" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="62" t="s">
+      <c r="I136" s="64" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="63"/>
-      <c r="B137" s="67"/>
-      <c r="C137" s="65"/>
-      <c r="D137" s="67"/>
-      <c r="E137" s="63"/>
-      <c r="F137" s="65"/>
-      <c r="G137" s="63"/>
+      <c r="A137" s="65"/>
+      <c r="B137" s="63"/>
+      <c r="C137" s="67"/>
+      <c r="D137" s="63"/>
+      <c r="E137" s="65"/>
+      <c r="F137" s="67"/>
+      <c r="G137" s="65"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="63"/>
+      <c r="I137" s="65"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="62">
+      <c r="A138" s="64">
         <v>103</v>
       </c>
-      <c r="B138" s="66">
+      <c r="B138" s="62">
         <v>46181</v>
       </c>
-      <c r="C138" s="64" t="s">
+      <c r="C138" s="66" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="66">
+      <c r="D138" s="62">
         <v>46177</v>
       </c>
-      <c r="E138" s="62" t="s">
+      <c r="E138" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="64" t="s">
+      <c r="F138" s="66" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="62" t="s">
+      <c r="G138" s="64" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="62" t="s">
+      <c r="I138" s="64" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="62" t="s">
+      <c r="J138" s="64" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="63"/>
-      <c r="B139" s="67"/>
-      <c r="C139" s="65"/>
-      <c r="D139" s="67"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="63"/>
+      <c r="A139" s="65"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="67"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="65"/>
+      <c r="F139" s="67"/>
+      <c r="G139" s="65"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="63"/>
-      <c r="J139" s="63"/>
+      <c r="I139" s="65"/>
+      <c r="J139" s="65"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7637,46 +7643,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="62">
+      <c r="A150" s="64">
         <v>114</v>
       </c>
-      <c r="B150" s="66">
+      <c r="B150" s="62">
         <v>46189</v>
       </c>
-      <c r="C150" s="64" t="s">
+      <c r="C150" s="66" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="66">
+      <c r="D150" s="62">
         <v>46186</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="64" t="s">
+      <c r="F150" s="66" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="62" t="s">
+      <c r="I150" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="63"/>
-      <c r="B151" s="67"/>
-      <c r="C151" s="65"/>
-      <c r="D151" s="67"/>
-      <c r="E151" s="63"/>
-      <c r="F151" s="65"/>
-      <c r="G151" s="63"/>
+      <c r="A151" s="65"/>
+      <c r="B151" s="63"/>
+      <c r="C151" s="67"/>
+      <c r="D151" s="63"/>
+      <c r="E151" s="65"/>
+      <c r="F151" s="67"/>
+      <c r="G151" s="65"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="63"/>
+      <c r="I151" s="65"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7705,41 +7711,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="62">
+      <c r="A153" s="64">
         <v>116</v>
       </c>
-      <c r="B153" s="66">
+      <c r="B153" s="62">
         <v>46191</v>
       </c>
-      <c r="C153" s="64" t="s">
+      <c r="C153" s="66" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="66">
+      <c r="D153" s="62">
         <v>46188</v>
       </c>
-      <c r="E153" s="62" t="s">
+      <c r="E153" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="64" t="s">
+      <c r="F153" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="62" t="s">
+      <c r="G153" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="62" t="s">
+      <c r="I153" s="64" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="70"/>
-      <c r="C154" s="69"/>
-      <c r="D154" s="70"/>
+      <c r="B154" s="69"/>
+      <c r="C154" s="70"/>
+      <c r="D154" s="69"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="69"/>
+      <c r="F154" s="70"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7748,11 +7754,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="70"/>
-      <c r="C155" s="69"/>
-      <c r="D155" s="70"/>
+      <c r="B155" s="69"/>
+      <c r="C155" s="70"/>
+      <c r="D155" s="69"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="69"/>
+      <c r="F155" s="70"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7760,17 +7766,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="63"/>
-      <c r="B156" s="67"/>
-      <c r="C156" s="65"/>
-      <c r="D156" s="67"/>
-      <c r="E156" s="63"/>
-      <c r="F156" s="65"/>
-      <c r="G156" s="63"/>
+      <c r="A156" s="65"/>
+      <c r="B156" s="63"/>
+      <c r="C156" s="67"/>
+      <c r="D156" s="63"/>
+      <c r="E156" s="65"/>
+      <c r="F156" s="67"/>
+      <c r="G156" s="65"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="63"/>
+      <c r="I156" s="65"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7831,41 +7837,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="62">
+      <c r="A159" s="64">
         <v>119</v>
       </c>
-      <c r="B159" s="66">
+      <c r="B159" s="62">
         <v>46203</v>
       </c>
-      <c r="C159" s="64" t="s">
+      <c r="C159" s="66" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="66">
+      <c r="D159" s="62">
         <v>46198</v>
       </c>
-      <c r="E159" s="62" t="s">
+      <c r="E159" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="64" t="s">
+      <c r="F159" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="64" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="62" t="s">
+      <c r="I159" s="64" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="70"/>
-      <c r="C160" s="69"/>
-      <c r="D160" s="70"/>
+      <c r="B160" s="69"/>
+      <c r="C160" s="70"/>
+      <c r="D160" s="69"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="69"/>
+      <c r="F160" s="70"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7874,11 +7880,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="70"/>
-      <c r="C161" s="69"/>
-      <c r="D161" s="70"/>
+      <c r="B161" s="69"/>
+      <c r="C161" s="70"/>
+      <c r="D161" s="69"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="69"/>
+      <c r="F161" s="70"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7887,11 +7893,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="70"/>
-      <c r="C162" s="69"/>
-      <c r="D162" s="70"/>
+      <c r="B162" s="69"/>
+      <c r="C162" s="70"/>
+      <c r="D162" s="69"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="69"/>
+      <c r="F162" s="70"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7899,17 +7905,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="63"/>
-      <c r="B163" s="67"/>
-      <c r="C163" s="65"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="63"/>
-      <c r="F163" s="65"/>
-      <c r="G163" s="63"/>
+      <c r="A163" s="65"/>
+      <c r="B163" s="63"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="63"/>
+      <c r="E163" s="65"/>
+      <c r="F163" s="67"/>
+      <c r="G163" s="65"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="63"/>
+      <c r="I163" s="65"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8199,46 +8205,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="62">
+      <c r="A174" s="64">
         <v>130</v>
       </c>
-      <c r="B174" s="66">
+      <c r="B174" s="62">
         <v>46217</v>
       </c>
-      <c r="C174" s="64" t="s">
+      <c r="C174" s="66" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="79">
+      <c r="D174" s="74">
         <v>46210</v>
       </c>
-      <c r="E174" s="62" t="s">
+      <c r="E174" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="64" t="s">
+      <c r="F174" s="66" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="62" t="s">
+      <c r="G174" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="62" t="s">
+      <c r="I174" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="63"/>
-      <c r="B175" s="67"/>
-      <c r="C175" s="65"/>
-      <c r="D175" s="80"/>
-      <c r="E175" s="63"/>
-      <c r="F175" s="65"/>
-      <c r="G175" s="63"/>
+      <c r="A175" s="65"/>
+      <c r="B175" s="63"/>
+      <c r="C175" s="67"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="65"/>
+      <c r="F175" s="67"/>
+      <c r="G175" s="65"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="63"/>
+      <c r="I175" s="65"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8380,41 +8386,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="62">
+      <c r="A181" s="64">
         <v>136</v>
       </c>
-      <c r="B181" s="66">
+      <c r="B181" s="62">
         <v>46223</v>
       </c>
-      <c r="C181" s="64" t="s">
+      <c r="C181" s="66" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="66">
+      <c r="D181" s="62">
         <v>46219</v>
       </c>
-      <c r="E181" s="62" t="s">
+      <c r="E181" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="76" t="s">
+      <c r="F181" s="71" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="62" t="s">
+      <c r="G181" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="62" t="s">
+      <c r="I181" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="70"/>
-      <c r="C182" s="69"/>
-      <c r="D182" s="70"/>
+      <c r="B182" s="69"/>
+      <c r="C182" s="70"/>
+      <c r="D182" s="69"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="77"/>
+      <c r="F182" s="72"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8423,11 +8429,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="70"/>
-      <c r="C183" s="69"/>
-      <c r="D183" s="70"/>
+      <c r="B183" s="69"/>
+      <c r="C183" s="70"/>
+      <c r="D183" s="69"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="77"/>
+      <c r="F183" s="72"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8436,11 +8442,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="70"/>
-      <c r="C184" s="69"/>
-      <c r="D184" s="70"/>
+      <c r="B184" s="69"/>
+      <c r="C184" s="70"/>
+      <c r="D184" s="69"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="77"/>
+      <c r="F184" s="72"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8448,59 +8454,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="63"/>
-      <c r="B185" s="67"/>
-      <c r="C185" s="65"/>
-      <c r="D185" s="67"/>
-      <c r="E185" s="63"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="63"/>
+      <c r="A185" s="65"/>
+      <c r="B185" s="63"/>
+      <c r="C185" s="67"/>
+      <c r="D185" s="63"/>
+      <c r="E185" s="65"/>
+      <c r="F185" s="73"/>
+      <c r="G185" s="65"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="63"/>
+      <c r="I185" s="65"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="62">
+      <c r="A186" s="64">
         <v>137</v>
       </c>
-      <c r="B186" s="66">
+      <c r="B186" s="62">
         <v>46223</v>
       </c>
-      <c r="C186" s="64" t="s">
+      <c r="C186" s="66" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="66">
+      <c r="D186" s="62">
         <v>46219</v>
       </c>
-      <c r="E186" s="62" t="s">
+      <c r="E186" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="64" t="s">
+      <c r="F186" s="66" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="62" t="s">
+      <c r="G186" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="62" t="s">
+      <c r="I186" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="63"/>
-      <c r="B187" s="67"/>
-      <c r="C187" s="65"/>
-      <c r="D187" s="67"/>
-      <c r="E187" s="63"/>
-      <c r="F187" s="65"/>
-      <c r="G187" s="63"/>
+      <c r="A187" s="65"/>
+      <c r="B187" s="63"/>
+      <c r="C187" s="67"/>
+      <c r="D187" s="63"/>
+      <c r="E187" s="65"/>
+      <c r="F187" s="67"/>
+      <c r="G187" s="65"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="63"/>
+      <c r="I187" s="65"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9168,31 +9174,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="62">
+      <c r="A211" s="64">
         <v>161</v>
       </c>
-      <c r="B211" s="66">
+      <c r="B211" s="62">
         <v>46241</v>
       </c>
-      <c r="C211" s="64" t="s">
+      <c r="C211" s="66" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="66">
+      <c r="D211" s="62">
         <v>46241</v>
       </c>
-      <c r="E211" s="62" t="s">
+      <c r="E211" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="64" t="s">
+      <c r="F211" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="62" t="s">
+      <c r="G211" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="62" t="s">
+      <c r="I211" s="64" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9201,11 +9207,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="70"/>
-      <c r="C212" s="69"/>
-      <c r="D212" s="70"/>
+      <c r="B212" s="69"/>
+      <c r="C212" s="70"/>
+      <c r="D212" s="69"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="69"/>
+      <c r="F212" s="70"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9214,11 +9220,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="70"/>
-      <c r="C213" s="69"/>
-      <c r="D213" s="70"/>
+      <c r="B213" s="69"/>
+      <c r="C213" s="70"/>
+      <c r="D213" s="69"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="69"/>
+      <c r="F213" s="70"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9226,17 +9232,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="63"/>
-      <c r="B214" s="67"/>
-      <c r="C214" s="65"/>
-      <c r="D214" s="67"/>
-      <c r="E214" s="63"/>
-      <c r="F214" s="65"/>
-      <c r="G214" s="63"/>
+      <c r="A214" s="65"/>
+      <c r="B214" s="63"/>
+      <c r="C214" s="67"/>
+      <c r="D214" s="63"/>
+      <c r="E214" s="65"/>
+      <c r="F214" s="67"/>
+      <c r="G214" s="65"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="63"/>
+      <c r="I214" s="65"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9503,46 +9509,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="62">
+      <c r="A224" s="64">
         <v>171</v>
       </c>
-      <c r="B224" s="66">
+      <c r="B224" s="62">
         <v>46263</v>
       </c>
-      <c r="C224" s="64" t="s">
+      <c r="C224" s="66" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="66">
+      <c r="D224" s="62">
         <v>46261</v>
       </c>
-      <c r="E224" s="62" t="s">
+      <c r="E224" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="64" t="s">
+      <c r="F224" s="66" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="62" t="s">
+      <c r="G224" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="62" t="s">
+      <c r="I224" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="63"/>
-      <c r="B225" s="67"/>
-      <c r="C225" s="65"/>
-      <c r="D225" s="67"/>
-      <c r="E225" s="63"/>
-      <c r="F225" s="65"/>
-      <c r="G225" s="63"/>
+      <c r="A225" s="65"/>
+      <c r="B225" s="63"/>
+      <c r="C225" s="67"/>
+      <c r="D225" s="63"/>
+      <c r="E225" s="65"/>
+      <c r="F225" s="67"/>
+      <c r="G225" s="65"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="63"/>
+      <c r="I225" s="65"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9574,88 +9580,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="62">
+      <c r="A227" s="64">
         <v>173</v>
       </c>
-      <c r="B227" s="66">
+      <c r="B227" s="62">
         <v>46263</v>
       </c>
-      <c r="C227" s="64" t="s">
+      <c r="C227" s="66" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="66">
+      <c r="D227" s="62">
         <v>46259</v>
       </c>
-      <c r="E227" s="62" t="s">
+      <c r="E227" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="64" t="s">
+      <c r="F227" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="62" t="s">
+      <c r="G227" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="62" t="s">
+      <c r="I227" s="64" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="63"/>
-      <c r="B228" s="67"/>
-      <c r="C228" s="65"/>
-      <c r="D228" s="67"/>
-      <c r="E228" s="63"/>
-      <c r="F228" s="65"/>
-      <c r="G228" s="63"/>
+      <c r="A228" s="65"/>
+      <c r="B228" s="63"/>
+      <c r="C228" s="67"/>
+      <c r="D228" s="63"/>
+      <c r="E228" s="65"/>
+      <c r="F228" s="67"/>
+      <c r="G228" s="65"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="63"/>
+      <c r="I228" s="65"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="62">
+      <c r="A229" s="64">
         <v>174</v>
       </c>
-      <c r="B229" s="66">
+      <c r="B229" s="62">
         <v>46266</v>
       </c>
-      <c r="C229" s="64" t="s">
+      <c r="C229" s="66" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="66">
+      <c r="D229" s="62">
         <v>46266</v>
       </c>
-      <c r="E229" s="62" t="s">
+      <c r="E229" s="64" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="64" t="s">
+      <c r="F229" s="66" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="62" t="s">
+      <c r="G229" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="62" t="s">
+      <c r="I229" s="64" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="63"/>
-      <c r="B230" s="67"/>
-      <c r="C230" s="65"/>
-      <c r="D230" s="67"/>
-      <c r="E230" s="63"/>
-      <c r="F230" s="65"/>
-      <c r="G230" s="63"/>
+      <c r="A230" s="65"/>
+      <c r="B230" s="63"/>
+      <c r="C230" s="67"/>
+      <c r="D230" s="63"/>
+      <c r="E230" s="65"/>
+      <c r="F230" s="67"/>
+      <c r="G230" s="65"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="63"/>
+      <c r="I230" s="65"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9716,46 +9722,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="62">
+      <c r="A233" s="64">
         <v>177</v>
       </c>
-      <c r="B233" s="66">
+      <c r="B233" s="62">
         <v>46268</v>
       </c>
-      <c r="C233" s="64" t="s">
+      <c r="C233" s="66" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="66">
+      <c r="D233" s="62">
         <v>46267</v>
       </c>
-      <c r="E233" s="62" t="s">
+      <c r="E233" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="64" t="s">
+      <c r="F233" s="66" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="62" t="s">
+      <c r="G233" s="64" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="62" t="s">
+      <c r="I233" s="64" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="63"/>
-      <c r="B234" s="67"/>
-      <c r="C234" s="65"/>
-      <c r="D234" s="67"/>
-      <c r="E234" s="63"/>
-      <c r="F234" s="65"/>
-      <c r="G234" s="63"/>
+      <c r="A234" s="65"/>
+      <c r="B234" s="63"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="63"/>
+      <c r="E234" s="65"/>
+      <c r="F234" s="67"/>
+      <c r="G234" s="65"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="63"/>
+      <c r="I234" s="65"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10396,46 +10402,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="62">
+      <c r="A257" s="64">
         <v>200</v>
       </c>
-      <c r="B257" s="66">
+      <c r="B257" s="62">
         <v>46300</v>
       </c>
-      <c r="C257" s="64" t="s">
+      <c r="C257" s="66" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="66">
+      <c r="D257" s="62">
         <v>46294</v>
       </c>
-      <c r="E257" s="62" t="s">
+      <c r="E257" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="64" t="s">
+      <c r="F257" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="62" t="s">
+      <c r="G257" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="62" t="s">
+      <c r="I257" s="64" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="63"/>
-      <c r="B258" s="67"/>
-      <c r="C258" s="65"/>
-      <c r="D258" s="67"/>
-      <c r="E258" s="63"/>
-      <c r="F258" s="65"/>
-      <c r="G258" s="63"/>
+      <c r="A258" s="65"/>
+      <c r="B258" s="63"/>
+      <c r="C258" s="67"/>
+      <c r="D258" s="63"/>
+      <c r="E258" s="65"/>
+      <c r="F258" s="67"/>
+      <c r="G258" s="65"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="63"/>
+      <c r="I258" s="65"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10525,46 +10531,46 @@
       </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A262" s="62">
+      <c r="A262" s="64">
         <v>204</v>
       </c>
-      <c r="B262" s="66">
+      <c r="B262" s="62">
         <v>46301</v>
       </c>
-      <c r="C262" s="64" t="s">
+      <c r="C262" s="66" t="s">
         <v>949</v>
       </c>
-      <c r="D262" s="66">
+      <c r="D262" s="62">
         <v>46301</v>
       </c>
-      <c r="E262" s="62" t="s">
+      <c r="E262" s="64" t="s">
         <v>308</v>
       </c>
-      <c r="F262" s="64" t="s">
+      <c r="F262" s="66" t="s">
         <v>926</v>
       </c>
-      <c r="G262" s="62" t="s">
+      <c r="G262" s="64" t="s">
         <v>48</v>
       </c>
       <c r="H262" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="I262" s="62" t="s">
+      <c r="I262" s="64" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A263" s="63"/>
-      <c r="B263" s="67"/>
-      <c r="C263" s="65"/>
-      <c r="D263" s="67"/>
-      <c r="E263" s="63"/>
-      <c r="F263" s="65"/>
-      <c r="G263" s="63"/>
+      <c r="A263" s="65"/>
+      <c r="B263" s="63"/>
+      <c r="C263" s="67"/>
+      <c r="D263" s="63"/>
+      <c r="E263" s="65"/>
+      <c r="F263" s="67"/>
+      <c r="G263" s="65"/>
       <c r="H263" s="34" t="s">
         <v>951</v>
       </c>
-      <c r="I263" s="63"/>
+      <c r="I263" s="65"/>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A264" s="21">
@@ -14166,6 +14172,248 @@
     </row>
   </sheetData>
   <mergeCells count="264">
+    <mergeCell ref="I262:I263"/>
+    <mergeCell ref="G262:G263"/>
+    <mergeCell ref="F262:F263"/>
+    <mergeCell ref="E262:E263"/>
+    <mergeCell ref="D262:D263"/>
+    <mergeCell ref="C262:C263"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="G257:G258"/>
+    <mergeCell ref="I257:I258"/>
+    <mergeCell ref="F257:F258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="B257:B258"/>
+    <mergeCell ref="A257:A258"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="E55:E56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="G55:G56"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
+    <mergeCell ref="E67:E70"/>
+    <mergeCell ref="F67:F70"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="I67:I70"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="A111:A115"/>
+    <mergeCell ref="B111:B115"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="E136:E137"/>
+    <mergeCell ref="F136:F137"/>
+    <mergeCell ref="G136:G137"/>
+    <mergeCell ref="I136:I137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="F138:F139"/>
+    <mergeCell ref="G138:G139"/>
+    <mergeCell ref="I138:I139"/>
+    <mergeCell ref="J138:J139"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="E150:E151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="I150:I151"/>
+    <mergeCell ref="F153:F156"/>
+    <mergeCell ref="G153:G156"/>
+    <mergeCell ref="I153:I156"/>
+    <mergeCell ref="A159:A163"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="C159:C163"/>
+    <mergeCell ref="D159:D163"/>
+    <mergeCell ref="E159:E163"/>
+    <mergeCell ref="F159:F163"/>
+    <mergeCell ref="G159:G163"/>
+    <mergeCell ref="I159:I163"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="C153:C156"/>
+    <mergeCell ref="D153:D156"/>
+    <mergeCell ref="E153:E156"/>
+    <mergeCell ref="F174:F175"/>
+    <mergeCell ref="G174:G175"/>
+    <mergeCell ref="I174:I175"/>
+    <mergeCell ref="A181:A185"/>
+    <mergeCell ref="B181:B185"/>
+    <mergeCell ref="C181:C185"/>
+    <mergeCell ref="D181:D185"/>
+    <mergeCell ref="E181:E185"/>
+    <mergeCell ref="F181:F185"/>
+    <mergeCell ref="G181:G185"/>
+    <mergeCell ref="I181:I185"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="C174:C175"/>
+    <mergeCell ref="D174:D175"/>
+    <mergeCell ref="E174:E175"/>
+    <mergeCell ref="F186:F187"/>
+    <mergeCell ref="G186:G187"/>
+    <mergeCell ref="I186:I187"/>
+    <mergeCell ref="A211:A214"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
+    <mergeCell ref="E211:E214"/>
+    <mergeCell ref="F211:F214"/>
+    <mergeCell ref="G211:G214"/>
+    <mergeCell ref="I211:I214"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="C186:C187"/>
+    <mergeCell ref="D186:D187"/>
+    <mergeCell ref="E186:E187"/>
+    <mergeCell ref="F224:F225"/>
+    <mergeCell ref="G224:G225"/>
+    <mergeCell ref="I224:I225"/>
+    <mergeCell ref="G227:G228"/>
+    <mergeCell ref="F227:F228"/>
+    <mergeCell ref="A224:A225"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="C224:C225"/>
+    <mergeCell ref="D224:D225"/>
+    <mergeCell ref="E224:E225"/>
     <mergeCell ref="B229:B230"/>
     <mergeCell ref="A229:A230"/>
     <mergeCell ref="I227:I228"/>
@@ -14188,248 +14436,6 @@
     <mergeCell ref="C227:C228"/>
     <mergeCell ref="B227:B228"/>
     <mergeCell ref="A227:A228"/>
-    <mergeCell ref="F224:F225"/>
-    <mergeCell ref="G224:G225"/>
-    <mergeCell ref="I224:I225"/>
-    <mergeCell ref="G227:G228"/>
-    <mergeCell ref="F227:F228"/>
-    <mergeCell ref="A224:A225"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="C224:C225"/>
-    <mergeCell ref="D224:D225"/>
-    <mergeCell ref="E224:E225"/>
-    <mergeCell ref="F186:F187"/>
-    <mergeCell ref="G186:G187"/>
-    <mergeCell ref="I186:I187"/>
-    <mergeCell ref="A211:A214"/>
-    <mergeCell ref="B211:B214"/>
-    <mergeCell ref="C211:C214"/>
-    <mergeCell ref="D211:D214"/>
-    <mergeCell ref="E211:E214"/>
-    <mergeCell ref="F211:F214"/>
-    <mergeCell ref="G211:G214"/>
-    <mergeCell ref="I211:I214"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="C186:C187"/>
-    <mergeCell ref="D186:D187"/>
-    <mergeCell ref="E186:E187"/>
-    <mergeCell ref="F174:F175"/>
-    <mergeCell ref="G174:G175"/>
-    <mergeCell ref="I174:I175"/>
-    <mergeCell ref="A181:A185"/>
-    <mergeCell ref="B181:B185"/>
-    <mergeCell ref="C181:C185"/>
-    <mergeCell ref="D181:D185"/>
-    <mergeCell ref="E181:E185"/>
-    <mergeCell ref="F181:F185"/>
-    <mergeCell ref="G181:G185"/>
-    <mergeCell ref="I181:I185"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="C174:C175"/>
-    <mergeCell ref="D174:D175"/>
-    <mergeCell ref="E174:E175"/>
-    <mergeCell ref="A159:A163"/>
-    <mergeCell ref="B159:B163"/>
-    <mergeCell ref="C159:C163"/>
-    <mergeCell ref="D159:D163"/>
-    <mergeCell ref="E159:E163"/>
-    <mergeCell ref="F159:F163"/>
-    <mergeCell ref="G159:G163"/>
-    <mergeCell ref="I159:I163"/>
-    <mergeCell ref="A153:A156"/>
-    <mergeCell ref="B153:B156"/>
-    <mergeCell ref="C153:C156"/>
-    <mergeCell ref="D153:D156"/>
-    <mergeCell ref="E153:E156"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
-    <mergeCell ref="E150:E151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="I150:I151"/>
-    <mergeCell ref="F153:F156"/>
-    <mergeCell ref="G153:G156"/>
-    <mergeCell ref="I153:I156"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="F138:F139"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="I138:I139"/>
-    <mergeCell ref="J138:J139"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="A111:A115"/>
-    <mergeCell ref="B111:B115"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E136:E137"/>
-    <mergeCell ref="F136:F137"/>
-    <mergeCell ref="G136:G137"/>
-    <mergeCell ref="I136:I137"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="C67:C70"/>
-    <mergeCell ref="D67:D70"/>
-    <mergeCell ref="E67:E70"/>
-    <mergeCell ref="F67:F70"/>
-    <mergeCell ref="G67:G70"/>
-    <mergeCell ref="I67:I70"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="E55:E56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="G55:G56"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="J43:J44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="I262:I263"/>
-    <mergeCell ref="G262:G263"/>
-    <mergeCell ref="F262:F263"/>
-    <mergeCell ref="E262:E263"/>
-    <mergeCell ref="D262:D263"/>
-    <mergeCell ref="C262:C263"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="G257:G258"/>
-    <mergeCell ref="I257:I258"/>
-    <mergeCell ref="F257:F258"/>
-    <mergeCell ref="E257:E258"/>
-    <mergeCell ref="D257:D258"/>
-    <mergeCell ref="C257:C258"/>
-    <mergeCell ref="B257:B258"/>
-    <mergeCell ref="A257:A258"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14461,23 +14467,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="45.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="89"/>
     </row>
     <row r="2" spans="1:16" s="16" customFormat="1" ht="57" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -14545,28 +14551,28 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A4" s="62">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="98">
+      <c r="B4" s="90">
         <v>46098</v>
       </c>
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="98">
+      <c r="D4" s="90">
         <v>46098</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="64" t="s">
+      <c r="H4" s="66" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="30" t="s">
@@ -14587,13 +14593,13 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A5" s="68"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="30" t="s">
         <v>24</v>
       </c>
@@ -14612,13 +14618,13 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A6" s="68"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
       <c r="I6" s="30" t="s">
         <v>25</v>
       </c>
@@ -14636,14 +14642,14 @@
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A7" s="63"/>
-      <c r="B7" s="100"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="I7" s="30" t="s">
         <v>30</v>
       </c>
@@ -14754,50 +14760,50 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>5</v>
       </c>
-      <c r="B11" s="93">
+      <c r="B11" s="99">
         <v>46102</v>
       </c>
-      <c r="C11" s="76" t="s">
+      <c r="C11" s="71" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="99">
         <v>46095</v>
       </c>
-      <c r="E11" s="76" t="s">
+      <c r="E11" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="F11" s="76" t="s">
+      <c r="F11" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="64" t="s">
+      <c r="H11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="66">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="65"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" ht="24.75" customHeight="1">
       <c r="A13" s="11">
@@ -14832,110 +14838,110 @@
       </c>
     </row>
     <row r="14" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A14" s="87">
+      <c r="A14" s="81">
         <v>7</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="83">
         <v>46105</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="85">
+      <c r="D14" s="83">
         <v>46105</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="83" t="s">
+      <c r="F14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="81" t="s">
+      <c r="H14" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="81" t="s">
+      <c r="J14" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A15" s="89"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
+      <c r="A15" s="96"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
       <c r="I15" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="94"/>
     </row>
     <row r="16" spans="1:16" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="88"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="84"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
       <c r="I16" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J16" s="82"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A17" s="87">
+      <c r="A17" s="81">
         <v>8</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="83">
         <v>46105</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="85">
+      <c r="D17" s="83">
         <v>46105</v>
       </c>
-      <c r="E17" s="83" t="s">
+      <c r="E17" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="81" t="s">
+      <c r="G17" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="81" t="s">
+      <c r="H17" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J17" s="81" t="s">
+      <c r="J17" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
+      <c r="A18" s="82"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
       <c r="I18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="J18" s="82"/>
+      <c r="J18" s="95"/>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A19" s="26">
@@ -15258,50 +15264,50 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A29" s="87">
+      <c r="A29" s="81">
         <v>19</v>
       </c>
-      <c r="B29" s="85">
+      <c r="B29" s="83">
         <v>46121</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="85">
+      <c r="D29" s="83">
         <v>46121</v>
       </c>
-      <c r="E29" s="83" t="s">
+      <c r="E29" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="83" t="s">
+      <c r="F29" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="G29" s="81" t="s">
+      <c r="G29" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="81" t="s">
+      <c r="H29" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I29" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="J29" s="81" t="s">
+      <c r="J29" s="93" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A30" s="88"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
+      <c r="A30" s="82"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="86"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="95"/>
+      <c r="H30" s="95"/>
       <c r="I30" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="J30" s="82"/>
+      <c r="J30" s="95"/>
     </row>
     <row r="31" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A31" s="26">
@@ -15394,74 +15400,74 @@
       </c>
     </row>
     <row r="34" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A34" s="87">
+      <c r="A34" s="81">
         <v>23</v>
       </c>
-      <c r="B34" s="85">
+      <c r="B34" s="83">
         <v>46128</v>
       </c>
-      <c r="C34" s="83" t="s">
+      <c r="C34" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="85">
+      <c r="D34" s="83">
         <v>46128</v>
       </c>
-      <c r="E34" s="83" t="s">
+      <c r="E34" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F34" s="83" t="s">
+      <c r="F34" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="81" t="s">
+      <c r="G34" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H34" s="81" t="s">
+      <c r="H34" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I34" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J34" s="81" t="s">
+      <c r="J34" s="93" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A35" s="88"/>
-      <c r="B35" s="86"/>
-      <c r="C35" s="84"/>
-      <c r="D35" s="86"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="86"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
       <c r="I35" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="J35" s="82"/>
+      <c r="J35" s="95"/>
     </row>
     <row r="36" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A36" s="87">
+      <c r="A36" s="81">
         <v>24</v>
       </c>
-      <c r="B36" s="85">
+      <c r="B36" s="83">
         <v>46132</v>
       </c>
-      <c r="C36" s="83" t="s">
+      <c r="C36" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="85">
+      <c r="D36" s="83">
         <v>46129</v>
       </c>
-      <c r="E36" s="83" t="s">
+      <c r="E36" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="83" t="s">
+      <c r="F36" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="81" t="s">
+      <c r="G36" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="81" t="s">
+      <c r="H36" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I36" s="28" t="s">
@@ -15472,14 +15478,14 @@
       </c>
     </row>
     <row r="37" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A37" s="88"/>
-      <c r="B37" s="86"/>
-      <c r="C37" s="84"/>
-      <c r="D37" s="86"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
       <c r="I37" s="28" t="s">
         <v>242</v>
       </c>
@@ -15582,50 +15588,50 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A41" s="87">
+      <c r="A41" s="81">
         <v>28</v>
       </c>
-      <c r="B41" s="85">
+      <c r="B41" s="83">
         <v>46139</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="D41" s="85">
+      <c r="D41" s="83">
         <v>46139</v>
       </c>
-      <c r="E41" s="83" t="s">
+      <c r="E41" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="83" t="s">
+      <c r="F41" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G41" s="81" t="s">
+      <c r="G41" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="81" t="s">
+      <c r="H41" s="93" t="s">
         <v>262</v>
       </c>
       <c r="I41" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="J41" s="81" t="s">
+      <c r="J41" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A42" s="88"/>
-      <c r="B42" s="86"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="86"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="82"/>
+      <c r="A42" s="82"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="86"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="86"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
       <c r="I42" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="J42" s="82"/>
+      <c r="J42" s="95"/>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A43" s="26">
@@ -15756,28 +15762,28 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A47" s="87">
+      <c r="A47" s="81">
         <v>33</v>
       </c>
-      <c r="B47" s="85">
+      <c r="B47" s="83">
         <v>46149</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C47" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D47" s="85">
+      <c r="D47" s="83">
         <v>46148</v>
       </c>
-      <c r="E47" s="83" t="s">
+      <c r="E47" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F47" s="83" t="s">
+      <c r="F47" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G47" s="81" t="s">
+      <c r="G47" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H47" s="81" t="s">
+      <c r="H47" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I47" s="28" t="s">
@@ -15788,14 +15794,14 @@
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A48" s="88"/>
-      <c r="B48" s="86"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="86"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="82"/>
-      <c r="H48" s="82"/>
+      <c r="A48" s="82"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="86"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="86"/>
+      <c r="F48" s="86"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
       <c r="I48" s="28" t="s">
         <v>333</v>
       </c>
@@ -15804,28 +15810,28 @@
       </c>
     </row>
     <row r="49" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A49" s="87">
+      <c r="A49" s="81">
         <v>34</v>
       </c>
-      <c r="B49" s="85">
+      <c r="B49" s="83">
         <v>46149</v>
       </c>
-      <c r="C49" s="83" t="s">
+      <c r="C49" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="85">
+      <c r="D49" s="83">
         <v>46148</v>
       </c>
-      <c r="E49" s="83" t="s">
+      <c r="E49" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F49" s="83" t="s">
+      <c r="F49" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="G49" s="81" t="s">
+      <c r="G49" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H49" s="81" t="s">
+      <c r="H49" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I49" s="28" t="s">
@@ -15836,14 +15842,14 @@
       </c>
     </row>
     <row r="50" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A50" s="88"/>
-      <c r="B50" s="86"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="84"/>
-      <c r="F50" s="84"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
+      <c r="A50" s="82"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="86"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="86"/>
+      <c r="F50" s="86"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
       <c r="I50" s="28" t="s">
         <v>348</v>
       </c>
@@ -16140,50 +16146,50 @@
       </c>
     </row>
     <row r="60" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A60" s="87">
+      <c r="A60" s="81">
         <v>44</v>
       </c>
-      <c r="B60" s="85">
+      <c r="B60" s="83">
         <v>46169</v>
       </c>
-      <c r="C60" s="83" t="s">
+      <c r="C60" s="85" t="s">
         <v>449</v>
       </c>
-      <c r="D60" s="85">
+      <c r="D60" s="83">
         <v>46169</v>
       </c>
-      <c r="E60" s="83" t="s">
+      <c r="E60" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="83" t="s">
+      <c r="F60" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G60" s="81" t="s">
+      <c r="G60" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H60" s="81" t="s">
+      <c r="H60" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I60" s="28" t="s">
         <v>450</v>
       </c>
-      <c r="J60" s="81" t="s">
+      <c r="J60" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A61" s="88"/>
-      <c r="B61" s="86"/>
-      <c r="C61" s="84"/>
-      <c r="D61" s="86"/>
-      <c r="E61" s="84"/>
-      <c r="F61" s="84"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="82"/>
+      <c r="A61" s="82"/>
+      <c r="B61" s="84"/>
+      <c r="C61" s="86"/>
+      <c r="D61" s="84"/>
+      <c r="E61" s="86"/>
+      <c r="F61" s="86"/>
+      <c r="G61" s="95"/>
+      <c r="H61" s="95"/>
       <c r="I61" s="28" t="s">
         <v>451</v>
       </c>
-      <c r="J61" s="82"/>
+      <c r="J61" s="95"/>
     </row>
     <row r="62" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A62" s="26">
@@ -16503,50 +16509,50 @@
       </c>
     </row>
     <row r="72" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A72" s="87">
+      <c r="A72" s="81">
         <v>55</v>
       </c>
-      <c r="B72" s="85">
+      <c r="B72" s="83">
         <v>46192</v>
       </c>
-      <c r="C72" s="83" t="s">
+      <c r="C72" s="85" t="s">
         <v>544</v>
       </c>
-      <c r="D72" s="85">
+      <c r="D72" s="83">
         <v>46191</v>
       </c>
-      <c r="E72" s="83" t="s">
+      <c r="E72" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F72" s="83" t="s">
+      <c r="F72" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G72" s="81" t="s">
+      <c r="G72" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H72" s="81" t="s">
+      <c r="H72" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="J72" s="81" t="s">
+      <c r="J72" s="93" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A73" s="88"/>
-      <c r="B73" s="86"/>
-      <c r="C73" s="84"/>
-      <c r="D73" s="86"/>
-      <c r="E73" s="84"/>
-      <c r="F73" s="84"/>
-      <c r="G73" s="82"/>
-      <c r="H73" s="82"/>
+      <c r="A73" s="82"/>
+      <c r="B73" s="84"/>
+      <c r="C73" s="86"/>
+      <c r="D73" s="84"/>
+      <c r="E73" s="86"/>
+      <c r="F73" s="86"/>
+      <c r="G73" s="95"/>
+      <c r="H73" s="95"/>
       <c r="I73" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="J73" s="82"/>
+      <c r="J73" s="95"/>
     </row>
     <row r="74" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A74" s="26">
@@ -16741,184 +16747,184 @@
       </c>
     </row>
     <row r="80" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A80" s="87">
+      <c r="A80" s="81">
         <v>62</v>
       </c>
-      <c r="B80" s="85">
+      <c r="B80" s="83">
         <v>46200</v>
       </c>
-      <c r="C80" s="83" t="s">
+      <c r="C80" s="85" t="s">
         <v>557</v>
       </c>
-      <c r="D80" s="85">
+      <c r="D80" s="83">
         <v>46200</v>
       </c>
-      <c r="E80" s="83" t="s">
+      <c r="E80" s="85" t="s">
         <v>558</v>
       </c>
-      <c r="F80" s="83" t="s">
+      <c r="F80" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="81" t="s">
+      <c r="G80" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H80" s="81" t="s">
+      <c r="H80" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="J80" s="81" t="s">
+      <c r="J80" s="93" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A81" s="89"/>
-      <c r="B81" s="90"/>
-      <c r="C81" s="91"/>
-      <c r="D81" s="90"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
+      <c r="A81" s="96"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="98"/>
+      <c r="D81" s="97"/>
+      <c r="E81" s="98"/>
+      <c r="F81" s="98"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="94"/>
       <c r="I81" s="28" t="s">
         <v>560</v>
       </c>
-      <c r="J81" s="92"/>
+      <c r="J81" s="94"/>
     </row>
     <row r="82" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A82" s="89"/>
-      <c r="B82" s="90"/>
-      <c r="C82" s="91"/>
-      <c r="D82" s="90"/>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="92"/>
-      <c r="H82" s="92"/>
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="97"/>
+      <c r="E82" s="98"/>
+      <c r="F82" s="98"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="94"/>
       <c r="I82" s="28" t="s">
         <v>561</v>
       </c>
-      <c r="J82" s="92"/>
+      <c r="J82" s="94"/>
     </row>
     <row r="83" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A83" s="89"/>
-      <c r="B83" s="90"/>
-      <c r="C83" s="91"/>
-      <c r="D83" s="90"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="92"/>
+      <c r="A83" s="96"/>
+      <c r="B83" s="97"/>
+      <c r="C83" s="98"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="98"/>
+      <c r="F83" s="98"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="94"/>
       <c r="I83" s="28" t="s">
         <v>562</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="94"/>
     </row>
     <row r="84" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A84" s="88"/>
-      <c r="B84" s="86"/>
-      <c r="C84" s="84"/>
-      <c r="D84" s="86"/>
-      <c r="E84" s="84"/>
-      <c r="F84" s="84"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
+      <c r="A84" s="82"/>
+      <c r="B84" s="84"/>
+      <c r="C84" s="86"/>
+      <c r="D84" s="84"/>
+      <c r="E84" s="86"/>
+      <c r="F84" s="86"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="95"/>
       <c r="I84" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="J84" s="82"/>
+      <c r="J84" s="95"/>
     </row>
     <row r="85" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A85" s="87">
+      <c r="A85" s="81">
         <v>63</v>
       </c>
-      <c r="B85" s="85">
+      <c r="B85" s="83">
         <v>46204</v>
       </c>
-      <c r="C85" s="83" t="s">
+      <c r="C85" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="85">
+      <c r="D85" s="83">
         <v>46204</v>
       </c>
-      <c r="E85" s="83" t="s">
+      <c r="E85" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="83" t="s">
+      <c r="F85" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G85" s="81" t="s">
+      <c r="G85" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H85" s="81" t="s">
+      <c r="H85" s="93" t="s">
         <v>43</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>565</v>
       </c>
-      <c r="J85" s="81" t="s">
+      <c r="J85" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A86" s="88"/>
-      <c r="B86" s="86"/>
-      <c r="C86" s="84"/>
-      <c r="D86" s="86"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="84"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
+      <c r="A86" s="82"/>
+      <c r="B86" s="84"/>
+      <c r="C86" s="86"/>
+      <c r="D86" s="84"/>
+      <c r="E86" s="86"/>
+      <c r="F86" s="86"/>
+      <c r="G86" s="95"/>
+      <c r="H86" s="95"/>
       <c r="I86" s="28" t="s">
         <v>566</v>
       </c>
-      <c r="J86" s="82"/>
+      <c r="J86" s="95"/>
     </row>
     <row r="87" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A87" s="87">
+      <c r="A87" s="81">
         <v>64</v>
       </c>
-      <c r="B87" s="85">
+      <c r="B87" s="83">
         <v>46210</v>
       </c>
-      <c r="C87" s="83" t="s">
+      <c r="C87" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="85">
+      <c r="D87" s="83">
         <v>46210</v>
       </c>
-      <c r="E87" s="83" t="s">
+      <c r="E87" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="83" t="s">
+      <c r="F87" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G87" s="81" t="s">
+      <c r="G87" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="H87" s="81" t="s">
+      <c r="H87" s="93" t="s">
         <v>22</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>570</v>
       </c>
-      <c r="J87" s="81" t="s">
+      <c r="J87" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A88" s="88"/>
-      <c r="B88" s="86"/>
-      <c r="C88" s="84"/>
-      <c r="D88" s="86"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="84"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
+      <c r="A88" s="82"/>
+      <c r="B88" s="84"/>
+      <c r="C88" s="86"/>
+      <c r="D88" s="84"/>
+      <c r="E88" s="86"/>
+      <c r="F88" s="86"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="95"/>
       <c r="I88" s="28" t="s">
         <v>571</v>
       </c>
-      <c r="J88" s="82"/>
+      <c r="J88" s="95"/>
     </row>
     <row r="89" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A89" s="26">
@@ -17524,64 +17530,64 @@
       </c>
     </row>
     <row r="108" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A108" s="87">
+      <c r="A108" s="81">
         <v>84</v>
       </c>
-      <c r="B108" s="85">
+      <c r="B108" s="83">
         <v>46231</v>
       </c>
-      <c r="C108" s="83" t="s">
+      <c r="C108" s="85" t="s">
         <v>671</v>
       </c>
-      <c r="D108" s="85">
+      <c r="D108" s="83">
         <v>46231</v>
       </c>
-      <c r="E108" s="83" t="s">
+      <c r="E108" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="83" t="s">
+      <c r="F108" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="G108" s="81" t="s">
+      <c r="G108" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H108" s="81" t="s">
+      <c r="H108" s="93" t="s">
         <v>209</v>
       </c>
       <c r="I108" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="J108" s="81" t="s">
+      <c r="J108" s="93" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A109" s="89"/>
-      <c r="B109" s="90"/>
-      <c r="C109" s="91"/>
-      <c r="D109" s="90"/>
-      <c r="E109" s="91"/>
-      <c r="F109" s="91"/>
-      <c r="G109" s="92"/>
-      <c r="H109" s="92"/>
+      <c r="A109" s="96"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="98"/>
+      <c r="D109" s="97"/>
+      <c r="E109" s="98"/>
+      <c r="F109" s="98"/>
+      <c r="G109" s="94"/>
+      <c r="H109" s="94"/>
       <c r="I109" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="J109" s="92"/>
+      <c r="J109" s="94"/>
     </row>
     <row r="110" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A110" s="88"/>
-      <c r="B110" s="86"/>
-      <c r="C110" s="84"/>
-      <c r="D110" s="86"/>
-      <c r="E110" s="84"/>
-      <c r="F110" s="84"/>
-      <c r="G110" s="82"/>
-      <c r="H110" s="82"/>
+      <c r="A110" s="82"/>
+      <c r="B110" s="84"/>
+      <c r="C110" s="86"/>
+      <c r="D110" s="84"/>
+      <c r="E110" s="86"/>
+      <c r="F110" s="86"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="95"/>
       <c r="I110" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="J110" s="82"/>
+      <c r="J110" s="95"/>
     </row>
     <row r="111" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A111" s="26">
@@ -18000,50 +18006,50 @@
       </c>
     </row>
     <row r="124" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A124" s="87">
+      <c r="A124" s="81">
         <v>98</v>
       </c>
-      <c r="B124" s="85">
+      <c r="B124" s="83">
         <v>46263</v>
       </c>
-      <c r="C124" s="83" t="s">
+      <c r="C124" s="85" t="s">
         <v>770</v>
       </c>
-      <c r="D124" s="85">
+      <c r="D124" s="83">
         <v>46260</v>
       </c>
-      <c r="E124" s="83" t="s">
+      <c r="E124" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F124" s="83" t="s">
+      <c r="F124" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G124" s="81" t="s">
+      <c r="G124" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H124" s="81" t="s">
+      <c r="H124" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I124" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J124" s="81" t="s">
+      <c r="J124" s="93" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="125" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A125" s="88"/>
-      <c r="B125" s="86"/>
-      <c r="C125" s="84"/>
-      <c r="D125" s="86"/>
-      <c r="E125" s="84"/>
-      <c r="F125" s="84"/>
-      <c r="G125" s="82"/>
-      <c r="H125" s="82"/>
+      <c r="A125" s="82"/>
+      <c r="B125" s="84"/>
+      <c r="C125" s="86"/>
+      <c r="D125" s="84"/>
+      <c r="E125" s="86"/>
+      <c r="F125" s="86"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="95"/>
       <c r="I125" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="J125" s="82"/>
+      <c r="J125" s="95"/>
     </row>
     <row r="126" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A126" s="26">
@@ -19053,25 +19059,25 @@
       </c>
     </row>
     <row r="157" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A157" s="87">
+      <c r="A157" s="81">
         <v>130</v>
       </c>
-      <c r="B157" s="85">
+      <c r="B157" s="83">
         <v>46294</v>
       </c>
-      <c r="C157" s="83" t="s">
+      <c r="C157" s="85" t="s">
         <v>901</v>
       </c>
-      <c r="D157" s="85">
+      <c r="D157" s="83">
         <v>46294</v>
       </c>
-      <c r="E157" s="83" t="s">
+      <c r="E157" s="85" t="s">
         <v>572</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>903</v>
       </c>
-      <c r="G157" s="81" t="s">
+      <c r="G157" s="93" t="s">
         <v>124</v>
       </c>
       <c r="H157" s="43" t="s">
@@ -19088,15 +19094,15 @@
       </c>
     </row>
     <row r="158" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A158" s="88"/>
-      <c r="B158" s="86"/>
-      <c r="C158" s="84"/>
-      <c r="D158" s="86"/>
-      <c r="E158" s="84"/>
+      <c r="A158" s="82"/>
+      <c r="B158" s="84"/>
+      <c r="C158" s="86"/>
+      <c r="D158" s="84"/>
+      <c r="E158" s="86"/>
       <c r="F158" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="G158" s="82"/>
+      <c r="G158" s="95"/>
       <c r="H158" s="43" t="s">
         <v>86</v>
       </c>
@@ -19367,50 +19373,50 @@
       </c>
     </row>
     <row r="167" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A167" s="87">
+      <c r="A167" s="81">
         <v>139</v>
       </c>
-      <c r="B167" s="85">
+      <c r="B167" s="83">
         <v>46300</v>
       </c>
-      <c r="C167" s="83" t="s">
+      <c r="C167" s="85" t="s">
         <v>936</v>
       </c>
-      <c r="D167" s="85">
+      <c r="D167" s="83">
         <v>46295</v>
       </c>
-      <c r="E167" s="83" t="s">
+      <c r="E167" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="F167" s="83" t="s">
+      <c r="F167" s="85" t="s">
         <v>332</v>
       </c>
-      <c r="G167" s="81" t="s">
+      <c r="G167" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H167" s="81" t="s">
+      <c r="H167" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I167" s="28" t="s">
         <v>934</v>
       </c>
-      <c r="J167" s="81" t="s">
+      <c r="J167" s="93" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="168" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A168" s="88"/>
-      <c r="B168" s="86"/>
-      <c r="C168" s="84"/>
-      <c r="D168" s="86"/>
-      <c r="E168" s="84"/>
-      <c r="F168" s="84"/>
-      <c r="G168" s="82"/>
-      <c r="H168" s="82"/>
+      <c r="A168" s="82"/>
+      <c r="B168" s="84"/>
+      <c r="C168" s="86"/>
+      <c r="D168" s="84"/>
+      <c r="E168" s="86"/>
+      <c r="F168" s="86"/>
+      <c r="G168" s="95"/>
+      <c r="H168" s="95"/>
       <c r="I168" s="28" t="s">
         <v>935</v>
       </c>
-      <c r="J168" s="82"/>
+      <c r="J168" s="95"/>
     </row>
     <row r="169" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A169" s="26">
@@ -19477,50 +19483,50 @@
       </c>
     </row>
     <row r="171" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A171" s="87">
+      <c r="A171" s="81">
         <v>142</v>
       </c>
-      <c r="B171" s="85">
+      <c r="B171" s="83">
         <v>46301</v>
       </c>
-      <c r="C171" s="83" t="s">
+      <c r="C171" s="85" t="s">
         <v>948</v>
       </c>
-      <c r="D171" s="85">
+      <c r="D171" s="83">
         <v>46301</v>
       </c>
-      <c r="E171" s="83" t="s">
+      <c r="E171" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="F171" s="83" t="s">
+      <c r="F171" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="G171" s="81" t="s">
+      <c r="G171" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="H171" s="81" t="s">
+      <c r="H171" s="93" t="s">
         <v>48</v>
       </c>
       <c r="I171" s="28" t="s">
         <v>946</v>
       </c>
-      <c r="J171" s="81" t="s">
+      <c r="J171" s="93" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="172" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A172" s="88"/>
-      <c r="B172" s="86"/>
-      <c r="C172" s="84"/>
-      <c r="D172" s="86"/>
-      <c r="E172" s="84"/>
-      <c r="F172" s="84"/>
-      <c r="G172" s="82"/>
-      <c r="H172" s="82"/>
+      <c r="A172" s="82"/>
+      <c r="B172" s="84"/>
+      <c r="C172" s="86"/>
+      <c r="D172" s="84"/>
+      <c r="E172" s="86"/>
+      <c r="F172" s="86"/>
+      <c r="G172" s="95"/>
+      <c r="H172" s="95"/>
       <c r="I172" s="28" t="s">
         <v>947</v>
       </c>
-      <c r="J172" s="82"/>
+      <c r="J172" s="95"/>
     </row>
     <row r="173" spans="1:15" s="10" customFormat="1" ht="24.75" customHeight="1">
       <c r="A173" s="26">
@@ -19656,6 +19662,9 @@
       </c>
       <c r="B177" s="52">
         <v>46307</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>961</v>
       </c>
       <c r="D177" s="52">
         <v>46307</v>
@@ -19683,6 +19692,9 @@
       <c r="A178" s="26"/>
       <c r="B178" s="43"/>
       <c r="D178" s="43"/>
+      <c r="F178" s="10" t="s">
+        <v>962</v>
+      </c>
       <c r="G178" s="43"/>
       <c r="H178" s="43"/>
       <c r="I178" s="28"/>
@@ -26926,6 +26938,156 @@
     </row>
   </sheetData>
   <mergeCells count="174">
+    <mergeCell ref="J171:J172"/>
+    <mergeCell ref="H171:H172"/>
+    <mergeCell ref="G171:G172"/>
+    <mergeCell ref="F171:F172"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="D171:D172"/>
+    <mergeCell ref="C171:C172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="H167:H168"/>
+    <mergeCell ref="G167:G168"/>
+    <mergeCell ref="J167:J168"/>
+    <mergeCell ref="F167:F168"/>
+    <mergeCell ref="E167:E168"/>
+    <mergeCell ref="D167:D168"/>
+    <mergeCell ref="C167:C168"/>
+    <mergeCell ref="B167:B168"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="D157:D158"/>
+    <mergeCell ref="E157:E158"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F124:F125"/>
+    <mergeCell ref="G124:G125"/>
+    <mergeCell ref="H124:H125"/>
+    <mergeCell ref="A108:A110"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="J87:J88"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="E108:E110"/>
+    <mergeCell ref="F108:F110"/>
+    <mergeCell ref="G108:G110"/>
+    <mergeCell ref="H108:H110"/>
+    <mergeCell ref="F80:F84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="H80:H84"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
     <mergeCell ref="A124:A125"/>
     <mergeCell ref="B124:B125"/>
     <mergeCell ref="C124:C125"/>
@@ -26950,156 +27112,6 @@
     <mergeCell ref="C80:C84"/>
     <mergeCell ref="D80:D84"/>
     <mergeCell ref="E80:E84"/>
-    <mergeCell ref="F80:F84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="H80:H84"/>
-    <mergeCell ref="J80:J84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F124:F125"/>
-    <mergeCell ref="G124:G125"/>
-    <mergeCell ref="H124:H125"/>
-    <mergeCell ref="A108:A110"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="J87:J88"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="E108:E110"/>
-    <mergeCell ref="F108:F110"/>
-    <mergeCell ref="G108:G110"/>
-    <mergeCell ref="H108:H110"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="J34:J35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="G60:G61"/>
-    <mergeCell ref="H60:H61"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="J60:J61"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="H167:H168"/>
-    <mergeCell ref="G167:G168"/>
-    <mergeCell ref="J167:J168"/>
-    <mergeCell ref="F167:F168"/>
-    <mergeCell ref="E167:E168"/>
-    <mergeCell ref="D167:D168"/>
-    <mergeCell ref="C167:C168"/>
-    <mergeCell ref="B167:B168"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="D157:D158"/>
-    <mergeCell ref="E157:E158"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="J171:J172"/>
-    <mergeCell ref="H171:H172"/>
-    <mergeCell ref="G171:G172"/>
-    <mergeCell ref="F171:F172"/>
-    <mergeCell ref="E171:E172"/>
-    <mergeCell ref="D171:D172"/>
-    <mergeCell ref="C171:C172"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="A171:A172"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/Material Inward_Outward Register 2026.xlsx
+++ b/Material Inward_Outward Register 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amalgam_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D21190-DEF6-4542-AE54-03CB92758CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDBC933-CCDC-44C9-872B-6681D067ED77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inward" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="965">
   <si>
     <t>Sr No.</t>
   </si>
@@ -2909,7 +2909,13 @@
     <t>AM/DOM/0017/2627</t>
   </si>
   <si>
-    <t>s</t>
+    <t>SHMPL/26-27/1811</t>
+  </si>
+  <si>
+    <t>Science House Medical Pvt Ltd.</t>
+  </si>
+  <si>
+    <t>Human Assayed Multi Sera Level 2 - Kit 2 / Human assayed Multi Sera Level 3 - Kit 1</t>
   </si>
 </sst>
 </file>
@@ -3414,12 +3420,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3432,28 +3432,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3471,11 +3462,32 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3484,10 +3496,28 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3505,30 +3535,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3831,21 +3837,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="47.45" customHeight="1" thickBot="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="78"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="73"/>
     </row>
     <row r="2" spans="1:13" s="20" customFormat="1" ht="63" customHeight="1" thickBot="1">
       <c r="A2" s="12" t="s">
@@ -3878,10 +3884,10 @@
       <c r="J2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="80"/>
+      <c r="L2" s="75"/>
       <c r="M2" s="19" t="s">
         <v>10</v>
       </c>
@@ -3994,46 +4000,46 @@
       </c>
     </row>
     <row r="7" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A7" s="64">
+      <c r="A7" s="62">
         <v>4</v>
       </c>
-      <c r="B7" s="62">
+      <c r="B7" s="66">
         <v>46099</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="64" t="s">
+      <c r="D7" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="64" t="s">
+      <c r="E7" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="62" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="62">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="65"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="63"/>
       <c r="H8" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="65"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="21">
@@ -4127,30 +4133,30 @@
       <c r="H11" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="64" t="s">
+      <c r="I11" s="62" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A12" s="64">
+      <c r="A12" s="62">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="66">
         <v>46104</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="66" t="s">
+      <c r="F12" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H12" s="27" t="s">
@@ -4161,10 +4167,10 @@
     <row r="13" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A13" s="68"/>
       <c r="B13" s="68"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="68"/>
-      <c r="F13" s="70"/>
+      <c r="F13" s="69"/>
       <c r="G13" s="68"/>
       <c r="H13" s="27" t="s">
         <v>85</v>
@@ -4172,54 +4178,54 @@
       <c r="I13" s="68"/>
     </row>
     <row r="14" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="65"/>
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="63"/>
       <c r="H14" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="65"/>
+      <c r="I14" s="63"/>
     </row>
     <row r="15" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A15" s="64">
+      <c r="A15" s="62">
         <v>9</v>
       </c>
-      <c r="B15" s="62">
+      <c r="B15" s="66">
         <v>46105</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="66">
         <v>46104</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="66" t="s">
+      <c r="F15" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="64" t="s">
+      <c r="I15" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="69"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="68"/>
-      <c r="F16" s="70"/>
+      <c r="F16" s="69"/>
       <c r="G16" s="68"/>
       <c r="H16" s="34" t="s">
         <v>90</v>
@@ -4227,17 +4233,17 @@
       <c r="I16" s="68"/>
     </row>
     <row r="17" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="63"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="65"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="65"/>
+      <c r="I17" s="63"/>
     </row>
     <row r="18" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A18" s="21">
@@ -4356,25 +4362,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A22" s="64">
+      <c r="A22" s="62">
         <v>14</v>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="66">
         <v>46112</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="62">
+      <c r="D22" s="66">
         <v>46105</v>
       </c>
-      <c r="E22" s="64" t="s">
+      <c r="E22" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H22" s="34" t="s">
@@ -4385,13 +4391,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A23" s="65"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="65"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="63"/>
       <c r="H23" s="34" t="s">
         <v>120</v>
       </c>
@@ -4516,46 +4522,46 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A28" s="64">
+      <c r="A28" s="62">
         <v>19</v>
       </c>
-      <c r="B28" s="62">
+      <c r="B28" s="66">
         <v>46121</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="66">
         <v>46120</v>
       </c>
-      <c r="E28" s="64" t="s">
+      <c r="E28" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="66" t="s">
+      <c r="F28" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I28" s="64" t="s">
+      <c r="I28" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A29" s="65"/>
-      <c r="B29" s="63"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="65"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="63"/>
       <c r="H29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="65"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A30" s="21">
@@ -4613,41 +4619,41 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A32" s="64">
+      <c r="A32" s="62">
         <v>22</v>
       </c>
-      <c r="B32" s="62">
+      <c r="B32" s="66">
         <v>46122</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="62">
+      <c r="D32" s="66">
         <v>46120</v>
       </c>
-      <c r="E32" s="64" t="s">
+      <c r="E32" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="I32" s="64" t="s">
+      <c r="I32" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A33" s="68"/>
-      <c r="B33" s="69"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="69"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="68"/>
-      <c r="F33" s="70"/>
+      <c r="F33" s="69"/>
       <c r="G33" s="68"/>
       <c r="H33" s="34" t="s">
         <v>189</v>
@@ -4655,59 +4661,59 @@
       <c r="I33" s="68"/>
     </row>
     <row r="34" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A34" s="65"/>
-      <c r="B34" s="63"/>
-      <c r="C34" s="67"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="65"/>
+      <c r="A34" s="63"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="63"/>
       <c r="H34" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="65"/>
+      <c r="I34" s="63"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A35" s="64">
+      <c r="A35" s="62">
         <v>23</v>
       </c>
-      <c r="B35" s="62">
+      <c r="B35" s="66">
         <v>46123</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="66">
         <v>46121</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I35" s="64" t="s">
+      <c r="I35" s="62" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A36" s="65"/>
-      <c r="B36" s="63"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="65"/>
+      <c r="A36" s="63"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="63"/>
       <c r="H36" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="65"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A37" s="21">
@@ -4823,117 +4829,117 @@
       </c>
     </row>
     <row r="41" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A41" s="64">
+      <c r="A41" s="62">
         <v>28</v>
       </c>
-      <c r="B41" s="64" t="s">
+      <c r="B41" s="62" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="66">
         <v>46123</v>
       </c>
-      <c r="E41" s="64" t="s">
+      <c r="E41" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="66" t="s">
+      <c r="F41" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="64" t="s">
+      <c r="I41" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="64" t="s">
+      <c r="J41" s="62" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A42" s="65"/>
-      <c r="B42" s="65"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="63"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="65"/>
+      <c r="A42" s="63"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="63"/>
       <c r="H42" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="65"/>
-      <c r="J42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A43" s="64">
+      <c r="A43" s="62">
         <v>29</v>
       </c>
-      <c r="B43" s="62">
+      <c r="B43" s="66">
         <v>46126</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>46122</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="66" t="s">
+      <c r="F43" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H43" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I43" s="64" t="s">
+      <c r="I43" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J43" s="64" t="s">
+      <c r="J43" s="62" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A44" s="65"/>
-      <c r="B44" s="63"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="65"/>
+      <c r="A44" s="63"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="65"/>
+      <c r="G44" s="63"/>
       <c r="H44" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A45" s="64">
+      <c r="A45" s="62">
         <v>30</v>
       </c>
-      <c r="B45" s="62">
+      <c r="B45" s="66">
         <v>46127</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="66">
         <v>46125</v>
       </c>
-      <c r="E45" s="64" t="s">
+      <c r="E45" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="66" t="s">
+      <c r="F45" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H45" s="34" t="s">
@@ -4944,13 +4950,13 @@
       </c>
     </row>
     <row r="46" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A46" s="65"/>
-      <c r="B46" s="63"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="63"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="63"/>
       <c r="H46" s="34" t="s">
         <v>222</v>
       </c>
@@ -4959,42 +4965,42 @@
       </c>
     </row>
     <row r="47" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A47" s="64">
+      <c r="A47" s="62">
         <v>31</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B47" s="66">
         <v>46127</v>
       </c>
-      <c r="C47" s="66">
+      <c r="C47" s="64">
         <v>360142</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="66">
         <v>46120</v>
       </c>
-      <c r="F47" s="66" t="s">
+      <c r="F47" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>225</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A48" s="65"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="63"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="63"/>
       <c r="H48" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="I48" s="65"/>
+      <c r="I48" s="63"/>
     </row>
     <row r="49" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A49" s="21">
@@ -5177,50 +5183,50 @@
       </c>
     </row>
     <row r="55" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A55" s="64">
+      <c r="A55" s="62">
         <v>38</v>
       </c>
-      <c r="B55" s="62">
+      <c r="B55" s="66">
         <v>46137</v>
       </c>
-      <c r="C55" s="66" t="s">
+      <c r="C55" s="64" t="s">
         <v>252</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="66">
         <v>46137</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="F55" s="66" t="s">
+      <c r="F55" s="64" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="64" t="s">
+      <c r="G55" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="J55" s="64" t="s">
+      <c r="J55" s="62" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A56" s="65"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="65"/>
+      <c r="A56" s="63"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="63"/>
       <c r="H56" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A57" s="21">
@@ -5519,41 +5525,41 @@
       </c>
     </row>
     <row r="67" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A67" s="64">
+      <c r="A67" s="62">
         <v>49</v>
       </c>
-      <c r="B67" s="62">
+      <c r="B67" s="66">
         <v>46146</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="64" t="s">
         <v>303</v>
       </c>
-      <c r="D67" s="62">
+      <c r="D67" s="66">
         <v>46142</v>
       </c>
-      <c r="E67" s="64" t="s">
+      <c r="E67" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="66" t="s">
+      <c r="F67" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="64" t="s">
+      <c r="I67" s="62" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A68" s="68"/>
-      <c r="B68" s="69"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="69"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="68"/>
-      <c r="F68" s="70"/>
+      <c r="F68" s="69"/>
       <c r="G68" s="68"/>
       <c r="H68" s="34" t="s">
         <v>305</v>
@@ -5562,11 +5568,11 @@
     </row>
     <row r="69" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A69" s="68"/>
-      <c r="B69" s="69"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="68"/>
-      <c r="F69" s="70"/>
+      <c r="F69" s="69"/>
       <c r="G69" s="68"/>
       <c r="H69" s="34" t="s">
         <v>306</v>
@@ -5574,17 +5580,17 @@
       <c r="I69" s="68"/>
     </row>
     <row r="70" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="63"/>
       <c r="H70" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="I70" s="65"/>
+      <c r="I70" s="63"/>
     </row>
     <row r="71" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A71" s="21">
@@ -5813,39 +5819,39 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A79" s="64">
+      <c r="A79" s="62">
         <v>58</v>
       </c>
-      <c r="B79" s="62">
+      <c r="B79" s="66">
         <v>46148</v>
       </c>
-      <c r="C79" s="66" t="s">
+      <c r="C79" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="66">
         <v>46143</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="66" t="s">
+      <c r="F79" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G79" s="64" t="s">
+      <c r="G79" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="I79" s="64"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A80" s="68"/>
-      <c r="B80" s="69"/>
-      <c r="C80" s="70"/>
-      <c r="D80" s="69"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="69"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="68"/>
-      <c r="F80" s="70"/>
+      <c r="F80" s="69"/>
       <c r="G80" s="68"/>
       <c r="H80" s="34" t="s">
         <v>341</v>
@@ -5854,11 +5860,11 @@
     </row>
     <row r="81" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A81" s="68"/>
-      <c r="B81" s="69"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="70"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="68"/>
-      <c r="F81" s="70"/>
+      <c r="F81" s="69"/>
       <c r="G81" s="68"/>
       <c r="H81" s="34" t="s">
         <v>342</v>
@@ -5867,11 +5873,11 @@
     </row>
     <row r="82" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A82" s="68"/>
-      <c r="B82" s="69"/>
-      <c r="C82" s="70"/>
-      <c r="D82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="69"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="68"/>
-      <c r="F82" s="70"/>
+      <c r="F82" s="69"/>
       <c r="G82" s="68"/>
       <c r="H82" s="34" t="s">
         <v>343</v>
@@ -5879,17 +5885,17 @@
       <c r="I82" s="68"/>
     </row>
     <row r="83" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A83" s="65"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="67"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="65"/>
-      <c r="F83" s="67"/>
-      <c r="G83" s="65"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="63"/>
       <c r="H83" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="I83" s="65"/>
+      <c r="I83" s="63"/>
     </row>
     <row r="84" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A84" s="21">
@@ -5921,22 +5927,22 @@
       </c>
     </row>
     <row r="85" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A85" s="64">
+      <c r="A85" s="62">
         <v>60</v>
       </c>
-      <c r="B85" s="62">
+      <c r="B85" s="66">
         <v>46149</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D85" s="62">
+      <c r="D85" s="66">
         <v>46142</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="62" t="s">
         <v>354</v>
       </c>
-      <c r="F85" s="66" t="s">
+      <c r="F85" s="64" t="s">
         <v>355</v>
       </c>
       <c r="H85" s="34" t="s">
@@ -5944,57 +5950,57 @@
       </c>
     </row>
     <row r="86" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A86" s="65"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="67"/>
+      <c r="A86" s="63"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="65"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="65"/>
       <c r="H86" s="34" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A87" s="64">
+      <c r="A87" s="62">
         <v>61</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="66">
         <v>46149</v>
       </c>
-      <c r="C87" s="66" t="s">
+      <c r="C87" s="64" t="s">
         <v>361</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="66">
         <v>46142</v>
       </c>
-      <c r="E87" s="64" t="s">
+      <c r="E87" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="66" t="s">
+      <c r="F87" s="64" t="s">
         <v>362</v>
       </c>
-      <c r="G87" s="64" t="s">
+      <c r="G87" s="62" t="s">
         <v>126</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>363</v>
       </c>
-      <c r="I87" s="64" t="s">
+      <c r="I87" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A88" s="65"/>
-      <c r="B88" s="63"/>
-      <c r="C88" s="67"/>
-      <c r="D88" s="63"/>
-      <c r="E88" s="65"/>
-      <c r="F88" s="67"/>
-      <c r="G88" s="65"/>
+      <c r="A88" s="63"/>
+      <c r="B88" s="67"/>
+      <c r="C88" s="65"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="65"/>
+      <c r="G88" s="63"/>
       <c r="H88" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="I88" s="65"/>
+      <c r="I88" s="63"/>
     </row>
     <row r="89" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A89" s="21">
@@ -6026,41 +6032,41 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A90" s="64">
+      <c r="A90" s="62">
         <v>63</v>
       </c>
-      <c r="B90" s="62">
+      <c r="B90" s="66">
         <v>46149</v>
       </c>
-      <c r="C90" s="66">
+      <c r="C90" s="64">
         <v>33</v>
       </c>
-      <c r="D90" s="62">
+      <c r="D90" s="66">
         <v>46140</v>
       </c>
-      <c r="E90" s="64" t="s">
+      <c r="E90" s="62" t="s">
         <v>250</v>
       </c>
-      <c r="F90" s="66" t="s">
+      <c r="F90" s="64" t="s">
         <v>369</v>
       </c>
-      <c r="G90" s="64" t="s">
+      <c r="G90" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="I90" s="64" t="s">
+      <c r="I90" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A91" s="68"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="70"/>
-      <c r="D91" s="69"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="69"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="68"/>
-      <c r="F91" s="70"/>
+      <c r="F91" s="69"/>
       <c r="G91" s="68"/>
       <c r="H91" s="34" t="s">
         <v>371</v>
@@ -6069,11 +6075,11 @@
     </row>
     <row r="92" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A92" s="68"/>
-      <c r="B92" s="69"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="69"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="69"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="68"/>
-      <c r="F92" s="70"/>
+      <c r="F92" s="69"/>
       <c r="G92" s="68"/>
       <c r="H92" s="34" t="s">
         <v>372</v>
@@ -6081,17 +6087,17 @@
       <c r="I92" s="68"/>
     </row>
     <row r="93" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A93" s="65"/>
-      <c r="B93" s="63"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="63"/>
-      <c r="E93" s="65"/>
-      <c r="F93" s="67"/>
-      <c r="G93" s="65"/>
+      <c r="A93" s="63"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="65"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="65"/>
+      <c r="G93" s="63"/>
       <c r="H93" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="I93" s="65"/>
+      <c r="I93" s="63"/>
     </row>
     <row r="94" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A94" s="21">
@@ -6572,87 +6578,87 @@
       </c>
     </row>
     <row r="111" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A111" s="64">
+      <c r="A111" s="62">
         <v>81</v>
       </c>
-      <c r="B111" s="62">
+      <c r="B111" s="66">
         <v>46167</v>
       </c>
       <c r="C111" s="46" t="s">
         <v>427</v>
       </c>
-      <c r="D111" s="62">
+      <c r="D111" s="66">
         <v>46164</v>
       </c>
-      <c r="E111" s="64" t="s">
+      <c r="E111" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F111" s="66" t="s">
+      <c r="F111" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="64" t="s">
+      <c r="G111" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>428</v>
       </c>
-      <c r="I111" s="71" t="s">
+      <c r="I111" s="76" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="112" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
+      <c r="B112" s="70"/>
       <c r="C112" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="D112" s="69"/>
+      <c r="D112" s="70"/>
       <c r="E112" s="68"/>
-      <c r="F112" s="70"/>
+      <c r="F112" s="69"/>
       <c r="G112" s="68"/>
       <c r="H112" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="72"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A113" s="68"/>
-      <c r="B113" s="69"/>
+      <c r="B113" s="70"/>
       <c r="C113" s="46"/>
-      <c r="D113" s="69"/>
+      <c r="D113" s="70"/>
       <c r="E113" s="68"/>
-      <c r="F113" s="70"/>
+      <c r="F113" s="69"/>
       <c r="G113" s="68"/>
       <c r="H113" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="I113" s="72"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A114" s="68"/>
-      <c r="B114" s="69"/>
+      <c r="B114" s="70"/>
       <c r="C114" s="46"/>
-      <c r="D114" s="69"/>
+      <c r="D114" s="70"/>
       <c r="E114" s="68"/>
-      <c r="F114" s="70"/>
+      <c r="F114" s="69"/>
       <c r="G114" s="68"/>
       <c r="H114" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="I114" s="72"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A115" s="65"/>
-      <c r="B115" s="63"/>
+      <c r="A115" s="63"/>
+      <c r="B115" s="67"/>
       <c r="C115" s="46"/>
-      <c r="D115" s="63"/>
-      <c r="E115" s="65"/>
-      <c r="F115" s="67"/>
-      <c r="G115" s="65"/>
+      <c r="D115" s="67"/>
+      <c r="E115" s="63"/>
+      <c r="F115" s="65"/>
+      <c r="G115" s="63"/>
       <c r="H115" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="I115" s="73"/>
+      <c r="I115" s="78"/>
     </row>
     <row r="116" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A116" s="21">
@@ -7235,92 +7241,92 @@
       </c>
     </row>
     <row r="136" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A136" s="64">
+      <c r="A136" s="62">
         <v>102</v>
       </c>
-      <c r="B136" s="62">
+      <c r="B136" s="66">
         <v>46181</v>
       </c>
-      <c r="C136" s="66" t="s">
+      <c r="C136" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="D136" s="62">
+      <c r="D136" s="66">
         <v>46177</v>
       </c>
-      <c r="E136" s="64" t="s">
+      <c r="E136" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F136" s="66" t="s">
+      <c r="F136" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G136" s="64" t="s">
+      <c r="G136" s="62" t="s">
         <v>22</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="I136" s="64" t="s">
+      <c r="I136" s="62" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="137" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A137" s="65"/>
-      <c r="B137" s="63"/>
-      <c r="C137" s="67"/>
-      <c r="D137" s="63"/>
-      <c r="E137" s="65"/>
-      <c r="F137" s="67"/>
-      <c r="G137" s="65"/>
+      <c r="A137" s="63"/>
+      <c r="B137" s="67"/>
+      <c r="C137" s="65"/>
+      <c r="D137" s="67"/>
+      <c r="E137" s="63"/>
+      <c r="F137" s="65"/>
+      <c r="G137" s="63"/>
       <c r="H137" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="I137" s="65"/>
+      <c r="I137" s="63"/>
     </row>
     <row r="138" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A138" s="64">
+      <c r="A138" s="62">
         <v>103</v>
       </c>
-      <c r="B138" s="62">
+      <c r="B138" s="66">
         <v>46181</v>
       </c>
-      <c r="C138" s="66" t="s">
+      <c r="C138" s="64" t="s">
         <v>499</v>
       </c>
-      <c r="D138" s="62">
+      <c r="D138" s="66">
         <v>46177</v>
       </c>
-      <c r="E138" s="64" t="s">
+      <c r="E138" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="64" t="s">
         <v>495</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="62" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="I138" s="64" t="s">
+      <c r="I138" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="J138" s="64" t="s">
+      <c r="J138" s="62" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="139" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A139" s="65"/>
-      <c r="B139" s="63"/>
-      <c r="C139" s="67"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="67"/>
-      <c r="G139" s="65"/>
+      <c r="A139" s="63"/>
+      <c r="B139" s="67"/>
+      <c r="C139" s="65"/>
+      <c r="D139" s="67"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="65"/>
+      <c r="G139" s="63"/>
       <c r="H139" s="34" t="s">
         <v>494</v>
       </c>
-      <c r="I139" s="65"/>
-      <c r="J139" s="65"/>
+      <c r="I139" s="63"/>
+      <c r="J139" s="63"/>
     </row>
     <row r="140" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A140" s="21">
@@ -7643,46 +7649,46 @@
       </c>
     </row>
     <row r="150" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A150" s="64">
+      <c r="A150" s="62">
         <v>114</v>
       </c>
-      <c r="B150" s="62">
+      <c r="B150" s="66">
         <v>46189</v>
       </c>
-      <c r="C150" s="66" t="s">
+      <c r="C150" s="64" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="62">
+      <c r="D150" s="66">
         <v>46186</v>
       </c>
-      <c r="E150" s="64" t="s">
+      <c r="E150" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F150" s="66" t="s">
+      <c r="F150" s="64" t="s">
         <v>288</v>
       </c>
-      <c r="G150" s="64" t="s">
+      <c r="G150" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H150" s="34" t="s">
         <v>528</v>
       </c>
-      <c r="I150" s="64" t="s">
+      <c r="I150" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A151" s="65"/>
-      <c r="B151" s="63"/>
-      <c r="C151" s="67"/>
-      <c r="D151" s="63"/>
-      <c r="E151" s="65"/>
-      <c r="F151" s="67"/>
-      <c r="G151" s="65"/>
+      <c r="A151" s="63"/>
+      <c r="B151" s="67"/>
+      <c r="C151" s="65"/>
+      <c r="D151" s="67"/>
+      <c r="E151" s="63"/>
+      <c r="F151" s="65"/>
+      <c r="G151" s="63"/>
       <c r="H151" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="I151" s="65"/>
+      <c r="I151" s="63"/>
     </row>
     <row r="152" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A152" s="21">
@@ -7711,41 +7717,41 @@
       </c>
     </row>
     <row r="153" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A153" s="64">
+      <c r="A153" s="62">
         <v>116</v>
       </c>
-      <c r="B153" s="62">
+      <c r="B153" s="66">
         <v>46191</v>
       </c>
-      <c r="C153" s="66" t="s">
+      <c r="C153" s="64" t="s">
         <v>534</v>
       </c>
-      <c r="D153" s="62">
+      <c r="D153" s="66">
         <v>46188</v>
       </c>
-      <c r="E153" s="64" t="s">
+      <c r="E153" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F153" s="66" t="s">
+      <c r="F153" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G153" s="64" t="s">
+      <c r="G153" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H153" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="I153" s="64" t="s">
+      <c r="I153" s="62" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A154" s="68"/>
-      <c r="B154" s="69"/>
-      <c r="C154" s="70"/>
-      <c r="D154" s="69"/>
+      <c r="B154" s="70"/>
+      <c r="C154" s="69"/>
+      <c r="D154" s="70"/>
       <c r="E154" s="68"/>
-      <c r="F154" s="70"/>
+      <c r="F154" s="69"/>
       <c r="G154" s="68"/>
       <c r="H154" s="34" t="s">
         <v>536</v>
@@ -7754,11 +7760,11 @@
     </row>
     <row r="155" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A155" s="68"/>
-      <c r="B155" s="69"/>
-      <c r="C155" s="70"/>
-      <c r="D155" s="69"/>
+      <c r="B155" s="70"/>
+      <c r="C155" s="69"/>
+      <c r="D155" s="70"/>
       <c r="E155" s="68"/>
-      <c r="F155" s="70"/>
+      <c r="F155" s="69"/>
       <c r="G155" s="68"/>
       <c r="H155" s="34" t="s">
         <v>537</v>
@@ -7766,17 +7772,17 @@
       <c r="I155" s="68"/>
     </row>
     <row r="156" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A156" s="65"/>
-      <c r="B156" s="63"/>
-      <c r="C156" s="67"/>
-      <c r="D156" s="63"/>
-      <c r="E156" s="65"/>
-      <c r="F156" s="67"/>
-      <c r="G156" s="65"/>
+      <c r="A156" s="63"/>
+      <c r="B156" s="67"/>
+      <c r="C156" s="65"/>
+      <c r="D156" s="67"/>
+      <c r="E156" s="63"/>
+      <c r="F156" s="65"/>
+      <c r="G156" s="63"/>
       <c r="H156" s="34" t="s">
         <v>538</v>
       </c>
-      <c r="I156" s="65"/>
+      <c r="I156" s="63"/>
     </row>
     <row r="157" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A157" s="21">
@@ -7837,41 +7843,41 @@
       </c>
     </row>
     <row r="159" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A159" s="64">
+      <c r="A159" s="62">
         <v>119</v>
       </c>
-      <c r="B159" s="62">
+      <c r="B159" s="66">
         <v>46203</v>
       </c>
-      <c r="C159" s="66" t="s">
+      <c r="C159" s="64" t="s">
         <v>582</v>
       </c>
-      <c r="D159" s="62">
+      <c r="D159" s="66">
         <v>46198</v>
       </c>
-      <c r="E159" s="64" t="s">
+      <c r="E159" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F159" s="66" t="s">
+      <c r="F159" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="64" t="s">
+      <c r="G159" s="62" t="s">
         <v>86</v>
       </c>
       <c r="H159" s="28" t="s">
         <v>559</v>
       </c>
-      <c r="I159" s="64" t="s">
+      <c r="I159" s="62" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A160" s="68"/>
-      <c r="B160" s="69"/>
-      <c r="C160" s="70"/>
-      <c r="D160" s="69"/>
+      <c r="B160" s="70"/>
+      <c r="C160" s="69"/>
+      <c r="D160" s="70"/>
       <c r="E160" s="68"/>
-      <c r="F160" s="70"/>
+      <c r="F160" s="69"/>
       <c r="G160" s="68"/>
       <c r="H160" s="28" t="s">
         <v>560</v>
@@ -7880,11 +7886,11 @@
     </row>
     <row r="161" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A161" s="68"/>
-      <c r="B161" s="69"/>
-      <c r="C161" s="70"/>
-      <c r="D161" s="69"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="69"/>
+      <c r="D161" s="70"/>
       <c r="E161" s="68"/>
-      <c r="F161" s="70"/>
+      <c r="F161" s="69"/>
       <c r="G161" s="68"/>
       <c r="H161" s="28" t="s">
         <v>561</v>
@@ -7893,11 +7899,11 @@
     </row>
     <row r="162" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A162" s="68"/>
-      <c r="B162" s="69"/>
-      <c r="C162" s="70"/>
-      <c r="D162" s="69"/>
+      <c r="B162" s="70"/>
+      <c r="C162" s="69"/>
+      <c r="D162" s="70"/>
       <c r="E162" s="68"/>
-      <c r="F162" s="70"/>
+      <c r="F162" s="69"/>
       <c r="G162" s="68"/>
       <c r="H162" s="28" t="s">
         <v>562</v>
@@ -7905,17 +7911,17 @@
       <c r="I162" s="68"/>
     </row>
     <row r="163" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A163" s="65"/>
-      <c r="B163" s="63"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="63"/>
-      <c r="E163" s="65"/>
-      <c r="F163" s="67"/>
-      <c r="G163" s="65"/>
+      <c r="A163" s="63"/>
+      <c r="B163" s="67"/>
+      <c r="C163" s="65"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="63"/>
+      <c r="F163" s="65"/>
+      <c r="G163" s="63"/>
       <c r="H163" s="28" t="s">
         <v>563</v>
       </c>
-      <c r="I163" s="65"/>
+      <c r="I163" s="63"/>
     </row>
     <row r="164" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A164" s="21">
@@ -8205,46 +8211,46 @@
       </c>
     </row>
     <row r="174" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A174" s="64">
+      <c r="A174" s="62">
         <v>130</v>
       </c>
-      <c r="B174" s="62">
+      <c r="B174" s="66">
         <v>46217</v>
       </c>
-      <c r="C174" s="66" t="s">
+      <c r="C174" s="64" t="s">
         <v>604</v>
       </c>
-      <c r="D174" s="74">
+      <c r="D174" s="79">
         <v>46210</v>
       </c>
-      <c r="E174" s="64" t="s">
+      <c r="E174" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F174" s="66" t="s">
+      <c r="F174" s="64" t="s">
         <v>605</v>
       </c>
-      <c r="G174" s="64" t="s">
+      <c r="G174" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H174" s="34" t="s">
         <v>606</v>
       </c>
-      <c r="I174" s="64" t="s">
+      <c r="I174" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A175" s="65"/>
-      <c r="B175" s="63"/>
-      <c r="C175" s="67"/>
-      <c r="D175" s="75"/>
-      <c r="E175" s="65"/>
-      <c r="F175" s="67"/>
-      <c r="G175" s="65"/>
+      <c r="A175" s="63"/>
+      <c r="B175" s="67"/>
+      <c r="C175" s="65"/>
+      <c r="D175" s="80"/>
+      <c r="E175" s="63"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="63"/>
       <c r="H175" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="I175" s="65"/>
+      <c r="I175" s="63"/>
     </row>
     <row r="176" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A176" s="21">
@@ -8386,41 +8392,41 @@
       </c>
     </row>
     <row r="181" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A181" s="64">
+      <c r="A181" s="62">
         <v>136</v>
       </c>
-      <c r="B181" s="62">
+      <c r="B181" s="66">
         <v>46223</v>
       </c>
-      <c r="C181" s="66" t="s">
+      <c r="C181" s="64" t="s">
         <v>632</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="66">
         <v>46219</v>
       </c>
-      <c r="E181" s="64" t="s">
+      <c r="E181" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F181" s="71" t="s">
+      <c r="F181" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="G181" s="64" t="s">
+      <c r="G181" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H181" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="I181" s="64" t="s">
+      <c r="I181" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A182" s="68"/>
-      <c r="B182" s="69"/>
-      <c r="C182" s="70"/>
-      <c r="D182" s="69"/>
+      <c r="B182" s="70"/>
+      <c r="C182" s="69"/>
+      <c r="D182" s="70"/>
       <c r="E182" s="68"/>
-      <c r="F182" s="72"/>
+      <c r="F182" s="77"/>
       <c r="G182" s="68"/>
       <c r="H182" s="34" t="s">
         <v>628</v>
@@ -8429,11 +8435,11 @@
     </row>
     <row r="183" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A183" s="68"/>
-      <c r="B183" s="69"/>
-      <c r="C183" s="70"/>
-      <c r="D183" s="69"/>
+      <c r="B183" s="70"/>
+      <c r="C183" s="69"/>
+      <c r="D183" s="70"/>
       <c r="E183" s="68"/>
-      <c r="F183" s="72"/>
+      <c r="F183" s="77"/>
       <c r="G183" s="68"/>
       <c r="H183" s="34" t="s">
         <v>629</v>
@@ -8442,11 +8448,11 @@
     </row>
     <row r="184" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A184" s="68"/>
-      <c r="B184" s="69"/>
-      <c r="C184" s="70"/>
-      <c r="D184" s="69"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="69"/>
+      <c r="D184" s="70"/>
       <c r="E184" s="68"/>
-      <c r="F184" s="72"/>
+      <c r="F184" s="77"/>
       <c r="G184" s="68"/>
       <c r="H184" s="34" t="s">
         <v>630</v>
@@ -8454,59 +8460,59 @@
       <c r="I184" s="68"/>
     </row>
     <row r="185" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A185" s="65"/>
-      <c r="B185" s="63"/>
-      <c r="C185" s="67"/>
-      <c r="D185" s="63"/>
-      <c r="E185" s="65"/>
-      <c r="F185" s="73"/>
-      <c r="G185" s="65"/>
+      <c r="A185" s="63"/>
+      <c r="B185" s="67"/>
+      <c r="C185" s="65"/>
+      <c r="D185" s="67"/>
+      <c r="E185" s="63"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="63"/>
       <c r="H185" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="I185" s="65"/>
+      <c r="I185" s="63"/>
     </row>
     <row r="186" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A186" s="64">
+      <c r="A186" s="62">
         <v>137</v>
       </c>
-      <c r="B186" s="62">
+      <c r="B186" s="66">
         <v>46223</v>
       </c>
-      <c r="C186" s="66" t="s">
+      <c r="C186" s="64" t="s">
         <v>633</v>
       </c>
-      <c r="D186" s="62">
+      <c r="D186" s="66">
         <v>46219</v>
       </c>
-      <c r="E186" s="64" t="s">
+      <c r="E186" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F186" s="66" t="s">
+      <c r="F186" s="64" t="s">
         <v>507</v>
       </c>
-      <c r="G186" s="64" t="s">
+      <c r="G186" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H186" s="34" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="64" t="s">
+      <c r="I186" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="187" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A187" s="65"/>
-      <c r="B187" s="63"/>
-      <c r="C187" s="67"/>
-      <c r="D187" s="63"/>
-      <c r="E187" s="65"/>
-      <c r="F187" s="67"/>
-      <c r="G187" s="65"/>
+      <c r="A187" s="63"/>
+      <c r="B187" s="67"/>
+      <c r="C187" s="65"/>
+      <c r="D187" s="67"/>
+      <c r="E187" s="63"/>
+      <c r="F187" s="65"/>
+      <c r="G187" s="63"/>
       <c r="H187" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="I187" s="65"/>
+      <c r="I187" s="63"/>
     </row>
     <row r="188" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A188" s="21">
@@ -9174,31 +9180,31 @@
       </c>
     </row>
     <row r="211" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A211" s="64">
+      <c r="A211" s="62">
         <v>161</v>
       </c>
-      <c r="B211" s="62">
+      <c r="B211" s="66">
         <v>46241</v>
       </c>
-      <c r="C211" s="66" t="s">
+      <c r="C211" s="64" t="s">
         <v>719</v>
       </c>
-      <c r="D211" s="62">
+      <c r="D211" s="66">
         <v>46241</v>
       </c>
-      <c r="E211" s="64" t="s">
+      <c r="E211" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F211" s="66" t="s">
+      <c r="F211" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G211" s="64" t="s">
+      <c r="G211" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H211" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="I211" s="64" t="s">
+      <c r="I211" s="62" t="s">
         <v>50</v>
       </c>
       <c r="M211" s="21" t="s">
@@ -9207,11 +9213,11 @@
     </row>
     <row r="212" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A212" s="68"/>
-      <c r="B212" s="69"/>
-      <c r="C212" s="70"/>
-      <c r="D212" s="69"/>
+      <c r="B212" s="70"/>
+      <c r="C212" s="69"/>
+      <c r="D212" s="70"/>
       <c r="E212" s="68"/>
-      <c r="F212" s="70"/>
+      <c r="F212" s="69"/>
       <c r="G212" s="68"/>
       <c r="H212" s="34" t="s">
         <v>723</v>
@@ -9220,11 +9226,11 @@
     </row>
     <row r="213" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A213" s="68"/>
-      <c r="B213" s="69"/>
-      <c r="C213" s="70"/>
-      <c r="D213" s="69"/>
+      <c r="B213" s="70"/>
+      <c r="C213" s="69"/>
+      <c r="D213" s="70"/>
       <c r="E213" s="68"/>
-      <c r="F213" s="70"/>
+      <c r="F213" s="69"/>
       <c r="G213" s="68"/>
       <c r="H213" s="34" t="s">
         <v>724</v>
@@ -9232,17 +9238,17 @@
       <c r="I213" s="68"/>
     </row>
     <row r="214" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A214" s="65"/>
-      <c r="B214" s="63"/>
-      <c r="C214" s="67"/>
-      <c r="D214" s="63"/>
-      <c r="E214" s="65"/>
-      <c r="F214" s="67"/>
-      <c r="G214" s="65"/>
+      <c r="A214" s="63"/>
+      <c r="B214" s="67"/>
+      <c r="C214" s="65"/>
+      <c r="D214" s="67"/>
+      <c r="E214" s="63"/>
+      <c r="F214" s="65"/>
+      <c r="G214" s="63"/>
       <c r="H214" s="34" t="s">
         <v>725</v>
       </c>
-      <c r="I214" s="65"/>
+      <c r="I214" s="63"/>
     </row>
     <row r="215" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A215" s="21">
@@ -9509,46 +9515,46 @@
       </c>
     </row>
     <row r="224" spans="1:13" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A224" s="64">
+      <c r="A224" s="62">
         <v>171</v>
       </c>
-      <c r="B224" s="62">
+      <c r="B224" s="66">
         <v>46263</v>
       </c>
-      <c r="C224" s="66" t="s">
+      <c r="C224" s="64" t="s">
         <v>759</v>
       </c>
-      <c r="D224" s="62">
+      <c r="D224" s="66">
         <v>46261</v>
       </c>
-      <c r="E224" s="64" t="s">
+      <c r="E224" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="F224" s="66" t="s">
+      <c r="F224" s="64" t="s">
         <v>760</v>
       </c>
-      <c r="G224" s="64" t="s">
+      <c r="G224" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H224" s="34" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="64" t="s">
+      <c r="I224" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="225" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A225" s="65"/>
-      <c r="B225" s="63"/>
-      <c r="C225" s="67"/>
-      <c r="D225" s="63"/>
-      <c r="E225" s="65"/>
-      <c r="F225" s="67"/>
-      <c r="G225" s="65"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="67"/>
+      <c r="C225" s="65"/>
+      <c r="D225" s="67"/>
+      <c r="E225" s="63"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="63"/>
       <c r="H225" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="I225" s="65"/>
+      <c r="I225" s="63"/>
     </row>
     <row r="226" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A226" s="21">
@@ -9580,88 +9586,88 @@
       </c>
     </row>
     <row r="227" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A227" s="64">
+      <c r="A227" s="62">
         <v>173</v>
       </c>
-      <c r="B227" s="62">
+      <c r="B227" s="66">
         <v>46263</v>
       </c>
-      <c r="C227" s="66" t="s">
+      <c r="C227" s="64" t="s">
         <v>766</v>
       </c>
-      <c r="D227" s="62">
+      <c r="D227" s="66">
         <v>46259</v>
       </c>
-      <c r="E227" s="64" t="s">
+      <c r="E227" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F227" s="66" t="s">
+      <c r="F227" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="G227" s="64" t="s">
+      <c r="G227" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H227" s="34" t="s">
         <v>767</v>
       </c>
-      <c r="I227" s="64" t="s">
+      <c r="I227" s="62" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="228" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A228" s="65"/>
-      <c r="B228" s="63"/>
-      <c r="C228" s="67"/>
-      <c r="D228" s="63"/>
-      <c r="E228" s="65"/>
-      <c r="F228" s="67"/>
-      <c r="G228" s="65"/>
+      <c r="A228" s="63"/>
+      <c r="B228" s="67"/>
+      <c r="C228" s="65"/>
+      <c r="D228" s="67"/>
+      <c r="E228" s="63"/>
+      <c r="F228" s="65"/>
+      <c r="G228" s="63"/>
       <c r="H228" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="I228" s="65"/>
+      <c r="I228" s="63"/>
     </row>
     <row r="229" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A229" s="64">
+      <c r="A229" s="62">
         <v>174</v>
       </c>
-      <c r="B229" s="62">
+      <c r="B229" s="66">
         <v>46266</v>
       </c>
-      <c r="C229" s="66" t="s">
+      <c r="C229" s="64" t="s">
         <v>778</v>
       </c>
-      <c r="D229" s="62">
+      <c r="D229" s="66">
         <v>46266</v>
       </c>
-      <c r="E229" s="64" t="s">
+      <c r="E229" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="F229" s="66" t="s">
+      <c r="F229" s="64" t="s">
         <v>721</v>
       </c>
-      <c r="G229" s="64" t="s">
+      <c r="G229" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H229" s="34" t="s">
         <v>779</v>
       </c>
-      <c r="I229" s="64" t="s">
+      <c r="I229" s="62" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="230" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A230" s="65"/>
-      <c r="B230" s="63"/>
-      <c r="C230" s="67"/>
-      <c r="D230" s="63"/>
-      <c r="E230" s="65"/>
-      <c r="F230" s="67"/>
-      <c r="G230" s="65"/>
+      <c r="A230" s="63"/>
+      <c r="B230" s="67"/>
+      <c r="C230" s="65"/>
+      <c r="D230" s="67"/>
+      <c r="E230" s="63"/>
+      <c r="F230" s="65"/>
+      <c r="G230" s="63"/>
       <c r="H230" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="I230" s="65"/>
+      <c r="I230" s="63"/>
     </row>
     <row r="231" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A231" s="21">
@@ -9722,46 +9728,46 @@
       </c>
     </row>
     <row r="233" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A233" s="64">
+      <c r="A233" s="62">
         <v>177</v>
       </c>
-      <c r="B233" s="62">
+      <c r="B233" s="66">
         <v>46268</v>
       </c>
-      <c r="C233" s="66" t="s">
+      <c r="C233" s="64" t="s">
         <v>795</v>
       </c>
-      <c r="D233" s="62">
+      <c r="D233" s="66">
         <v>46267</v>
       </c>
-      <c r="E233" s="64" t="s">
+      <c r="E233" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F233" s="66" t="s">
+      <c r="F233" s="64" t="s">
         <v>796</v>
       </c>
-      <c r="G233" s="64" t="s">
+      <c r="G233" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H233" s="34" t="s">
         <v>797</v>
       </c>
-      <c r="I233" s="64" t="s">
+      <c r="I233" s="62" t="s">
         <v>799</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A234" s="65"/>
-      <c r="B234" s="63"/>
-      <c r="C234" s="67"/>
-      <c r="D234" s="63"/>
-      <c r="E234" s="65"/>
-      <c r="F234" s="67"/>
-      <c r="G234" s="65"/>
+      <c r="A234" s="63"/>
+      <c r="B234" s="67"/>
+      <c r="C234" s="65"/>
+      <c r="D234" s="67"/>
+      <c r="E234" s="63"/>
+      <c r="F234" s="65"/>
+      <c r="G234" s="63"/>
       <c r="H234" s="34" t="s">
         <v>798</v>
       </c>
-      <c r="I234" s="65"/>
+      <c r="I234" s="63"/>
     </row>
     <row r="235" spans="1:10" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A235" s="21">
@@ -10402,46 +10408,46 @@
       </c>
     </row>
     <row r="257" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A257" s="64">
+      <c r="A257" s="62">
         <v>200</v>
       </c>
-      <c r="B257" s="62">
+      <c r="B257" s="66">
         <v>46300</v>
       </c>
-      <c r="C257" s="66" t="s">
+      <c r="C257" s="64" t="s">
         <v>925</v>
       </c>
-      <c r="D257" s="62">
+      <c r="D257" s="66">
         <v>46294</v>
       </c>
-      <c r="E257" s="64" t="s">
+      <c r="E257" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F257" s="66" t="s">
+      <c r="F257" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G257" s="64" t="s">
+      <c r="G257" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H257" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="I257" s="64" t="s">
+      <c r="I257" s="62" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="258" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A258" s="65"/>
-      <c r="B258" s="63"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="63"/>
-      <c r="E258" s="65"/>
-      <c r="F258" s="67"/>
-      <c r="G258" s="65"/>
+      <c r="A258" s="63"/>
+      <c r="B258" s="67"/>
+      <c r="C258" s="65"/>
+      <c r="D258" s="67"/>
+      <c r="E258" s="63"/>
+      <c r="F258" s="65"/>
+      <c r="G258" s="63"/>
       <c r="H258" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="I258" s="65"/>
+      <c r="I258" s="63"/>
     </row>
     <row r="259" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A259" s="21">
@@ -10531,54 +10537,75 @@
       </c>
     </row>
     <row r="262" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A262" s="64">
+      <c r="A262" s="62">
         <v>204</v>
       </c>
-      <c r="B262" s="62">
+      <c r="B262" s="66">
         <v>46301</v>
       </c>
-      <c r="C262" s="66" t="s">
+      <c r="C262" s="64" t="s">
         <v>949</v>
       </c>
-      <c r="D262" s="62">
+      <c r="D262" s="66">
         <v>46301</v>
       </c>
-      <c r="E262" s="64" t="s">
+      <c r="E262" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="F262" s="66" t="s">
+      <c r="F262" s="64" t="s">
         <v>926</v>
       </c>
-      <c r="G262" s="64" t="s">
+      <c r="G262" s="62" t="s">
         <v>48</v>
       </c>
       <c r="H262" s="34" t="s">
         <v>950</v>
       </c>
-      <c r="I262" s="64" t="s">
+      <c r="I262" s="62" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="263" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A263" s="65"/>
-      <c r="B263" s="63"/>
-      <c r="C263" s="67"/>
-      <c r="D263" s="63"/>
-      <c r="E263" s="65"/>
-      <c r="F263" s="67"/>
-      <c r="G263" s="65"/>
+      <c r="A263" s="63"/>
+      <c r="B263" s="67"/>
+      <c r="C263" s="65"/>
+      <c r="D263" s="67"/>
+      <c r="E263" s="63"/>
+      <c r="F263" s="65"/>
+      <c r="G263" s="63"/>
       <c r="H263" s="34" t="s">
         <v>951</v>
       </c>
-      <c r="I263" s="65"/>
+      <c r="I263" s="63"/>
     </row>
     <row r="264" spans="1:9" s="21" customFormat="1" ht="22.5" customHeight="1">
       <c r="A264" s="21">
         <v>205</v>
       </c>
-      <c r="C264" s="46"/>
-      <c r="F264" s="46"/>
-      <c r="H264" s="34"/>
+      <c r="B264" s="25">
+        <v>46307</v>
+      </c>
+      <c r="C264" s="46" t="s">
+        <v>962</v>
+      </c>
+      <c r="D264" s="25">
+        <v>46305</v>
+      </c>
+      <c r="E264" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F264" s="46" t="s">
+        <v>963</v>
+      </c>
+      <c r="G264" s="21" t="s">
+        <v>217</v>
+      </c>